--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -302,7 +302,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -311,12 +311,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>158.54242</v>
+        <v>157.18907</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -325,12 +325,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>164.71995</v>
+        <v>150.64053</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -339,12 +339,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>155.58</v>
+        <v>145.49496</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -353,12 +353,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>152.21669</v>
+        <v>144.63093</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -367,12 +367,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>152.97</v>
+        <v>141.79719</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -381,12 +381,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>152.97</v>
+        <v>138.97641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -395,12 +395,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>150.99</v>
+        <v>144.59409</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -409,12 +409,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>147.7</v>
+        <v>138.32796</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -423,12 +423,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>147.7</v>
+        <v>143.17546</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -437,12 +437,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>147.7</v>
+        <v>143.45058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -451,12 +451,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>147.7</v>
+        <v>141.92327</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -465,12 +465,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>147.7</v>
+        <v>143.20264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -479,12 +479,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>131.86</v>
+        <v>138.19465</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -493,12 +493,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>131.86</v>
+        <v>138.95633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -507,12 +507,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>131.86</v>
+        <v>136.62921</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -521,12 +521,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>131.86</v>
+        <v>136.62905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -535,12 +535,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>131.86</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -549,12 +549,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>131.86</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -563,12 +563,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>131.86</v>
+        <v>133.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -577,12 +577,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>131.9</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -591,12 +591,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>131.86</v>
+        <v>130.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -605,12 +605,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>131.86</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -619,12 +619,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>131.86</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -633,12 +633,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>138.05</v>
+        <v>136.30808</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -647,12 +647,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>135.97502</v>
+        <v>138.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -661,12 +661,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>147.7</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -675,12 +675,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>149.96</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -689,12 +689,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>152.97</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -703,12 +703,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>153.0</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -717,12 +717,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>155.58</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -731,12 +731,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>155.58</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -745,12 +745,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>154.64</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -759,12 +759,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>155.58</v>
+        <v>160.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -773,12 +773,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>152.97</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -787,12 +787,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>150.0</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -801,12 +801,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>147.7</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -815,12 +815,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>152.97</v>
+        <v>160.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -829,12 +829,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>145.0</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -843,12 +843,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>131.86</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -857,12 +857,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>130.3</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -871,12 +871,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>131.86</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -885,12 +885,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>140.92</v>
+        <v>153.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -899,12 +899,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>131.27</v>
+        <v>136.72214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -913,12 +913,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>116.35</v>
+        <v>133.33103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -927,12 +927,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>127.82</v>
+        <v>141.52577</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -941,12 +941,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>131.86</v>
+        <v>141.48854</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -955,12 +955,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>131.86</v>
+        <v>132.15539</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -969,12 +969,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>128.86</v>
+        <v>131.72075</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -983,12 +983,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>131.86</v>
+        <v>136.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -997,12 +997,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>125.46</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1011,12 +1011,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>119.35</v>
+        <v>127.70527</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1025,12 +1025,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>110.0</v>
+        <v>121.47314</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1039,12 +1039,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>108.93</v>
+        <v>120.98031</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1053,12 +1053,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>119.06</v>
+        <v>128.92244</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1067,12 +1067,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>120.0</v>
+        <v>133.80536</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1081,12 +1081,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>127.0</v>
+        <v>136.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1095,12 +1095,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>116.77671</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1109,12 +1109,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>125.78333</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1123,12 +1123,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>121.60286</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1137,12 +1137,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>129.53754</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1151,12 +1151,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>129.52789</v>
+        <v>121.32303</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1165,12 +1165,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>129.53539</v>
+        <v>124.24882</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1179,12 +1179,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>129.53178</v>
+        <v>131.13526</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1193,12 +1193,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>137.51871</v>
+        <v>131.17712</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1207,12 +1207,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>141.45761</v>
+        <v>131.21609</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1221,12 +1221,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>145.20365</v>
+        <v>148.11655</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1235,12 +1235,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>145.77378</v>
+        <v>145.2717</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1249,12 +1249,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>150.58623</v>
+        <v>142.82897</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1263,12 +1263,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>146.80737</v>
+        <v>132.24634</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1277,12 +1277,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>147.7</v>
+        <v>132.58296</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1291,12 +1291,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>149.9</v>
+        <v>145.88641</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1305,12 +1305,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>152.97</v>
+        <v>159.98573</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1319,12 +1319,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>147.7</v>
+        <v>137.44783</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1333,12 +1333,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>152.69268</v>
+        <v>154.09613</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1347,12 +1347,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>155.58</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1361,12 +1361,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>161.53</v>
+        <v>160.66</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1375,12 +1375,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>159.13</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1389,12 +1389,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>171.11</v>
+        <v>160.86</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1403,12 +1403,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>174.78</v>
+        <v>171.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1417,12 +1417,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>191.82764</v>
+        <v>177.68042</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1431,12 +1431,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>176.18066</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1445,12 +1445,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>176.0081</v>
+        <v>174.0756</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1459,12 +1459,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>181.95123</v>
+        <v>187.72362</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1473,12 +1473,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>178.32836</v>
+        <v>181.4386</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1487,12 +1487,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>184.40693</v>
+        <v>190.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1501,12 +1501,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>178.82748</v>
+        <v>170.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1515,12 +1515,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>173.95767</v>
+        <v>168.36</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1529,12 +1529,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>164.38146</v>
+        <v>163.13557</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1543,12 +1543,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>173.72968</v>
+        <v>165.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1557,12 +1557,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>172.16459</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1571,12 +1571,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>159.87796</v>
+        <v>157.21641</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1585,12 +1585,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>149.95693</v>
+        <v>140.06902</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1599,12 +1599,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>170.46596</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1613,12 +1613,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>155.9366</v>
+        <v>144.64899</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1627,12 +1627,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>147.80849</v>
+        <v>141.04407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1641,7 +1641,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>143.8911</v>
+        <v>134.62869</v>
       </c>
     </row>
   </sheetData>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -43,6 +43,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -59,11 +64,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -296,13 +304,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>46183.0</v>
+      <c r="A2" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -311,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>157.18907</v>
+        <v>158.54242</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>46183.0</v>
+      <c r="A3" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -325,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>150.64053</v>
+        <v>164.71995</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>46183.0</v>
+      <c r="A4" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -339,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>145.49496</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>46183.0</v>
+      <c r="A5" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -353,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>144.63093</v>
+        <v>152.21669</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
-        <v>46183.0</v>
+      <c r="A6" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -367,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>141.79719</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2">
-        <v>46183.0</v>
+      <c r="A7" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -381,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>138.97641</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2">
-        <v>46183.0</v>
+      <c r="A8" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -395,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>144.59409</v>
+        <v>150.99</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2">
-        <v>46183.0</v>
+      <c r="A9" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -409,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>138.32796</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2">
-        <v>46183.0</v>
+      <c r="A10" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -423,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>143.17546</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2">
-        <v>46183.0</v>
+      <c r="A11" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -437,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>143.45058</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2">
-        <v>46183.0</v>
+      <c r="A12" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -451,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>141.92327</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2">
-        <v>46183.0</v>
+      <c r="A13" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -465,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>143.20264</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2">
-        <v>46183.0</v>
+      <c r="A14" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -479,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>138.19465</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2">
-        <v>46183.0</v>
+      <c r="A15" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -493,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>138.95633</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2">
-        <v>46183.0</v>
+      <c r="A16" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -507,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>136.62921</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2">
-        <v>46183.0</v>
+      <c r="A17" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -521,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>136.62905</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2">
-        <v>46183.0</v>
+      <c r="A18" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -535,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>134.54</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2">
-        <v>46183.0</v>
+      <c r="A19" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -549,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>134.54</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2">
-        <v>46183.0</v>
+      <c r="A20" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -563,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>133.21</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2">
-        <v>46183.0</v>
+      <c r="A21" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -577,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>134.54</v>
+        <v>131.9</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2">
-        <v>46183.0</v>
+      <c r="A22" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -591,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>130.88</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2">
-        <v>46183.0</v>
+      <c r="A23" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -605,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>129.0</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2">
-        <v>46183.0</v>
+      <c r="A24" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -619,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>129.0</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2">
-        <v>46183.0</v>
+      <c r="A25" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -633,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>136.30808</v>
+        <v>138.05</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2">
-        <v>46183.0</v>
+      <c r="A26" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -647,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>138.98</v>
+        <v>135.97502</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2">
-        <v>46183.0</v>
+      <c r="A27" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -661,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>143.83</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2">
-        <v>46183.0</v>
+      <c r="A28" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -675,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>155.0</v>
+        <v>149.96</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2">
-        <v>46183.0</v>
+      <c r="A29" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -689,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>158.2</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2">
-        <v>46183.0</v>
+      <c r="A30" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -703,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>158.2</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2">
-        <v>46183.0</v>
+      <c r="A31" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -717,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>158.2</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2">
-        <v>46183.0</v>
+      <c r="A32" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -731,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>158.43</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2">
-        <v>46183.0</v>
+      <c r="A33" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -745,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>158.2</v>
+        <v>154.64</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2">
-        <v>46183.0</v>
+      <c r="A34" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -759,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>160.66</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2">
-        <v>46183.0</v>
+      <c r="A35" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -773,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>158.43</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2">
-        <v>46183.0</v>
+      <c r="A36" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -787,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>158.2</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2">
-        <v>46183.0</v>
+      <c r="A37" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -801,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>158.2</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2">
-        <v>46183.0</v>
+      <c r="A38" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -815,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>160.66</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2">
-        <v>46183.0</v>
+      <c r="A39" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -829,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>158.43</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2">
-        <v>46183.0</v>
+      <c r="A40" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -843,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>158.2</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2">
-        <v>46183.0</v>
+      <c r="A41" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -857,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>157.0</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2">
-        <v>46183.0</v>
+      <c r="A42" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -871,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>158.2</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2">
-        <v>46183.0</v>
+      <c r="A43" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -885,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>153.45</v>
+        <v>140.92</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2">
-        <v>46183.0</v>
+      <c r="A44" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -899,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>136.72214</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2">
-        <v>46183.0</v>
+      <c r="A45" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -913,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>133.33103</v>
+        <v>116.35</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2">
-        <v>46183.0</v>
+      <c r="A46" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -927,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>141.52577</v>
+        <v>127.82</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2">
-        <v>46183.0</v>
+      <c r="A47" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -941,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>141.48854</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2">
-        <v>46183.0</v>
+      <c r="A48" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -955,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>132.15539</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2">
-        <v>46183.0</v>
+      <c r="A49" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -969,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>131.72075</v>
+        <v>128.86</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2">
-        <v>46183.0</v>
+      <c r="A50" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -983,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>136.66</v>
+        <v>131.86</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2">
-        <v>46183.0</v>
+      <c r="A51" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -997,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>134.54</v>
+        <v>125.46</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2">
-        <v>46183.0</v>
+      <c r="A52" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1011,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>127.70527</v>
+        <v>119.35</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
-        <v>46183.0</v>
+      <c r="A53" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1025,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>121.47314</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
-        <v>46183.0</v>
+      <c r="A54" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1039,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>120.98031</v>
+        <v>108.93</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2">
-        <v>46183.0</v>
+      <c r="A55" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1053,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>128.92244</v>
+        <v>119.06</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2">
-        <v>46183.0</v>
+      <c r="A56" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1067,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>133.80536</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2">
-        <v>46183.0</v>
+      <c r="A57" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1081,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>136.39</v>
+        <v>127.0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2">
-        <v>46183.0</v>
+      <c r="A58" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1095,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>134.54</v>
+        <v>116.77671</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2">
-        <v>46183.0</v>
+      <c r="A59" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1109,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>133.9</v>
+        <v>125.78333</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2">
-        <v>46183.0</v>
+      <c r="A60" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1123,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>134.54</v>
+        <v>121.60286</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2">
-        <v>46183.0</v>
+      <c r="A61" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1137,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>134.54</v>
+        <v>129.53754</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2">
-        <v>46183.0</v>
+      <c r="A62" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1151,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>121.32303</v>
+        <v>129.52789</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2">
-        <v>46183.0</v>
+      <c r="A63" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1165,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>124.24882</v>
+        <v>129.53539</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2">
-        <v>46183.0</v>
+      <c r="A64" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1179,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>131.13526</v>
+        <v>129.53178</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2">
-        <v>46183.0</v>
+      <c r="A65" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1193,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>131.17712</v>
+        <v>137.51871</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2">
-        <v>46183.0</v>
+      <c r="A66" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1207,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>131.21609</v>
+        <v>141.45761</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2">
-        <v>46183.0</v>
+      <c r="A67" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1221,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>148.11655</v>
+        <v>145.20365</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2">
-        <v>46183.0</v>
+      <c r="A68" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1235,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>145.2717</v>
+        <v>145.77378</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2">
-        <v>46183.0</v>
+      <c r="A69" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1249,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>142.82897</v>
+        <v>150.58623</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2">
-        <v>46183.0</v>
+      <c r="A70" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1263,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>132.24634</v>
+        <v>146.80737</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2">
-        <v>46183.0</v>
+      <c r="A71" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1277,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>132.58296</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2">
-        <v>46183.0</v>
+      <c r="A72" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1291,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>145.88641</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2">
-        <v>46183.0</v>
+      <c r="A73" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1305,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>159.98573</v>
+        <v>152.97</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2">
-        <v>46183.0</v>
+      <c r="A74" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1319,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>137.44783</v>
+        <v>147.7</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2">
-        <v>46183.0</v>
+      <c r="A75" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1333,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>154.09613</v>
+        <v>152.69268</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2">
-        <v>46183.0</v>
+      <c r="A76" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1347,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>158.2</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2">
-        <v>46183.0</v>
+      <c r="A77" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1361,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>160.66</v>
+        <v>161.53</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2">
-        <v>46183.0</v>
+      <c r="A78" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1375,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>158.2</v>
+        <v>159.13</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2">
-        <v>46183.0</v>
+      <c r="A79" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1389,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>160.86</v>
+        <v>171.11</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2">
-        <v>46183.0</v>
+      <c r="A80" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1403,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>171.0</v>
+        <v>174.78</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2">
-        <v>46183.0</v>
+      <c r="A81" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1417,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>177.68042</v>
+        <v>191.82764</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2">
-        <v>46183.0</v>
+      <c r="A82" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1431,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>168.0</v>
+        <v>176.18066</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2">
-        <v>46183.0</v>
+      <c r="A83" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1445,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>174.0756</v>
+        <v>176.0081</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2">
-        <v>46183.0</v>
+      <c r="A84" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1459,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>187.72362</v>
+        <v>181.95123</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2">
-        <v>46183.0</v>
+      <c r="A85" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1473,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>181.4386</v>
+        <v>178.32836</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2">
-        <v>46183.0</v>
+      <c r="A86" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1487,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>190.46</v>
+        <v>184.40693</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2">
-        <v>46183.0</v>
+      <c r="A87" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1501,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>170.46</v>
+        <v>178.82748</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2">
-        <v>46183.0</v>
+      <c r="A88" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1515,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>168.36</v>
+        <v>173.95767</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2">
-        <v>46183.0</v>
+      <c r="A89" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1529,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>163.13557</v>
+        <v>164.38146</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2">
-        <v>46183.0</v>
+      <c r="A90" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1543,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>165.17</v>
+        <v>173.72968</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2">
-        <v>46183.0</v>
+      <c r="A91" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1557,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>158.43</v>
+        <v>172.16459</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2">
-        <v>46183.0</v>
+      <c r="A92" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1571,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>157.21641</v>
+        <v>159.87796</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2">
-        <v>46183.0</v>
+      <c r="A93" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1585,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>140.06902</v>
+        <v>149.95693</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2">
-        <v>46183.0</v>
+      <c r="A94" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1599,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>158.2</v>
+        <v>170.46596</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2">
-        <v>46183.0</v>
+      <c r="A95" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1613,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>144.64899</v>
+        <v>155.9366</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2">
-        <v>46183.0</v>
+      <c r="A96" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1627,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>141.04407</v>
+        <v>147.80849</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2">
-        <v>46183.0</v>
+      <c r="A97" s="3">
+        <v>46182.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1641,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>134.62869</v>
+        <v>143.8911</v>
       </c>
     </row>
   </sheetData>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>158.54242</v>
+        <v>157.18907</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>164.71995</v>
+        <v>150.64053</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>155.58</v>
+        <v>145.49496</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>152.21669</v>
+        <v>144.63093</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>152.97</v>
+        <v>141.79719</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>152.97</v>
+        <v>138.97641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>150.99</v>
+        <v>144.59409</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>147.7</v>
+        <v>138.32796</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>147.7</v>
+        <v>143.17546</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>147.7</v>
+        <v>143.45058</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>147.7</v>
+        <v>141.92327</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>147.7</v>
+        <v>143.20264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>131.86</v>
+        <v>138.19465</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>131.86</v>
+        <v>138.95633</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>131.86</v>
+        <v>136.62921</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>131.86</v>
+        <v>136.62905</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>131.86</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>131.86</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>131.86</v>
+        <v>133.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>131.9</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>131.86</v>
+        <v>130.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>131.86</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>131.86</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>138.05</v>
+        <v>136.30808</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>135.97502</v>
+        <v>138.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>147.7</v>
+        <v>143.83</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>149.96</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>152.97</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>153.0</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>155.58</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>155.58</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>154.64</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>155.58</v>
+        <v>160.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>152.97</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>150.0</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>147.7</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>152.97</v>
+        <v>160.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>145.0</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>131.86</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>130.3</v>
+        <v>157.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>131.86</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>140.92</v>
+        <v>153.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>131.27</v>
+        <v>136.72214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>116.35</v>
+        <v>133.33103</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>127.82</v>
+        <v>141.52577</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>131.86</v>
+        <v>141.48854</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>131.86</v>
+        <v>132.15539</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>128.86</v>
+        <v>131.72075</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>131.86</v>
+        <v>136.66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>125.46</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>119.35</v>
+        <v>127.70527</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>110.0</v>
+        <v>121.47314</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>108.93</v>
+        <v>120.98031</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>119.06</v>
+        <v>128.92244</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>120.0</v>
+        <v>133.80536</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>127.0</v>
+        <v>136.39</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>116.77671</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>125.78333</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>121.60286</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>129.53754</v>
+        <v>134.54</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>129.52789</v>
+        <v>121.32303</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>129.53539</v>
+        <v>124.24882</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>129.53178</v>
+        <v>131.13526</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>137.51871</v>
+        <v>131.17712</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>141.45761</v>
+        <v>131.21609</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>145.20365</v>
+        <v>148.11655</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>145.77378</v>
+        <v>145.2717</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>150.58623</v>
+        <v>142.82897</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>146.80737</v>
+        <v>132.24634</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>147.7</v>
+        <v>132.58296</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>149.9</v>
+        <v>145.88641</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>152.97</v>
+        <v>159.98573</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>147.7</v>
+        <v>137.44783</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>152.69268</v>
+        <v>154.09613</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>155.58</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>161.53</v>
+        <v>160.66</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>159.13</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>171.11</v>
+        <v>160.86</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>174.78</v>
+        <v>171.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>191.82764</v>
+        <v>177.68042</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>176.18066</v>
+        <v>168.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>176.0081</v>
+        <v>174.0756</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>181.95123</v>
+        <v>187.72362</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>178.32836</v>
+        <v>181.4386</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>184.40693</v>
+        <v>190.46</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>178.82748</v>
+        <v>170.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>173.95767</v>
+        <v>168.36</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>164.38146</v>
+        <v>163.13557</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>173.72968</v>
+        <v>165.17</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>172.16459</v>
+        <v>158.43</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>159.87796</v>
+        <v>157.21641</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>149.95693</v>
+        <v>140.06902</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>170.46596</v>
+        <v>158.2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>155.9366</v>
+        <v>144.64899</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>147.80849</v>
+        <v>141.04407</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46182.0</v>
+        <v>46183.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>143.8911</v>
+        <v>134.62869</v>
       </c>
     </row>
   </sheetData>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>157.18907</v>
+        <v>132.76904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>150.64053</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>145.49496</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>144.63093</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>141.79719</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>138.97641</v>
+        <v>129.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>144.59409</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>138.32796</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>143.17546</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>143.45058</v>
+        <v>132.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>141.92327</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>143.20264</v>
+        <v>130.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>138.19465</v>
+        <v>130.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>138.95633</v>
+        <v>131.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>136.62921</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>136.62905</v>
+        <v>127.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>134.54</v>
+        <v>127.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>134.54</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>133.21</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>134.54</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>130.88</v>
+        <v>134.64</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>129.0</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>129.0</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>136.30808</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>138.98</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>143.83</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>155.0</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>158.2</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>158.2</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>158.2</v>
+        <v>157.79104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>158.43</v>
+        <v>158.48612</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>158.2</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>160.66</v>
+        <v>160.84468</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>158.43</v>
+        <v>159.1928</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>158.2</v>
+        <v>154.7106</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>158.2</v>
+        <v>149.52925</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>160.66</v>
+        <v>145.16686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>158.43</v>
+        <v>143.7738</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>158.2</v>
+        <v>125.78061</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>157.0</v>
+        <v>125.71971</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>158.2</v>
+        <v>131.99215</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>153.45</v>
+        <v>131.35197</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>136.72214</v>
+        <v>120.72313</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>133.33103</v>
+        <v>118.95059</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>141.52577</v>
+        <v>111.5533</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>141.48854</v>
+        <v>119.83895</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>132.15539</v>
+        <v>110.53382</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>131.72075</v>
+        <v>109.42048</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>136.66</v>
+        <v>98.81551</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>134.54</v>
+        <v>71.99453</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>127.70527</v>
+        <v>65.53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>121.47314</v>
+        <v>59.85408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>120.98031</v>
+        <v>64.09058</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>128.92244</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>133.80536</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>136.39</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>134.54</v>
+        <v>58.79054</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>133.9</v>
+        <v>62.00186</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>134.54</v>
+        <v>67.49352</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>134.54</v>
+        <v>63.83128</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>121.32303</v>
+        <v>68.42088</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>124.24882</v>
+        <v>70.72727</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>131.13526</v>
+        <v>87.3876</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>131.17712</v>
+        <v>86.8819</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>131.21609</v>
+        <v>99.2409</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>148.11655</v>
+        <v>107.91397</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>145.2717</v>
+        <v>110.07345</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>142.82897</v>
+        <v>116.9011</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>132.24634</v>
+        <v>110.20582</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>132.58296</v>
+        <v>110.57037</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>145.88641</v>
+        <v>121.44532</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>159.98573</v>
+        <v>130.54751</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>137.44783</v>
+        <v>130.14517</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>154.09613</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>158.2</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>160.66</v>
+        <v>157.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>158.2</v>
+        <v>156.95</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>160.86</v>
+        <v>159.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>171.0</v>
+        <v>161.46258</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>177.68042</v>
+        <v>173.83887</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>168.0</v>
+        <v>164.00586</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>174.0756</v>
+        <v>167.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>187.72362</v>
+        <v>174.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>181.4386</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>190.46</v>
+        <v>168.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>170.46</v>
+        <v>164.08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>168.36</v>
+        <v>160.95</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>163.13557</v>
+        <v>158.84</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>165.17</v>
+        <v>157.84</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>158.43</v>
+        <v>153.46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>157.21641</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>140.06902</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>158.2</v>
+        <v>151.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>144.64899</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>141.04407</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46183.0</v>
+        <v>46184.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>134.62869</v>
+        <v>126.31</v>
       </c>
     </row>
   </sheetData>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Foglio1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Foglio2" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>132.76904</v>
+        <v>144.59036</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>132.15</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>132.15</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>132.15</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>132.15</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>129.21</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>132.15</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>132.15</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>129.08</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>132.04</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>129.08</v>
+        <v>130.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>130.2</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>130.75</v>
+        <v>131.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>131.18</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>131.16</v>
+        <v>129.78</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>127.31</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>127.31</v>
+        <v>130.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>132.15</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>132.15</v>
+        <v>130.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>132.15</v>
+        <v>131.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>134.64</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>132.15</v>
+        <v>131.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>132.15</v>
+        <v>127.85</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>132.15</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>151.0</v>
+        <v>131.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>157.8</v>
+        <v>135.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>157.8</v>
+        <v>137.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>161.5</v>
+        <v>148.87487</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>157.8</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>157.79104</v>
+        <v>145.54</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>158.48612</v>
+        <v>141.97</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>161.5</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>160.84468</v>
+        <v>158.93032</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>159.1928</v>
+        <v>146.24836</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>154.7106</v>
+        <v>120.70042</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>149.52925</v>
+        <v>88.52097</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>145.16686</v>
+        <v>117.99368</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>143.7738</v>
+        <v>107.26054</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>125.78061</v>
+        <v>93.99105</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>125.71971</v>
+        <v>87.53532</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>131.99215</v>
+        <v>87.84902</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>131.35197</v>
+        <v>87.77706</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>120.72313</v>
+        <v>87.04207</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>118.95059</v>
+        <v>86.90036</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>111.5533</v>
+        <v>87.34679</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>119.83895</v>
+        <v>87.33688</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>110.53382</v>
+        <v>87.3178</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>109.42048</v>
+        <v>80.65866</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>98.81551</v>
+        <v>60.75824</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>71.99453</v>
+        <v>57.43571</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>65.53</v>
+        <v>64.47992</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>59.85408</v>
+        <v>62.16836</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>64.09058</v>
+        <v>54.98116</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>60.0</v>
+        <v>54.14716</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>61.0</v>
+        <v>53.94106</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>61.0</v>
+        <v>51.27988</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>58.79054</v>
+        <v>47.68457</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>62.00186</v>
+        <v>48.2903</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>67.49352</v>
+        <v>50.23247</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>63.83128</v>
+        <v>57.15579</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>68.42088</v>
+        <v>40.04595</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>70.72727</v>
+        <v>38.98678</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>87.3876</v>
+        <v>44.18225</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>86.8819</v>
+        <v>47.70304</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>99.2409</v>
+        <v>41.09</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>107.91397</v>
+        <v>48.85254</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>110.07345</v>
+        <v>55.13811</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>116.9011</v>
+        <v>66.03885</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>110.20582</v>
+        <v>56.55302</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>110.57037</v>
+        <v>73.3655</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>121.44532</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>130.54751</v>
+        <v>112.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>130.14517</v>
+        <v>103.03652</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>127.2</v>
+        <v>113.87066</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>132.15</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>157.8</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>156.95</v>
+        <v>132.49</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>159.81</v>
+        <v>139.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>161.46258</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>173.83887</v>
+        <v>162.08</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>164.00586</v>
+        <v>156.94</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>167.3</v>
+        <v>162.44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>174.0</v>
+        <v>164.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>172.13</v>
+        <v>165.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>168.86</v>
+        <v>173.98</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>164.08</v>
+        <v>162.08</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>160.95</v>
+        <v>155.72</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>158.84</v>
+        <v>156.32</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>157.84</v>
+        <v>165.08</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>153.46</v>
+        <v>161.61</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>151.8</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>132.15</v>
+        <v>155.03</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>151.0</v>
+        <v>155.35</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>132.15</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>132.15</v>
+        <v>138.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46184.0</v>
+        <v>46185.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,2695 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>126.31</v>
+        <v>135.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D98" s="1">
+        <v>150.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B99" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D99" s="1">
+        <v>158.0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D100" s="1">
+        <v>149.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B101" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D101" s="1">
+        <v>146.71</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B102" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>146.71</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C103" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D103" s="1">
+        <v>132.49</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C104" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D104" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B105" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C105" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D105" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C106" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D107" s="1">
+        <v>131.4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C108" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D108" s="1">
+        <v>130.35</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C109" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D109" s="1">
+        <v>135.99</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>132.56</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C111" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D111" s="1">
+        <v>126.26</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D112" s="1">
+        <v>128.6</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C113" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D113" s="1">
+        <v>132.98</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B114" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C114" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D114" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B115" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C115" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D115" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C116" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B117" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C117" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D117" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C118" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D118" s="1">
+        <v>129.29</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C119" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D119" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C120" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D120" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C121" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>120.1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B122" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D122" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B123" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D123" s="1">
+        <v>129.29</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C124" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B125" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C125" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D125" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B126" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>146.71</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B127" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C127" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D127" s="1">
+        <v>135.81</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B128" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D128" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B129" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D129" s="1">
+        <v>115.22</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>143.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B131" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C131" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D131" s="1">
+        <v>122.66</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B132" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C132" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D132" s="1">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B133" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C133" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D133" s="1">
+        <v>30.94</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B134" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D134" s="1">
+        <v>124.95</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B135" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D135" s="1">
+        <v>113.9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B136" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C136" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>78.17</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B137" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C137" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D137" s="1">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B138" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C138" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>40.0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B139" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C139" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D139" s="1">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B140" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C140" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B141" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C141" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B142" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B143" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B144" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D145" s="1">
+        <v>28.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B146" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D146" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B147" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C147" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D147" s="1">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B148" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C148" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D148" s="1">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B149" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C149" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D149" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B150" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C150" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D150" s="1">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B151" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C151" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D151" s="1">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B152" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C152" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D152" s="1">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B153" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C153" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D153" s="1">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B154" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C154" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D154" s="1">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B155" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C155" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D155" s="1">
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B156" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C156" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D156" s="1">
+        <v>23.58</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B157" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C157" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D157" s="1">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B158" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C158" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D158" s="1">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B159" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C159" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D159" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C160" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D160" s="1">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B161" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C161" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D161" s="1">
+        <v>32.52</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B162" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C162" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D162" s="1">
+        <v>0.9678</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B163" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C163" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>4.83698</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B164" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C164" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D164" s="1">
+        <v>9.67924</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B165" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C165" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>23.39896</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B166" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C166" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D166" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B167" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C167" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D167" s="1">
+        <v>28.88</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B168" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C168" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B169" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C169" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D169" s="1">
+        <v>99.52</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B170" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C170" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B171" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C171" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D171" s="1">
+        <v>109.77</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B172" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C172" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D172" s="1">
+        <v>142.49</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B173" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C173" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>155.72</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B174" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C174" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D174" s="1">
+        <v>140.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C175" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D175" s="1">
+        <v>147.17</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B176" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C176" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>164.5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B177" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C177" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D177" s="1">
+        <v>162.58</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B178" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C178" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>159.85872</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B179" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C179" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D179" s="1">
+        <v>150.87</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B180" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C180" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D180" s="1">
+        <v>156.5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B181" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C181" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>163.64072</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B182" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C182" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D182" s="1">
+        <v>160.717</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B183" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C183" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>159.71796</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B184" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C184" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D184" s="1">
+        <v>159.69968</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B185" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C185" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D185" s="1">
+        <v>155.57416</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B186" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C186" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D186" s="1">
+        <v>156.09</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B187" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C187" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D187" s="1">
+        <v>149.68</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B188" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C188" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D188" s="1">
+        <v>149.08</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B189" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C189" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D189" s="1">
+        <v>146.71</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C190" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D190" s="1">
+        <v>161.5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B191" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C191" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D191" s="1">
+        <v>156.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B192" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C192" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D192" s="1">
+        <v>146.71</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3">
+        <v>46186.0</v>
+      </c>
+      <c r="B193" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C193" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D193" s="1">
+        <v>138.75043</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B194" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C194" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D194" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B195" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C195" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D195" s="1">
+        <v>146.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B196" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C196" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D196" s="1">
+        <v>148.92</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B197" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C197" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D197" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B198" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C198" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D198" s="1">
+        <v>146.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B199" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C199" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D199" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B200" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C200" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D200" s="1">
+        <v>143.39</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B201" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C201" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D201" s="1">
+        <v>132.32363</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B202" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C202" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D202" s="1">
+        <v>140.70128</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B203" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C203" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D203" s="1">
+        <v>129.83</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B204" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C204" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D204" s="1">
+        <v>125.52</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B205" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C205" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D205" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B206" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C206" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D206" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B207" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C207" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D207" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B208" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C208" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D208" s="1">
+        <v>124.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B209" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C209" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D209" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B210" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C210" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D210" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B211" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C211" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D211" s="1">
+        <v>120.41</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B212" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C212" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D212" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B213" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C213" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D213" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B214" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C214" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D214" s="1">
+        <v>132.8</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B215" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C215" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D215" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B216" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C216" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D216" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B217" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C217" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D217" s="1">
+        <v>120.1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B218" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C218" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D218" s="1">
+        <v>124.12</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B219" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C219" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D219" s="1">
+        <v>132.39</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B220" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C220" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D220" s="1">
+        <v>140.34</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B221" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C221" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D221" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B222" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C222" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D222" s="1">
+        <v>146.24</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B223" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C223" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D223" s="1">
+        <v>136.31</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B224" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C224" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D224" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B225" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C225" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D225" s="1">
+        <v>114.3</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B226" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C226" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D226" s="1">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B227" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C227" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D227" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B228" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C228" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D228" s="1">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B229" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C229" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D229" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B230" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C230" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D230" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B231" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C231" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D231" s="1">
+        <v>123.55</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B232" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C232" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D232" s="1">
+        <v>90.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B233" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C233" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D233" s="1">
+        <v>54.99</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B234" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C234" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D234" s="1">
+        <v>49.25081</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B235" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C235" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D235" s="1">
+        <v>30.62298</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B236" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C236" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D236" s="1">
+        <v>30.46615</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B237" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C237" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D237" s="1">
+        <v>29.11711</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B238" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C238" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D238" s="1">
+        <v>9.79809</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B239" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D239" s="1">
+        <v>9.79933</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B240" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C240" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D240" s="1">
+        <v>9.80014</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B241" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C241" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D241" s="1">
+        <v>9.79987</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B242" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C242" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D242" s="1">
+        <v>9.79921</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B243" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C243" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D243" s="1">
+        <v>4.96696</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B244" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C244" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D244" s="1">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B245" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C245" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D245" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B246" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C246" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D246" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B247" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C247" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D247" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B248" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C248" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D248" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B249" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C249" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D249" s="1">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B250" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C250" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D250" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B251" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C251" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D251" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B252" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C252" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D252" s="1">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B253" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C253" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D253" s="1">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B254" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C254" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D254" s="1">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B255" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C255" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D255" s="1">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B256" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C256" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D256" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B257" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C257" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D257" s="1">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B258" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C258" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D258" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B259" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C259" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D259" s="1">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B260" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C260" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D260" s="1">
+        <v>0.00967</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B261" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C261" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D261" s="1">
+        <v>0.96777</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B262" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C262" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D262" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B263" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C263" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D263" s="1">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B264" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C264" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D264" s="1">
+        <v>35.0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B265" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C265" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D265" s="1">
+        <v>94.93</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B266" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C266" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D266" s="1">
+        <v>44.87</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B267" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C267" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D267" s="1">
+        <v>108.74</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B268" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C268" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D268" s="1">
+        <v>134.4</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B269" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C269" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D269" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B270" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C270" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D270" s="1">
+        <v>130.0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B271" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C271" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D271" s="1">
+        <v>147.67</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B272" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C272" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D272" s="1">
+        <v>155.72</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B273" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C273" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D273" s="1">
+        <v>150.94</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B274" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C274" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D274" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B275" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C275" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D275" s="1">
+        <v>144.78</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B276" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C276" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D276" s="1">
+        <v>148.92</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B277" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C277" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D277" s="1">
+        <v>148.92</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B278" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C278" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D278" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B279" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C279" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D279" s="1">
+        <v>146.05</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B280" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C280" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D280" s="1">
+        <v>144.55</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B281" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C281" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D281" s="1">
+        <v>144.4</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B282" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C282" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D282" s="1">
+        <v>137.07</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B283" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C283" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D283" s="1">
+        <v>133.35</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B284" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C284" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D284" s="1">
+        <v>140.4</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B285" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C285" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D285" s="1">
+        <v>141.0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B286" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C286" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D286" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B287" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C287" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D287" s="1">
+        <v>144.49</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B288" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C288" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D288" s="1">
+        <v>126.71</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="3">
+        <v>46187.0</v>
+      </c>
+      <c r="B289" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C289" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D289" s="1">
+        <v>123.55</v>
       </c>
     </row>
   </sheetData>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Foglio1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Foglio2" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>125.77</v>
+        <v>136.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>125.77</v>
+        <v>135.22206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>125.77</v>
+        <v>132.56212</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>125.77</v>
+        <v>129.77143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>125.77</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>119.96</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>119.96</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>107.55</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>110.9</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>112.65</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>123.49</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>123.48</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>122.75</v>
+        <v>122.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>125.77</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>119.96</v>
+        <v>123.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>119.96</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>118.55</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>119.96</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>125.77</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>125.77</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>122.75</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>125.71</v>
+        <v>121.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>125.77</v>
+        <v>122.96</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>125.77</v>
+        <v>122.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>132.89</v>
+        <v>128.47856</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>148.84</v>
+        <v>134.84795</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>148.84</v>
+        <v>136.62471</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>148.84</v>
+        <v>135.75316</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>148.84</v>
+        <v>138.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>148.84</v>
+        <v>133.30604</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>157.03</v>
+        <v>133.74926</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>149.15</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>151.31798</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>155.97089</v>
+        <v>137.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>154.27918</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>148.84</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>155.97349</v>
+        <v>146.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>154.18493</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>144.0</v>
+        <v>125.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>132.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>139.35</v>
+        <v>139.54029</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>125.77</v>
+        <v>125.06246</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>120.30527</v>
+        <v>125.19057</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>106.53171</v>
+        <v>118.88356</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>107.44</v>
+        <v>123.66299</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>106.66</v>
+        <v>124.94376</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>97.44</v>
+        <v>123.6465</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>73.97094</v>
+        <v>124.88693</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>69.5</v>
+        <v>115.73997</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>61.0</v>
+        <v>109.83</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>60.0</v>
+        <v>108.97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>60.0</v>
+        <v>106.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>65.74308</v>
+        <v>110.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>76.98397</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>92.28963</v>
+        <v>117.38865</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>90.3662</v>
+        <v>120.13744</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>106.0531</v>
+        <v>125.34432</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>110.08965</v>
+        <v>128.85031</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>117.6277</v>
+        <v>125.35296</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>113.48541</v>
+        <v>127.63582</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>112.24285</v>
+        <v>102.89067</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>114.99801</v>
+        <v>112.30964</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>122.14309</v>
+        <v>123.51288</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>128.81254</v>
+        <v>123.65405</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>125.08484</v>
+        <v>120.75845</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>129.36892</v>
+        <v>116.40424</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>136.29429</v>
+        <v>123.3936</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>145.65944</v>
+        <v>123.76001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>125.77</v>
+        <v>124.47794</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>130.0</v>
+        <v>125.58313</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>148.84</v>
+        <v>128.94</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>155.39</v>
+        <v>137.48987</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>132.88</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>142.51</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>149.0</v>
+        <v>135.50675</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>157.05</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>148.84</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>152.34</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>158.26</v>
+        <v>157.14</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>172.99</v>
+        <v>168.12878</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>157.05</v>
+        <v>160.57315</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>162.48</v>
+        <v>163.58823</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>165.77</v>
+        <v>171.99416</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>171.86613</v>
+        <v>180.06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>162.60391</v>
+        <v>176.59842</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>160.0</v>
+        <v>172.56</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>163.26097</v>
+        <v>165.92</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>152.64</v>
+        <v>162.50102</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>162.70075</v>
+        <v>162.72</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>155.88538</v>
+        <v>155.1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>155.0821</v>
+        <v>153.99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>144.71696</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>156.57</v>
+        <v>151.64</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>148.84</v>
+        <v>147.2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>140.0</v>
+        <v>139.26965</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,8 +1649,1928 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>127.88759</v>
-      </c>
+        <v>133.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D98" s="1">
+        <v>148.08</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B99" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D99" s="1">
+        <v>145.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D100" s="1">
+        <v>142.36</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B101" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D101" s="1">
+        <v>135.06</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B102" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>145.5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C103" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D103" s="1">
+        <v>137.13579</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C104" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D104" s="1">
+        <v>135.96256</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B105" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C105" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D105" s="1">
+        <v>130.80707</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C106" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>132.55341</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D107" s="1">
+        <v>129.22475</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C108" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D108" s="1">
+        <v>129.26089</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C109" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D109" s="1">
+        <v>129.36095</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>128.93081</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C111" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D111" s="1">
+        <v>127.72016</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D112" s="1">
+        <v>129.14547</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C113" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D113" s="1">
+        <v>128.28357</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B114" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C114" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D114" s="1">
+        <v>126.51628</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B115" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C115" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D115" s="1">
+        <v>129.20629</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C116" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>129.17576</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B117" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C117" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D117" s="1">
+        <v>130.29893</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C118" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D118" s="1">
+        <v>134.52894</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C119" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D119" s="1">
+        <v>128.47408</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C120" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D120" s="1">
+        <v>128.89985</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C121" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>132.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B122" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D122" s="1">
+        <v>143.00149</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B123" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D123" s="1">
+        <v>148.02744</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C124" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>146.8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B125" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C125" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D125" s="1">
+        <v>149.3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B126" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>155.22</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B127" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C127" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D127" s="1">
+        <v>155.22</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B128" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D128" s="1">
+        <v>155.22</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B129" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D129" s="1">
+        <v>152.76</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>152.56744</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B131" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C131" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D131" s="1">
+        <v>150.46474</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B132" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C132" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D132" s="1">
+        <v>145.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B133" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C133" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D133" s="1">
+        <v>138.56</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B134" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D134" s="1">
+        <v>129.89</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B135" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D135" s="1">
+        <v>121.76</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B136" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C136" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>121.76</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B137" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C137" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D137" s="1">
+        <v>111.15</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B138" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C138" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>119.85</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B139" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C139" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D139" s="1">
+        <v>112.83</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B140" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C140" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>118.9</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B141" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C141" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>111.56</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B142" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>120.56</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B143" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>123.77477</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B144" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>120.31546</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D145" s="1">
+        <v>118.44214</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B146" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D146" s="1">
+        <v>102.32325</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B147" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C147" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D147" s="1">
+        <v>109.50161</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B148" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C148" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D148" s="1">
+        <v>102.32801</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B149" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C149" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D149" s="1">
+        <v>101.40367</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B150" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C150" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D150" s="1">
+        <v>112.56908</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B151" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C151" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D151" s="1">
+        <v>102.15349</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B152" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C152" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D152" s="1">
+        <v>108.72584</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B153" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C153" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D153" s="1">
+        <v>110.03914</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B154" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C154" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D154" s="1">
+        <v>104.72763</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B155" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C155" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D155" s="1">
+        <v>109.41678</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B156" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C156" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D156" s="1">
+        <v>113.48321</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B157" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C157" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D157" s="1">
+        <v>118.05063</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B158" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C158" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D158" s="1">
+        <v>119.76243</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B159" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C159" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D159" s="1">
+        <v>119.89012</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C160" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D160" s="1">
+        <v>123.58221</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B161" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C161" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D161" s="1">
+        <v>137.34721</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B162" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C162" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D162" s="1">
+        <v>128.56206</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B163" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C163" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>128.66173</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B164" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C164" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D164" s="1">
+        <v>128.68768</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B165" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C165" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>129.42451</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B166" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C166" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D166" s="1">
+        <v>121.5796</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B167" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C167" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D167" s="1">
+        <v>121.76</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B168" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C168" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>132.74</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B169" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C169" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D169" s="1">
+        <v>136.26</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B170" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C170" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>120.06</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B171" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C171" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D171" s="1">
+        <v>128.07</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B172" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C172" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D172" s="1">
+        <v>134.84608</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B173" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C173" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>147.11155</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B174" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C174" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D174" s="1">
+        <v>143.64456</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C175" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D175" s="1">
+        <v>145.5</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B176" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C176" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>152.76</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B177" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C177" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D177" s="1">
+        <v>164.33128</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B178" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C178" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>154.58798</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B179" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C179" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D179" s="1">
+        <v>160.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B180" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C180" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D180" s="1">
+        <v>176.69881</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B181" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C181" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>177.51321</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B182" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C182" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D182" s="1">
+        <v>176.6</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B183" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C183" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>170.96439</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B184" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C184" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D184" s="1">
+        <v>161.48994</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B185" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C185" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D185" s="1">
+        <v>152.76</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B186" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C186" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D186" s="1">
+        <v>171.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B187" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C187" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D187" s="1">
+        <v>160.78198</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B188" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C188" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D188" s="1">
+        <v>154.54153</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B189" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C189" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D189" s="1">
+        <v>148.11598</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C190" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D190" s="1">
+        <v>152.77</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B191" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C191" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D191" s="1">
+        <v>146.45784</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B192" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C192" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D192" s="1">
+        <v>139.54674</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3">
+        <v>46190.0</v>
+      </c>
+      <c r="B193" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C193" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D193" s="1">
+        <v>135.04655</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>136.21</v>
+        <v>145.13452</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>135.22206</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>132.56212</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>129.77143</v>
+        <v>132.26056</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>125.66</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>125.66</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>125.66</v>
+        <v>125.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>125.66</v>
+        <v>131.37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>125.66</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>125.66</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>125.66</v>
+        <v>139.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>125.66</v>
+        <v>132.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>122.26</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>121.6</v>
+        <v>134.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>123.47</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>123.45</v>
+        <v>128.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>121.6</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>121.6</v>
+        <v>132.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>121.6</v>
+        <v>126.96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>121.6</v>
+        <v>127.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>121.6</v>
+        <v>134.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>121.6</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>122.96</v>
+        <v>126.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>122.08</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>128.47856</v>
+        <v>133.02</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>134.84795</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>136.62471</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>135.75316</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>138.99</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>133.30604</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>133.74926</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>125.66</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>145.1</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>137.05</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>135.0</v>
+        <v>130.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>125.66</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>146.5</v>
+        <v>138.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>138.2</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>125.66</v>
+        <v>132.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>125.0</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>139.54029</v>
+        <v>142.7064</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>125.06246</v>
+        <v>133.02766</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>125.19057</v>
+        <v>120.57885</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>118.88356</v>
+        <v>118.83465</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>123.66299</v>
+        <v>118.44122</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>124.94376</v>
+        <v>118.41387</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>123.6465</v>
+        <v>118.37978</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>124.88693</v>
+        <v>118.37243</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>115.73997</v>
+        <v>113.94975</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>109.83</v>
+        <v>111.65314</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>108.97</v>
+        <v>101.0428</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>106.03</v>
+        <v>104.02</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>110.68</v>
+        <v>108.08</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>111.5</v>
+        <v>105.54941</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>117.38865</v>
+        <v>106.21342</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>120.13744</v>
+        <v>110.94016</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>125.34432</v>
+        <v>112.61885</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>128.85031</v>
+        <v>113.63996</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>125.35296</v>
+        <v>113.78756</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>127.63582</v>
+        <v>113.74743</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>102.89067</v>
+        <v>114.50408</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>112.30964</v>
+        <v>118.02852</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>123.51288</v>
+        <v>121.40887</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>123.65405</v>
+        <v>128.23871</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>120.75845</v>
+        <v>123.01509</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>116.40424</v>
+        <v>137.5554</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>123.3936</v>
+        <v>141.36752</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>123.76001</v>
+        <v>141.58457</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>124.47794</v>
+        <v>142.8712</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>125.58313</v>
+        <v>149.1858</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>128.94</v>
+        <v>153.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>137.48987</v>
+        <v>153.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>124.0</v>
+        <v>153.41</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>128.85</v>
+        <v>153.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>135.50675</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>148.0</v>
+        <v>169.74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>147.2</v>
+        <v>153.44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>152.0</v>
+        <v>165.00404</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>157.14</v>
+        <v>178.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>168.12878</v>
+        <v>191.46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>160.57315</v>
+        <v>175.22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>163.58823</v>
+        <v>178.72</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>171.99416</v>
+        <v>186.03</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>180.06</v>
+        <v>180.03</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>176.59842</v>
+        <v>186.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>172.56</v>
+        <v>178.72</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>165.92</v>
+        <v>175.22</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>162.50102</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>162.72</v>
+        <v>176.99</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>155.1</v>
+        <v>173.78</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>153.99</v>
+        <v>167.44</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>147.2</v>
+        <v>154.51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>151.64</v>
+        <v>168.85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>147.2</v>
+        <v>154.51</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>139.26965</v>
+        <v>150.98</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46189.0</v>
+        <v>46191.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,1352 +1649,584 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>133.0</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B98" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D98" s="1">
-        <v>148.08</v>
-      </c>
+      <c r="A98" s="3"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
     </row>
     <row r="99">
-      <c r="A99" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B99" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C99" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D99" s="1">
-        <v>145.5</v>
-      </c>
+      <c r="A99" s="3"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
     </row>
     <row r="100">
-      <c r="A100" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B100" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C100" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D100" s="1">
-        <v>142.36</v>
-      </c>
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
     </row>
     <row r="101">
-      <c r="A101" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B101" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C101" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D101" s="1">
-        <v>135.06</v>
-      </c>
+      <c r="A101" s="3"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
     </row>
     <row r="102">
-      <c r="A102" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B102" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C102" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D102" s="1">
-        <v>145.5</v>
-      </c>
+      <c r="A102" s="3"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
     </row>
     <row r="103">
-      <c r="A103" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B103" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C103" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D103" s="1">
-        <v>137.13579</v>
-      </c>
+      <c r="A103" s="3"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
     </row>
     <row r="104">
-      <c r="A104" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B104" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C104" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D104" s="1">
-        <v>135.96256</v>
-      </c>
+      <c r="A104" s="3"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
     </row>
     <row r="105">
-      <c r="A105" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B105" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C105" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D105" s="1">
-        <v>130.80707</v>
-      </c>
+      <c r="A105" s="3"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106">
-      <c r="A106" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B106" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C106" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D106" s="1">
-        <v>132.55341</v>
-      </c>
+      <c r="A106" s="3"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
     </row>
     <row r="107">
-      <c r="A107" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B107" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C107" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D107" s="1">
-        <v>129.22475</v>
-      </c>
+      <c r="A107" s="3"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
     </row>
     <row r="108">
-      <c r="A108" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B108" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C108" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D108" s="1">
-        <v>129.26089</v>
-      </c>
+      <c r="A108" s="3"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
     </row>
     <row r="109">
-      <c r="A109" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B109" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C109" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D109" s="1">
-        <v>129.36095</v>
-      </c>
+      <c r="A109" s="3"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
     </row>
     <row r="110">
-      <c r="A110" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B110" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C110" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D110" s="1">
-        <v>128.93081</v>
-      </c>
+      <c r="A110" s="3"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
     </row>
     <row r="111">
-      <c r="A111" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B111" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C111" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D111" s="1">
-        <v>127.72016</v>
-      </c>
+      <c r="A111" s="3"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
     </row>
     <row r="112">
-      <c r="A112" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B112" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C112" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D112" s="1">
-        <v>129.14547</v>
-      </c>
+      <c r="A112" s="3"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
     </row>
     <row r="113">
-      <c r="A113" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B113" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C113" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="D113" s="1">
-        <v>128.28357</v>
-      </c>
+      <c r="A113" s="3"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
     </row>
     <row r="114">
-      <c r="A114" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B114" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C114" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D114" s="1">
-        <v>126.51628</v>
-      </c>
+      <c r="A114" s="3"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
     </row>
     <row r="115">
-      <c r="A115" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B115" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C115" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>129.20629</v>
-      </c>
+      <c r="A115" s="3"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
     </row>
     <row r="116">
-      <c r="A116" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B116" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C116" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D116" s="1">
-        <v>129.17576</v>
-      </c>
+      <c r="A116" s="3"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
     </row>
     <row r="117">
-      <c r="A117" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B117" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C117" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D117" s="1">
-        <v>130.29893</v>
-      </c>
+      <c r="A117" s="3"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
     </row>
     <row r="118">
-      <c r="A118" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B118" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C118" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D118" s="1">
-        <v>134.52894</v>
-      </c>
+      <c r="A118" s="3"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
     </row>
     <row r="119">
-      <c r="A119" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B119" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C119" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="D119" s="1">
-        <v>128.47408</v>
-      </c>
+      <c r="A119" s="3"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
     </row>
     <row r="120">
-      <c r="A120" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B120" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C120" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D120" s="1">
-        <v>128.89985</v>
-      </c>
+      <c r="A120" s="3"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
     </row>
     <row r="121">
-      <c r="A121" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B121" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C121" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="D121" s="1">
-        <v>132.0</v>
-      </c>
+      <c r="A121" s="3"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
     </row>
     <row r="122">
-      <c r="A122" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B122" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C122" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="D122" s="1">
-        <v>143.00149</v>
-      </c>
+      <c r="A122" s="3"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
     </row>
     <row r="123">
-      <c r="A123" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B123" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C123" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D123" s="1">
-        <v>148.02744</v>
-      </c>
+      <c r="A123" s="3"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
     </row>
     <row r="124">
-      <c r="A124" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B124" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C124" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D124" s="1">
-        <v>146.8</v>
-      </c>
+      <c r="A124" s="3"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
     </row>
     <row r="125">
-      <c r="A125" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B125" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C125" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="D125" s="1">
-        <v>149.3</v>
-      </c>
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
     </row>
     <row r="126">
-      <c r="A126" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B126" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C126" s="1">
-        <v>29.0</v>
-      </c>
-      <c r="D126" s="1">
-        <v>155.22</v>
-      </c>
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
     </row>
     <row r="127">
-      <c r="A127" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B127" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C127" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D127" s="1">
-        <v>155.22</v>
-      </c>
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
     </row>
     <row r="128">
-      <c r="A128" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B128" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C128" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="D128" s="1">
-        <v>155.22</v>
-      </c>
+      <c r="A128" s="3"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
     </row>
     <row r="129">
-      <c r="A129" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B129" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C129" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="D129" s="1">
-        <v>152.76</v>
-      </c>
+      <c r="A129" s="3"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
     </row>
     <row r="130">
-      <c r="A130" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B130" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C130" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D130" s="1">
-        <v>152.56744</v>
-      </c>
+      <c r="A130" s="3"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
     </row>
     <row r="131">
-      <c r="A131" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B131" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C131" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="D131" s="1">
-        <v>150.46474</v>
-      </c>
+      <c r="A131" s="3"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
     </row>
     <row r="132">
-      <c r="A132" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B132" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C132" s="1">
-        <v>35.0</v>
-      </c>
-      <c r="D132" s="1">
-        <v>145.5</v>
-      </c>
+      <c r="A132" s="3"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
     </row>
     <row r="133">
-      <c r="A133" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B133" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C133" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D133" s="1">
-        <v>138.56</v>
-      </c>
+      <c r="A133" s="3"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
     </row>
     <row r="134">
-      <c r="A134" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B134" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C134" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D134" s="1">
-        <v>129.89</v>
-      </c>
+      <c r="A134" s="3"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
     </row>
     <row r="135">
-      <c r="A135" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B135" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C135" s="1">
-        <v>38.0</v>
-      </c>
-      <c r="D135" s="1">
-        <v>121.76</v>
-      </c>
+      <c r="A135" s="3"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
     </row>
     <row r="136">
-      <c r="A136" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B136" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C136" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D136" s="1">
-        <v>121.76</v>
-      </c>
+      <c r="A136" s="3"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
     </row>
     <row r="137">
-      <c r="A137" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B137" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C137" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="D137" s="1">
-        <v>111.15</v>
-      </c>
+      <c r="A137" s="3"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
     </row>
     <row r="138">
-      <c r="A138" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B138" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C138" s="1">
-        <v>41.0</v>
-      </c>
-      <c r="D138" s="1">
-        <v>119.85</v>
-      </c>
+      <c r="A138" s="3"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
     </row>
     <row r="139">
-      <c r="A139" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B139" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C139" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="D139" s="1">
-        <v>112.83</v>
-      </c>
+      <c r="A139" s="3"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
     </row>
     <row r="140">
-      <c r="A140" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B140" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C140" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D140" s="1">
-        <v>118.9</v>
-      </c>
+      <c r="A140" s="3"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141">
-      <c r="A141" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B141" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C141" s="1">
-        <v>44.0</v>
-      </c>
-      <c r="D141" s="1">
-        <v>111.56</v>
-      </c>
+      <c r="A141" s="3"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
     </row>
     <row r="142">
-      <c r="A142" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B142" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C142" s="1">
-        <v>45.0</v>
-      </c>
-      <c r="D142" s="1">
-        <v>120.56</v>
-      </c>
+      <c r="A142" s="3"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
     </row>
     <row r="143">
-      <c r="A143" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B143" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C143" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D143" s="1">
-        <v>123.77477</v>
-      </c>
+      <c r="A143" s="3"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
     </row>
     <row r="144">
-      <c r="A144" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B144" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C144" s="1">
-        <v>47.0</v>
-      </c>
-      <c r="D144" s="1">
-        <v>120.31546</v>
-      </c>
+      <c r="A144" s="3"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
     </row>
     <row r="145">
-      <c r="A145" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B145" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C145" s="1">
-        <v>48.0</v>
-      </c>
-      <c r="D145" s="1">
-        <v>118.44214</v>
-      </c>
+      <c r="A145" s="3"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
     </row>
     <row r="146">
-      <c r="A146" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B146" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C146" s="1">
-        <v>49.0</v>
-      </c>
-      <c r="D146" s="1">
-        <v>102.32325</v>
-      </c>
+      <c r="A146" s="3"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
     </row>
     <row r="147">
-      <c r="A147" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B147" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C147" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D147" s="1">
-        <v>109.50161</v>
-      </c>
+      <c r="A147" s="3"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
     </row>
     <row r="148">
-      <c r="A148" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B148" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C148" s="1">
-        <v>51.0</v>
-      </c>
-      <c r="D148" s="1">
-        <v>102.32801</v>
-      </c>
+      <c r="A148" s="3"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
     </row>
     <row r="149">
-      <c r="A149" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B149" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C149" s="1">
-        <v>52.0</v>
-      </c>
-      <c r="D149" s="1">
-        <v>101.40367</v>
-      </c>
+      <c r="A149" s="3"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
     </row>
     <row r="150">
-      <c r="A150" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B150" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C150" s="1">
-        <v>53.0</v>
-      </c>
-      <c r="D150" s="1">
-        <v>112.56908</v>
-      </c>
+      <c r="A150" s="3"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
     </row>
     <row r="151">
-      <c r="A151" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B151" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C151" s="1">
-        <v>54.0</v>
-      </c>
-      <c r="D151" s="1">
-        <v>102.15349</v>
-      </c>
+      <c r="A151" s="3"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152">
-      <c r="A152" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B152" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C152" s="1">
-        <v>55.0</v>
-      </c>
-      <c r="D152" s="1">
-        <v>108.72584</v>
-      </c>
+      <c r="A152" s="3"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
     </row>
     <row r="153">
-      <c r="A153" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B153" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C153" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D153" s="1">
-        <v>110.03914</v>
-      </c>
+      <c r="A153" s="3"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154">
-      <c r="A154" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B154" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C154" s="1">
-        <v>57.0</v>
-      </c>
-      <c r="D154" s="1">
-        <v>104.72763</v>
-      </c>
+      <c r="A154" s="3"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
     </row>
     <row r="155">
-      <c r="A155" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B155" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C155" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="D155" s="1">
-        <v>109.41678</v>
-      </c>
+      <c r="A155" s="3"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
     </row>
     <row r="156">
-      <c r="A156" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B156" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C156" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D156" s="1">
-        <v>113.48321</v>
-      </c>
+      <c r="A156" s="3"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157">
-      <c r="A157" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B157" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C157" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="D157" s="1">
-        <v>118.05063</v>
-      </c>
+      <c r="A157" s="3"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
     </row>
     <row r="158">
-      <c r="A158" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B158" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C158" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="D158" s="1">
-        <v>119.76243</v>
-      </c>
+      <c r="A158" s="3"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
     </row>
     <row r="159">
-      <c r="A159" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B159" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C159" s="1">
-        <v>62.0</v>
-      </c>
-      <c r="D159" s="1">
-        <v>119.89012</v>
-      </c>
+      <c r="A159" s="3"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
     </row>
     <row r="160">
-      <c r="A160" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B160" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C160" s="1">
-        <v>63.0</v>
-      </c>
-      <c r="D160" s="1">
-        <v>123.58221</v>
-      </c>
+      <c r="A160" s="3"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
     </row>
     <row r="161">
-      <c r="A161" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B161" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C161" s="1">
-        <v>64.0</v>
-      </c>
-      <c r="D161" s="1">
-        <v>137.34721</v>
-      </c>
+      <c r="A161" s="3"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
     </row>
     <row r="162">
-      <c r="A162" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B162" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C162" s="1">
-        <v>65.0</v>
-      </c>
-      <c r="D162" s="1">
-        <v>128.56206</v>
-      </c>
+      <c r="A162" s="3"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
     </row>
     <row r="163">
-      <c r="A163" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B163" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C163" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D163" s="1">
-        <v>128.66173</v>
-      </c>
+      <c r="A163" s="3"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
     </row>
     <row r="164">
-      <c r="A164" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B164" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C164" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="D164" s="1">
-        <v>128.68768</v>
-      </c>
+      <c r="A164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
     </row>
     <row r="165">
-      <c r="A165" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B165" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C165" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D165" s="1">
-        <v>129.42451</v>
-      </c>
+      <c r="A165" s="3"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
     </row>
     <row r="166">
-      <c r="A166" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B166" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C166" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D166" s="1">
-        <v>121.5796</v>
-      </c>
+      <c r="A166" s="3"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
     </row>
     <row r="167">
-      <c r="A167" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B167" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C167" s="1">
-        <v>70.0</v>
-      </c>
-      <c r="D167" s="1">
-        <v>121.76</v>
-      </c>
+      <c r="A167" s="3"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
     </row>
     <row r="168">
-      <c r="A168" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B168" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C168" s="1">
-        <v>71.0</v>
-      </c>
-      <c r="D168" s="1">
-        <v>132.74</v>
-      </c>
+      <c r="A168" s="3"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
     </row>
     <row r="169">
-      <c r="A169" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B169" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C169" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D169" s="1">
-        <v>136.26</v>
-      </c>
+      <c r="A169" s="3"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
     </row>
     <row r="170">
-      <c r="A170" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B170" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C170" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="D170" s="1">
-        <v>120.06</v>
-      </c>
+      <c r="A170" s="3"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171">
-      <c r="A171" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B171" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C171" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="D171" s="1">
-        <v>128.07</v>
-      </c>
+      <c r="A171" s="3"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
     </row>
     <row r="172">
-      <c r="A172" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B172" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C172" s="1">
-        <v>75.0</v>
-      </c>
-      <c r="D172" s="1">
-        <v>134.84608</v>
-      </c>
+      <c r="A172" s="3"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173">
-      <c r="A173" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B173" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C173" s="1">
-        <v>76.0</v>
-      </c>
-      <c r="D173" s="1">
-        <v>147.11155</v>
-      </c>
+      <c r="A173" s="3"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
     </row>
     <row r="174">
-      <c r="A174" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B174" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C174" s="1">
-        <v>77.0</v>
-      </c>
-      <c r="D174" s="1">
-        <v>143.64456</v>
-      </c>
+      <c r="A174" s="3"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175">
-      <c r="A175" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B175" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C175" s="1">
-        <v>78.0</v>
-      </c>
-      <c r="D175" s="1">
-        <v>145.5</v>
-      </c>
+      <c r="A175" s="3"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176">
-      <c r="A176" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B176" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C176" s="1">
-        <v>79.0</v>
-      </c>
-      <c r="D176" s="1">
-        <v>152.76</v>
-      </c>
+      <c r="A176" s="3"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177">
-      <c r="A177" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B177" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C177" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="D177" s="1">
-        <v>164.33128</v>
-      </c>
+      <c r="A177" s="3"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
     </row>
     <row r="178">
-      <c r="A178" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B178" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C178" s="1">
-        <v>81.0</v>
-      </c>
-      <c r="D178" s="1">
-        <v>154.58798</v>
-      </c>
+      <c r="A178" s="3"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179">
-      <c r="A179" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B179" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C179" s="1">
-        <v>82.0</v>
-      </c>
-      <c r="D179" s="1">
-        <v>160.0</v>
-      </c>
+      <c r="A179" s="3"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
     </row>
     <row r="180">
-      <c r="A180" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B180" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C180" s="1">
-        <v>83.0</v>
-      </c>
-      <c r="D180" s="1">
-        <v>176.69881</v>
-      </c>
+      <c r="A180" s="3"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
     </row>
     <row r="181">
-      <c r="A181" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B181" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C181" s="1">
-        <v>84.0</v>
-      </c>
-      <c r="D181" s="1">
-        <v>177.51321</v>
-      </c>
+      <c r="A181" s="3"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
     </row>
     <row r="182">
-      <c r="A182" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B182" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C182" s="1">
-        <v>85.0</v>
-      </c>
-      <c r="D182" s="1">
-        <v>176.6</v>
-      </c>
+      <c r="A182" s="3"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
     </row>
     <row r="183">
-      <c r="A183" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B183" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C183" s="1">
-        <v>86.0</v>
-      </c>
-      <c r="D183" s="1">
-        <v>170.96439</v>
-      </c>
+      <c r="A183" s="3"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
     </row>
     <row r="184">
-      <c r="A184" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B184" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C184" s="1">
-        <v>87.0</v>
-      </c>
-      <c r="D184" s="1">
-        <v>161.48994</v>
-      </c>
+      <c r="A184" s="3"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
     </row>
     <row r="185">
-      <c r="A185" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B185" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C185" s="1">
-        <v>88.0</v>
-      </c>
-      <c r="D185" s="1">
-        <v>152.76</v>
-      </c>
+      <c r="A185" s="3"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
     </row>
     <row r="186">
-      <c r="A186" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B186" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C186" s="1">
-        <v>89.0</v>
-      </c>
-      <c r="D186" s="1">
-        <v>171.0</v>
-      </c>
+      <c r="A186" s="3"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
     </row>
     <row r="187">
-      <c r="A187" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B187" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C187" s="1">
-        <v>90.0</v>
-      </c>
-      <c r="D187" s="1">
-        <v>160.78198</v>
-      </c>
+      <c r="A187" s="3"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
     </row>
     <row r="188">
-      <c r="A188" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B188" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C188" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D188" s="1">
-        <v>154.54153</v>
-      </c>
+      <c r="A188" s="3"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189">
-      <c r="A189" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B189" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C189" s="1">
-        <v>92.0</v>
-      </c>
-      <c r="D189" s="1">
-        <v>148.11598</v>
-      </c>
+      <c r="A189" s="3"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
     </row>
     <row r="190">
-      <c r="A190" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B190" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C190" s="1">
-        <v>93.0</v>
-      </c>
-      <c r="D190" s="1">
-        <v>152.77</v>
-      </c>
+      <c r="A190" s="3"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191">
-      <c r="A191" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B191" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C191" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D191" s="1">
-        <v>146.45784</v>
-      </c>
+      <c r="A191" s="3"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
     </row>
     <row r="192">
-      <c r="A192" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B192" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C192" s="1">
-        <v>95.0</v>
-      </c>
-      <c r="D192" s="1">
-        <v>139.54674</v>
-      </c>
+      <c r="A192" s="3"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
     </row>
     <row r="193">
-      <c r="A193" s="3">
-        <v>46190.0</v>
-      </c>
-      <c r="B193" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C193" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="D193" s="1">
-        <v>135.04655</v>
-      </c>
+      <c r="A193" s="3"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="3"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>145.13452</v>
+        <v>148.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>143.78</v>
+        <v>143.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>143.78</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>132.26056</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>143.78</v>
+        <v>143.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>139.0</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>125.85</v>
+        <v>137.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>131.37</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>143.78</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>140.0</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>139.37</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>132.26</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>130.0</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>134.24</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>130.0</v>
+        <v>136.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>128.25</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>134.12</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>132.0</v>
+        <v>133.84</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>126.96</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>127.32</v>
+        <v>131.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>134.31</v>
+        <v>132.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>130.5</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>126.59</v>
+        <v>125.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>129.0</v>
+        <v>131.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>133.02</v>
+        <v>128.32517</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>143.78</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>143.78</v>
+        <v>141.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>143.78</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>143.78</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>143.78</v>
+        <v>138.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>143.78</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>143.78</v>
+        <v>133.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>143.78</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>139.0</v>
+        <v>136.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>130.5</v>
+        <v>127.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>120.3</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>138.18</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>140.0</v>
+        <v>140.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>132.26</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>120.3</v>
+        <v>116.74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>142.7064</v>
+        <v>136.57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>133.02766</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>120.57885</v>
+        <v>119.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>118.83465</v>
+        <v>118.28809</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>118.44122</v>
+        <v>115.4879</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>118.41387</v>
+        <v>113.03064</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>118.37978</v>
+        <v>114.4669</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>118.37243</v>
+        <v>109.1353</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>113.94975</v>
+        <v>113.17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>111.65314</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>101.0428</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>104.02</v>
+        <v>108.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>108.08</v>
+        <v>105.92876</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>105.54941</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>106.21342</v>
+        <v>114.27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>110.94016</v>
+        <v>115.12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>112.61885</v>
+        <v>116.26462</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>113.63996</v>
+        <v>116.58047</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>113.78756</v>
+        <v>117.50597</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>113.74743</v>
+        <v>118.36822</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>114.50408</v>
+        <v>118.00024</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>118.02852</v>
+        <v>117.82056</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>121.40887</v>
+        <v>123.19458</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>128.23871</v>
+        <v>134.00871</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>123.01509</v>
+        <v>118.43261</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>137.5554</v>
+        <v>119.08847</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>141.36752</v>
+        <v>140.53825</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>141.58457</v>
+        <v>140.71441</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>142.8712</v>
+        <v>132.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>149.1858</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>153.41</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>153.44</v>
+        <v>143.82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>153.41</v>
+        <v>135.91</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>153.44</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>164.0</v>
+        <v>148.23</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>169.74</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>153.44</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>165.00404</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>178.04</v>
+        <v>169.92</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>175.22</v>
+        <v>169.06614</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>178.72</v>
+        <v>170.18386</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>186.03</v>
+        <v>180.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>180.03</v>
+        <v>178.7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>186.03</v>
+        <v>178.7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>178.72</v>
+        <v>177.02446</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>175.22</v>
+        <v>167.38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>164.0</v>
+        <v>156.89554</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>176.99</v>
+        <v>168.10239</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>173.78</v>
+        <v>159.8262</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>167.44</v>
+        <v>150.05235</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>154.51</v>
+        <v>145.93</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>168.85</v>
+        <v>148.85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>154.51</v>
+        <v>143.82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>150.98</v>
+        <v>141.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46191.0</v>
+        <v>46192.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,1160 +1649,2696 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>143.78</v>
+        <v>129.83458</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+      <c r="A98" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D98" s="1">
+        <v>144.08109</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="A99" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B99" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D99" s="1">
+        <v>148.78</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+      <c r="A100" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D100" s="1">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="3"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="A101" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B101" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D101" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+      <c r="A102" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B102" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
+      <c r="A103" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C103" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D103" s="1">
+        <v>139.78</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
+      <c r="A104" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C104" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D104" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="3"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
+      <c r="A105" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B105" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C105" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D105" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="3"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
+      <c r="A106" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C106" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="3"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="A107" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D107" s="1">
+        <v>132.65</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="3"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
+      <c r="A108" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C108" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D108" s="1">
+        <v>132.65</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="3"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
+      <c r="A109" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C109" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D109" s="1">
+        <v>132.65</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="3"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
+      <c r="A110" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="3"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
+      <c r="A111" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C111" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D111" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="3"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
+      <c r="A112" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D112" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="3"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
+      <c r="A113" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C113" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D113" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="3"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
+      <c r="A114" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B114" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C114" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D114" s="1">
+        <v>132.22</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="3"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
+      <c r="A115" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B115" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C115" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D115" s="1">
+        <v>132.22</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="3"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
+      <c r="A116" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C116" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="3"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
+      <c r="A117" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B117" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C117" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D117" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="3"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
+      <c r="A118" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C118" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D118" s="1">
+        <v>132.22</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="3"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
+      <c r="A119" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C119" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D119" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="3"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
+      <c r="A120" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C120" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D120" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="3"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
+      <c r="A121" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C121" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>126.62</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="3"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="A122" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B122" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D122" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="3"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+      <c r="A123" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B123" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D123" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="3"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+      <c r="A124" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C124" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>129.1</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="3"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="A125" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B125" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C125" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D125" s="1">
+        <v>129.74</v>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="3"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+      <c r="A126" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B126" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>122.63</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="3"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
+      <c r="A127" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B127" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C127" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D127" s="1">
+        <v>114.91</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="3"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
+      <c r="A128" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B128" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D128" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="3"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
+      <c r="A129" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B129" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D129" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="3"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
+      <c r="A130" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="3"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
+      <c r="A131" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B131" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C131" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D131" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="3"/>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+      <c r="A132" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B132" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C132" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D132" s="1">
+        <v>118.0</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="3"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+      <c r="A133" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B133" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C133" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D133" s="1">
+        <v>129.99</v>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="3"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+      <c r="A134" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B134" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D134" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="3"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
+      <c r="A135" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B135" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D135" s="1">
+        <v>131.73</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="3"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
+      <c r="A136" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B136" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C136" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="3"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="A137" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B137" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C137" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D137" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="3"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
+      <c r="A138" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B138" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C138" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>129.74</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="3"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
+      <c r="A139" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B139" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C139" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D139" s="1">
+        <v>124.99</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="3"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
+      <c r="A140" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B140" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C140" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="3"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="A141" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B141" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C141" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="3"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
+      <c r="A142" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B142" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>99.08</v>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="3"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
+      <c r="A143" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B143" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>105.88</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="3"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
+      <c r="A144" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B144" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>109.64</v>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="3"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
+      <c r="A145" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D145" s="1">
+        <v>108.0</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="3"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
+      <c r="A146" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B146" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D146" s="1">
+        <v>73.17</v>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="3"/>
-      <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
+      <c r="A147" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B147" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C147" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D147" s="1">
+        <v>66.0</v>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="3"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
+      <c r="A148" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B148" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C148" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D148" s="1">
+        <v>65.33</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="3"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
+      <c r="A149" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B149" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C149" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D149" s="1">
+        <v>58.0</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="3"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
+      <c r="A150" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B150" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C150" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D150" s="1">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="3"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
+      <c r="A151" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B151" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C151" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D151" s="1">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="3"/>
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
+      <c r="A152" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B152" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C152" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D152" s="1">
+        <v>54.8</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="3"/>
-      <c r="B153" s="1"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
+      <c r="A153" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B153" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C153" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D153" s="1">
+        <v>67.0</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="3"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
+      <c r="A154" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B154" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C154" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D154" s="1">
+        <v>76.26</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="3"/>
-      <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
+      <c r="A155" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B155" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C155" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D155" s="1">
+        <v>77.0</v>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="3"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+      <c r="A156" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B156" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C156" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D156" s="1">
+        <v>84.5</v>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="3"/>
-      <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
+      <c r="A157" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B157" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C157" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D157" s="1">
+        <v>87.96</v>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="3"/>
-      <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
+      <c r="A158" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B158" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C158" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D158" s="1">
+        <v>95.18</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="3"/>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
+      <c r="A159" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B159" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C159" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D159" s="1">
+        <v>85.31</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="3"/>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="A160" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C160" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D160" s="1">
+        <v>101.24</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="3"/>
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="A161" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B161" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C161" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D161" s="1">
+        <v>94.5</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="3"/>
-      <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="A162" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B162" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C162" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D162" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="3"/>
-      <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="A163" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B163" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C163" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>114.49</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="3"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="A164" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B164" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C164" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D164" s="1">
+        <v>120.72</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="3"/>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="A165" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B165" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C165" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>129.74</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="3"/>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="A166" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B166" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C166" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D166" s="1">
+        <v>129.74</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="3"/>
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="A167" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B167" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C167" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D167" s="1">
+        <v>127.75</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="3"/>
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="A168" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B168" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C168" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>130.69</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="3"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="A169" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B169" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C169" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D169" s="1">
+        <v>132.22</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="3"/>
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="A170" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B170" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C170" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="3"/>
-      <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="A171" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B171" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C171" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D171" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="3"/>
-      <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="A172" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B172" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C172" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D172" s="1">
+        <v>132.65</v>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="3"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="A173" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B173" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C173" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>153.73</v>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="3"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="A174" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B174" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C174" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D174" s="1">
+        <v>134.3</v>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="3"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="A175" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C175" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D175" s="1">
+        <v>154.81</v>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="3"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="A176" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B176" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C176" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>154.81</v>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="3"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="A177" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B177" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C177" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D177" s="1">
+        <v>163.72</v>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="3"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="A178" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B178" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C178" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>154.29057</v>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="3"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
+      <c r="A179" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B179" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C179" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D179" s="1">
+        <v>156.28332</v>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="3"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+      <c r="A180" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B180" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C180" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D180" s="1">
+        <v>164.03</v>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="3"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="A181" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B181" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C181" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>174.03611</v>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="3"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="A182" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B182" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C182" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D182" s="1">
+        <v>164.75</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="3"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="A183" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B183" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C183" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>165.71</v>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="3"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="A184" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B184" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C184" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D184" s="1">
+        <v>163.72</v>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="3"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="A185" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B185" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C185" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D185" s="1">
+        <v>154.81</v>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="3"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="A186" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B186" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C186" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D186" s="1">
+        <v>154.81</v>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="3"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="A187" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B187" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C187" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D187" s="1">
+        <v>154.81</v>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="3"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="A188" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B188" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C188" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D188" s="1">
+        <v>154.7099</v>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="3"/>
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="A189" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B189" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C189" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D189" s="1">
+        <v>145.34461</v>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="3"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="A190" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C190" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D190" s="1">
+        <v>154.81</v>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="3"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="A191" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B191" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C191" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D191" s="1">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="3"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="A192" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B192" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C192" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D192" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="3"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="A193" s="3">
+        <v>46193.0</v>
+      </c>
+      <c r="B193" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C193" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D193" s="1">
+        <v>132.67048</v>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="3"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
+      <c r="A194" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B194" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C194" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D194" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="3"/>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
+      <c r="A195" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B195" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C195" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D195" s="1">
+        <v>138.92228</v>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="3"/>
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="A196" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B196" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C196" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D196" s="1">
+        <v>133.94371</v>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="3"/>
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="A197" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B197" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C197" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D197" s="1">
+        <v>131.94813</v>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="3"/>
-      <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
+      <c r="A198" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B198" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C198" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D198" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="3"/>
-      <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
+      <c r="A199" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B199" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C199" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D199" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="3"/>
-      <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
+      <c r="A200" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B200" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C200" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D200" s="1">
+        <v>130.0</v>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="3"/>
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="A201" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B201" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C201" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D201" s="1">
+        <v>128.5</v>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="3"/>
-      <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
+      <c r="A202" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B202" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C202" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D202" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="3"/>
-      <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
+      <c r="A203" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B203" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C203" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D203" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="3"/>
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
+      <c r="A204" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B204" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C204" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D204" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="3"/>
-      <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
+      <c r="A205" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B205" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C205" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D205" s="1">
+        <v>128.52</v>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="3"/>
-      <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="A206" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B206" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C206" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D206" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="3"/>
-      <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
+      <c r="A207" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B207" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C207" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D207" s="1">
+        <v>132.0</v>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="3"/>
-      <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+      <c r="A208" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B208" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C208" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D208" s="1">
+        <v>131.15</v>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="3"/>
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="A209" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B209" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C209" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D209" s="1">
+        <v>132.15</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="3"/>
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="A210" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B210" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C210" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D210" s="1">
+        <v>130.78</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="3"/>
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="A211" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B211" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C211" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D211" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="3"/>
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="A212" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B212" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C212" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D212" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="3"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="A213" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B213" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C213" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D213" s="1">
+        <v>128.12</v>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="3"/>
-      <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="A214" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B214" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C214" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D214" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="3"/>
-      <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="A215" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B215" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C215" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D215" s="1">
+        <v>124.4684</v>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="3"/>
-      <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="A216" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B216" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C216" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D216" s="1">
+        <v>124.11671</v>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="3"/>
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="A217" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B217" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C217" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D217" s="1">
+        <v>119.4205</v>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="3"/>
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="A218" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B218" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C218" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D218" s="1">
+        <v>124.91</v>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="3"/>
-      <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="A219" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B219" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C219" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D219" s="1">
+        <v>121.44</v>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="3"/>
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="A220" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B220" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C220" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D220" s="1">
+        <v>116.03</v>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="3"/>
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="A221" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B221" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C221" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D221" s="1">
+        <v>113.9</v>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="3"/>
-      <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="A222" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B222" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C222" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D222" s="1">
+        <v>113.72</v>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="3"/>
-      <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="A223" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B223" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C223" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D223" s="1">
+        <v>110.0</v>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="3"/>
-      <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
+      <c r="A224" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B224" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C224" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D224" s="1">
+        <v>105.47</v>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="3"/>
-      <c r="B225" s="1"/>
-      <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
+      <c r="A225" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B225" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C225" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D225" s="1">
+        <v>98.3</v>
+      </c>
     </row>
     <row r="226">
-      <c r="A226" s="3"/>
-      <c r="B226" s="1"/>
-      <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
+      <c r="A226" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B226" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C226" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D226" s="1">
+        <v>100.23</v>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="3"/>
-      <c r="B227" s="1"/>
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
+      <c r="A227" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B227" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C227" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D227" s="1">
+        <v>100.23</v>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="3"/>
-      <c r="B228" s="1"/>
-      <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
+      <c r="A228" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B228" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C228" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D228" s="1">
+        <v>100.72</v>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="3"/>
-      <c r="B229" s="1"/>
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
+      <c r="A229" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B229" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C229" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D229" s="1">
+        <v>100.23</v>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="3"/>
-      <c r="B230" s="1"/>
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+      <c r="A230" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B230" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C230" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D230" s="1">
+        <v>90.0</v>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="3"/>
-      <c r="B231" s="1"/>
-      <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
+      <c r="A231" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B231" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C231" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D231" s="1">
+        <v>90.0</v>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="3"/>
-      <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
+      <c r="A232" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B232" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C232" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D232" s="1">
+        <v>57.0</v>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="3"/>
-      <c r="B233" s="1"/>
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
+      <c r="A233" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B233" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C233" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D233" s="1">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="3"/>
-      <c r="B234" s="1"/>
-      <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
+      <c r="A234" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B234" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C234" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D234" s="1">
+        <v>12.44</v>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="3"/>
-      <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+      <c r="A235" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B235" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C235" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D235" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="3"/>
-      <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+      <c r="A236" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B236" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C236" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D236" s="1">
+        <v>2.84</v>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="3"/>
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
+      <c r="A237" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B237" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C237" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D237" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="3"/>
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
+      <c r="A238" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B238" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C238" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D238" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="3"/>
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
+      <c r="A239" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B239" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D239" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="3"/>
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
+      <c r="A240" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B240" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C240" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D240" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="3"/>
-      <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
-      <c r="D241" s="1"/>
+      <c r="A241" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B241" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C241" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D241" s="1">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="3"/>
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
+      <c r="A242" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B242" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C242" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D242" s="1">
+        <v>13.67</v>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="3"/>
-      <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
-      <c r="D243" s="1"/>
+      <c r="A243" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B243" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C243" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D243" s="1">
+        <v>12.44</v>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="3"/>
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
-      <c r="D244" s="1"/>
+      <c r="A244" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B244" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C244" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D244" s="1">
+        <v>16.0</v>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="3"/>
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
-      <c r="D245" s="1"/>
+      <c r="A245" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B245" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C245" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D245" s="1">
+        <v>12.44</v>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="3"/>
-      <c r="B246" s="1"/>
-      <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
+      <c r="A246" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B246" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C246" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D246" s="1">
+        <v>12.41</v>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="3"/>
-      <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
-      <c r="D247" s="1"/>
+      <c r="A247" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B247" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C247" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D247" s="1">
+        <v>12.41</v>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="3"/>
-      <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
+      <c r="A248" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B248" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C248" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D248" s="1">
+        <v>12.41</v>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="3"/>
-      <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
-      <c r="D249" s="1"/>
+      <c r="A249" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B249" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C249" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D249" s="1">
+        <v>12.41</v>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="3"/>
-      <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
+      <c r="A250" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B250" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C250" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D250" s="1">
+        <v>12.41</v>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="3"/>
-      <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
+      <c r="A251" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B251" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C251" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D251" s="1">
+        <v>12.44</v>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="3"/>
-      <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
+      <c r="A252" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B252" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C252" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D252" s="1">
+        <v>12.44</v>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="3"/>
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
+      <c r="A253" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B253" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C253" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D253" s="1">
+        <v>12.41</v>
+      </c>
     </row>
     <row r="254">
-      <c r="A254" s="3"/>
-      <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-      <c r="D254" s="1"/>
+      <c r="A254" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B254" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C254" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D254" s="1">
+        <v>12.44</v>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="3"/>
-      <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
+      <c r="A255" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B255" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C255" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D255" s="1">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="256">
-      <c r="A256" s="3"/>
-      <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
+      <c r="A256" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B256" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C256" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D256" s="1">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="257">
-      <c r="A257" s="3"/>
-      <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
-      <c r="D257" s="1"/>
+      <c r="A257" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B257" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C257" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D257" s="1">
+        <v>32.82</v>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="3"/>
-      <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
+      <c r="A258" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B258" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C258" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D258" s="1">
+        <v>76.03</v>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="3"/>
-      <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
+      <c r="A259" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B259" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C259" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D259" s="1">
+        <v>79.98</v>
+      </c>
     </row>
     <row r="260">
-      <c r="A260" s="3"/>
-      <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
-      <c r="D260" s="1"/>
+      <c r="A260" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B260" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C260" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D260" s="1">
+        <v>90.08</v>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="3"/>
-      <c r="B261" s="1"/>
-      <c r="C261" s="1"/>
-      <c r="D261" s="1"/>
+      <c r="A261" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B261" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C261" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D261" s="1">
+        <v>106.06</v>
+      </c>
     </row>
     <row r="262">
-      <c r="A262" s="3"/>
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
-      <c r="D262" s="1"/>
+      <c r="A262" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B262" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C262" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D262" s="1">
+        <v>110.0</v>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="3"/>
-      <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
-      <c r="D263" s="1"/>
+      <c r="A263" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B263" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C263" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D263" s="1">
+        <v>116.03</v>
+      </c>
     </row>
     <row r="264">
-      <c r="A264" s="3"/>
-      <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
-      <c r="D264" s="1"/>
+      <c r="A264" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B264" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C264" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D264" s="1">
+        <v>116.03</v>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="3"/>
-      <c r="B265" s="1"/>
-      <c r="C265" s="1"/>
-      <c r="D265" s="1"/>
+      <c r="A265" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B265" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C265" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D265" s="1">
+        <v>130.55</v>
+      </c>
     </row>
     <row r="266">
-      <c r="A266" s="3"/>
-      <c r="B266" s="1"/>
-      <c r="C266" s="1"/>
-      <c r="D266" s="1"/>
+      <c r="A266" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B266" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C266" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D266" s="1">
+        <v>129.07</v>
+      </c>
     </row>
     <row r="267">
-      <c r="A267" s="3"/>
-      <c r="B267" s="1"/>
-      <c r="C267" s="1"/>
-      <c r="D267" s="1"/>
+      <c r="A267" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B267" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C267" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D267" s="1">
+        <v>126.41</v>
+      </c>
     </row>
     <row r="268">
-      <c r="A268" s="3"/>
-      <c r="B268" s="1"/>
-      <c r="C268" s="1"/>
-      <c r="D268" s="1"/>
+      <c r="A268" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B268" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C268" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D268" s="1">
+        <v>131.48</v>
+      </c>
     </row>
     <row r="269">
-      <c r="A269" s="3"/>
-      <c r="B269" s="1"/>
-      <c r="C269" s="1"/>
-      <c r="D269" s="1"/>
+      <c r="A269" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B269" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C269" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D269" s="1">
+        <v>133.44</v>
+      </c>
     </row>
     <row r="270">
-      <c r="A270" s="3"/>
-      <c r="B270" s="1"/>
-      <c r="C270" s="1"/>
-      <c r="D270" s="1"/>
+      <c r="A270" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B270" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C270" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D270" s="1">
+        <v>132.65</v>
+      </c>
     </row>
     <row r="271">
-      <c r="A271" s="3"/>
-      <c r="B271" s="1"/>
-      <c r="C271" s="1"/>
-      <c r="D271" s="1"/>
+      <c r="A271" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B271" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C271" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D271" s="1">
+        <v>135.89</v>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="3"/>
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
+      <c r="A272" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B272" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C272" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D272" s="1">
+        <v>139.48794</v>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="3"/>
-      <c r="B273" s="1"/>
-      <c r="C273" s="1"/>
-      <c r="D273" s="1"/>
+      <c r="A273" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B273" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C273" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D273" s="1">
+        <v>146.21</v>
+      </c>
     </row>
     <row r="274">
-      <c r="A274" s="3"/>
-      <c r="B274" s="1"/>
-      <c r="C274" s="1"/>
-      <c r="D274" s="1"/>
+      <c r="A274" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B274" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C274" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D274" s="1">
+        <v>144.35</v>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="3"/>
-      <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
+      <c r="A275" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B275" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C275" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D275" s="1">
+        <v>151.06261</v>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="3"/>
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
+      <c r="A276" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B276" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C276" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D276" s="1">
+        <v>157.14236</v>
+      </c>
     </row>
     <row r="277">
-      <c r="A277" s="3"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
+      <c r="A277" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B277" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C277" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D277" s="1">
+        <v>159.60668</v>
+      </c>
     </row>
     <row r="278">
-      <c r="A278" s="3"/>
-      <c r="B278" s="1"/>
-      <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
+      <c r="A278" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B278" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C278" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D278" s="1">
+        <v>156.75</v>
+      </c>
     </row>
     <row r="279">
-      <c r="A279" s="3"/>
-      <c r="B279" s="1"/>
-      <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
+      <c r="A279" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B279" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C279" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D279" s="1">
+        <v>154.33814</v>
+      </c>
     </row>
     <row r="280">
-      <c r="A280" s="3"/>
-      <c r="B280" s="1"/>
-      <c r="C280" s="1"/>
-      <c r="D280" s="1"/>
+      <c r="A280" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B280" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C280" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D280" s="1">
+        <v>151.16</v>
+      </c>
     </row>
     <row r="281">
-      <c r="A281" s="3"/>
-      <c r="B281" s="1"/>
-      <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
+      <c r="A281" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B281" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C281" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D281" s="1">
+        <v>146.33419</v>
+      </c>
     </row>
     <row r="282">
-      <c r="A282" s="3"/>
-      <c r="B282" s="1"/>
-      <c r="C282" s="1"/>
-      <c r="D282" s="1"/>
+      <c r="A282" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B282" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C282" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D282" s="1">
+        <v>153.65041</v>
+      </c>
     </row>
     <row r="283">
-      <c r="A283" s="3"/>
-      <c r="B283" s="1"/>
-      <c r="C283" s="1"/>
-      <c r="D283" s="1"/>
+      <c r="A283" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B283" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C283" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D283" s="1">
+        <v>150.53736</v>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="3"/>
-      <c r="B284" s="1"/>
-      <c r="C284" s="1"/>
-      <c r="D284" s="1"/>
+      <c r="A284" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B284" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C284" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D284" s="1">
+        <v>145.94253</v>
+      </c>
     </row>
     <row r="285">
-      <c r="A285" s="3"/>
-      <c r="B285" s="1"/>
-      <c r="C285" s="1"/>
-      <c r="D285" s="1"/>
+      <c r="A285" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B285" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C285" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D285" s="1">
+        <v>139.14478</v>
+      </c>
     </row>
     <row r="286">
-      <c r="A286" s="3"/>
-      <c r="B286" s="1"/>
-      <c r="C286" s="1"/>
-      <c r="D286" s="1"/>
+      <c r="A286" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B286" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C286" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D286" s="1">
+        <v>146.29057</v>
+      </c>
     </row>
     <row r="287">
-      <c r="A287" s="3"/>
-      <c r="B287" s="1"/>
-      <c r="C287" s="1"/>
-      <c r="D287" s="1"/>
+      <c r="A287" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B287" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C287" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D287" s="1">
+        <v>136.89679</v>
+      </c>
     </row>
     <row r="288">
-      <c r="A288" s="3"/>
-      <c r="B288" s="1"/>
-      <c r="C288" s="1"/>
-      <c r="D288" s="1"/>
+      <c r="A288" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B288" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C288" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D288" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="289">
-      <c r="A289" s="3"/>
-      <c r="B289" s="1"/>
-      <c r="C289" s="1"/>
-      <c r="D289" s="1"/>
+      <c r="A289" s="3">
+        <v>46194.0</v>
+      </c>
+      <c r="B289" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C289" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D289" s="1">
+        <v>132.15</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>145.13452</v>
+        <v>154.13095</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>143.78</v>
+        <v>148.65412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>143.78</v>
+        <v>144.03314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>132.26056</v>
+        <v>139.32589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>143.78</v>
+        <v>144.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>139.0</v>
+        <v>140.26501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>125.85</v>
+        <v>138.81774</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>131.37</v>
+        <v>137.07811</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>143.78</v>
+        <v>137.3916</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>140.0</v>
+        <v>136.07408</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>139.37</v>
+        <v>134.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>132.26</v>
+        <v>135.51076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>130.0</v>
+        <v>133.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>134.24</v>
+        <v>137.83</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>130.0</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>128.25</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>134.12</v>
+        <v>136.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>132.0</v>
+        <v>135.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>126.96</v>
+        <v>133.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>127.32</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>134.31</v>
+        <v>136.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>130.5</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>126.59</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>129.0</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>133.02</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>143.78</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>143.78</v>
+        <v>140.43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>143.78</v>
+        <v>143.51</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>143.78</v>
+        <v>142.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>143.78</v>
+        <v>149.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>143.78</v>
+        <v>147.37994</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>143.78</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>143.78</v>
+        <v>150.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>139.0</v>
+        <v>135.7134</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>130.5</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>120.3</v>
+        <v>120.35276</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>138.18</v>
+        <v>131.3179</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>140.0</v>
+        <v>124.24518</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>132.26</v>
+        <v>119.89936</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>120.3</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>142.7064</v>
+        <v>120.43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>133.02766</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>120.57885</v>
+        <v>115.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>118.83465</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>118.44122</v>
+        <v>116.27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>118.41387</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>118.37978</v>
+        <v>117.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>118.37243</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>113.94975</v>
+        <v>126.71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>111.65314</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>101.0428</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>104.02</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>108.08</v>
+        <v>123.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>105.54941</v>
+        <v>125.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>106.21342</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>110.94016</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>112.61885</v>
+        <v>132.45</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>113.63996</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>113.78756</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>113.74743</v>
+        <v>131.27</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>114.50408</v>
+        <v>124.63</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>118.02852</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>121.40887</v>
+        <v>133.53</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>128.23871</v>
+        <v>134.53</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>123.01509</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>137.5554</v>
+        <v>132.53</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>141.36752</v>
+        <v>132.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>141.58457</v>
+        <v>136.60747</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>142.8712</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>149.1858</v>
+        <v>131.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>153.41</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>153.44</v>
+        <v>148.07385</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>153.41</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>153.44</v>
+        <v>147.23239</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>164.0</v>
+        <v>178.52085</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>169.74</v>
+        <v>231.48038</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>153.44</v>
+        <v>180.96575</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>165.00404</v>
+        <v>240.79495</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>178.04</v>
+        <v>249.30394</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>191.46</v>
+        <v>272.62526</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>175.22</v>
+        <v>263.2816</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>178.72</v>
+        <v>264.5514</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>186.03</v>
+        <v>272.92339</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>180.03</v>
+        <v>256.2005</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>186.03</v>
+        <v>271.07688</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>178.72</v>
+        <v>247.02522</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>175.22</v>
+        <v>209.93</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>164.0</v>
+        <v>183.52</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>176.99</v>
+        <v>247.44546</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>173.78</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>167.44</v>
+        <v>224.74993</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>154.51</v>
+        <v>183.46</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>168.85</v>
+        <v>209.33</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>154.51</v>
+        <v>171.69</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>150.98</v>
+        <v>169.33</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46191.0</v>
+        <v>46196.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>143.78</v>
+        <v>152.21</v>
       </c>
     </row>
     <row r="98">
@@ -2804,6 +2804,3462 @@
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
     </row>
+    <row r="290">
+      <c r="A290" s="3"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3"/>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3"/>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3"/>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3"/>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3"/>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3"/>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3"/>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3"/>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3"/>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3"/>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3"/>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="3"/>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="3"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="3"/>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="3"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="3"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="3"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="3"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="3"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="3"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3"/>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="3"/>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3"/>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="3"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3"/>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="3"/>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="3"/>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="3"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="3"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="3"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="3"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="3"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="3"/>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="3"/>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="3"/>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="3"/>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="3"/>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="3"/>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="3"/>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="3"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="3"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="3"/>
+      <c r="B356" s="1"/>
+      <c r="C356" s="1"/>
+      <c r="D356" s="1"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="3"/>
+      <c r="B357" s="1"/>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="3"/>
+      <c r="B358" s="1"/>
+      <c r="C358" s="1"/>
+      <c r="D358" s="1"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="3"/>
+      <c r="B359" s="1"/>
+      <c r="C359" s="1"/>
+      <c r="D359" s="1"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="3"/>
+      <c r="B360" s="1"/>
+      <c r="C360" s="1"/>
+      <c r="D360" s="1"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="3"/>
+      <c r="B361" s="1"/>
+      <c r="C361" s="1"/>
+      <c r="D361" s="1"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="3"/>
+      <c r="B362" s="1"/>
+      <c r="C362" s="1"/>
+      <c r="D362" s="1"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="3"/>
+      <c r="B363" s="1"/>
+      <c r="C363" s="1"/>
+      <c r="D363" s="1"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="3"/>
+      <c r="B364" s="1"/>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="3"/>
+      <c r="B365" s="1"/>
+      <c r="C365" s="1"/>
+      <c r="D365" s="1"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="3"/>
+      <c r="B366" s="1"/>
+      <c r="C366" s="1"/>
+      <c r="D366" s="1"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="3"/>
+      <c r="B367" s="1"/>
+      <c r="C367" s="1"/>
+      <c r="D367" s="1"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="3"/>
+      <c r="B368" s="1"/>
+      <c r="C368" s="1"/>
+      <c r="D368" s="1"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="3"/>
+      <c r="B369" s="1"/>
+      <c r="C369" s="1"/>
+      <c r="D369" s="1"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="3"/>
+      <c r="B370" s="1"/>
+      <c r="C370" s="1"/>
+      <c r="D370" s="1"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="3"/>
+      <c r="B371" s="1"/>
+      <c r="C371" s="1"/>
+      <c r="D371" s="1"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="3"/>
+      <c r="B372" s="1"/>
+      <c r="C372" s="1"/>
+      <c r="D372" s="1"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="3"/>
+      <c r="B373" s="1"/>
+      <c r="C373" s="1"/>
+      <c r="D373" s="1"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="3"/>
+      <c r="B374" s="1"/>
+      <c r="C374" s="1"/>
+      <c r="D374" s="1"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="3"/>
+      <c r="B375" s="1"/>
+      <c r="C375" s="1"/>
+      <c r="D375" s="1"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="3"/>
+      <c r="B376" s="1"/>
+      <c r="C376" s="1"/>
+      <c r="D376" s="1"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="3"/>
+      <c r="B377" s="1"/>
+      <c r="C377" s="1"/>
+      <c r="D377" s="1"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="3"/>
+      <c r="B378" s="1"/>
+      <c r="C378" s="1"/>
+      <c r="D378" s="1"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="3"/>
+      <c r="B379" s="1"/>
+      <c r="C379" s="1"/>
+      <c r="D379" s="1"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="3"/>
+      <c r="B380" s="1"/>
+      <c r="C380" s="1"/>
+      <c r="D380" s="1"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="3"/>
+      <c r="B381" s="1"/>
+      <c r="C381" s="1"/>
+      <c r="D381" s="1"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="3"/>
+      <c r="B382" s="1"/>
+      <c r="C382" s="1"/>
+      <c r="D382" s="1"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="3"/>
+      <c r="B383" s="1"/>
+      <c r="C383" s="1"/>
+      <c r="D383" s="1"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="3"/>
+      <c r="B384" s="1"/>
+      <c r="C384" s="1"/>
+      <c r="D384" s="1"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="3"/>
+      <c r="B385" s="1"/>
+      <c r="C385" s="1"/>
+      <c r="D385" s="1"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="3"/>
+      <c r="B386" s="1"/>
+      <c r="C386" s="1"/>
+      <c r="D386" s="1"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="3"/>
+      <c r="B387" s="1"/>
+      <c r="C387" s="1"/>
+      <c r="D387" s="1"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="3"/>
+      <c r="B388" s="1"/>
+      <c r="C388" s="1"/>
+      <c r="D388" s="1"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="3"/>
+      <c r="B389" s="1"/>
+      <c r="C389" s="1"/>
+      <c r="D389" s="1"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="3"/>
+      <c r="B390" s="1"/>
+      <c r="C390" s="1"/>
+      <c r="D390" s="1"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="3"/>
+      <c r="B391" s="1"/>
+      <c r="C391" s="1"/>
+      <c r="D391" s="1"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="3"/>
+      <c r="B392" s="1"/>
+      <c r="C392" s="1"/>
+      <c r="D392" s="1"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="3"/>
+      <c r="B393" s="1"/>
+      <c r="C393" s="1"/>
+      <c r="D393" s="1"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="3"/>
+      <c r="B394" s="1"/>
+      <c r="C394" s="1"/>
+      <c r="D394" s="1"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="3"/>
+      <c r="B395" s="1"/>
+      <c r="C395" s="1"/>
+      <c r="D395" s="1"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="3"/>
+      <c r="B396" s="1"/>
+      <c r="C396" s="1"/>
+      <c r="D396" s="1"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="3"/>
+      <c r="B397" s="1"/>
+      <c r="C397" s="1"/>
+      <c r="D397" s="1"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="3"/>
+      <c r="B398" s="1"/>
+      <c r="C398" s="1"/>
+      <c r="D398" s="1"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="3"/>
+      <c r="B399" s="1"/>
+      <c r="C399" s="1"/>
+      <c r="D399" s="1"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="3"/>
+      <c r="B400" s="1"/>
+      <c r="C400" s="1"/>
+      <c r="D400" s="1"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="3"/>
+      <c r="B401" s="1"/>
+      <c r="C401" s="1"/>
+      <c r="D401" s="1"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="3"/>
+      <c r="B402" s="1"/>
+      <c r="C402" s="1"/>
+      <c r="D402" s="1"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="3"/>
+      <c r="B403" s="1"/>
+      <c r="C403" s="1"/>
+      <c r="D403" s="1"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="3"/>
+      <c r="B404" s="1"/>
+      <c r="C404" s="1"/>
+      <c r="D404" s="1"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="3"/>
+      <c r="B405" s="1"/>
+      <c r="C405" s="1"/>
+      <c r="D405" s="1"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="3"/>
+      <c r="B406" s="1"/>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="3"/>
+      <c r="B407" s="1"/>
+      <c r="C407" s="1"/>
+      <c r="D407" s="1"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="3"/>
+      <c r="B408" s="1"/>
+      <c r="C408" s="1"/>
+      <c r="D408" s="1"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="3"/>
+      <c r="B409" s="1"/>
+      <c r="C409" s="1"/>
+      <c r="D409" s="1"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="3"/>
+      <c r="B410" s="1"/>
+      <c r="C410" s="1"/>
+      <c r="D410" s="1"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="3"/>
+      <c r="B411" s="1"/>
+      <c r="C411" s="1"/>
+      <c r="D411" s="1"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="3"/>
+      <c r="B412" s="1"/>
+      <c r="C412" s="1"/>
+      <c r="D412" s="1"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="3"/>
+      <c r="B413" s="1"/>
+      <c r="C413" s="1"/>
+      <c r="D413" s="1"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="3"/>
+      <c r="B414" s="1"/>
+      <c r="C414" s="1"/>
+      <c r="D414" s="1"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="3"/>
+      <c r="B415" s="1"/>
+      <c r="C415" s="1"/>
+      <c r="D415" s="1"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="3"/>
+      <c r="B416" s="1"/>
+      <c r="C416" s="1"/>
+      <c r="D416" s="1"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="3"/>
+      <c r="B417" s="1"/>
+      <c r="C417" s="1"/>
+      <c r="D417" s="1"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="3"/>
+      <c r="B418" s="1"/>
+      <c r="C418" s="1"/>
+      <c r="D418" s="1"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="3"/>
+      <c r="B419" s="1"/>
+      <c r="C419" s="1"/>
+      <c r="D419" s="1"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="3"/>
+      <c r="B420" s="1"/>
+      <c r="C420" s="1"/>
+      <c r="D420" s="1"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="3"/>
+      <c r="B421" s="1"/>
+      <c r="C421" s="1"/>
+      <c r="D421" s="1"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="3"/>
+      <c r="B422" s="1"/>
+      <c r="C422" s="1"/>
+      <c r="D422" s="1"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="3"/>
+      <c r="B423" s="1"/>
+      <c r="C423" s="1"/>
+      <c r="D423" s="1"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="3"/>
+      <c r="B424" s="1"/>
+      <c r="C424" s="1"/>
+      <c r="D424" s="1"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="3"/>
+      <c r="B425" s="1"/>
+      <c r="C425" s="1"/>
+      <c r="D425" s="1"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="3"/>
+      <c r="B426" s="1"/>
+      <c r="C426" s="1"/>
+      <c r="D426" s="1"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="3"/>
+      <c r="B427" s="1"/>
+      <c r="C427" s="1"/>
+      <c r="D427" s="1"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="3"/>
+      <c r="B428" s="1"/>
+      <c r="C428" s="1"/>
+      <c r="D428" s="1"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="3"/>
+      <c r="B429" s="1"/>
+      <c r="C429" s="1"/>
+      <c r="D429" s="1"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="3"/>
+      <c r="B430" s="1"/>
+      <c r="C430" s="1"/>
+      <c r="D430" s="1"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="3"/>
+      <c r="B431" s="1"/>
+      <c r="C431" s="1"/>
+      <c r="D431" s="1"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="3"/>
+      <c r="B432" s="1"/>
+      <c r="C432" s="1"/>
+      <c r="D432" s="1"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="3"/>
+      <c r="B433" s="1"/>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="3"/>
+      <c r="B434" s="1"/>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="3"/>
+      <c r="B435" s="1"/>
+      <c r="C435" s="1"/>
+      <c r="D435" s="1"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="3"/>
+      <c r="B436" s="1"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="3"/>
+      <c r="B437" s="1"/>
+      <c r="C437" s="1"/>
+      <c r="D437" s="1"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="3"/>
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="3"/>
+      <c r="B439" s="1"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="3"/>
+      <c r="B440" s="1"/>
+      <c r="C440" s="1"/>
+      <c r="D440" s="1"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="3"/>
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
+      <c r="D441" s="1"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="3"/>
+      <c r="B442" s="1"/>
+      <c r="C442" s="1"/>
+      <c r="D442" s="1"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="3"/>
+      <c r="B443" s="1"/>
+      <c r="C443" s="1"/>
+      <c r="D443" s="1"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="3"/>
+      <c r="B444" s="1"/>
+      <c r="C444" s="1"/>
+      <c r="D444" s="1"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="3"/>
+      <c r="B445" s="1"/>
+      <c r="C445" s="1"/>
+      <c r="D445" s="1"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="3"/>
+      <c r="B446" s="1"/>
+      <c r="C446" s="1"/>
+      <c r="D446" s="1"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="3"/>
+      <c r="B447" s="1"/>
+      <c r="C447" s="1"/>
+      <c r="D447" s="1"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="3"/>
+      <c r="B448" s="1"/>
+      <c r="C448" s="1"/>
+      <c r="D448" s="1"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="3"/>
+      <c r="B449" s="1"/>
+      <c r="C449" s="1"/>
+      <c r="D449" s="1"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="3"/>
+      <c r="B450" s="1"/>
+      <c r="C450" s="1"/>
+      <c r="D450" s="1"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="3"/>
+      <c r="B451" s="1"/>
+      <c r="C451" s="1"/>
+      <c r="D451" s="1"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="3"/>
+      <c r="B452" s="1"/>
+      <c r="C452" s="1"/>
+      <c r="D452" s="1"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="3"/>
+      <c r="B453" s="1"/>
+      <c r="C453" s="1"/>
+      <c r="D453" s="1"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="3"/>
+      <c r="B454" s="1"/>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="3"/>
+      <c r="B455" s="1"/>
+      <c r="C455" s="1"/>
+      <c r="D455" s="1"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="3"/>
+      <c r="B456" s="1"/>
+      <c r="C456" s="1"/>
+      <c r="D456" s="1"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="3"/>
+      <c r="B457" s="1"/>
+      <c r="C457" s="1"/>
+      <c r="D457" s="1"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="3"/>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
+      <c r="D458" s="1"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="3"/>
+      <c r="B459" s="1"/>
+      <c r="C459" s="1"/>
+      <c r="D459" s="1"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="3"/>
+      <c r="B460" s="1"/>
+      <c r="C460" s="1"/>
+      <c r="D460" s="1"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="3"/>
+      <c r="B461" s="1"/>
+      <c r="C461" s="1"/>
+      <c r="D461" s="1"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="3"/>
+      <c r="B462" s="1"/>
+      <c r="C462" s="1"/>
+      <c r="D462" s="1"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="3"/>
+      <c r="B463" s="1"/>
+      <c r="C463" s="1"/>
+      <c r="D463" s="1"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="3"/>
+      <c r="B464" s="1"/>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="3"/>
+      <c r="B465" s="1"/>
+      <c r="C465" s="1"/>
+      <c r="D465" s="1"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="3"/>
+      <c r="B466" s="1"/>
+      <c r="C466" s="1"/>
+      <c r="D466" s="1"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="3"/>
+      <c r="B467" s="1"/>
+      <c r="C467" s="1"/>
+      <c r="D467" s="1"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="3"/>
+      <c r="B468" s="1"/>
+      <c r="C468" s="1"/>
+      <c r="D468" s="1"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="3"/>
+      <c r="B469" s="1"/>
+      <c r="C469" s="1"/>
+      <c r="D469" s="1"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="3"/>
+      <c r="B470" s="1"/>
+      <c r="C470" s="1"/>
+      <c r="D470" s="1"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="3"/>
+      <c r="B471" s="1"/>
+      <c r="C471" s="1"/>
+      <c r="D471" s="1"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="3"/>
+      <c r="B472" s="1"/>
+      <c r="C472" s="1"/>
+      <c r="D472" s="1"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="3"/>
+      <c r="B473" s="1"/>
+      <c r="C473" s="1"/>
+      <c r="D473" s="1"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="3"/>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
+      <c r="D474" s="1"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="3"/>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
+      <c r="D475" s="1"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="3"/>
+      <c r="B476" s="1"/>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="3"/>
+      <c r="B477" s="1"/>
+      <c r="C477" s="1"/>
+      <c r="D477" s="1"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="3"/>
+      <c r="B478" s="1"/>
+      <c r="C478" s="1"/>
+      <c r="D478" s="1"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="3"/>
+      <c r="B479" s="1"/>
+      <c r="C479" s="1"/>
+      <c r="D479" s="1"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="3"/>
+      <c r="B480" s="1"/>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="3"/>
+      <c r="B481" s="1"/>
+      <c r="C481" s="1"/>
+      <c r="D481" s="1"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="3"/>
+      <c r="B482" s="1"/>
+      <c r="C482" s="1"/>
+      <c r="D482" s="1"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="3"/>
+      <c r="B483" s="1"/>
+      <c r="C483" s="1"/>
+      <c r="D483" s="1"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="3"/>
+      <c r="B484" s="1"/>
+      <c r="C484" s="1"/>
+      <c r="D484" s="1"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="3"/>
+      <c r="B485" s="1"/>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="3"/>
+      <c r="B486" s="1"/>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="3"/>
+      <c r="B487" s="1"/>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="3"/>
+      <c r="B488" s="1"/>
+      <c r="C488" s="1"/>
+      <c r="D488" s="1"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="3"/>
+      <c r="B489" s="1"/>
+      <c r="C489" s="1"/>
+      <c r="D489" s="1"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="3"/>
+      <c r="B490" s="1"/>
+      <c r="C490" s="1"/>
+      <c r="D490" s="1"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="3"/>
+      <c r="B491" s="1"/>
+      <c r="C491" s="1"/>
+      <c r="D491" s="1"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="3"/>
+      <c r="B492" s="1"/>
+      <c r="C492" s="1"/>
+      <c r="D492" s="1"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="3"/>
+      <c r="B493" s="1"/>
+      <c r="C493" s="1"/>
+      <c r="D493" s="1"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="3"/>
+      <c r="B494" s="1"/>
+      <c r="C494" s="1"/>
+      <c r="D494" s="1"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="3"/>
+      <c r="B495" s="1"/>
+      <c r="C495" s="1"/>
+      <c r="D495" s="1"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="3"/>
+      <c r="B496" s="1"/>
+      <c r="C496" s="1"/>
+      <c r="D496" s="1"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="3"/>
+      <c r="B497" s="1"/>
+      <c r="C497" s="1"/>
+      <c r="D497" s="1"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="3"/>
+      <c r="B498" s="1"/>
+      <c r="C498" s="1"/>
+      <c r="D498" s="1"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="3"/>
+      <c r="B499" s="1"/>
+      <c r="C499" s="1"/>
+      <c r="D499" s="1"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="3"/>
+      <c r="B500" s="1"/>
+      <c r="C500" s="1"/>
+      <c r="D500" s="1"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="3"/>
+      <c r="B501" s="1"/>
+      <c r="C501" s="1"/>
+      <c r="D501" s="1"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="3"/>
+      <c r="B502" s="1"/>
+      <c r="C502" s="1"/>
+      <c r="D502" s="1"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="3"/>
+      <c r="B503" s="1"/>
+      <c r="C503" s="1"/>
+      <c r="D503" s="1"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="3"/>
+      <c r="B504" s="1"/>
+      <c r="C504" s="1"/>
+      <c r="D504" s="1"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="3"/>
+      <c r="B505" s="1"/>
+      <c r="C505" s="1"/>
+      <c r="D505" s="1"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="3"/>
+      <c r="B506" s="1"/>
+      <c r="C506" s="1"/>
+      <c r="D506" s="1"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="3"/>
+      <c r="B507" s="1"/>
+      <c r="C507" s="1"/>
+      <c r="D507" s="1"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="3"/>
+      <c r="B508" s="1"/>
+      <c r="C508" s="1"/>
+      <c r="D508" s="1"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="3"/>
+      <c r="B509" s="1"/>
+      <c r="C509" s="1"/>
+      <c r="D509" s="1"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="3"/>
+      <c r="B510" s="1"/>
+      <c r="C510" s="1"/>
+      <c r="D510" s="1"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="3"/>
+      <c r="B511" s="1"/>
+      <c r="C511" s="1"/>
+      <c r="D511" s="1"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="3"/>
+      <c r="B512" s="1"/>
+      <c r="C512" s="1"/>
+      <c r="D512" s="1"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="3"/>
+      <c r="B513" s="1"/>
+      <c r="C513" s="1"/>
+      <c r="D513" s="1"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="3"/>
+      <c r="B514" s="1"/>
+      <c r="C514" s="1"/>
+      <c r="D514" s="1"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="3"/>
+      <c r="B515" s="1"/>
+      <c r="C515" s="1"/>
+      <c r="D515" s="1"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="3"/>
+      <c r="B516" s="1"/>
+      <c r="C516" s="1"/>
+      <c r="D516" s="1"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="3"/>
+      <c r="B517" s="1"/>
+      <c r="C517" s="1"/>
+      <c r="D517" s="1"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="3"/>
+      <c r="B518" s="1"/>
+      <c r="C518" s="1"/>
+      <c r="D518" s="1"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="3"/>
+      <c r="B519" s="1"/>
+      <c r="C519" s="1"/>
+      <c r="D519" s="1"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="3"/>
+      <c r="B520" s="1"/>
+      <c r="C520" s="1"/>
+      <c r="D520" s="1"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="3"/>
+      <c r="B521" s="1"/>
+      <c r="C521" s="1"/>
+      <c r="D521" s="1"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="3"/>
+      <c r="B522" s="1"/>
+      <c r="C522" s="1"/>
+      <c r="D522" s="1"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="3"/>
+      <c r="B523" s="1"/>
+      <c r="C523" s="1"/>
+      <c r="D523" s="1"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="3"/>
+      <c r="B524" s="1"/>
+      <c r="C524" s="1"/>
+      <c r="D524" s="1"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="3"/>
+      <c r="B525" s="1"/>
+      <c r="C525" s="1"/>
+      <c r="D525" s="1"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="3"/>
+      <c r="B526" s="1"/>
+      <c r="C526" s="1"/>
+      <c r="D526" s="1"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="3"/>
+      <c r="B527" s="1"/>
+      <c r="C527" s="1"/>
+      <c r="D527" s="1"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="3"/>
+      <c r="B528" s="1"/>
+      <c r="C528" s="1"/>
+      <c r="D528" s="1"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="3"/>
+      <c r="B529" s="1"/>
+      <c r="C529" s="1"/>
+      <c r="D529" s="1"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="3"/>
+      <c r="B530" s="1"/>
+      <c r="C530" s="1"/>
+      <c r="D530" s="1"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="3"/>
+      <c r="B531" s="1"/>
+      <c r="C531" s="1"/>
+      <c r="D531" s="1"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="3"/>
+      <c r="B532" s="1"/>
+      <c r="C532" s="1"/>
+      <c r="D532" s="1"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="3"/>
+      <c r="B533" s="1"/>
+      <c r="C533" s="1"/>
+      <c r="D533" s="1"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="3"/>
+      <c r="B534" s="1"/>
+      <c r="C534" s="1"/>
+      <c r="D534" s="1"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="3"/>
+      <c r="B535" s="1"/>
+      <c r="C535" s="1"/>
+      <c r="D535" s="1"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="3"/>
+      <c r="B536" s="1"/>
+      <c r="C536" s="1"/>
+      <c r="D536" s="1"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="3"/>
+      <c r="B537" s="1"/>
+      <c r="C537" s="1"/>
+      <c r="D537" s="1"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="3"/>
+      <c r="B538" s="1"/>
+      <c r="C538" s="1"/>
+      <c r="D538" s="1"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="3"/>
+      <c r="B539" s="1"/>
+      <c r="C539" s="1"/>
+      <c r="D539" s="1"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="3"/>
+      <c r="B540" s="1"/>
+      <c r="C540" s="1"/>
+      <c r="D540" s="1"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="3"/>
+      <c r="B541" s="1"/>
+      <c r="C541" s="1"/>
+      <c r="D541" s="1"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="3"/>
+      <c r="B542" s="1"/>
+      <c r="C542" s="1"/>
+      <c r="D542" s="1"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="3"/>
+      <c r="B543" s="1"/>
+      <c r="C543" s="1"/>
+      <c r="D543" s="1"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="3"/>
+      <c r="B544" s="1"/>
+      <c r="C544" s="1"/>
+      <c r="D544" s="1"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="3"/>
+      <c r="B545" s="1"/>
+      <c r="C545" s="1"/>
+      <c r="D545" s="1"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="3"/>
+      <c r="B546" s="1"/>
+      <c r="C546" s="1"/>
+      <c r="D546" s="1"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="3"/>
+      <c r="B547" s="1"/>
+      <c r="C547" s="1"/>
+      <c r="D547" s="1"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="3"/>
+      <c r="B548" s="1"/>
+      <c r="C548" s="1"/>
+      <c r="D548" s="1"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="3"/>
+      <c r="B549" s="1"/>
+      <c r="C549" s="1"/>
+      <c r="D549" s="1"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="3"/>
+      <c r="B550" s="1"/>
+      <c r="C550" s="1"/>
+      <c r="D550" s="1"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="3"/>
+      <c r="B551" s="1"/>
+      <c r="C551" s="1"/>
+      <c r="D551" s="1"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="3"/>
+      <c r="B552" s="1"/>
+      <c r="C552" s="1"/>
+      <c r="D552" s="1"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="3"/>
+      <c r="B553" s="1"/>
+      <c r="C553" s="1"/>
+      <c r="D553" s="1"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="3"/>
+      <c r="B554" s="1"/>
+      <c r="C554" s="1"/>
+      <c r="D554" s="1"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="3"/>
+      <c r="B555" s="1"/>
+      <c r="C555" s="1"/>
+      <c r="D555" s="1"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="3"/>
+      <c r="B556" s="1"/>
+      <c r="C556" s="1"/>
+      <c r="D556" s="1"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="3"/>
+      <c r="B557" s="1"/>
+      <c r="C557" s="1"/>
+      <c r="D557" s="1"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="3"/>
+      <c r="B558" s="1"/>
+      <c r="C558" s="1"/>
+      <c r="D558" s="1"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="3"/>
+      <c r="B559" s="1"/>
+      <c r="C559" s="1"/>
+      <c r="D559" s="1"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="3"/>
+      <c r="B560" s="1"/>
+      <c r="C560" s="1"/>
+      <c r="D560" s="1"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="3"/>
+      <c r="B561" s="1"/>
+      <c r="C561" s="1"/>
+      <c r="D561" s="1"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="3"/>
+      <c r="B562" s="1"/>
+      <c r="C562" s="1"/>
+      <c r="D562" s="1"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="3"/>
+      <c r="B563" s="1"/>
+      <c r="C563" s="1"/>
+      <c r="D563" s="1"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="3"/>
+      <c r="B564" s="1"/>
+      <c r="C564" s="1"/>
+      <c r="D564" s="1"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="3"/>
+      <c r="B565" s="1"/>
+      <c r="C565" s="1"/>
+      <c r="D565" s="1"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="3"/>
+      <c r="B566" s="1"/>
+      <c r="C566" s="1"/>
+      <c r="D566" s="1"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="3"/>
+      <c r="B567" s="1"/>
+      <c r="C567" s="1"/>
+      <c r="D567" s="1"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="3"/>
+      <c r="B568" s="1"/>
+      <c r="C568" s="1"/>
+      <c r="D568" s="1"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="3"/>
+      <c r="B569" s="1"/>
+      <c r="C569" s="1"/>
+      <c r="D569" s="1"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="3"/>
+      <c r="B570" s="1"/>
+      <c r="C570" s="1"/>
+      <c r="D570" s="1"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="3"/>
+      <c r="B571" s="1"/>
+      <c r="C571" s="1"/>
+      <c r="D571" s="1"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="3"/>
+      <c r="B572" s="1"/>
+      <c r="C572" s="1"/>
+      <c r="D572" s="1"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="3"/>
+      <c r="B573" s="1"/>
+      <c r="C573" s="1"/>
+      <c r="D573" s="1"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="3"/>
+      <c r="B574" s="1"/>
+      <c r="C574" s="1"/>
+      <c r="D574" s="1"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="3"/>
+      <c r="B575" s="1"/>
+      <c r="C575" s="1"/>
+      <c r="D575" s="1"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="3"/>
+      <c r="B576" s="1"/>
+      <c r="C576" s="1"/>
+      <c r="D576" s="1"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="3"/>
+      <c r="B577" s="1"/>
+      <c r="C577" s="1"/>
+      <c r="D577" s="1"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="3"/>
+      <c r="B578" s="1"/>
+      <c r="C578" s="1"/>
+      <c r="D578" s="1"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="3"/>
+      <c r="B579" s="1"/>
+      <c r="C579" s="1"/>
+      <c r="D579" s="1"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="3"/>
+      <c r="B580" s="1"/>
+      <c r="C580" s="1"/>
+      <c r="D580" s="1"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="3"/>
+      <c r="B581" s="1"/>
+      <c r="C581" s="1"/>
+      <c r="D581" s="1"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="3"/>
+      <c r="B582" s="1"/>
+      <c r="C582" s="1"/>
+      <c r="D582" s="1"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="3"/>
+      <c r="B583" s="1"/>
+      <c r="C583" s="1"/>
+      <c r="D583" s="1"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="3"/>
+      <c r="B584" s="1"/>
+      <c r="C584" s="1"/>
+      <c r="D584" s="1"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="3"/>
+      <c r="B585" s="1"/>
+      <c r="C585" s="1"/>
+      <c r="D585" s="1"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="3"/>
+      <c r="B586" s="1"/>
+      <c r="C586" s="1"/>
+      <c r="D586" s="1"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="3"/>
+      <c r="B587" s="1"/>
+      <c r="C587" s="1"/>
+      <c r="D587" s="1"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="3"/>
+      <c r="B588" s="1"/>
+      <c r="C588" s="1"/>
+      <c r="D588" s="1"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="3"/>
+      <c r="B589" s="1"/>
+      <c r="C589" s="1"/>
+      <c r="D589" s="1"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="3"/>
+      <c r="B590" s="1"/>
+      <c r="C590" s="1"/>
+      <c r="D590" s="1"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="3"/>
+      <c r="B591" s="1"/>
+      <c r="C591" s="1"/>
+      <c r="D591" s="1"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="3"/>
+      <c r="B592" s="1"/>
+      <c r="C592" s="1"/>
+      <c r="D592" s="1"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="3"/>
+      <c r="B593" s="1"/>
+      <c r="C593" s="1"/>
+      <c r="D593" s="1"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="3"/>
+      <c r="B594" s="1"/>
+      <c r="C594" s="1"/>
+      <c r="D594" s="1"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="3"/>
+      <c r="B595" s="1"/>
+      <c r="C595" s="1"/>
+      <c r="D595" s="1"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="3"/>
+      <c r="B596" s="1"/>
+      <c r="C596" s="1"/>
+      <c r="D596" s="1"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="3"/>
+      <c r="B597" s="1"/>
+      <c r="C597" s="1"/>
+      <c r="D597" s="1"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="3"/>
+      <c r="B598" s="1"/>
+      <c r="C598" s="1"/>
+      <c r="D598" s="1"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="3"/>
+      <c r="B599" s="1"/>
+      <c r="C599" s="1"/>
+      <c r="D599" s="1"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="3"/>
+      <c r="B600" s="1"/>
+      <c r="C600" s="1"/>
+      <c r="D600" s="1"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="3"/>
+      <c r="B601" s="1"/>
+      <c r="C601" s="1"/>
+      <c r="D601" s="1"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="3"/>
+      <c r="B602" s="1"/>
+      <c r="C602" s="1"/>
+      <c r="D602" s="1"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="3"/>
+      <c r="B603" s="1"/>
+      <c r="C603" s="1"/>
+      <c r="D603" s="1"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="3"/>
+      <c r="B604" s="1"/>
+      <c r="C604" s="1"/>
+      <c r="D604" s="1"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="3"/>
+      <c r="B605" s="1"/>
+      <c r="C605" s="1"/>
+      <c r="D605" s="1"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="3"/>
+      <c r="B606" s="1"/>
+      <c r="C606" s="1"/>
+      <c r="D606" s="1"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="3"/>
+      <c r="B607" s="1"/>
+      <c r="C607" s="1"/>
+      <c r="D607" s="1"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="3"/>
+      <c r="B608" s="1"/>
+      <c r="C608" s="1"/>
+      <c r="D608" s="1"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="3"/>
+      <c r="B609" s="1"/>
+      <c r="C609" s="1"/>
+      <c r="D609" s="1"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="3"/>
+      <c r="B610" s="1"/>
+      <c r="C610" s="1"/>
+      <c r="D610" s="1"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="3"/>
+      <c r="B611" s="1"/>
+      <c r="C611" s="1"/>
+      <c r="D611" s="1"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="3"/>
+      <c r="B612" s="1"/>
+      <c r="C612" s="1"/>
+      <c r="D612" s="1"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="3"/>
+      <c r="B613" s="1"/>
+      <c r="C613" s="1"/>
+      <c r="D613" s="1"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="3"/>
+      <c r="B614" s="1"/>
+      <c r="C614" s="1"/>
+      <c r="D614" s="1"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="3"/>
+      <c r="B615" s="1"/>
+      <c r="C615" s="1"/>
+      <c r="D615" s="1"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="3"/>
+      <c r="B616" s="1"/>
+      <c r="C616" s="1"/>
+      <c r="D616" s="1"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="3"/>
+      <c r="B617" s="1"/>
+      <c r="C617" s="1"/>
+      <c r="D617" s="1"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="3"/>
+      <c r="B618" s="1"/>
+      <c r="C618" s="1"/>
+      <c r="D618" s="1"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="3"/>
+      <c r="B619" s="1"/>
+      <c r="C619" s="1"/>
+      <c r="D619" s="1"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="3"/>
+      <c r="B620" s="1"/>
+      <c r="C620" s="1"/>
+      <c r="D620" s="1"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="3"/>
+      <c r="B621" s="1"/>
+      <c r="C621" s="1"/>
+      <c r="D621" s="1"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="3"/>
+      <c r="B622" s="1"/>
+      <c r="C622" s="1"/>
+      <c r="D622" s="1"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="3"/>
+      <c r="B623" s="1"/>
+      <c r="C623" s="1"/>
+      <c r="D623" s="1"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="3"/>
+      <c r="B624" s="1"/>
+      <c r="C624" s="1"/>
+      <c r="D624" s="1"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="3"/>
+      <c r="B625" s="1"/>
+      <c r="C625" s="1"/>
+      <c r="D625" s="1"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="3"/>
+      <c r="B626" s="1"/>
+      <c r="C626" s="1"/>
+      <c r="D626" s="1"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="3"/>
+      <c r="B627" s="1"/>
+      <c r="C627" s="1"/>
+      <c r="D627" s="1"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="3"/>
+      <c r="B628" s="1"/>
+      <c r="C628" s="1"/>
+      <c r="D628" s="1"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="3"/>
+      <c r="B629" s="1"/>
+      <c r="C629" s="1"/>
+      <c r="D629" s="1"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="3"/>
+      <c r="B630" s="1"/>
+      <c r="C630" s="1"/>
+      <c r="D630" s="1"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="3"/>
+      <c r="B631" s="1"/>
+      <c r="C631" s="1"/>
+      <c r="D631" s="1"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="3"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="1"/>
+      <c r="D632" s="1"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="3"/>
+      <c r="B633" s="1"/>
+      <c r="C633" s="1"/>
+      <c r="D633" s="1"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="3"/>
+      <c r="B634" s="1"/>
+      <c r="C634" s="1"/>
+      <c r="D634" s="1"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="3"/>
+      <c r="B635" s="1"/>
+      <c r="C635" s="1"/>
+      <c r="D635" s="1"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="3"/>
+      <c r="B636" s="1"/>
+      <c r="C636" s="1"/>
+      <c r="D636" s="1"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="3"/>
+      <c r="B637" s="1"/>
+      <c r="C637" s="1"/>
+      <c r="D637" s="1"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="3"/>
+      <c r="B638" s="1"/>
+      <c r="C638" s="1"/>
+      <c r="D638" s="1"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="3"/>
+      <c r="B639" s="1"/>
+      <c r="C639" s="1"/>
+      <c r="D639" s="1"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="3"/>
+      <c r="B640" s="1"/>
+      <c r="C640" s="1"/>
+      <c r="D640" s="1"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="3"/>
+      <c r="B641" s="1"/>
+      <c r="C641" s="1"/>
+      <c r="D641" s="1"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="3"/>
+      <c r="B642" s="1"/>
+      <c r="C642" s="1"/>
+      <c r="D642" s="1"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="3"/>
+      <c r="B643" s="1"/>
+      <c r="C643" s="1"/>
+      <c r="D643" s="1"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="3"/>
+      <c r="B644" s="1"/>
+      <c r="C644" s="1"/>
+      <c r="D644" s="1"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="3"/>
+      <c r="B645" s="1"/>
+      <c r="C645" s="1"/>
+      <c r="D645" s="1"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="3"/>
+      <c r="B646" s="1"/>
+      <c r="C646" s="1"/>
+      <c r="D646" s="1"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="3"/>
+      <c r="B647" s="1"/>
+      <c r="C647" s="1"/>
+      <c r="D647" s="1"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="3"/>
+      <c r="B648" s="1"/>
+      <c r="C648" s="1"/>
+      <c r="D648" s="1"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="3"/>
+      <c r="B649" s="1"/>
+      <c r="C649" s="1"/>
+      <c r="D649" s="1"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="3"/>
+      <c r="B650" s="1"/>
+      <c r="C650" s="1"/>
+      <c r="D650" s="1"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="3"/>
+      <c r="B651" s="1"/>
+      <c r="C651" s="1"/>
+      <c r="D651" s="1"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="3"/>
+      <c r="B652" s="1"/>
+      <c r="C652" s="1"/>
+      <c r="D652" s="1"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="3"/>
+      <c r="B653" s="1"/>
+      <c r="C653" s="1"/>
+      <c r="D653" s="1"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="3"/>
+      <c r="B654" s="1"/>
+      <c r="C654" s="1"/>
+      <c r="D654" s="1"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="3"/>
+      <c r="B655" s="1"/>
+      <c r="C655" s="1"/>
+      <c r="D655" s="1"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="3"/>
+      <c r="B656" s="1"/>
+      <c r="C656" s="1"/>
+      <c r="D656" s="1"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="3"/>
+      <c r="B657" s="1"/>
+      <c r="C657" s="1"/>
+      <c r="D657" s="1"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="3"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="1"/>
+      <c r="D658" s="1"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="3"/>
+      <c r="B659" s="1"/>
+      <c r="C659" s="1"/>
+      <c r="D659" s="1"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="3"/>
+      <c r="B660" s="1"/>
+      <c r="C660" s="1"/>
+      <c r="D660" s="1"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="3"/>
+      <c r="B661" s="1"/>
+      <c r="C661" s="1"/>
+      <c r="D661" s="1"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="3"/>
+      <c r="B662" s="1"/>
+      <c r="C662" s="1"/>
+      <c r="D662" s="1"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="3"/>
+      <c r="B663" s="1"/>
+      <c r="C663" s="1"/>
+      <c r="D663" s="1"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="3"/>
+      <c r="B664" s="1"/>
+      <c r="C664" s="1"/>
+      <c r="D664" s="1"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="3"/>
+      <c r="B665" s="1"/>
+      <c r="C665" s="1"/>
+      <c r="D665" s="1"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="3"/>
+      <c r="B666" s="1"/>
+      <c r="C666" s="1"/>
+      <c r="D666" s="1"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="3"/>
+      <c r="B667" s="1"/>
+      <c r="C667" s="1"/>
+      <c r="D667" s="1"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="3"/>
+      <c r="B668" s="1"/>
+      <c r="C668" s="1"/>
+      <c r="D668" s="1"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="3"/>
+      <c r="B669" s="1"/>
+      <c r="C669" s="1"/>
+      <c r="D669" s="1"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="3"/>
+      <c r="B670" s="1"/>
+      <c r="C670" s="1"/>
+      <c r="D670" s="1"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="3"/>
+      <c r="B671" s="1"/>
+      <c r="C671" s="1"/>
+      <c r="D671" s="1"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="3"/>
+      <c r="B672" s="1"/>
+      <c r="C672" s="1"/>
+      <c r="D672" s="1"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="3"/>
+      <c r="B673" s="1"/>
+      <c r="C673" s="1"/>
+      <c r="D673" s="1"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="3"/>
+      <c r="B674" s="1"/>
+      <c r="C674" s="1"/>
+      <c r="D674" s="1"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="3"/>
+      <c r="B675" s="1"/>
+      <c r="C675" s="1"/>
+      <c r="D675" s="1"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="3"/>
+      <c r="B676" s="1"/>
+      <c r="C676" s="1"/>
+      <c r="D676" s="1"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="3"/>
+      <c r="B677" s="1"/>
+      <c r="C677" s="1"/>
+      <c r="D677" s="1"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="3"/>
+      <c r="B678" s="1"/>
+      <c r="C678" s="1"/>
+      <c r="D678" s="1"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="3"/>
+      <c r="B679" s="1"/>
+      <c r="C679" s="1"/>
+      <c r="D679" s="1"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="3"/>
+      <c r="B680" s="1"/>
+      <c r="C680" s="1"/>
+      <c r="D680" s="1"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="3"/>
+      <c r="B681" s="1"/>
+      <c r="C681" s="1"/>
+      <c r="D681" s="1"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="3"/>
+      <c r="B682" s="1"/>
+      <c r="C682" s="1"/>
+      <c r="D682" s="1"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="3"/>
+      <c r="B683" s="1"/>
+      <c r="C683" s="1"/>
+      <c r="D683" s="1"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="3"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="1"/>
+      <c r="D684" s="1"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="3"/>
+      <c r="B685" s="1"/>
+      <c r="C685" s="1"/>
+      <c r="D685" s="1"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="3"/>
+      <c r="B686" s="1"/>
+      <c r="C686" s="1"/>
+      <c r="D686" s="1"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="3"/>
+      <c r="B687" s="1"/>
+      <c r="C687" s="1"/>
+      <c r="D687" s="1"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="3"/>
+      <c r="B688" s="1"/>
+      <c r="C688" s="1"/>
+      <c r="D688" s="1"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="3"/>
+      <c r="B689" s="1"/>
+      <c r="C689" s="1"/>
+      <c r="D689" s="1"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="3"/>
+      <c r="B690" s="1"/>
+      <c r="C690" s="1"/>
+      <c r="D690" s="1"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="3"/>
+      <c r="B691" s="1"/>
+      <c r="C691" s="1"/>
+      <c r="D691" s="1"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="3"/>
+      <c r="B692" s="1"/>
+      <c r="C692" s="1"/>
+      <c r="D692" s="1"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="3"/>
+      <c r="B693" s="1"/>
+      <c r="C693" s="1"/>
+      <c r="D693" s="1"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="3"/>
+      <c r="B694" s="1"/>
+      <c r="C694" s="1"/>
+      <c r="D694" s="1"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="3"/>
+      <c r="B695" s="1"/>
+      <c r="C695" s="1"/>
+      <c r="D695" s="1"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="3"/>
+      <c r="B696" s="1"/>
+      <c r="C696" s="1"/>
+      <c r="D696" s="1"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="3"/>
+      <c r="B697" s="1"/>
+      <c r="C697" s="1"/>
+      <c r="D697" s="1"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="3"/>
+      <c r="B698" s="1"/>
+      <c r="C698" s="1"/>
+      <c r="D698" s="1"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="3"/>
+      <c r="B699" s="1"/>
+      <c r="C699" s="1"/>
+      <c r="D699" s="1"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="3"/>
+      <c r="B700" s="1"/>
+      <c r="C700" s="1"/>
+      <c r="D700" s="1"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="3"/>
+      <c r="B701" s="1"/>
+      <c r="C701" s="1"/>
+      <c r="D701" s="1"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="3"/>
+      <c r="B702" s="1"/>
+      <c r="C702" s="1"/>
+      <c r="D702" s="1"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="3"/>
+      <c r="B703" s="1"/>
+      <c r="C703" s="1"/>
+      <c r="D703" s="1"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="3"/>
+      <c r="B704" s="1"/>
+      <c r="C704" s="1"/>
+      <c r="D704" s="1"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="3"/>
+      <c r="B705" s="1"/>
+      <c r="C705" s="1"/>
+      <c r="D705" s="1"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="3"/>
+      <c r="B706" s="1"/>
+      <c r="C706" s="1"/>
+      <c r="D706" s="1"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="3"/>
+      <c r="B707" s="1"/>
+      <c r="C707" s="1"/>
+      <c r="D707" s="1"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="3"/>
+      <c r="B708" s="1"/>
+      <c r="C708" s="1"/>
+      <c r="D708" s="1"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="3"/>
+      <c r="B709" s="1"/>
+      <c r="C709" s="1"/>
+      <c r="D709" s="1"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="3"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="1"/>
+      <c r="D710" s="1"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="3"/>
+      <c r="B711" s="1"/>
+      <c r="C711" s="1"/>
+      <c r="D711" s="1"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="3"/>
+      <c r="B712" s="1"/>
+      <c r="C712" s="1"/>
+      <c r="D712" s="1"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="3"/>
+      <c r="B713" s="1"/>
+      <c r="C713" s="1"/>
+      <c r="D713" s="1"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="3"/>
+      <c r="B714" s="1"/>
+      <c r="C714" s="1"/>
+      <c r="D714" s="1"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="3"/>
+      <c r="B715" s="1"/>
+      <c r="C715" s="1"/>
+      <c r="D715" s="1"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="3"/>
+      <c r="B716" s="1"/>
+      <c r="C716" s="1"/>
+      <c r="D716" s="1"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="3"/>
+      <c r="B717" s="1"/>
+      <c r="C717" s="1"/>
+      <c r="D717" s="1"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="3"/>
+      <c r="B718" s="1"/>
+      <c r="C718" s="1"/>
+      <c r="D718" s="1"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="3"/>
+      <c r="B719" s="1"/>
+      <c r="C719" s="1"/>
+      <c r="D719" s="1"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="3"/>
+      <c r="B720" s="1"/>
+      <c r="C720" s="1"/>
+      <c r="D720" s="1"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="3"/>
+      <c r="B721" s="1"/>
+      <c r="C721" s="1"/>
+      <c r="D721" s="1"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="3"/>
+      <c r="B722" s="1"/>
+      <c r="C722" s="1"/>
+      <c r="D722" s="1"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="3"/>
+      <c r="B723" s="1"/>
+      <c r="C723" s="1"/>
+      <c r="D723" s="1"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="3"/>
+      <c r="B724" s="1"/>
+      <c r="C724" s="1"/>
+      <c r="D724" s="1"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="3"/>
+      <c r="B725" s="1"/>
+      <c r="C725" s="1"/>
+      <c r="D725" s="1"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="3"/>
+      <c r="B726" s="1"/>
+      <c r="C726" s="1"/>
+      <c r="D726" s="1"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="3"/>
+      <c r="B727" s="1"/>
+      <c r="C727" s="1"/>
+      <c r="D727" s="1"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="3"/>
+      <c r="B728" s="1"/>
+      <c r="C728" s="1"/>
+      <c r="D728" s="1"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="3"/>
+      <c r="B729" s="1"/>
+      <c r="C729" s="1"/>
+      <c r="D729" s="1"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="3"/>
+      <c r="B730" s="1"/>
+      <c r="C730" s="1"/>
+      <c r="D730" s="1"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="3"/>
+      <c r="B731" s="1"/>
+      <c r="C731" s="1"/>
+      <c r="D731" s="1"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="3"/>
+      <c r="B732" s="1"/>
+      <c r="C732" s="1"/>
+      <c r="D732" s="1"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="3"/>
+      <c r="B733" s="1"/>
+      <c r="C733" s="1"/>
+      <c r="D733" s="1"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="3"/>
+      <c r="B734" s="1"/>
+      <c r="C734" s="1"/>
+      <c r="D734" s="1"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="3"/>
+      <c r="B735" s="1"/>
+      <c r="C735" s="1"/>
+      <c r="D735" s="1"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="3"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="1"/>
+      <c r="D736" s="1"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="3"/>
+      <c r="B737" s="1"/>
+      <c r="C737" s="1"/>
+      <c r="D737" s="1"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="3"/>
+      <c r="B738" s="1"/>
+      <c r="C738" s="1"/>
+      <c r="D738" s="1"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="3"/>
+      <c r="B739" s="1"/>
+      <c r="C739" s="1"/>
+      <c r="D739" s="1"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="3"/>
+      <c r="B740" s="1"/>
+      <c r="C740" s="1"/>
+      <c r="D740" s="1"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="3"/>
+      <c r="B741" s="1"/>
+      <c r="C741" s="1"/>
+      <c r="D741" s="1"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="3"/>
+      <c r="B742" s="1"/>
+      <c r="C742" s="1"/>
+      <c r="D742" s="1"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="3"/>
+      <c r="B743" s="1"/>
+      <c r="C743" s="1"/>
+      <c r="D743" s="1"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="3"/>
+      <c r="B744" s="1"/>
+      <c r="C744" s="1"/>
+      <c r="D744" s="1"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="3"/>
+      <c r="B745" s="1"/>
+      <c r="C745" s="1"/>
+      <c r="D745" s="1"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="3"/>
+      <c r="B746" s="1"/>
+      <c r="C746" s="1"/>
+      <c r="D746" s="1"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="3"/>
+      <c r="B747" s="1"/>
+      <c r="C747" s="1"/>
+      <c r="D747" s="1"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="3"/>
+      <c r="B748" s="1"/>
+      <c r="C748" s="1"/>
+      <c r="D748" s="1"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="3"/>
+      <c r="B749" s="1"/>
+      <c r="C749" s="1"/>
+      <c r="D749" s="1"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="3"/>
+      <c r="B750" s="1"/>
+      <c r="C750" s="1"/>
+      <c r="D750" s="1"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="3"/>
+      <c r="B751" s="1"/>
+      <c r="C751" s="1"/>
+      <c r="D751" s="1"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="3"/>
+      <c r="B752" s="1"/>
+      <c r="C752" s="1"/>
+      <c r="D752" s="1"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="3"/>
+      <c r="B753" s="1"/>
+      <c r="C753" s="1"/>
+      <c r="D753" s="1"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="3"/>
+      <c r="B754" s="1"/>
+      <c r="C754" s="1"/>
+      <c r="D754" s="1"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="3"/>
+      <c r="B755" s="1"/>
+      <c r="C755" s="1"/>
+      <c r="D755" s="1"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="3"/>
+      <c r="B756" s="1"/>
+      <c r="C756" s="1"/>
+      <c r="D756" s="1"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="3"/>
+      <c r="B757" s="1"/>
+      <c r="C757" s="1"/>
+      <c r="D757" s="1"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="3"/>
+      <c r="B758" s="1"/>
+      <c r="C758" s="1"/>
+      <c r="D758" s="1"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="3"/>
+      <c r="B759" s="1"/>
+      <c r="C759" s="1"/>
+      <c r="D759" s="1"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="3"/>
+      <c r="B760" s="1"/>
+      <c r="C760" s="1"/>
+      <c r="D760" s="1"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="3"/>
+      <c r="B761" s="1"/>
+      <c r="C761" s="1"/>
+      <c r="D761" s="1"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="3"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="1"/>
+      <c r="D762" s="1"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="3"/>
+      <c r="B763" s="1"/>
+      <c r="C763" s="1"/>
+      <c r="D763" s="1"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="3"/>
+      <c r="B764" s="1"/>
+      <c r="C764" s="1"/>
+      <c r="D764" s="1"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="3"/>
+      <c r="B765" s="1"/>
+      <c r="C765" s="1"/>
+      <c r="D765" s="1"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="3"/>
+      <c r="B766" s="1"/>
+      <c r="C766" s="1"/>
+      <c r="D766" s="1"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="3"/>
+      <c r="B767" s="1"/>
+      <c r="C767" s="1"/>
+      <c r="D767" s="1"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="3"/>
+      <c r="B768" s="1"/>
+      <c r="C768" s="1"/>
+      <c r="D768" s="1"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="3"/>
+      <c r="B769" s="1"/>
+      <c r="C769" s="1"/>
+      <c r="D769" s="1"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="3"/>
+      <c r="B770" s="1"/>
+      <c r="C770" s="1"/>
+      <c r="D770" s="1"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="3"/>
+      <c r="B771" s="1"/>
+      <c r="C771" s="1"/>
+      <c r="D771" s="1"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="3"/>
+      <c r="B772" s="1"/>
+      <c r="C772" s="1"/>
+      <c r="D772" s="1"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="3"/>
+      <c r="B773" s="1"/>
+      <c r="C773" s="1"/>
+      <c r="D773" s="1"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="3"/>
+      <c r="B774" s="1"/>
+      <c r="C774" s="1"/>
+      <c r="D774" s="1"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="3"/>
+      <c r="B775" s="1"/>
+      <c r="C775" s="1"/>
+      <c r="D775" s="1"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="3"/>
+      <c r="B776" s="1"/>
+      <c r="C776" s="1"/>
+      <c r="D776" s="1"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="3"/>
+      <c r="B777" s="1"/>
+      <c r="C777" s="1"/>
+      <c r="D777" s="1"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="3"/>
+      <c r="B778" s="1"/>
+      <c r="C778" s="1"/>
+      <c r="D778" s="1"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="3"/>
+      <c r="B779" s="1"/>
+      <c r="C779" s="1"/>
+      <c r="D779" s="1"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="3"/>
+      <c r="B780" s="1"/>
+      <c r="C780" s="1"/>
+      <c r="D780" s="1"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="3"/>
+      <c r="B781" s="1"/>
+      <c r="C781" s="1"/>
+      <c r="D781" s="1"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="3"/>
+      <c r="B782" s="1"/>
+      <c r="C782" s="1"/>
+      <c r="D782" s="1"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="3"/>
+      <c r="B783" s="1"/>
+      <c r="C783" s="1"/>
+      <c r="D783" s="1"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="3"/>
+      <c r="B784" s="1"/>
+      <c r="C784" s="1"/>
+      <c r="D784" s="1"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="3"/>
+      <c r="B785" s="1"/>
+      <c r="C785" s="1"/>
+      <c r="D785" s="1"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="3"/>
+      <c r="B786" s="1"/>
+      <c r="C786" s="1"/>
+      <c r="D786" s="1"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="3"/>
+      <c r="B787" s="1"/>
+      <c r="C787" s="1"/>
+      <c r="D787" s="1"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="3"/>
+      <c r="B788" s="1"/>
+      <c r="C788" s="1"/>
+      <c r="D788" s="1"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="3"/>
+      <c r="B789" s="1"/>
+      <c r="C789" s="1"/>
+      <c r="D789" s="1"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="3"/>
+      <c r="B790" s="1"/>
+      <c r="C790" s="1"/>
+      <c r="D790" s="1"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="3"/>
+      <c r="B791" s="1"/>
+      <c r="C791" s="1"/>
+      <c r="D791" s="1"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="3"/>
+      <c r="B792" s="1"/>
+      <c r="C792" s="1"/>
+      <c r="D792" s="1"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="3"/>
+      <c r="B793" s="1"/>
+      <c r="C793" s="1"/>
+      <c r="D793" s="1"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="3"/>
+      <c r="B794" s="1"/>
+      <c r="C794" s="1"/>
+      <c r="D794" s="1"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="3"/>
+      <c r="B795" s="1"/>
+      <c r="C795" s="1"/>
+      <c r="D795" s="1"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="3"/>
+      <c r="B796" s="1"/>
+      <c r="C796" s="1"/>
+      <c r="D796" s="1"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="3"/>
+      <c r="B797" s="1"/>
+      <c r="C797" s="1"/>
+      <c r="D797" s="1"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="3"/>
+      <c r="B798" s="1"/>
+      <c r="C798" s="1"/>
+      <c r="D798" s="1"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="3"/>
+      <c r="B799" s="1"/>
+      <c r="C799" s="1"/>
+      <c r="D799" s="1"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="3"/>
+      <c r="B800" s="1"/>
+      <c r="C800" s="1"/>
+      <c r="D800" s="1"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="3"/>
+      <c r="B801" s="1"/>
+      <c r="C801" s="1"/>
+      <c r="D801" s="1"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="3"/>
+      <c r="B802" s="1"/>
+      <c r="C802" s="1"/>
+      <c r="D802" s="1"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="3"/>
+      <c r="B803" s="1"/>
+      <c r="C803" s="1"/>
+      <c r="D803" s="1"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="3"/>
+      <c r="B804" s="1"/>
+      <c r="C804" s="1"/>
+      <c r="D804" s="1"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="3"/>
+      <c r="B805" s="1"/>
+      <c r="C805" s="1"/>
+      <c r="D805" s="1"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="3"/>
+      <c r="B806" s="1"/>
+      <c r="C806" s="1"/>
+      <c r="D806" s="1"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="3"/>
+      <c r="B807" s="1"/>
+      <c r="C807" s="1"/>
+      <c r="D807" s="1"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="3"/>
+      <c r="B808" s="1"/>
+      <c r="C808" s="1"/>
+      <c r="D808" s="1"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="3"/>
+      <c r="B809" s="1"/>
+      <c r="C809" s="1"/>
+      <c r="D809" s="1"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="3"/>
+      <c r="B810" s="1"/>
+      <c r="C810" s="1"/>
+      <c r="D810" s="1"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="3"/>
+      <c r="B811" s="1"/>
+      <c r="C811" s="1"/>
+      <c r="D811" s="1"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="3"/>
+      <c r="B812" s="1"/>
+      <c r="C812" s="1"/>
+      <c r="D812" s="1"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="3"/>
+      <c r="B813" s="1"/>
+      <c r="C813" s="1"/>
+      <c r="D813" s="1"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="3"/>
+      <c r="B814" s="1"/>
+      <c r="C814" s="1"/>
+      <c r="D814" s="1"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="3"/>
+      <c r="B815" s="1"/>
+      <c r="C815" s="1"/>
+      <c r="D815" s="1"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="3"/>
+      <c r="B816" s="1"/>
+      <c r="C816" s="1"/>
+      <c r="D816" s="1"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="3"/>
+      <c r="B817" s="1"/>
+      <c r="C817" s="1"/>
+      <c r="D817" s="1"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="3"/>
+      <c r="B818" s="1"/>
+      <c r="C818" s="1"/>
+      <c r="D818" s="1"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="3"/>
+      <c r="B819" s="1"/>
+      <c r="C819" s="1"/>
+      <c r="D819" s="1"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="3"/>
+      <c r="B820" s="1"/>
+      <c r="C820" s="1"/>
+      <c r="D820" s="1"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="3"/>
+      <c r="B821" s="1"/>
+      <c r="C821" s="1"/>
+      <c r="D821" s="1"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="3"/>
+      <c r="B822" s="1"/>
+      <c r="C822" s="1"/>
+      <c r="D822" s="1"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="3"/>
+      <c r="B823" s="1"/>
+      <c r="C823" s="1"/>
+      <c r="D823" s="1"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="3"/>
+      <c r="B824" s="1"/>
+      <c r="C824" s="1"/>
+      <c r="D824" s="1"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="3"/>
+      <c r="B825" s="1"/>
+      <c r="C825" s="1"/>
+      <c r="D825" s="1"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="3"/>
+      <c r="B826" s="1"/>
+      <c r="C826" s="1"/>
+      <c r="D826" s="1"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="3"/>
+      <c r="B827" s="1"/>
+      <c r="C827" s="1"/>
+      <c r="D827" s="1"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="3"/>
+      <c r="B828" s="1"/>
+      <c r="C828" s="1"/>
+      <c r="D828" s="1"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="3"/>
+      <c r="B829" s="1"/>
+      <c r="C829" s="1"/>
+      <c r="D829" s="1"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="3"/>
+      <c r="B830" s="1"/>
+      <c r="C830" s="1"/>
+      <c r="D830" s="1"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="3"/>
+      <c r="B831" s="1"/>
+      <c r="C831" s="1"/>
+      <c r="D831" s="1"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="3"/>
+      <c r="B832" s="1"/>
+      <c r="C832" s="1"/>
+      <c r="D832" s="1"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="3"/>
+      <c r="B833" s="1"/>
+      <c r="C833" s="1"/>
+      <c r="D833" s="1"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="3"/>
+      <c r="B834" s="1"/>
+      <c r="C834" s="1"/>
+      <c r="D834" s="1"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="3"/>
+      <c r="B835" s="1"/>
+      <c r="C835" s="1"/>
+      <c r="D835" s="1"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="3"/>
+      <c r="B836" s="1"/>
+      <c r="C836" s="1"/>
+      <c r="D836" s="1"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="3"/>
+      <c r="B837" s="1"/>
+      <c r="C837" s="1"/>
+      <c r="D837" s="1"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="3"/>
+      <c r="B838" s="1"/>
+      <c r="C838" s="1"/>
+      <c r="D838" s="1"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="3"/>
+      <c r="B839" s="1"/>
+      <c r="C839" s="1"/>
+      <c r="D839" s="1"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="3"/>
+      <c r="B840" s="1"/>
+      <c r="C840" s="1"/>
+      <c r="D840" s="1"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="3"/>
+      <c r="B841" s="1"/>
+      <c r="C841" s="1"/>
+      <c r="D841" s="1"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="3"/>
+      <c r="B842" s="1"/>
+      <c r="C842" s="1"/>
+      <c r="D842" s="1"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="3"/>
+      <c r="B843" s="1"/>
+      <c r="C843" s="1"/>
+      <c r="D843" s="1"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="3"/>
+      <c r="B844" s="1"/>
+      <c r="C844" s="1"/>
+      <c r="D844" s="1"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="3"/>
+      <c r="B845" s="1"/>
+      <c r="C845" s="1"/>
+      <c r="D845" s="1"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="3"/>
+      <c r="B846" s="1"/>
+      <c r="C846" s="1"/>
+      <c r="D846" s="1"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="3"/>
+      <c r="B847" s="1"/>
+      <c r="C847" s="1"/>
+      <c r="D847" s="1"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="3"/>
+      <c r="B848" s="1"/>
+      <c r="C848" s="1"/>
+      <c r="D848" s="1"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="3"/>
+      <c r="B849" s="1"/>
+      <c r="C849" s="1"/>
+      <c r="D849" s="1"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="3"/>
+      <c r="B850" s="1"/>
+      <c r="C850" s="1"/>
+      <c r="D850" s="1"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="3"/>
+      <c r="B851" s="1"/>
+      <c r="C851" s="1"/>
+      <c r="D851" s="1"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="3"/>
+      <c r="B852" s="1"/>
+      <c r="C852" s="1"/>
+      <c r="D852" s="1"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="3"/>
+      <c r="B853" s="1"/>
+      <c r="C853" s="1"/>
+      <c r="D853" s="1"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="3"/>
+      <c r="B854" s="1"/>
+      <c r="C854" s="1"/>
+      <c r="D854" s="1"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="3"/>
+      <c r="B855" s="1"/>
+      <c r="C855" s="1"/>
+      <c r="D855" s="1"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="3"/>
+      <c r="B856" s="1"/>
+      <c r="C856" s="1"/>
+      <c r="D856" s="1"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="3"/>
+      <c r="B857" s="1"/>
+      <c r="C857" s="1"/>
+      <c r="D857" s="1"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="3"/>
+      <c r="B858" s="1"/>
+      <c r="C858" s="1"/>
+      <c r="D858" s="1"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="3"/>
+      <c r="B859" s="1"/>
+      <c r="C859" s="1"/>
+      <c r="D859" s="1"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="3"/>
+      <c r="B860" s="1"/>
+      <c r="C860" s="1"/>
+      <c r="D860" s="1"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="3"/>
+      <c r="B861" s="1"/>
+      <c r="C861" s="1"/>
+      <c r="D861" s="1"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="3"/>
+      <c r="B862" s="1"/>
+      <c r="C862" s="1"/>
+      <c r="D862" s="1"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="3"/>
+      <c r="B863" s="1"/>
+      <c r="C863" s="1"/>
+      <c r="D863" s="1"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="3"/>
+      <c r="B864" s="1"/>
+      <c r="C864" s="1"/>
+      <c r="D864" s="1"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="3"/>
+      <c r="B865" s="1"/>
+      <c r="C865" s="1"/>
+      <c r="D865" s="1"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>154.13095</v>
+        <v>183.22611</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>148.65412</v>
+        <v>161.7448</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>144.03314</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>139.32589</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>144.99</v>
+        <v>150.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>140.26501</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>138.81774</v>
+        <v>143.11145</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>137.07811</v>
+        <v>141.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>137.3916</v>
+        <v>144.71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>136.07408</v>
+        <v>141.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>134.9</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>135.51076</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>133.59</v>
+        <v>141.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>137.83</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>138.03</v>
+        <v>140.16627</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>138.03</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>136.97</v>
+        <v>139.28006</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>135.07</v>
+        <v>139.21618</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>133.59</v>
+        <v>139.09652</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>134.37</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>136.88</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>138.03</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>138.03</v>
+        <v>137.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>138.03</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>138.03</v>
+        <v>141.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>138.03</v>
+        <v>145.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>140.43</v>
+        <v>150.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>143.51</v>
+        <v>150.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>142.41</v>
+        <v>155.22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>149.98</v>
+        <v>155.22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>147.37994</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>135.0</v>
+        <v>141.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>150.04</v>
+        <v>163.93667</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>135.7134</v>
+        <v>150.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>130.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>120.35276</v>
+        <v>127.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>131.3179</v>
+        <v>141.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>124.24518</v>
+        <v>132.05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>119.89936</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>120.43</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>120.43</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>120.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>115.27</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>120.0</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>116.27</v>
+        <v>118.225</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>115.2</v>
+        <v>115.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>117.27</v>
+        <v>114.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>120.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>126.71</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>125.16</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>131.27</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>131.0</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>123.98</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>125.83</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>131.27</v>
+        <v>121.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>132.96</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>132.45</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>132.96</v>
+        <v>125.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>132.96</v>
+        <v>127.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>131.27</v>
+        <v>131.52</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>124.63</v>
+        <v>125.13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>131.0</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>133.53</v>
+        <v>133.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>134.53</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>129.8</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>132.53</v>
+        <v>125.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>132.96</v>
+        <v>132.72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>136.60747</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>125.0</v>
+        <v>120.98321</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>131.93</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>138.03</v>
+        <v>140.19026</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>148.07385</v>
+        <v>154.92</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>134.37</v>
+        <v>139.75264</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>147.23239</v>
+        <v>156.55213</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>178.52085</v>
+        <v>204.30646</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>231.48038</v>
+        <v>270.0057</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>180.96575</v>
+        <v>236.568</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>240.79495</v>
+        <v>263.25508</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>249.30394</v>
+        <v>283.42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>272.62526</v>
+        <v>296.56066</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>263.2816</v>
+        <v>287.45389</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>264.5514</v>
+        <v>288.06068</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>272.92339</v>
+        <v>288.29223</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>256.2005</v>
+        <v>277.78414</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>271.07688</v>
+        <v>279.37054</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>247.02522</v>
+        <v>276.42802</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>209.93</v>
+        <v>274.8751</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>183.52</v>
+        <v>238.01709</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>247.44546</v>
+        <v>277.79921</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>208.0</v>
+        <v>256.97224</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>224.74993</v>
+        <v>257.56433</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>183.46</v>
+        <v>236.35648</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>209.33</v>
+        <v>240.85421</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>171.69</v>
+        <v>177.19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>169.33</v>
+        <v>176.18</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46196.0</v>
+        <v>46197.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>152.21</v>
+        <v>158.82</v>
       </c>
     </row>
     <row r="98">

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>200.1</v>
+        <v>155.47769</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>171.00412</v>
+        <v>152.16539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>150.5</v>
+        <v>144.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>142.18</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>155.99</v>
+        <v>143.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>143.96</v>
+        <v>141.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>142.18</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>139.87</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>141.0</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>139.87</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>139.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>139.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>139.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>139.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>139.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>139.87</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>139.7</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>139.87</v>
+        <v>138.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>139.7</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>139.7</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>139.7</v>
+        <v>136.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>139.7</v>
+        <v>136.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>139.14</v>
+        <v>136.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>139.7</v>
+        <v>136.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>139.7</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>142.18</v>
+        <v>144.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>143.96</v>
+        <v>144.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>147.19369</v>
+        <v>143.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>143.96</v>
+        <v>158.80297</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>143.17</v>
+        <v>147.86402</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>143.13</v>
+        <v>147.82452</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>139.14</v>
+        <v>141.29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>140.84303</v>
+        <v>150.41315</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>139.7</v>
+        <v>151.99766</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>138.45</v>
+        <v>141.94133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>137.95</v>
+        <v>141.9401</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>139.0</v>
+        <v>155.81801</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>138.45</v>
+        <v>145.95335</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>132.0</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>120.94</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>133.5356</v>
+        <v>139.98425</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>128.14158</v>
+        <v>139.92502</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>118.82146</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>116.19151</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>127.79234</v>
+        <v>137.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>125.69651</v>
+        <v>137.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>118.56165</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>127.7</v>
+        <v>135.47545</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>115.1</v>
+        <v>136.2823</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>125.0</v>
+        <v>133.49</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>135.0</v>
+        <v>133.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>136.39</v>
+        <v>134.86</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>132.5</v>
+        <v>133.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>130.22417</v>
+        <v>133.2192</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>135.75</v>
+        <v>135.91864</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>130.0</v>
+        <v>135.97898</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>135.0</v>
+        <v>135.98456</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>136.39</v>
+        <v>137.8316</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>136.39</v>
+        <v>137.63979</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>137.95</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>138.45</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>139.14</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>139.7</v>
+        <v>139.97149</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>139.87</v>
+        <v>143.22123</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>132.0</v>
+        <v>139.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>136.39</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>137.95</v>
+        <v>141.29</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>139.87</v>
+        <v>141.95638</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>139.14</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>139.14</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>142.18</v>
+        <v>143.6396</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>152.84834</v>
+        <v>151.54106</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>139.87</v>
+        <v>139.77</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>149.73</v>
+        <v>144.74347</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>164.74</v>
+        <v>172.94217</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>192.36268</v>
+        <v>207.93923</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>165.23453</v>
+        <v>158.70309</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>193.16101</v>
+        <v>189.4795</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>210.10966</v>
+        <v>244.11318</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>255.83306</v>
+        <v>255.78303</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>210.93077</v>
+        <v>234.66526</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>209.16491</v>
+        <v>233.72165</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>210.0099</v>
+        <v>254.91257</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>210.22648</v>
+        <v>243.86462</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>209.34619</v>
+        <v>250.21256</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>205.51866</v>
+        <v>232.75707</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>191.39405</v>
+        <v>211.66</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>175.8783</v>
+        <v>194.74</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>182.19176</v>
+        <v>250.32911</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>177.19</v>
+        <v>201.78535</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>171.95676</v>
+        <v>182.4432</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>159.24853</v>
+        <v>160.13984</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>162.48</v>
+        <v>174.20296</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>146.23</v>
+        <v>156.56539</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>139.87</v>
+        <v>145.74574</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46198.0</v>
+        <v>46199.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,8 +1649,4616 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>139.7</v>
-      </c>
+        <v>139.62</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3"/>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3"/>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3"/>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3"/>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3"/>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3"/>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3"/>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3"/>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3"/>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3"/>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3"/>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="3"/>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="3"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="3"/>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="3"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="3"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="3"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="3"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="3"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="3"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3"/>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="3"/>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3"/>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="3"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3"/>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="3"/>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="3"/>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="3"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="3"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="3"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="3"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="3"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="3"/>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="3"/>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="3"/>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="3"/>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="3"/>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="3"/>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="3"/>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="3"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="3"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="3"/>
+      <c r="B356" s="1"/>
+      <c r="C356" s="1"/>
+      <c r="D356" s="1"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="3"/>
+      <c r="B357" s="1"/>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="3"/>
+      <c r="B358" s="1"/>
+      <c r="C358" s="1"/>
+      <c r="D358" s="1"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="3"/>
+      <c r="B359" s="1"/>
+      <c r="C359" s="1"/>
+      <c r="D359" s="1"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="3"/>
+      <c r="B360" s="1"/>
+      <c r="C360" s="1"/>
+      <c r="D360" s="1"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="3"/>
+      <c r="B361" s="1"/>
+      <c r="C361" s="1"/>
+      <c r="D361" s="1"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="3"/>
+      <c r="B362" s="1"/>
+      <c r="C362" s="1"/>
+      <c r="D362" s="1"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="3"/>
+      <c r="B363" s="1"/>
+      <c r="C363" s="1"/>
+      <c r="D363" s="1"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="3"/>
+      <c r="B364" s="1"/>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="3"/>
+      <c r="B365" s="1"/>
+      <c r="C365" s="1"/>
+      <c r="D365" s="1"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="3"/>
+      <c r="B366" s="1"/>
+      <c r="C366" s="1"/>
+      <c r="D366" s="1"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="3"/>
+      <c r="B367" s="1"/>
+      <c r="C367" s="1"/>
+      <c r="D367" s="1"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="3"/>
+      <c r="B368" s="1"/>
+      <c r="C368" s="1"/>
+      <c r="D368" s="1"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="3"/>
+      <c r="B369" s="1"/>
+      <c r="C369" s="1"/>
+      <c r="D369" s="1"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="3"/>
+      <c r="B370" s="1"/>
+      <c r="C370" s="1"/>
+      <c r="D370" s="1"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="3"/>
+      <c r="B371" s="1"/>
+      <c r="C371" s="1"/>
+      <c r="D371" s="1"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="3"/>
+      <c r="B372" s="1"/>
+      <c r="C372" s="1"/>
+      <c r="D372" s="1"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="3"/>
+      <c r="B373" s="1"/>
+      <c r="C373" s="1"/>
+      <c r="D373" s="1"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="3"/>
+      <c r="B374" s="1"/>
+      <c r="C374" s="1"/>
+      <c r="D374" s="1"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="3"/>
+      <c r="B375" s="1"/>
+      <c r="C375" s="1"/>
+      <c r="D375" s="1"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="3"/>
+      <c r="B376" s="1"/>
+      <c r="C376" s="1"/>
+      <c r="D376" s="1"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="3"/>
+      <c r="B377" s="1"/>
+      <c r="C377" s="1"/>
+      <c r="D377" s="1"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="3"/>
+      <c r="B378" s="1"/>
+      <c r="C378" s="1"/>
+      <c r="D378" s="1"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="3"/>
+      <c r="B379" s="1"/>
+      <c r="C379" s="1"/>
+      <c r="D379" s="1"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="3"/>
+      <c r="B380" s="1"/>
+      <c r="C380" s="1"/>
+      <c r="D380" s="1"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="3"/>
+      <c r="B381" s="1"/>
+      <c r="C381" s="1"/>
+      <c r="D381" s="1"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="3"/>
+      <c r="B382" s="1"/>
+      <c r="C382" s="1"/>
+      <c r="D382" s="1"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="3"/>
+      <c r="B383" s="1"/>
+      <c r="C383" s="1"/>
+      <c r="D383" s="1"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="3"/>
+      <c r="B384" s="1"/>
+      <c r="C384" s="1"/>
+      <c r="D384" s="1"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="3"/>
+      <c r="B385" s="1"/>
+      <c r="C385" s="1"/>
+      <c r="D385" s="1"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="3"/>
+      <c r="B386" s="1"/>
+      <c r="C386" s="1"/>
+      <c r="D386" s="1"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="3"/>
+      <c r="B387" s="1"/>
+      <c r="C387" s="1"/>
+      <c r="D387" s="1"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="3"/>
+      <c r="B388" s="1"/>
+      <c r="C388" s="1"/>
+      <c r="D388" s="1"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="3"/>
+      <c r="B389" s="1"/>
+      <c r="C389" s="1"/>
+      <c r="D389" s="1"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="3"/>
+      <c r="B390" s="1"/>
+      <c r="C390" s="1"/>
+      <c r="D390" s="1"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="3"/>
+      <c r="B391" s="1"/>
+      <c r="C391" s="1"/>
+      <c r="D391" s="1"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="3"/>
+      <c r="B392" s="1"/>
+      <c r="C392" s="1"/>
+      <c r="D392" s="1"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="3"/>
+      <c r="B393" s="1"/>
+      <c r="C393" s="1"/>
+      <c r="D393" s="1"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="3"/>
+      <c r="B394" s="1"/>
+      <c r="C394" s="1"/>
+      <c r="D394" s="1"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="3"/>
+      <c r="B395" s="1"/>
+      <c r="C395" s="1"/>
+      <c r="D395" s="1"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="3"/>
+      <c r="B396" s="1"/>
+      <c r="C396" s="1"/>
+      <c r="D396" s="1"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="3"/>
+      <c r="B397" s="1"/>
+      <c r="C397" s="1"/>
+      <c r="D397" s="1"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="3"/>
+      <c r="B398" s="1"/>
+      <c r="C398" s="1"/>
+      <c r="D398" s="1"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="3"/>
+      <c r="B399" s="1"/>
+      <c r="C399" s="1"/>
+      <c r="D399" s="1"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="3"/>
+      <c r="B400" s="1"/>
+      <c r="C400" s="1"/>
+      <c r="D400" s="1"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="3"/>
+      <c r="B401" s="1"/>
+      <c r="C401" s="1"/>
+      <c r="D401" s="1"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="3"/>
+      <c r="B402" s="1"/>
+      <c r="C402" s="1"/>
+      <c r="D402" s="1"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="3"/>
+      <c r="B403" s="1"/>
+      <c r="C403" s="1"/>
+      <c r="D403" s="1"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="3"/>
+      <c r="B404" s="1"/>
+      <c r="C404" s="1"/>
+      <c r="D404" s="1"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="3"/>
+      <c r="B405" s="1"/>
+      <c r="C405" s="1"/>
+      <c r="D405" s="1"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="3"/>
+      <c r="B406" s="1"/>
+      <c r="C406" s="1"/>
+      <c r="D406" s="1"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="3"/>
+      <c r="B407" s="1"/>
+      <c r="C407" s="1"/>
+      <c r="D407" s="1"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="3"/>
+      <c r="B408" s="1"/>
+      <c r="C408" s="1"/>
+      <c r="D408" s="1"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="3"/>
+      <c r="B409" s="1"/>
+      <c r="C409" s="1"/>
+      <c r="D409" s="1"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="3"/>
+      <c r="B410" s="1"/>
+      <c r="C410" s="1"/>
+      <c r="D410" s="1"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="3"/>
+      <c r="B411" s="1"/>
+      <c r="C411" s="1"/>
+      <c r="D411" s="1"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="3"/>
+      <c r="B412" s="1"/>
+      <c r="C412" s="1"/>
+      <c r="D412" s="1"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="3"/>
+      <c r="B413" s="1"/>
+      <c r="C413" s="1"/>
+      <c r="D413" s="1"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="3"/>
+      <c r="B414" s="1"/>
+      <c r="C414" s="1"/>
+      <c r="D414" s="1"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="3"/>
+      <c r="B415" s="1"/>
+      <c r="C415" s="1"/>
+      <c r="D415" s="1"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="3"/>
+      <c r="B416" s="1"/>
+      <c r="C416" s="1"/>
+      <c r="D416" s="1"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="3"/>
+      <c r="B417" s="1"/>
+      <c r="C417" s="1"/>
+      <c r="D417" s="1"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="3"/>
+      <c r="B418" s="1"/>
+      <c r="C418" s="1"/>
+      <c r="D418" s="1"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="3"/>
+      <c r="B419" s="1"/>
+      <c r="C419" s="1"/>
+      <c r="D419" s="1"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="3"/>
+      <c r="B420" s="1"/>
+      <c r="C420" s="1"/>
+      <c r="D420" s="1"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="3"/>
+      <c r="B421" s="1"/>
+      <c r="C421" s="1"/>
+      <c r="D421" s="1"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="3"/>
+      <c r="B422" s="1"/>
+      <c r="C422" s="1"/>
+      <c r="D422" s="1"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="3"/>
+      <c r="B423" s="1"/>
+      <c r="C423" s="1"/>
+      <c r="D423" s="1"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="3"/>
+      <c r="B424" s="1"/>
+      <c r="C424" s="1"/>
+      <c r="D424" s="1"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="3"/>
+      <c r="B425" s="1"/>
+      <c r="C425" s="1"/>
+      <c r="D425" s="1"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="3"/>
+      <c r="B426" s="1"/>
+      <c r="C426" s="1"/>
+      <c r="D426" s="1"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="3"/>
+      <c r="B427" s="1"/>
+      <c r="C427" s="1"/>
+      <c r="D427" s="1"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="3"/>
+      <c r="B428" s="1"/>
+      <c r="C428" s="1"/>
+      <c r="D428" s="1"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="3"/>
+      <c r="B429" s="1"/>
+      <c r="C429" s="1"/>
+      <c r="D429" s="1"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="3"/>
+      <c r="B430" s="1"/>
+      <c r="C430" s="1"/>
+      <c r="D430" s="1"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="3"/>
+      <c r="B431" s="1"/>
+      <c r="C431" s="1"/>
+      <c r="D431" s="1"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="3"/>
+      <c r="B432" s="1"/>
+      <c r="C432" s="1"/>
+      <c r="D432" s="1"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="3"/>
+      <c r="B433" s="1"/>
+      <c r="C433" s="1"/>
+      <c r="D433" s="1"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="3"/>
+      <c r="B434" s="1"/>
+      <c r="C434" s="1"/>
+      <c r="D434" s="1"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="3"/>
+      <c r="B435" s="1"/>
+      <c r="C435" s="1"/>
+      <c r="D435" s="1"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="3"/>
+      <c r="B436" s="1"/>
+      <c r="C436" s="1"/>
+      <c r="D436" s="1"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="3"/>
+      <c r="B437" s="1"/>
+      <c r="C437" s="1"/>
+      <c r="D437" s="1"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="3"/>
+      <c r="B438" s="1"/>
+      <c r="C438" s="1"/>
+      <c r="D438" s="1"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="3"/>
+      <c r="B439" s="1"/>
+      <c r="C439" s="1"/>
+      <c r="D439" s="1"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="3"/>
+      <c r="B440" s="1"/>
+      <c r="C440" s="1"/>
+      <c r="D440" s="1"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="3"/>
+      <c r="B441" s="1"/>
+      <c r="C441" s="1"/>
+      <c r="D441" s="1"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="3"/>
+      <c r="B442" s="1"/>
+      <c r="C442" s="1"/>
+      <c r="D442" s="1"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="3"/>
+      <c r="B443" s="1"/>
+      <c r="C443" s="1"/>
+      <c r="D443" s="1"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="3"/>
+      <c r="B444" s="1"/>
+      <c r="C444" s="1"/>
+      <c r="D444" s="1"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="3"/>
+      <c r="B445" s="1"/>
+      <c r="C445" s="1"/>
+      <c r="D445" s="1"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="3"/>
+      <c r="B446" s="1"/>
+      <c r="C446" s="1"/>
+      <c r="D446" s="1"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="3"/>
+      <c r="B447" s="1"/>
+      <c r="C447" s="1"/>
+      <c r="D447" s="1"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="3"/>
+      <c r="B448" s="1"/>
+      <c r="C448" s="1"/>
+      <c r="D448" s="1"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="3"/>
+      <c r="B449" s="1"/>
+      <c r="C449" s="1"/>
+      <c r="D449" s="1"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="3"/>
+      <c r="B450" s="1"/>
+      <c r="C450" s="1"/>
+      <c r="D450" s="1"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="3"/>
+      <c r="B451" s="1"/>
+      <c r="C451" s="1"/>
+      <c r="D451" s="1"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="3"/>
+      <c r="B452" s="1"/>
+      <c r="C452" s="1"/>
+      <c r="D452" s="1"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="3"/>
+      <c r="B453" s="1"/>
+      <c r="C453" s="1"/>
+      <c r="D453" s="1"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="3"/>
+      <c r="B454" s="1"/>
+      <c r="C454" s="1"/>
+      <c r="D454" s="1"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="3"/>
+      <c r="B455" s="1"/>
+      <c r="C455" s="1"/>
+      <c r="D455" s="1"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="3"/>
+      <c r="B456" s="1"/>
+      <c r="C456" s="1"/>
+      <c r="D456" s="1"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="3"/>
+      <c r="B457" s="1"/>
+      <c r="C457" s="1"/>
+      <c r="D457" s="1"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="3"/>
+      <c r="B458" s="1"/>
+      <c r="C458" s="1"/>
+      <c r="D458" s="1"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="3"/>
+      <c r="B459" s="1"/>
+      <c r="C459" s="1"/>
+      <c r="D459" s="1"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="3"/>
+      <c r="B460" s="1"/>
+      <c r="C460" s="1"/>
+      <c r="D460" s="1"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="3"/>
+      <c r="B461" s="1"/>
+      <c r="C461" s="1"/>
+      <c r="D461" s="1"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="3"/>
+      <c r="B462" s="1"/>
+      <c r="C462" s="1"/>
+      <c r="D462" s="1"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="3"/>
+      <c r="B463" s="1"/>
+      <c r="C463" s="1"/>
+      <c r="D463" s="1"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="3"/>
+      <c r="B464" s="1"/>
+      <c r="C464" s="1"/>
+      <c r="D464" s="1"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="3"/>
+      <c r="B465" s="1"/>
+      <c r="C465" s="1"/>
+      <c r="D465" s="1"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="3"/>
+      <c r="B466" s="1"/>
+      <c r="C466" s="1"/>
+      <c r="D466" s="1"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="3"/>
+      <c r="B467" s="1"/>
+      <c r="C467" s="1"/>
+      <c r="D467" s="1"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="3"/>
+      <c r="B468" s="1"/>
+      <c r="C468" s="1"/>
+      <c r="D468" s="1"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="3"/>
+      <c r="B469" s="1"/>
+      <c r="C469" s="1"/>
+      <c r="D469" s="1"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="3"/>
+      <c r="B470" s="1"/>
+      <c r="C470" s="1"/>
+      <c r="D470" s="1"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="3"/>
+      <c r="B471" s="1"/>
+      <c r="C471" s="1"/>
+      <c r="D471" s="1"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="3"/>
+      <c r="B472" s="1"/>
+      <c r="C472" s="1"/>
+      <c r="D472" s="1"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="3"/>
+      <c r="B473" s="1"/>
+      <c r="C473" s="1"/>
+      <c r="D473" s="1"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="3"/>
+      <c r="B474" s="1"/>
+      <c r="C474" s="1"/>
+      <c r="D474" s="1"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="3"/>
+      <c r="B475" s="1"/>
+      <c r="C475" s="1"/>
+      <c r="D475" s="1"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="3"/>
+      <c r="B476" s="1"/>
+      <c r="C476" s="1"/>
+      <c r="D476" s="1"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="3"/>
+      <c r="B477" s="1"/>
+      <c r="C477" s="1"/>
+      <c r="D477" s="1"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="3"/>
+      <c r="B478" s="1"/>
+      <c r="C478" s="1"/>
+      <c r="D478" s="1"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="3"/>
+      <c r="B479" s="1"/>
+      <c r="C479" s="1"/>
+      <c r="D479" s="1"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="3"/>
+      <c r="B480" s="1"/>
+      <c r="C480" s="1"/>
+      <c r="D480" s="1"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="3"/>
+      <c r="B481" s="1"/>
+      <c r="C481" s="1"/>
+      <c r="D481" s="1"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="3"/>
+      <c r="B482" s="1"/>
+      <c r="C482" s="1"/>
+      <c r="D482" s="1"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="3"/>
+      <c r="B483" s="1"/>
+      <c r="C483" s="1"/>
+      <c r="D483" s="1"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="3"/>
+      <c r="B484" s="1"/>
+      <c r="C484" s="1"/>
+      <c r="D484" s="1"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="3"/>
+      <c r="B485" s="1"/>
+      <c r="C485" s="1"/>
+      <c r="D485" s="1"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="3"/>
+      <c r="B486" s="1"/>
+      <c r="C486" s="1"/>
+      <c r="D486" s="1"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="3"/>
+      <c r="B487" s="1"/>
+      <c r="C487" s="1"/>
+      <c r="D487" s="1"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="3"/>
+      <c r="B488" s="1"/>
+      <c r="C488" s="1"/>
+      <c r="D488" s="1"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="3"/>
+      <c r="B489" s="1"/>
+      <c r="C489" s="1"/>
+      <c r="D489" s="1"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="3"/>
+      <c r="B490" s="1"/>
+      <c r="C490" s="1"/>
+      <c r="D490" s="1"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="3"/>
+      <c r="B491" s="1"/>
+      <c r="C491" s="1"/>
+      <c r="D491" s="1"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="3"/>
+      <c r="B492" s="1"/>
+      <c r="C492" s="1"/>
+      <c r="D492" s="1"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="3"/>
+      <c r="B493" s="1"/>
+      <c r="C493" s="1"/>
+      <c r="D493" s="1"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="3"/>
+      <c r="B494" s="1"/>
+      <c r="C494" s="1"/>
+      <c r="D494" s="1"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="3"/>
+      <c r="B495" s="1"/>
+      <c r="C495" s="1"/>
+      <c r="D495" s="1"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="3"/>
+      <c r="B496" s="1"/>
+      <c r="C496" s="1"/>
+      <c r="D496" s="1"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="3"/>
+      <c r="B497" s="1"/>
+      <c r="C497" s="1"/>
+      <c r="D497" s="1"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="3"/>
+      <c r="B498" s="1"/>
+      <c r="C498" s="1"/>
+      <c r="D498" s="1"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="3"/>
+      <c r="B499" s="1"/>
+      <c r="C499" s="1"/>
+      <c r="D499" s="1"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="3"/>
+      <c r="B500" s="1"/>
+      <c r="C500" s="1"/>
+      <c r="D500" s="1"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="3"/>
+      <c r="B501" s="1"/>
+      <c r="C501" s="1"/>
+      <c r="D501" s="1"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="3"/>
+      <c r="B502" s="1"/>
+      <c r="C502" s="1"/>
+      <c r="D502" s="1"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="3"/>
+      <c r="B503" s="1"/>
+      <c r="C503" s="1"/>
+      <c r="D503" s="1"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="3"/>
+      <c r="B504" s="1"/>
+      <c r="C504" s="1"/>
+      <c r="D504" s="1"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="3"/>
+      <c r="B505" s="1"/>
+      <c r="C505" s="1"/>
+      <c r="D505" s="1"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="3"/>
+      <c r="B506" s="1"/>
+      <c r="C506" s="1"/>
+      <c r="D506" s="1"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="3"/>
+      <c r="B507" s="1"/>
+      <c r="C507" s="1"/>
+      <c r="D507" s="1"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="3"/>
+      <c r="B508" s="1"/>
+      <c r="C508" s="1"/>
+      <c r="D508" s="1"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="3"/>
+      <c r="B509" s="1"/>
+      <c r="C509" s="1"/>
+      <c r="D509" s="1"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="3"/>
+      <c r="B510" s="1"/>
+      <c r="C510" s="1"/>
+      <c r="D510" s="1"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="3"/>
+      <c r="B511" s="1"/>
+      <c r="C511" s="1"/>
+      <c r="D511" s="1"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="3"/>
+      <c r="B512" s="1"/>
+      <c r="C512" s="1"/>
+      <c r="D512" s="1"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="3"/>
+      <c r="B513" s="1"/>
+      <c r="C513" s="1"/>
+      <c r="D513" s="1"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="3"/>
+      <c r="B514" s="1"/>
+      <c r="C514" s="1"/>
+      <c r="D514" s="1"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="3"/>
+      <c r="B515" s="1"/>
+      <c r="C515" s="1"/>
+      <c r="D515" s="1"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="3"/>
+      <c r="B516" s="1"/>
+      <c r="C516" s="1"/>
+      <c r="D516" s="1"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="3"/>
+      <c r="B517" s="1"/>
+      <c r="C517" s="1"/>
+      <c r="D517" s="1"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="3"/>
+      <c r="B518" s="1"/>
+      <c r="C518" s="1"/>
+      <c r="D518" s="1"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="3"/>
+      <c r="B519" s="1"/>
+      <c r="C519" s="1"/>
+      <c r="D519" s="1"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="3"/>
+      <c r="B520" s="1"/>
+      <c r="C520" s="1"/>
+      <c r="D520" s="1"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="3"/>
+      <c r="B521" s="1"/>
+      <c r="C521" s="1"/>
+      <c r="D521" s="1"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="3"/>
+      <c r="B522" s="1"/>
+      <c r="C522" s="1"/>
+      <c r="D522" s="1"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="3"/>
+      <c r="B523" s="1"/>
+      <c r="C523" s="1"/>
+      <c r="D523" s="1"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="3"/>
+      <c r="B524" s="1"/>
+      <c r="C524" s="1"/>
+      <c r="D524" s="1"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="3"/>
+      <c r="B525" s="1"/>
+      <c r="C525" s="1"/>
+      <c r="D525" s="1"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="3"/>
+      <c r="B526" s="1"/>
+      <c r="C526" s="1"/>
+      <c r="D526" s="1"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="3"/>
+      <c r="B527" s="1"/>
+      <c r="C527" s="1"/>
+      <c r="D527" s="1"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="3"/>
+      <c r="B528" s="1"/>
+      <c r="C528" s="1"/>
+      <c r="D528" s="1"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="3"/>
+      <c r="B529" s="1"/>
+      <c r="C529" s="1"/>
+      <c r="D529" s="1"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="3"/>
+      <c r="B530" s="1"/>
+      <c r="C530" s="1"/>
+      <c r="D530" s="1"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="3"/>
+      <c r="B531" s="1"/>
+      <c r="C531" s="1"/>
+      <c r="D531" s="1"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="3"/>
+      <c r="B532" s="1"/>
+      <c r="C532" s="1"/>
+      <c r="D532" s="1"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="3"/>
+      <c r="B533" s="1"/>
+      <c r="C533" s="1"/>
+      <c r="D533" s="1"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="3"/>
+      <c r="B534" s="1"/>
+      <c r="C534" s="1"/>
+      <c r="D534" s="1"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="3"/>
+      <c r="B535" s="1"/>
+      <c r="C535" s="1"/>
+      <c r="D535" s="1"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="3"/>
+      <c r="B536" s="1"/>
+      <c r="C536" s="1"/>
+      <c r="D536" s="1"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="3"/>
+      <c r="B537" s="1"/>
+      <c r="C537" s="1"/>
+      <c r="D537" s="1"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="3"/>
+      <c r="B538" s="1"/>
+      <c r="C538" s="1"/>
+      <c r="D538" s="1"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="3"/>
+      <c r="B539" s="1"/>
+      <c r="C539" s="1"/>
+      <c r="D539" s="1"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="3"/>
+      <c r="B540" s="1"/>
+      <c r="C540" s="1"/>
+      <c r="D540" s="1"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="3"/>
+      <c r="B541" s="1"/>
+      <c r="C541" s="1"/>
+      <c r="D541" s="1"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="3"/>
+      <c r="B542" s="1"/>
+      <c r="C542" s="1"/>
+      <c r="D542" s="1"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="3"/>
+      <c r="B543" s="1"/>
+      <c r="C543" s="1"/>
+      <c r="D543" s="1"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="3"/>
+      <c r="B544" s="1"/>
+      <c r="C544" s="1"/>
+      <c r="D544" s="1"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="3"/>
+      <c r="B545" s="1"/>
+      <c r="C545" s="1"/>
+      <c r="D545" s="1"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="3"/>
+      <c r="B546" s="1"/>
+      <c r="C546" s="1"/>
+      <c r="D546" s="1"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="3"/>
+      <c r="B547" s="1"/>
+      <c r="C547" s="1"/>
+      <c r="D547" s="1"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="3"/>
+      <c r="B548" s="1"/>
+      <c r="C548" s="1"/>
+      <c r="D548" s="1"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="3"/>
+      <c r="B549" s="1"/>
+      <c r="C549" s="1"/>
+      <c r="D549" s="1"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="3"/>
+      <c r="B550" s="1"/>
+      <c r="C550" s="1"/>
+      <c r="D550" s="1"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="3"/>
+      <c r="B551" s="1"/>
+      <c r="C551" s="1"/>
+      <c r="D551" s="1"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="3"/>
+      <c r="B552" s="1"/>
+      <c r="C552" s="1"/>
+      <c r="D552" s="1"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="3"/>
+      <c r="B553" s="1"/>
+      <c r="C553" s="1"/>
+      <c r="D553" s="1"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="3"/>
+      <c r="B554" s="1"/>
+      <c r="C554" s="1"/>
+      <c r="D554" s="1"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="3"/>
+      <c r="B555" s="1"/>
+      <c r="C555" s="1"/>
+      <c r="D555" s="1"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="3"/>
+      <c r="B556" s="1"/>
+      <c r="C556" s="1"/>
+      <c r="D556" s="1"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="3"/>
+      <c r="B557" s="1"/>
+      <c r="C557" s="1"/>
+      <c r="D557" s="1"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="3"/>
+      <c r="B558" s="1"/>
+      <c r="C558" s="1"/>
+      <c r="D558" s="1"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="3"/>
+      <c r="B559" s="1"/>
+      <c r="C559" s="1"/>
+      <c r="D559" s="1"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="3"/>
+      <c r="B560" s="1"/>
+      <c r="C560" s="1"/>
+      <c r="D560" s="1"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="3"/>
+      <c r="B561" s="1"/>
+      <c r="C561" s="1"/>
+      <c r="D561" s="1"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="3"/>
+      <c r="B562" s="1"/>
+      <c r="C562" s="1"/>
+      <c r="D562" s="1"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="3"/>
+      <c r="B563" s="1"/>
+      <c r="C563" s="1"/>
+      <c r="D563" s="1"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="3"/>
+      <c r="B564" s="1"/>
+      <c r="C564" s="1"/>
+      <c r="D564" s="1"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="3"/>
+      <c r="B565" s="1"/>
+      <c r="C565" s="1"/>
+      <c r="D565" s="1"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="3"/>
+      <c r="B566" s="1"/>
+      <c r="C566" s="1"/>
+      <c r="D566" s="1"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="3"/>
+      <c r="B567" s="1"/>
+      <c r="C567" s="1"/>
+      <c r="D567" s="1"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="3"/>
+      <c r="B568" s="1"/>
+      <c r="C568" s="1"/>
+      <c r="D568" s="1"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="3"/>
+      <c r="B569" s="1"/>
+      <c r="C569" s="1"/>
+      <c r="D569" s="1"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="3"/>
+      <c r="B570" s="1"/>
+      <c r="C570" s="1"/>
+      <c r="D570" s="1"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="3"/>
+      <c r="B571" s="1"/>
+      <c r="C571" s="1"/>
+      <c r="D571" s="1"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="3"/>
+      <c r="B572" s="1"/>
+      <c r="C572" s="1"/>
+      <c r="D572" s="1"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="3"/>
+      <c r="B573" s="1"/>
+      <c r="C573" s="1"/>
+      <c r="D573" s="1"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="3"/>
+      <c r="B574" s="1"/>
+      <c r="C574" s="1"/>
+      <c r="D574" s="1"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="3"/>
+      <c r="B575" s="1"/>
+      <c r="C575" s="1"/>
+      <c r="D575" s="1"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="3"/>
+      <c r="B576" s="1"/>
+      <c r="C576" s="1"/>
+      <c r="D576" s="1"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="3"/>
+      <c r="B577" s="1"/>
+      <c r="C577" s="1"/>
+      <c r="D577" s="1"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="3"/>
+      <c r="B578" s="1"/>
+      <c r="C578" s="1"/>
+      <c r="D578" s="1"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="3"/>
+      <c r="B579" s="1"/>
+      <c r="C579" s="1"/>
+      <c r="D579" s="1"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="3"/>
+      <c r="B580" s="1"/>
+      <c r="C580" s="1"/>
+      <c r="D580" s="1"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="3"/>
+      <c r="B581" s="1"/>
+      <c r="C581" s="1"/>
+      <c r="D581" s="1"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="3"/>
+      <c r="B582" s="1"/>
+      <c r="C582" s="1"/>
+      <c r="D582" s="1"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="3"/>
+      <c r="B583" s="1"/>
+      <c r="C583" s="1"/>
+      <c r="D583" s="1"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="3"/>
+      <c r="B584" s="1"/>
+      <c r="C584" s="1"/>
+      <c r="D584" s="1"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="3"/>
+      <c r="B585" s="1"/>
+      <c r="C585" s="1"/>
+      <c r="D585" s="1"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="3"/>
+      <c r="B586" s="1"/>
+      <c r="C586" s="1"/>
+      <c r="D586" s="1"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="3"/>
+      <c r="B587" s="1"/>
+      <c r="C587" s="1"/>
+      <c r="D587" s="1"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="3"/>
+      <c r="B588" s="1"/>
+      <c r="C588" s="1"/>
+      <c r="D588" s="1"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="3"/>
+      <c r="B589" s="1"/>
+      <c r="C589" s="1"/>
+      <c r="D589" s="1"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="3"/>
+      <c r="B590" s="1"/>
+      <c r="C590" s="1"/>
+      <c r="D590" s="1"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="3"/>
+      <c r="B591" s="1"/>
+      <c r="C591" s="1"/>
+      <c r="D591" s="1"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="3"/>
+      <c r="B592" s="1"/>
+      <c r="C592" s="1"/>
+      <c r="D592" s="1"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="3"/>
+      <c r="B593" s="1"/>
+      <c r="C593" s="1"/>
+      <c r="D593" s="1"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="3"/>
+      <c r="B594" s="1"/>
+      <c r="C594" s="1"/>
+      <c r="D594" s="1"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="3"/>
+      <c r="B595" s="1"/>
+      <c r="C595" s="1"/>
+      <c r="D595" s="1"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="3"/>
+      <c r="B596" s="1"/>
+      <c r="C596" s="1"/>
+      <c r="D596" s="1"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="3"/>
+      <c r="B597" s="1"/>
+      <c r="C597" s="1"/>
+      <c r="D597" s="1"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="3"/>
+      <c r="B598" s="1"/>
+      <c r="C598" s="1"/>
+      <c r="D598" s="1"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="3"/>
+      <c r="B599" s="1"/>
+      <c r="C599" s="1"/>
+      <c r="D599" s="1"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="3"/>
+      <c r="B600" s="1"/>
+      <c r="C600" s="1"/>
+      <c r="D600" s="1"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="3"/>
+      <c r="B601" s="1"/>
+      <c r="C601" s="1"/>
+      <c r="D601" s="1"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="3"/>
+      <c r="B602" s="1"/>
+      <c r="C602" s="1"/>
+      <c r="D602" s="1"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="3"/>
+      <c r="B603" s="1"/>
+      <c r="C603" s="1"/>
+      <c r="D603" s="1"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="3"/>
+      <c r="B604" s="1"/>
+      <c r="C604" s="1"/>
+      <c r="D604" s="1"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="3"/>
+      <c r="B605" s="1"/>
+      <c r="C605" s="1"/>
+      <c r="D605" s="1"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="3"/>
+      <c r="B606" s="1"/>
+      <c r="C606" s="1"/>
+      <c r="D606" s="1"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="3"/>
+      <c r="B607" s="1"/>
+      <c r="C607" s="1"/>
+      <c r="D607" s="1"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="3"/>
+      <c r="B608" s="1"/>
+      <c r="C608" s="1"/>
+      <c r="D608" s="1"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="3"/>
+      <c r="B609" s="1"/>
+      <c r="C609" s="1"/>
+      <c r="D609" s="1"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="3"/>
+      <c r="B610" s="1"/>
+      <c r="C610" s="1"/>
+      <c r="D610" s="1"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="3"/>
+      <c r="B611" s="1"/>
+      <c r="C611" s="1"/>
+      <c r="D611" s="1"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="3"/>
+      <c r="B612" s="1"/>
+      <c r="C612" s="1"/>
+      <c r="D612" s="1"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="3"/>
+      <c r="B613" s="1"/>
+      <c r="C613" s="1"/>
+      <c r="D613" s="1"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="3"/>
+      <c r="B614" s="1"/>
+      <c r="C614" s="1"/>
+      <c r="D614" s="1"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="3"/>
+      <c r="B615" s="1"/>
+      <c r="C615" s="1"/>
+      <c r="D615" s="1"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="3"/>
+      <c r="B616" s="1"/>
+      <c r="C616" s="1"/>
+      <c r="D616" s="1"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="3"/>
+      <c r="B617" s="1"/>
+      <c r="C617" s="1"/>
+      <c r="D617" s="1"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="3"/>
+      <c r="B618" s="1"/>
+      <c r="C618" s="1"/>
+      <c r="D618" s="1"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="3"/>
+      <c r="B619" s="1"/>
+      <c r="C619" s="1"/>
+      <c r="D619" s="1"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="3"/>
+      <c r="B620" s="1"/>
+      <c r="C620" s="1"/>
+      <c r="D620" s="1"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="3"/>
+      <c r="B621" s="1"/>
+      <c r="C621" s="1"/>
+      <c r="D621" s="1"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="3"/>
+      <c r="B622" s="1"/>
+      <c r="C622" s="1"/>
+      <c r="D622" s="1"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="3"/>
+      <c r="B623" s="1"/>
+      <c r="C623" s="1"/>
+      <c r="D623" s="1"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="3"/>
+      <c r="B624" s="1"/>
+      <c r="C624" s="1"/>
+      <c r="D624" s="1"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="3"/>
+      <c r="B625" s="1"/>
+      <c r="C625" s="1"/>
+      <c r="D625" s="1"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="3"/>
+      <c r="B626" s="1"/>
+      <c r="C626" s="1"/>
+      <c r="D626" s="1"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="3"/>
+      <c r="B627" s="1"/>
+      <c r="C627" s="1"/>
+      <c r="D627" s="1"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="3"/>
+      <c r="B628" s="1"/>
+      <c r="C628" s="1"/>
+      <c r="D628" s="1"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="3"/>
+      <c r="B629" s="1"/>
+      <c r="C629" s="1"/>
+      <c r="D629" s="1"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="3"/>
+      <c r="B630" s="1"/>
+      <c r="C630" s="1"/>
+      <c r="D630" s="1"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="3"/>
+      <c r="B631" s="1"/>
+      <c r="C631" s="1"/>
+      <c r="D631" s="1"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="3"/>
+      <c r="B632" s="1"/>
+      <c r="C632" s="1"/>
+      <c r="D632" s="1"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="3"/>
+      <c r="B633" s="1"/>
+      <c r="C633" s="1"/>
+      <c r="D633" s="1"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="3"/>
+      <c r="B634" s="1"/>
+      <c r="C634" s="1"/>
+      <c r="D634" s="1"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="3"/>
+      <c r="B635" s="1"/>
+      <c r="C635" s="1"/>
+      <c r="D635" s="1"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="3"/>
+      <c r="B636" s="1"/>
+      <c r="C636" s="1"/>
+      <c r="D636" s="1"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="3"/>
+      <c r="B637" s="1"/>
+      <c r="C637" s="1"/>
+      <c r="D637" s="1"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="3"/>
+      <c r="B638" s="1"/>
+      <c r="C638" s="1"/>
+      <c r="D638" s="1"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="3"/>
+      <c r="B639" s="1"/>
+      <c r="C639" s="1"/>
+      <c r="D639" s="1"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="3"/>
+      <c r="B640" s="1"/>
+      <c r="C640" s="1"/>
+      <c r="D640" s="1"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="3"/>
+      <c r="B641" s="1"/>
+      <c r="C641" s="1"/>
+      <c r="D641" s="1"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="3"/>
+      <c r="B642" s="1"/>
+      <c r="C642" s="1"/>
+      <c r="D642" s="1"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="3"/>
+      <c r="B643" s="1"/>
+      <c r="C643" s="1"/>
+      <c r="D643" s="1"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="3"/>
+      <c r="B644" s="1"/>
+      <c r="C644" s="1"/>
+      <c r="D644" s="1"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="3"/>
+      <c r="B645" s="1"/>
+      <c r="C645" s="1"/>
+      <c r="D645" s="1"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="3"/>
+      <c r="B646" s="1"/>
+      <c r="C646" s="1"/>
+      <c r="D646" s="1"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="3"/>
+      <c r="B647" s="1"/>
+      <c r="C647" s="1"/>
+      <c r="D647" s="1"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="3"/>
+      <c r="B648" s="1"/>
+      <c r="C648" s="1"/>
+      <c r="D648" s="1"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="3"/>
+      <c r="B649" s="1"/>
+      <c r="C649" s="1"/>
+      <c r="D649" s="1"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="3"/>
+      <c r="B650" s="1"/>
+      <c r="C650" s="1"/>
+      <c r="D650" s="1"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="3"/>
+      <c r="B651" s="1"/>
+      <c r="C651" s="1"/>
+      <c r="D651" s="1"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="3"/>
+      <c r="B652" s="1"/>
+      <c r="C652" s="1"/>
+      <c r="D652" s="1"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="3"/>
+      <c r="B653" s="1"/>
+      <c r="C653" s="1"/>
+      <c r="D653" s="1"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="3"/>
+      <c r="B654" s="1"/>
+      <c r="C654" s="1"/>
+      <c r="D654" s="1"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="3"/>
+      <c r="B655" s="1"/>
+      <c r="C655" s="1"/>
+      <c r="D655" s="1"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="3"/>
+      <c r="B656" s="1"/>
+      <c r="C656" s="1"/>
+      <c r="D656" s="1"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="3"/>
+      <c r="B657" s="1"/>
+      <c r="C657" s="1"/>
+      <c r="D657" s="1"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="3"/>
+      <c r="B658" s="1"/>
+      <c r="C658" s="1"/>
+      <c r="D658" s="1"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="3"/>
+      <c r="B659" s="1"/>
+      <c r="C659" s="1"/>
+      <c r="D659" s="1"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="3"/>
+      <c r="B660" s="1"/>
+      <c r="C660" s="1"/>
+      <c r="D660" s="1"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="3"/>
+      <c r="B661" s="1"/>
+      <c r="C661" s="1"/>
+      <c r="D661" s="1"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="3"/>
+      <c r="B662" s="1"/>
+      <c r="C662" s="1"/>
+      <c r="D662" s="1"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="3"/>
+      <c r="B663" s="1"/>
+      <c r="C663" s="1"/>
+      <c r="D663" s="1"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="3"/>
+      <c r="B664" s="1"/>
+      <c r="C664" s="1"/>
+      <c r="D664" s="1"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="3"/>
+      <c r="B665" s="1"/>
+      <c r="C665" s="1"/>
+      <c r="D665" s="1"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="3"/>
+      <c r="B666" s="1"/>
+      <c r="C666" s="1"/>
+      <c r="D666" s="1"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="3"/>
+      <c r="B667" s="1"/>
+      <c r="C667" s="1"/>
+      <c r="D667" s="1"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="3"/>
+      <c r="B668" s="1"/>
+      <c r="C668" s="1"/>
+      <c r="D668" s="1"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="3"/>
+      <c r="B669" s="1"/>
+      <c r="C669" s="1"/>
+      <c r="D669" s="1"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="3"/>
+      <c r="B670" s="1"/>
+      <c r="C670" s="1"/>
+      <c r="D670" s="1"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="3"/>
+      <c r="B671" s="1"/>
+      <c r="C671" s="1"/>
+      <c r="D671" s="1"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="3"/>
+      <c r="B672" s="1"/>
+      <c r="C672" s="1"/>
+      <c r="D672" s="1"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="3"/>
+      <c r="B673" s="1"/>
+      <c r="C673" s="1"/>
+      <c r="D673" s="1"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="3"/>
+      <c r="B674" s="1"/>
+      <c r="C674" s="1"/>
+      <c r="D674" s="1"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="3"/>
+      <c r="B675" s="1"/>
+      <c r="C675" s="1"/>
+      <c r="D675" s="1"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="3"/>
+      <c r="B676" s="1"/>
+      <c r="C676" s="1"/>
+      <c r="D676" s="1"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="3"/>
+      <c r="B677" s="1"/>
+      <c r="C677" s="1"/>
+      <c r="D677" s="1"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="3"/>
+      <c r="B678" s="1"/>
+      <c r="C678" s="1"/>
+      <c r="D678" s="1"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="3"/>
+      <c r="B679" s="1"/>
+      <c r="C679" s="1"/>
+      <c r="D679" s="1"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="3"/>
+      <c r="B680" s="1"/>
+      <c r="C680" s="1"/>
+      <c r="D680" s="1"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="3"/>
+      <c r="B681" s="1"/>
+      <c r="C681" s="1"/>
+      <c r="D681" s="1"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="3"/>
+      <c r="B682" s="1"/>
+      <c r="C682" s="1"/>
+      <c r="D682" s="1"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="3"/>
+      <c r="B683" s="1"/>
+      <c r="C683" s="1"/>
+      <c r="D683" s="1"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="3"/>
+      <c r="B684" s="1"/>
+      <c r="C684" s="1"/>
+      <c r="D684" s="1"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="3"/>
+      <c r="B685" s="1"/>
+      <c r="C685" s="1"/>
+      <c r="D685" s="1"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="3"/>
+      <c r="B686" s="1"/>
+      <c r="C686" s="1"/>
+      <c r="D686" s="1"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="3"/>
+      <c r="B687" s="1"/>
+      <c r="C687" s="1"/>
+      <c r="D687" s="1"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="3"/>
+      <c r="B688" s="1"/>
+      <c r="C688" s="1"/>
+      <c r="D688" s="1"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="3"/>
+      <c r="B689" s="1"/>
+      <c r="C689" s="1"/>
+      <c r="D689" s="1"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="3"/>
+      <c r="B690" s="1"/>
+      <c r="C690" s="1"/>
+      <c r="D690" s="1"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="3"/>
+      <c r="B691" s="1"/>
+      <c r="C691" s="1"/>
+      <c r="D691" s="1"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="3"/>
+      <c r="B692" s="1"/>
+      <c r="C692" s="1"/>
+      <c r="D692" s="1"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="3"/>
+      <c r="B693" s="1"/>
+      <c r="C693" s="1"/>
+      <c r="D693" s="1"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="3"/>
+      <c r="B694" s="1"/>
+      <c r="C694" s="1"/>
+      <c r="D694" s="1"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="3"/>
+      <c r="B695" s="1"/>
+      <c r="C695" s="1"/>
+      <c r="D695" s="1"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="3"/>
+      <c r="B696" s="1"/>
+      <c r="C696" s="1"/>
+      <c r="D696" s="1"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="3"/>
+      <c r="B697" s="1"/>
+      <c r="C697" s="1"/>
+      <c r="D697" s="1"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="3"/>
+      <c r="B698" s="1"/>
+      <c r="C698" s="1"/>
+      <c r="D698" s="1"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="3"/>
+      <c r="B699" s="1"/>
+      <c r="C699" s="1"/>
+      <c r="D699" s="1"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="3"/>
+      <c r="B700" s="1"/>
+      <c r="C700" s="1"/>
+      <c r="D700" s="1"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="3"/>
+      <c r="B701" s="1"/>
+      <c r="C701" s="1"/>
+      <c r="D701" s="1"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="3"/>
+      <c r="B702" s="1"/>
+      <c r="C702" s="1"/>
+      <c r="D702" s="1"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="3"/>
+      <c r="B703" s="1"/>
+      <c r="C703" s="1"/>
+      <c r="D703" s="1"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="3"/>
+      <c r="B704" s="1"/>
+      <c r="C704" s="1"/>
+      <c r="D704" s="1"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="3"/>
+      <c r="B705" s="1"/>
+      <c r="C705" s="1"/>
+      <c r="D705" s="1"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="3"/>
+      <c r="B706" s="1"/>
+      <c r="C706" s="1"/>
+      <c r="D706" s="1"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="3"/>
+      <c r="B707" s="1"/>
+      <c r="C707" s="1"/>
+      <c r="D707" s="1"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="3"/>
+      <c r="B708" s="1"/>
+      <c r="C708" s="1"/>
+      <c r="D708" s="1"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="3"/>
+      <c r="B709" s="1"/>
+      <c r="C709" s="1"/>
+      <c r="D709" s="1"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="3"/>
+      <c r="B710" s="1"/>
+      <c r="C710" s="1"/>
+      <c r="D710" s="1"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="3"/>
+      <c r="B711" s="1"/>
+      <c r="C711" s="1"/>
+      <c r="D711" s="1"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="3"/>
+      <c r="B712" s="1"/>
+      <c r="C712" s="1"/>
+      <c r="D712" s="1"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="3"/>
+      <c r="B713" s="1"/>
+      <c r="C713" s="1"/>
+      <c r="D713" s="1"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="3"/>
+      <c r="B714" s="1"/>
+      <c r="C714" s="1"/>
+      <c r="D714" s="1"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="3"/>
+      <c r="B715" s="1"/>
+      <c r="C715" s="1"/>
+      <c r="D715" s="1"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="3"/>
+      <c r="B716" s="1"/>
+      <c r="C716" s="1"/>
+      <c r="D716" s="1"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="3"/>
+      <c r="B717" s="1"/>
+      <c r="C717" s="1"/>
+      <c r="D717" s="1"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="3"/>
+      <c r="B718" s="1"/>
+      <c r="C718" s="1"/>
+      <c r="D718" s="1"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="3"/>
+      <c r="B719" s="1"/>
+      <c r="C719" s="1"/>
+      <c r="D719" s="1"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="3"/>
+      <c r="B720" s="1"/>
+      <c r="C720" s="1"/>
+      <c r="D720" s="1"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="3"/>
+      <c r="B721" s="1"/>
+      <c r="C721" s="1"/>
+      <c r="D721" s="1"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="3"/>
+      <c r="B722" s="1"/>
+      <c r="C722" s="1"/>
+      <c r="D722" s="1"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="3"/>
+      <c r="B723" s="1"/>
+      <c r="C723" s="1"/>
+      <c r="D723" s="1"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="3"/>
+      <c r="B724" s="1"/>
+      <c r="C724" s="1"/>
+      <c r="D724" s="1"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="3"/>
+      <c r="B725" s="1"/>
+      <c r="C725" s="1"/>
+      <c r="D725" s="1"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="3"/>
+      <c r="B726" s="1"/>
+      <c r="C726" s="1"/>
+      <c r="D726" s="1"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="3"/>
+      <c r="B727" s="1"/>
+      <c r="C727" s="1"/>
+      <c r="D727" s="1"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="3"/>
+      <c r="B728" s="1"/>
+      <c r="C728" s="1"/>
+      <c r="D728" s="1"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="3"/>
+      <c r="B729" s="1"/>
+      <c r="C729" s="1"/>
+      <c r="D729" s="1"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="3"/>
+      <c r="B730" s="1"/>
+      <c r="C730" s="1"/>
+      <c r="D730" s="1"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="3"/>
+      <c r="B731" s="1"/>
+      <c r="C731" s="1"/>
+      <c r="D731" s="1"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="3"/>
+      <c r="B732" s="1"/>
+      <c r="C732" s="1"/>
+      <c r="D732" s="1"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="3"/>
+      <c r="B733" s="1"/>
+      <c r="C733" s="1"/>
+      <c r="D733" s="1"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="3"/>
+      <c r="B734" s="1"/>
+      <c r="C734" s="1"/>
+      <c r="D734" s="1"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="3"/>
+      <c r="B735" s="1"/>
+      <c r="C735" s="1"/>
+      <c r="D735" s="1"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="3"/>
+      <c r="B736" s="1"/>
+      <c r="C736" s="1"/>
+      <c r="D736" s="1"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="3"/>
+      <c r="B737" s="1"/>
+      <c r="C737" s="1"/>
+      <c r="D737" s="1"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="3"/>
+      <c r="B738" s="1"/>
+      <c r="C738" s="1"/>
+      <c r="D738" s="1"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="3"/>
+      <c r="B739" s="1"/>
+      <c r="C739" s="1"/>
+      <c r="D739" s="1"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="3"/>
+      <c r="B740" s="1"/>
+      <c r="C740" s="1"/>
+      <c r="D740" s="1"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="3"/>
+      <c r="B741" s="1"/>
+      <c r="C741" s="1"/>
+      <c r="D741" s="1"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="3"/>
+      <c r="B742" s="1"/>
+      <c r="C742" s="1"/>
+      <c r="D742" s="1"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="3"/>
+      <c r="B743" s="1"/>
+      <c r="C743" s="1"/>
+      <c r="D743" s="1"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="3"/>
+      <c r="B744" s="1"/>
+      <c r="C744" s="1"/>
+      <c r="D744" s="1"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="3"/>
+      <c r="B745" s="1"/>
+      <c r="C745" s="1"/>
+      <c r="D745" s="1"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="3"/>
+      <c r="B746" s="1"/>
+      <c r="C746" s="1"/>
+      <c r="D746" s="1"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="3"/>
+      <c r="B747" s="1"/>
+      <c r="C747" s="1"/>
+      <c r="D747" s="1"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="3"/>
+      <c r="B748" s="1"/>
+      <c r="C748" s="1"/>
+      <c r="D748" s="1"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="3"/>
+      <c r="B749" s="1"/>
+      <c r="C749" s="1"/>
+      <c r="D749" s="1"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="3"/>
+      <c r="B750" s="1"/>
+      <c r="C750" s="1"/>
+      <c r="D750" s="1"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="3"/>
+      <c r="B751" s="1"/>
+      <c r="C751" s="1"/>
+      <c r="D751" s="1"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="3"/>
+      <c r="B752" s="1"/>
+      <c r="C752" s="1"/>
+      <c r="D752" s="1"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="3"/>
+      <c r="B753" s="1"/>
+      <c r="C753" s="1"/>
+      <c r="D753" s="1"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="3"/>
+      <c r="B754" s="1"/>
+      <c r="C754" s="1"/>
+      <c r="D754" s="1"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="3"/>
+      <c r="B755" s="1"/>
+      <c r="C755" s="1"/>
+      <c r="D755" s="1"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="3"/>
+      <c r="B756" s="1"/>
+      <c r="C756" s="1"/>
+      <c r="D756" s="1"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="3"/>
+      <c r="B757" s="1"/>
+      <c r="C757" s="1"/>
+      <c r="D757" s="1"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="3"/>
+      <c r="B758" s="1"/>
+      <c r="C758" s="1"/>
+      <c r="D758" s="1"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="3"/>
+      <c r="B759" s="1"/>
+      <c r="C759" s="1"/>
+      <c r="D759" s="1"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="3"/>
+      <c r="B760" s="1"/>
+      <c r="C760" s="1"/>
+      <c r="D760" s="1"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="3"/>
+      <c r="B761" s="1"/>
+      <c r="C761" s="1"/>
+      <c r="D761" s="1"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="3"/>
+      <c r="B762" s="1"/>
+      <c r="C762" s="1"/>
+      <c r="D762" s="1"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="3"/>
+      <c r="B763" s="1"/>
+      <c r="C763" s="1"/>
+      <c r="D763" s="1"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="3"/>
+      <c r="B764" s="1"/>
+      <c r="C764" s="1"/>
+      <c r="D764" s="1"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="3"/>
+      <c r="B765" s="1"/>
+      <c r="C765" s="1"/>
+      <c r="D765" s="1"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="3"/>
+      <c r="B766" s="1"/>
+      <c r="C766" s="1"/>
+      <c r="D766" s="1"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="3"/>
+      <c r="B767" s="1"/>
+      <c r="C767" s="1"/>
+      <c r="D767" s="1"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="3"/>
+      <c r="B768" s="1"/>
+      <c r="C768" s="1"/>
+      <c r="D768" s="1"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="3"/>
+      <c r="B769" s="1"/>
+      <c r="C769" s="1"/>
+      <c r="D769" s="1"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="3"/>
+      <c r="B770" s="1"/>
+      <c r="C770" s="1"/>
+      <c r="D770" s="1"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="3"/>
+      <c r="B771" s="1"/>
+      <c r="C771" s="1"/>
+      <c r="D771" s="1"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="3"/>
+      <c r="B772" s="1"/>
+      <c r="C772" s="1"/>
+      <c r="D772" s="1"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="3"/>
+      <c r="B773" s="1"/>
+      <c r="C773" s="1"/>
+      <c r="D773" s="1"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="3"/>
+      <c r="B774" s="1"/>
+      <c r="C774" s="1"/>
+      <c r="D774" s="1"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="3"/>
+      <c r="B775" s="1"/>
+      <c r="C775" s="1"/>
+      <c r="D775" s="1"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="3"/>
+      <c r="B776" s="1"/>
+      <c r="C776" s="1"/>
+      <c r="D776" s="1"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="3"/>
+      <c r="B777" s="1"/>
+      <c r="C777" s="1"/>
+      <c r="D777" s="1"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="3"/>
+      <c r="B778" s="1"/>
+      <c r="C778" s="1"/>
+      <c r="D778" s="1"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="3"/>
+      <c r="B779" s="1"/>
+      <c r="C779" s="1"/>
+      <c r="D779" s="1"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="3"/>
+      <c r="B780" s="1"/>
+      <c r="C780" s="1"/>
+      <c r="D780" s="1"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="3"/>
+      <c r="B781" s="1"/>
+      <c r="C781" s="1"/>
+      <c r="D781" s="1"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="3"/>
+      <c r="B782" s="1"/>
+      <c r="C782" s="1"/>
+      <c r="D782" s="1"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="3"/>
+      <c r="B783" s="1"/>
+      <c r="C783" s="1"/>
+      <c r="D783" s="1"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="3"/>
+      <c r="B784" s="1"/>
+      <c r="C784" s="1"/>
+      <c r="D784" s="1"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="3"/>
+      <c r="B785" s="1"/>
+      <c r="C785" s="1"/>
+      <c r="D785" s="1"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="3"/>
+      <c r="B786" s="1"/>
+      <c r="C786" s="1"/>
+      <c r="D786" s="1"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="3"/>
+      <c r="B787" s="1"/>
+      <c r="C787" s="1"/>
+      <c r="D787" s="1"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="3"/>
+      <c r="B788" s="1"/>
+      <c r="C788" s="1"/>
+      <c r="D788" s="1"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="3"/>
+      <c r="B789" s="1"/>
+      <c r="C789" s="1"/>
+      <c r="D789" s="1"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="3"/>
+      <c r="B790" s="1"/>
+      <c r="C790" s="1"/>
+      <c r="D790" s="1"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="3"/>
+      <c r="B791" s="1"/>
+      <c r="C791" s="1"/>
+      <c r="D791" s="1"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="3"/>
+      <c r="B792" s="1"/>
+      <c r="C792" s="1"/>
+      <c r="D792" s="1"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="3"/>
+      <c r="B793" s="1"/>
+      <c r="C793" s="1"/>
+      <c r="D793" s="1"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="3"/>
+      <c r="B794" s="1"/>
+      <c r="C794" s="1"/>
+      <c r="D794" s="1"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="3"/>
+      <c r="B795" s="1"/>
+      <c r="C795" s="1"/>
+      <c r="D795" s="1"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="3"/>
+      <c r="B796" s="1"/>
+      <c r="C796" s="1"/>
+      <c r="D796" s="1"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="3"/>
+      <c r="B797" s="1"/>
+      <c r="C797" s="1"/>
+      <c r="D797" s="1"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="3"/>
+      <c r="B798" s="1"/>
+      <c r="C798" s="1"/>
+      <c r="D798" s="1"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="3"/>
+      <c r="B799" s="1"/>
+      <c r="C799" s="1"/>
+      <c r="D799" s="1"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="3"/>
+      <c r="B800" s="1"/>
+      <c r="C800" s="1"/>
+      <c r="D800" s="1"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="3"/>
+      <c r="B801" s="1"/>
+      <c r="C801" s="1"/>
+      <c r="D801" s="1"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="3"/>
+      <c r="B802" s="1"/>
+      <c r="C802" s="1"/>
+      <c r="D802" s="1"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="3"/>
+      <c r="B803" s="1"/>
+      <c r="C803" s="1"/>
+      <c r="D803" s="1"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="3"/>
+      <c r="B804" s="1"/>
+      <c r="C804" s="1"/>
+      <c r="D804" s="1"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="3"/>
+      <c r="B805" s="1"/>
+      <c r="C805" s="1"/>
+      <c r="D805" s="1"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="3"/>
+      <c r="B806" s="1"/>
+      <c r="C806" s="1"/>
+      <c r="D806" s="1"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="3"/>
+      <c r="B807" s="1"/>
+      <c r="C807" s="1"/>
+      <c r="D807" s="1"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="3"/>
+      <c r="B808" s="1"/>
+      <c r="C808" s="1"/>
+      <c r="D808" s="1"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="3"/>
+      <c r="B809" s="1"/>
+      <c r="C809" s="1"/>
+      <c r="D809" s="1"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="3"/>
+      <c r="B810" s="1"/>
+      <c r="C810" s="1"/>
+      <c r="D810" s="1"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="3"/>
+      <c r="B811" s="1"/>
+      <c r="C811" s="1"/>
+      <c r="D811" s="1"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="3"/>
+      <c r="B812" s="1"/>
+      <c r="C812" s="1"/>
+      <c r="D812" s="1"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="3"/>
+      <c r="B813" s="1"/>
+      <c r="C813" s="1"/>
+      <c r="D813" s="1"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="3"/>
+      <c r="B814" s="1"/>
+      <c r="C814" s="1"/>
+      <c r="D814" s="1"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="3"/>
+      <c r="B815" s="1"/>
+      <c r="C815" s="1"/>
+      <c r="D815" s="1"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="3"/>
+      <c r="B816" s="1"/>
+      <c r="C816" s="1"/>
+      <c r="D816" s="1"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="3"/>
+      <c r="B817" s="1"/>
+      <c r="C817" s="1"/>
+      <c r="D817" s="1"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="3"/>
+      <c r="B818" s="1"/>
+      <c r="C818" s="1"/>
+      <c r="D818" s="1"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="3"/>
+      <c r="B819" s="1"/>
+      <c r="C819" s="1"/>
+      <c r="D819" s="1"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="3"/>
+      <c r="B820" s="1"/>
+      <c r="C820" s="1"/>
+      <c r="D820" s="1"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="3"/>
+      <c r="B821" s="1"/>
+      <c r="C821" s="1"/>
+      <c r="D821" s="1"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="3"/>
+      <c r="B822" s="1"/>
+      <c r="C822" s="1"/>
+      <c r="D822" s="1"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="3"/>
+      <c r="B823" s="1"/>
+      <c r="C823" s="1"/>
+      <c r="D823" s="1"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="3"/>
+      <c r="B824" s="1"/>
+      <c r="C824" s="1"/>
+      <c r="D824" s="1"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="3"/>
+      <c r="B825" s="1"/>
+      <c r="C825" s="1"/>
+      <c r="D825" s="1"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="3"/>
+      <c r="B826" s="1"/>
+      <c r="C826" s="1"/>
+      <c r="D826" s="1"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="3"/>
+      <c r="B827" s="1"/>
+      <c r="C827" s="1"/>
+      <c r="D827" s="1"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="3"/>
+      <c r="B828" s="1"/>
+      <c r="C828" s="1"/>
+      <c r="D828" s="1"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="3"/>
+      <c r="B829" s="1"/>
+      <c r="C829" s="1"/>
+      <c r="D829" s="1"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="3"/>
+      <c r="B830" s="1"/>
+      <c r="C830" s="1"/>
+      <c r="D830" s="1"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="3"/>
+      <c r="B831" s="1"/>
+      <c r="C831" s="1"/>
+      <c r="D831" s="1"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="3"/>
+      <c r="B832" s="1"/>
+      <c r="C832" s="1"/>
+      <c r="D832" s="1"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="3"/>
+      <c r="B833" s="1"/>
+      <c r="C833" s="1"/>
+      <c r="D833" s="1"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="3"/>
+      <c r="B834" s="1"/>
+      <c r="C834" s="1"/>
+      <c r="D834" s="1"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="3"/>
+      <c r="B835" s="1"/>
+      <c r="C835" s="1"/>
+      <c r="D835" s="1"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="3"/>
+      <c r="B836" s="1"/>
+      <c r="C836" s="1"/>
+      <c r="D836" s="1"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="3"/>
+      <c r="B837" s="1"/>
+      <c r="C837" s="1"/>
+      <c r="D837" s="1"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="3"/>
+      <c r="B838" s="1"/>
+      <c r="C838" s="1"/>
+      <c r="D838" s="1"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="3"/>
+      <c r="B839" s="1"/>
+      <c r="C839" s="1"/>
+      <c r="D839" s="1"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="3"/>
+      <c r="B840" s="1"/>
+      <c r="C840" s="1"/>
+      <c r="D840" s="1"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="3"/>
+      <c r="B841" s="1"/>
+      <c r="C841" s="1"/>
+      <c r="D841" s="1"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="3"/>
+      <c r="B842" s="1"/>
+      <c r="C842" s="1"/>
+      <c r="D842" s="1"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="3"/>
+      <c r="B843" s="1"/>
+      <c r="C843" s="1"/>
+      <c r="D843" s="1"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="3"/>
+      <c r="B844" s="1"/>
+      <c r="C844" s="1"/>
+      <c r="D844" s="1"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="3"/>
+      <c r="B845" s="1"/>
+      <c r="C845" s="1"/>
+      <c r="D845" s="1"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="3"/>
+      <c r="B846" s="1"/>
+      <c r="C846" s="1"/>
+      <c r="D846" s="1"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="3"/>
+      <c r="B847" s="1"/>
+      <c r="C847" s="1"/>
+      <c r="D847" s="1"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="3"/>
+      <c r="B848" s="1"/>
+      <c r="C848" s="1"/>
+      <c r="D848" s="1"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="3"/>
+      <c r="B849" s="1"/>
+      <c r="C849" s="1"/>
+      <c r="D849" s="1"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="3"/>
+      <c r="B850" s="1"/>
+      <c r="C850" s="1"/>
+      <c r="D850" s="1"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="3"/>
+      <c r="B851" s="1"/>
+      <c r="C851" s="1"/>
+      <c r="D851" s="1"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="3"/>
+      <c r="B852" s="1"/>
+      <c r="C852" s="1"/>
+      <c r="D852" s="1"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="3"/>
+      <c r="B853" s="1"/>
+      <c r="C853" s="1"/>
+      <c r="D853" s="1"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="3"/>
+      <c r="B854" s="1"/>
+      <c r="C854" s="1"/>
+      <c r="D854" s="1"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="3"/>
+      <c r="B855" s="1"/>
+      <c r="C855" s="1"/>
+      <c r="D855" s="1"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="3"/>
+      <c r="B856" s="1"/>
+      <c r="C856" s="1"/>
+      <c r="D856" s="1"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="3"/>
+      <c r="B857" s="1"/>
+      <c r="C857" s="1"/>
+      <c r="D857" s="1"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="3"/>
+      <c r="B858" s="1"/>
+      <c r="C858" s="1"/>
+      <c r="D858" s="1"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="3"/>
+      <c r="B859" s="1"/>
+      <c r="C859" s="1"/>
+      <c r="D859" s="1"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="3"/>
+      <c r="B860" s="1"/>
+      <c r="C860" s="1"/>
+      <c r="D860" s="1"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="3"/>
+      <c r="B861" s="1"/>
+      <c r="C861" s="1"/>
+      <c r="D861" s="1"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="3"/>
+      <c r="B862" s="1"/>
+      <c r="C862" s="1"/>
+      <c r="D862" s="1"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="3"/>
+      <c r="B863" s="1"/>
+      <c r="C863" s="1"/>
+      <c r="D863" s="1"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="3"/>
+      <c r="B864" s="1"/>
+      <c r="C864" s="1"/>
+      <c r="D864" s="1"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="3"/>
+      <c r="B865" s="1"/>
+      <c r="C865" s="1"/>
+      <c r="D865" s="1"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>155.47769</v>
+        <v>146.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>152.16539</v>
+        <v>146.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>144.08</v>
+        <v>141.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>140.0</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>143.71</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>141.29</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>139.77</v>
+        <v>134.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>139.62</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>142.1</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>140.0</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>139.77</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>139.77</v>
+        <v>129.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>139.77</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>139.77</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>139.77</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>139.62</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>139.62</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>138.04</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>139.62</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>137.87</v>
+        <v>121.81</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>136.31</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>136.31</v>
+        <v>131.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>136.31</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>136.22</v>
+        <v>121.81</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>139.62</v>
+        <v>118.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>144.08</v>
+        <v>128.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>144.08</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>143.71</v>
+        <v>116.81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>158.80297</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>147.86402</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>147.82452</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>141.29</v>
+        <v>125.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>150.41315</v>
+        <v>118.85</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>151.99766</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>141.94133</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>141.9401</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>155.81801</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>145.95335</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>139.77</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>139.62</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>139.98425</v>
+        <v>107.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>139.92502</v>
+        <v>108.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>139.77</v>
+        <v>104.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>137.87</v>
+        <v>108.41</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>137.47</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>137.18</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>137.87</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>135.47545</v>
+        <v>100.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>136.2823</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>133.49</v>
+        <v>101.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>133.66</v>
+        <v>101.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>134.86</v>
+        <v>107.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>133.48</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>133.2192</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>135.91864</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>135.97898</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>135.98456</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>137.8316</v>
+        <v>60.81467</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>137.63979</v>
+        <v>73.57735</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>139.62</v>
+        <v>87.04</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>137.87</v>
+        <v>99.74704</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>139.62</v>
+        <v>106.47114</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>139.97149</v>
+        <v>114.97931</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>143.22123</v>
+        <v>117.75653</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>139.62</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>139.77</v>
+        <v>120.35</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>141.29</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>141.95638</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>139.77</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>139.77</v>
+        <v>124.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>143.6396</v>
+        <v>132.28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>151.54106</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>139.77</v>
+        <v>116.14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>144.74347</v>
+        <v>130.70501</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>172.94217</v>
+        <v>134.91</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>207.93923</v>
+        <v>141.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>158.70309</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>189.4795</v>
+        <v>154.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>244.11318</v>
+        <v>163.05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>255.78303</v>
+        <v>181.53</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>234.66526</v>
+        <v>163.91</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>233.72165</v>
+        <v>176.50022</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>254.91257</v>
+        <v>177.19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>243.86462</v>
+        <v>187.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>250.21256</v>
+        <v>177.19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>232.75707</v>
+        <v>177.27594</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>211.66</v>
+        <v>177.19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>194.74</v>
+        <v>173.54406</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>250.32911</v>
+        <v>176.78</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>201.78535</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>182.4432</v>
+        <v>165.66817</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>160.13984</v>
+        <v>151.85563</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>174.20296</v>
+        <v>154.82902</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>156.56539</v>
+        <v>142.32</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>145.74574</v>
+        <v>137.85944</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46199.0</v>
+        <v>46200.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,584 +1649,1352 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>139.62</v>
+        <v>134.80648</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+      <c r="A98" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D98" s="1">
+        <v>147.17</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="A99" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B99" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D99" s="1">
+        <v>137.91</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+      <c r="A100" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D100" s="1">
+        <v>137.91</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="3"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="A101" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B101" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D101" s="1">
+        <v>134.98843</v>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+      <c r="A102" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B102" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>134.93421</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
+      <c r="A103" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C103" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D103" s="1">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
+      <c r="A104" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C104" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D104" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="3"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
+      <c r="A105" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B105" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C105" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D105" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="3"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
+      <c r="A106" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C106" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="3"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="A107" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D107" s="1">
+        <v>132.4</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="3"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
+      <c r="A108" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C108" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D108" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="3"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
+      <c r="A109" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C109" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D109" s="1">
+        <v>125.73</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="3"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
+      <c r="A110" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="3"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
+      <c r="A111" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C111" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D111" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="3"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
+      <c r="A112" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D112" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="3"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
+      <c r="A113" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C113" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D113" s="1">
+        <v>128.83</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="3"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
+      <c r="A114" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B114" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C114" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D114" s="1">
+        <v>130.38</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="3"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
+      <c r="A115" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B115" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C115" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D115" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="3"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
+      <c r="A116" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C116" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>129.2</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="3"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
+      <c r="A117" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B117" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C117" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D117" s="1">
+        <v>129.07</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="3"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
+      <c r="A118" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C118" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D118" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="3"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
+      <c r="A119" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C119" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D119" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="3"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
+      <c r="A120" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C120" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D120" s="1">
+        <v>116.14</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="3"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
+      <c r="A121" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C121" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>116.14</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="3"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="A122" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B122" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D122" s="1">
+        <v>130.49</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="3"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+      <c r="A123" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B123" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D123" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="3"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+      <c r="A124" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C124" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>124.4</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="3"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="A125" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B125" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C125" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D125" s="1">
+        <v>119.11</v>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="3"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+      <c r="A126" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B126" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="3"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
+      <c r="A127" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B127" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C127" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D127" s="1">
+        <v>130.65</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="3"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
+      <c r="A128" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B128" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D128" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="3"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
+      <c r="A129" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B129" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D129" s="1">
+        <v>124.9</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="3"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
+      <c r="A130" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>132.4</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="3"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
+      <c r="A131" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B131" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C131" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D131" s="1">
+        <v>129.2</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="3"/>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+      <c r="A132" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B132" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C132" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D132" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="3"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+      <c r="A133" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B133" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C133" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D133" s="1">
+        <v>120.0</v>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="3"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+      <c r="A134" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B134" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D134" s="1">
+        <v>116.14</v>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="3"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
+      <c r="A135" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B135" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D135" s="1">
+        <v>116.14</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="3"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
+      <c r="A136" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B136" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C136" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>116.14</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="3"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="A137" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B137" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C137" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D137" s="1">
+        <v>111.58</v>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="3"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
+      <c r="A138" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B138" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C138" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>71.05</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="3"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
+      <c r="A139" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B139" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C139" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D139" s="1">
+        <v>66.0</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="3"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
+      <c r="A140" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B140" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C140" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>65.36</v>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="3"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="A141" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B141" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C141" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="3"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
+      <c r="A142" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B142" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="3"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
+      <c r="A143" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B143" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>50.0</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="3"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
+      <c r="A144" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B144" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="3"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
+      <c r="A145" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D145" s="1">
+        <v>79.0</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="3"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
+      <c r="A146" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B146" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D146" s="1">
+        <v>94.0</v>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="3"/>
-      <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
+      <c r="A147" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B147" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C147" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D147" s="1">
+        <v>90.93</v>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="3"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
+      <c r="A148" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B148" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C148" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D148" s="1">
+        <v>91.93</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="3"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
+      <c r="A149" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B149" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C149" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D149" s="1">
+        <v>93.11</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="3"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
+      <c r="A150" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B150" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C150" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D150" s="1">
+        <v>87.0</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="3"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
+      <c r="A151" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B151" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C151" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D151" s="1">
+        <v>89.75</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="3"/>
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
+      <c r="A152" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B152" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C152" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D152" s="1">
+        <v>90.93</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="3"/>
-      <c r="B153" s="1"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
+      <c r="A153" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B153" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C153" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D153" s="1">
+        <v>93.24</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="3"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
+      <c r="A154" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B154" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C154" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D154" s="1">
+        <v>90.0</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="3"/>
-      <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
+      <c r="A155" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B155" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C155" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D155" s="1">
+        <v>94.47</v>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="3"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+      <c r="A156" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B156" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C156" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D156" s="1">
+        <v>94.0</v>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="3"/>
-      <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
+      <c r="A157" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B157" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C157" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D157" s="1">
+        <v>66.0</v>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="3"/>
-      <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
+      <c r="A158" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B158" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C158" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D158" s="1">
+        <v>50.06</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="3"/>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
+      <c r="A159" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B159" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C159" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D159" s="1">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="3"/>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="A160" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C160" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D160" s="1">
+        <v>68.57</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="3"/>
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="A161" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B161" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C161" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D161" s="1">
+        <v>97.76</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="3"/>
-      <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="A162" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B162" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C162" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D162" s="1">
+        <v>111.48</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="3"/>
-      <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="A163" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B163" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C163" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>115.85</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="3"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="A164" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B164" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C164" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D164" s="1">
+        <v>129.2</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="3"/>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="A165" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B165" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C165" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="3"/>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="A166" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B166" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C166" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D166" s="1">
+        <v>120.5</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="3"/>
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="A167" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B167" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C167" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D167" s="1">
+        <v>131.75</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="3"/>
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="A168" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B168" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C168" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>132.78</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="3"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="A169" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B169" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C169" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D169" s="1">
+        <v>134.19</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="3"/>
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="A170" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B170" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C170" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>116.64</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="3"/>
-      <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="A171" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B171" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C171" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D171" s="1">
+        <v>133.1</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="3"/>
-      <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="A172" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B172" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C172" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D172" s="1">
+        <v>137.91</v>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="3"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="A173" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B173" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C173" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>147.17</v>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="3"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="A174" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B174" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C174" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D174" s="1">
+        <v>147.17</v>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="3"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="A175" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C175" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D175" s="1">
+        <v>151.66</v>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="3"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="A176" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B176" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C176" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>161.59</v>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="3"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="A177" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B177" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C177" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D177" s="1">
+        <v>175.63</v>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="3"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="A178" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B178" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C178" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>151.66</v>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="3"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
+      <c r="A179" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B179" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C179" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D179" s="1">
+        <v>152.71</v>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="3"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+      <c r="A180" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B180" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C180" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D180" s="1">
+        <v>159.8</v>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="3"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="A181" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B181" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C181" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>160.65147</v>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="3"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="A182" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B182" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C182" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D182" s="1">
+        <v>159.8</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="3"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="A183" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B183" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C183" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>159.8</v>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="3"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="A184" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B184" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C184" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D184" s="1">
+        <v>158.14</v>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="3"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="A185" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B185" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C185" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D185" s="1">
+        <v>157.47</v>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="3"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="A186" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B186" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C186" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D186" s="1">
+        <v>163.51832</v>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="3"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="A187" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B187" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C187" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D187" s="1">
+        <v>159.8</v>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="3"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="A188" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B188" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C188" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D188" s="1">
+        <v>151.66</v>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="3"/>
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="A189" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B189" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C189" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D189" s="1">
+        <v>148.75</v>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="3"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="A190" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C190" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D190" s="1">
+        <v>152.0</v>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="3"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="A191" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B191" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C191" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D191" s="1">
+        <v>147.17</v>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="3"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="A192" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B192" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C192" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D192" s="1">
+        <v>139.4798</v>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="3"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="A193" s="3">
+        <v>46201.0</v>
+      </c>
+      <c r="B193" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C193" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D193" s="1">
+        <v>134.8</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>146.65</v>
+        <v>167.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>146.65</v>
+        <v>155.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>141.28</v>
+        <v>150.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>134.91</v>
+        <v>149.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>134.91</v>
+        <v>150.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>134.91</v>
+        <v>149.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>134.8</v>
+        <v>142.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>131.75</v>
+        <v>139.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>133.0</v>
+        <v>139.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>131.75</v>
+        <v>139.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>134.91</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>129.2</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>128.83</v>
+        <v>137.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>130.99</v>
+        <v>136.57</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>131.75</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>128.83</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>131.75</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>128.83</v>
+        <v>130.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>128.83</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>121.81</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>133.1</v>
+        <v>132.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>131.75</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>128.83</v>
+        <v>133.01967</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>121.81</v>
+        <v>137.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>118.2</v>
+        <v>139.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>128.98</v>
+        <v>145.5653</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>128.83</v>
+        <v>144.12693</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>116.81</v>
+        <v>145.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>128.83</v>
+        <v>154.33392</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>128.83</v>
+        <v>153.39944</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>128.83</v>
+        <v>150.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>125.55</v>
+        <v>149.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>118.85</v>
+        <v>161.17933</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>116.14</v>
+        <v>149.51087</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>128.83</v>
+        <v>143.15774</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>120.0</v>
+        <v>143.22355</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>118.0</v>
+        <v>137.14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>116.14</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>116.14</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>116.14</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>107.71</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>108.61</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>104.39</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>108.41</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>100.54</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>100.54</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>100.54</v>
+        <v>135.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>100.54</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>106.0</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>101.89</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>101.55</v>
+        <v>130.43</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>107.19</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>100.0</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>99.5</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>96.25</v>
+        <v>136.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>90.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>60.0</v>
+        <v>139.11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>60.81467</v>
+        <v>139.69927</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>73.57735</v>
+        <v>147.42753</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>87.04</v>
+        <v>146.13097</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>99.74704</v>
+        <v>154.27663</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>106.47114</v>
+        <v>160.32159</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>114.97931</v>
+        <v>169.9185</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>117.75653</v>
+        <v>175.12151</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>118.0</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>120.35</v>
+        <v>152.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>128.83</v>
+        <v>158.56</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>133.1</v>
+        <v>183.28</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>120.0</v>
+        <v>156.39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>124.9</v>
+        <v>162.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>132.28</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>134.91</v>
+        <v>194.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>116.14</v>
+        <v>155.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>130.70501</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>134.91</v>
+        <v>191.42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>141.28</v>
+        <v>201.4914</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>140.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>154.81</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>163.05</v>
+        <v>207.72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>181.53</v>
+        <v>252.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>163.91</v>
+        <v>213.96</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>176.50022</v>
+        <v>205.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>177.19</v>
+        <v>203.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>187.25</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>177.19</v>
+        <v>205.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>177.27594</v>
+        <v>191.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>177.19</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>173.54406</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>176.78</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>164.0</v>
+        <v>204.76</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>165.66817</v>
+        <v>205.99</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>151.85563</v>
+        <v>172.2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>154.82902</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>142.32</v>
+        <v>174.44</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>137.85944</v>
+        <v>167.27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46200.0</v>
+        <v>46202.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,1352 +1649,584 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>134.80648</v>
+        <v>149.69</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B98" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D98" s="1">
-        <v>147.17</v>
-      </c>
+      <c r="A98" s="3"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
     </row>
     <row r="99">
-      <c r="A99" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B99" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C99" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D99" s="1">
-        <v>137.91</v>
-      </c>
+      <c r="A99" s="3"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
     </row>
     <row r="100">
-      <c r="A100" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B100" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C100" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D100" s="1">
-        <v>137.91</v>
-      </c>
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
     </row>
     <row r="101">
-      <c r="A101" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B101" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C101" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D101" s="1">
-        <v>134.98843</v>
-      </c>
+      <c r="A101" s="3"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
     </row>
     <row r="102">
-      <c r="A102" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B102" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C102" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D102" s="1">
-        <v>134.93421</v>
-      </c>
+      <c r="A102" s="3"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
     </row>
     <row r="103">
-      <c r="A103" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B103" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C103" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D103" s="1">
-        <v>134.19</v>
-      </c>
+      <c r="A103" s="3"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
     </row>
     <row r="104">
-      <c r="A104" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B104" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C104" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D104" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A104" s="3"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
     </row>
     <row r="105">
-      <c r="A105" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B105" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C105" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D105" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A105" s="3"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106">
-      <c r="A106" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B106" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C106" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D106" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A106" s="3"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
     </row>
     <row r="107">
-      <c r="A107" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B107" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C107" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D107" s="1">
-        <v>132.4</v>
-      </c>
+      <c r="A107" s="3"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
     </row>
     <row r="108">
-      <c r="A108" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B108" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C108" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D108" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A108" s="3"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
     </row>
     <row r="109">
-      <c r="A109" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B109" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C109" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D109" s="1">
-        <v>125.73</v>
-      </c>
+      <c r="A109" s="3"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
     </row>
     <row r="110">
-      <c r="A110" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B110" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C110" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D110" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A110" s="3"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
     </row>
     <row r="111">
-      <c r="A111" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B111" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C111" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D111" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A111" s="3"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
     </row>
     <row r="112">
-      <c r="A112" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B112" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C112" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D112" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A112" s="3"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
     </row>
     <row r="113">
-      <c r="A113" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B113" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C113" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="D113" s="1">
-        <v>128.83</v>
-      </c>
+      <c r="A113" s="3"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
     </row>
     <row r="114">
-      <c r="A114" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B114" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C114" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D114" s="1">
-        <v>130.38</v>
-      </c>
+      <c r="A114" s="3"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
     </row>
     <row r="115">
-      <c r="A115" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B115" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C115" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A115" s="3"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
     </row>
     <row r="116">
-      <c r="A116" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B116" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C116" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D116" s="1">
-        <v>129.2</v>
-      </c>
+      <c r="A116" s="3"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
     </row>
     <row r="117">
-      <c r="A117" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B117" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C117" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D117" s="1">
-        <v>129.07</v>
-      </c>
+      <c r="A117" s="3"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
     </row>
     <row r="118">
-      <c r="A118" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B118" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C118" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D118" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A118" s="3"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
     </row>
     <row r="119">
-      <c r="A119" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B119" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C119" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="D119" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A119" s="3"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
     </row>
     <row r="120">
-      <c r="A120" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B120" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C120" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D120" s="1">
-        <v>116.14</v>
-      </c>
+      <c r="A120" s="3"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
     </row>
     <row r="121">
-      <c r="A121" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B121" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C121" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="D121" s="1">
-        <v>116.14</v>
-      </c>
+      <c r="A121" s="3"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
     </row>
     <row r="122">
-      <c r="A122" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B122" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C122" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="D122" s="1">
-        <v>130.49</v>
-      </c>
+      <c r="A122" s="3"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
     </row>
     <row r="123">
-      <c r="A123" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B123" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C123" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D123" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A123" s="3"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
     </row>
     <row r="124">
-      <c r="A124" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B124" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C124" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D124" s="1">
-        <v>124.4</v>
-      </c>
+      <c r="A124" s="3"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
     </row>
     <row r="125">
-      <c r="A125" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B125" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C125" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="D125" s="1">
-        <v>119.11</v>
-      </c>
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
     </row>
     <row r="126">
-      <c r="A126" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B126" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C126" s="1">
-        <v>29.0</v>
-      </c>
-      <c r="D126" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
     </row>
     <row r="127">
-      <c r="A127" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B127" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C127" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D127" s="1">
-        <v>130.65</v>
-      </c>
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
     </row>
     <row r="128">
-      <c r="A128" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B128" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C128" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="D128" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A128" s="3"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
     </row>
     <row r="129">
-      <c r="A129" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B129" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C129" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="D129" s="1">
-        <v>124.9</v>
-      </c>
+      <c r="A129" s="3"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
     </row>
     <row r="130">
-      <c r="A130" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B130" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C130" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D130" s="1">
-        <v>132.4</v>
-      </c>
+      <c r="A130" s="3"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
     </row>
     <row r="131">
-      <c r="A131" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B131" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C131" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="D131" s="1">
-        <v>129.2</v>
-      </c>
+      <c r="A131" s="3"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
     </row>
     <row r="132">
-      <c r="A132" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B132" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C132" s="1">
-        <v>35.0</v>
-      </c>
-      <c r="D132" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A132" s="3"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
     </row>
     <row r="133">
-      <c r="A133" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B133" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C133" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D133" s="1">
-        <v>120.0</v>
-      </c>
+      <c r="A133" s="3"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
     </row>
     <row r="134">
-      <c r="A134" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B134" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C134" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D134" s="1">
-        <v>116.14</v>
-      </c>
+      <c r="A134" s="3"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
     </row>
     <row r="135">
-      <c r="A135" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B135" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C135" s="1">
-        <v>38.0</v>
-      </c>
-      <c r="D135" s="1">
-        <v>116.14</v>
-      </c>
+      <c r="A135" s="3"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
     </row>
     <row r="136">
-      <c r="A136" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B136" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C136" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D136" s="1">
-        <v>116.14</v>
-      </c>
+      <c r="A136" s="3"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
     </row>
     <row r="137">
-      <c r="A137" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B137" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C137" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="D137" s="1">
-        <v>111.58</v>
-      </c>
+      <c r="A137" s="3"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
     </row>
     <row r="138">
-      <c r="A138" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B138" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C138" s="1">
-        <v>41.0</v>
-      </c>
-      <c r="D138" s="1">
-        <v>71.05</v>
-      </c>
+      <c r="A138" s="3"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
     </row>
     <row r="139">
-      <c r="A139" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B139" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C139" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="D139" s="1">
-        <v>66.0</v>
-      </c>
+      <c r="A139" s="3"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
     </row>
     <row r="140">
-      <c r="A140" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B140" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C140" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D140" s="1">
-        <v>65.36</v>
-      </c>
+      <c r="A140" s="3"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141">
-      <c r="A141" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B141" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C141" s="1">
-        <v>44.0</v>
-      </c>
-      <c r="D141" s="1">
-        <v>60.0</v>
-      </c>
+      <c r="A141" s="3"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
     </row>
     <row r="142">
-      <c r="A142" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B142" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C142" s="1">
-        <v>45.0</v>
-      </c>
-      <c r="D142" s="1">
-        <v>50.0</v>
-      </c>
+      <c r="A142" s="3"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
     </row>
     <row r="143">
-      <c r="A143" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B143" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C143" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D143" s="1">
-        <v>50.0</v>
-      </c>
+      <c r="A143" s="3"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
     </row>
     <row r="144">
-      <c r="A144" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B144" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C144" s="1">
-        <v>47.0</v>
-      </c>
-      <c r="D144" s="1">
-        <v>60.0</v>
-      </c>
+      <c r="A144" s="3"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
     </row>
     <row r="145">
-      <c r="A145" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B145" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C145" s="1">
-        <v>48.0</v>
-      </c>
-      <c r="D145" s="1">
-        <v>79.0</v>
-      </c>
+      <c r="A145" s="3"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
     </row>
     <row r="146">
-      <c r="A146" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B146" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C146" s="1">
-        <v>49.0</v>
-      </c>
-      <c r="D146" s="1">
-        <v>94.0</v>
-      </c>
+      <c r="A146" s="3"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
     </row>
     <row r="147">
-      <c r="A147" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B147" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C147" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D147" s="1">
-        <v>90.93</v>
-      </c>
+      <c r="A147" s="3"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
     </row>
     <row r="148">
-      <c r="A148" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B148" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C148" s="1">
-        <v>51.0</v>
-      </c>
-      <c r="D148" s="1">
-        <v>91.93</v>
-      </c>
+      <c r="A148" s="3"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
     </row>
     <row r="149">
-      <c r="A149" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B149" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C149" s="1">
-        <v>52.0</v>
-      </c>
-      <c r="D149" s="1">
-        <v>93.11</v>
-      </c>
+      <c r="A149" s="3"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
     </row>
     <row r="150">
-      <c r="A150" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B150" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C150" s="1">
-        <v>53.0</v>
-      </c>
-      <c r="D150" s="1">
-        <v>87.0</v>
-      </c>
+      <c r="A150" s="3"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
     </row>
     <row r="151">
-      <c r="A151" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B151" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C151" s="1">
-        <v>54.0</v>
-      </c>
-      <c r="D151" s="1">
-        <v>89.75</v>
-      </c>
+      <c r="A151" s="3"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152">
-      <c r="A152" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B152" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C152" s="1">
-        <v>55.0</v>
-      </c>
-      <c r="D152" s="1">
-        <v>90.93</v>
-      </c>
+      <c r="A152" s="3"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
     </row>
     <row r="153">
-      <c r="A153" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B153" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C153" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D153" s="1">
-        <v>93.24</v>
-      </c>
+      <c r="A153" s="3"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154">
-      <c r="A154" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B154" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C154" s="1">
-        <v>57.0</v>
-      </c>
-      <c r="D154" s="1">
-        <v>90.0</v>
-      </c>
+      <c r="A154" s="3"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
     </row>
     <row r="155">
-      <c r="A155" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B155" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C155" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="D155" s="1">
-        <v>94.47</v>
-      </c>
+      <c r="A155" s="3"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
     </row>
     <row r="156">
-      <c r="A156" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B156" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C156" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D156" s="1">
-        <v>94.0</v>
-      </c>
+      <c r="A156" s="3"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157">
-      <c r="A157" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B157" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C157" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="D157" s="1">
-        <v>66.0</v>
-      </c>
+      <c r="A157" s="3"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
     </row>
     <row r="158">
-      <c r="A158" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B158" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C158" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="D158" s="1">
-        <v>50.06</v>
-      </c>
+      <c r="A158" s="3"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
     </row>
     <row r="159">
-      <c r="A159" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B159" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C159" s="1">
-        <v>62.0</v>
-      </c>
-      <c r="D159" s="1">
-        <v>60.0</v>
-      </c>
+      <c r="A159" s="3"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
     </row>
     <row r="160">
-      <c r="A160" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B160" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C160" s="1">
-        <v>63.0</v>
-      </c>
-      <c r="D160" s="1">
-        <v>68.57</v>
-      </c>
+      <c r="A160" s="3"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
     </row>
     <row r="161">
-      <c r="A161" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B161" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C161" s="1">
-        <v>64.0</v>
-      </c>
-      <c r="D161" s="1">
-        <v>97.76</v>
-      </c>
+      <c r="A161" s="3"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
     </row>
     <row r="162">
-      <c r="A162" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B162" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C162" s="1">
-        <v>65.0</v>
-      </c>
-      <c r="D162" s="1">
-        <v>111.48</v>
-      </c>
+      <c r="A162" s="3"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
     </row>
     <row r="163">
-      <c r="A163" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B163" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C163" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D163" s="1">
-        <v>115.85</v>
-      </c>
+      <c r="A163" s="3"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
     </row>
     <row r="164">
-      <c r="A164" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B164" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C164" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="D164" s="1">
-        <v>129.2</v>
-      </c>
+      <c r="A164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
     </row>
     <row r="165">
-      <c r="A165" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B165" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C165" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D165" s="1">
-        <v>134.19</v>
-      </c>
+      <c r="A165" s="3"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
     </row>
     <row r="166">
-      <c r="A166" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B166" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C166" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D166" s="1">
-        <v>120.5</v>
-      </c>
+      <c r="A166" s="3"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
     </row>
     <row r="167">
-      <c r="A167" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B167" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C167" s="1">
-        <v>70.0</v>
-      </c>
-      <c r="D167" s="1">
-        <v>131.75</v>
-      </c>
+      <c r="A167" s="3"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
     </row>
     <row r="168">
-      <c r="A168" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B168" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C168" s="1">
-        <v>71.0</v>
-      </c>
-      <c r="D168" s="1">
-        <v>132.78</v>
-      </c>
+      <c r="A168" s="3"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
     </row>
     <row r="169">
-      <c r="A169" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B169" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C169" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D169" s="1">
-        <v>134.19</v>
-      </c>
+      <c r="A169" s="3"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
     </row>
     <row r="170">
-      <c r="A170" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B170" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C170" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="D170" s="1">
-        <v>116.64</v>
-      </c>
+      <c r="A170" s="3"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171">
-      <c r="A171" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B171" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C171" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="D171" s="1">
-        <v>133.1</v>
-      </c>
+      <c r="A171" s="3"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
     </row>
     <row r="172">
-      <c r="A172" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B172" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C172" s="1">
-        <v>75.0</v>
-      </c>
-      <c r="D172" s="1">
-        <v>137.91</v>
-      </c>
+      <c r="A172" s="3"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173">
-      <c r="A173" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B173" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C173" s="1">
-        <v>76.0</v>
-      </c>
-      <c r="D173" s="1">
-        <v>147.17</v>
-      </c>
+      <c r="A173" s="3"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
     </row>
     <row r="174">
-      <c r="A174" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B174" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C174" s="1">
-        <v>77.0</v>
-      </c>
-      <c r="D174" s="1">
-        <v>147.17</v>
-      </c>
+      <c r="A174" s="3"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175">
-      <c r="A175" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B175" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C175" s="1">
-        <v>78.0</v>
-      </c>
-      <c r="D175" s="1">
-        <v>151.66</v>
-      </c>
+      <c r="A175" s="3"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176">
-      <c r="A176" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B176" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C176" s="1">
-        <v>79.0</v>
-      </c>
-      <c r="D176" s="1">
-        <v>161.59</v>
-      </c>
+      <c r="A176" s="3"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177">
-      <c r="A177" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B177" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C177" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="D177" s="1">
-        <v>175.63</v>
-      </c>
+      <c r="A177" s="3"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
     </row>
     <row r="178">
-      <c r="A178" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B178" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C178" s="1">
-        <v>81.0</v>
-      </c>
-      <c r="D178" s="1">
-        <v>151.66</v>
-      </c>
+      <c r="A178" s="3"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179">
-      <c r="A179" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B179" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C179" s="1">
-        <v>82.0</v>
-      </c>
-      <c r="D179" s="1">
-        <v>152.71</v>
-      </c>
+      <c r="A179" s="3"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
     </row>
     <row r="180">
-      <c r="A180" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B180" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C180" s="1">
-        <v>83.0</v>
-      </c>
-      <c r="D180" s="1">
-        <v>159.8</v>
-      </c>
+      <c r="A180" s="3"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
     </row>
     <row r="181">
-      <c r="A181" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B181" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C181" s="1">
-        <v>84.0</v>
-      </c>
-      <c r="D181" s="1">
-        <v>160.65147</v>
-      </c>
+      <c r="A181" s="3"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
     </row>
     <row r="182">
-      <c r="A182" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B182" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C182" s="1">
-        <v>85.0</v>
-      </c>
-      <c r="D182" s="1">
-        <v>159.8</v>
-      </c>
+      <c r="A182" s="3"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
     </row>
     <row r="183">
-      <c r="A183" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B183" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C183" s="1">
-        <v>86.0</v>
-      </c>
-      <c r="D183" s="1">
-        <v>159.8</v>
-      </c>
+      <c r="A183" s="3"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
     </row>
     <row r="184">
-      <c r="A184" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B184" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C184" s="1">
-        <v>87.0</v>
-      </c>
-      <c r="D184" s="1">
-        <v>158.14</v>
-      </c>
+      <c r="A184" s="3"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
     </row>
     <row r="185">
-      <c r="A185" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B185" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C185" s="1">
-        <v>88.0</v>
-      </c>
-      <c r="D185" s="1">
-        <v>157.47</v>
-      </c>
+      <c r="A185" s="3"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
     </row>
     <row r="186">
-      <c r="A186" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B186" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C186" s="1">
-        <v>89.0</v>
-      </c>
-      <c r="D186" s="1">
-        <v>163.51832</v>
-      </c>
+      <c r="A186" s="3"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
     </row>
     <row r="187">
-      <c r="A187" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B187" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C187" s="1">
-        <v>90.0</v>
-      </c>
-      <c r="D187" s="1">
-        <v>159.8</v>
-      </c>
+      <c r="A187" s="3"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
     </row>
     <row r="188">
-      <c r="A188" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B188" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C188" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D188" s="1">
-        <v>151.66</v>
-      </c>
+      <c r="A188" s="3"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189">
-      <c r="A189" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B189" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C189" s="1">
-        <v>92.0</v>
-      </c>
-      <c r="D189" s="1">
-        <v>148.75</v>
-      </c>
+      <c r="A189" s="3"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
     </row>
     <row r="190">
-      <c r="A190" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B190" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C190" s="1">
-        <v>93.0</v>
-      </c>
-      <c r="D190" s="1">
-        <v>152.0</v>
-      </c>
+      <c r="A190" s="3"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191">
-      <c r="A191" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B191" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C191" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D191" s="1">
-        <v>147.17</v>
-      </c>
+      <c r="A191" s="3"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
     </row>
     <row r="192">
-      <c r="A192" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B192" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C192" s="1">
-        <v>95.0</v>
-      </c>
-      <c r="D192" s="1">
-        <v>139.4798</v>
-      </c>
+      <c r="A192" s="3"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
     </row>
     <row r="193">
-      <c r="A193" s="3">
-        <v>46201.0</v>
-      </c>
-      <c r="B193" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C193" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="D193" s="1">
-        <v>134.8</v>
-      </c>
+      <c r="A193" s="3"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
     </row>
     <row r="194">
       <c r="A194" s="3"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>167.99</v>
+        <v>174.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>155.09</v>
+        <v>166.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>150.26</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>149.69</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>150.26</v>
+        <v>166.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>149.69</v>
+        <v>153.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>142.3</v>
+        <v>141.67505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>139.11</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>139.11</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>139.11</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>138.2</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>138.2</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>137.14</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>136.57</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>135.41</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>135.41</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>130.43</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>130.45</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>130.43</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>130.43</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>132.63</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>130.43</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>133.01967</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>137.14</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>139.11</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>145.5653</v>
+        <v>146.06</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>144.12693</v>
+        <v>162.37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>145.68</v>
+        <v>158.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>154.33392</v>
+        <v>166.06</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>153.39944</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>150.26</v>
+        <v>173.71208</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>149.69</v>
+        <v>157.43935</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>161.17933</v>
+        <v>173.68606</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>149.51087</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>143.15774</v>
+        <v>136.73318</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>143.22355</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>137.14</v>
+        <v>156.16824</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>136.84</v>
+        <v>150.92628</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>136.84</v>
+        <v>146.64421</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>136.84</v>
+        <v>138.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>135.41</v>
+        <v>141.878</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>135.41</v>
+        <v>141.8779</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>130.43</v>
+        <v>140.05108</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>130.43</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>135.41</v>
+        <v>133.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>135.41</v>
+        <v>141.34535</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>135.53</v>
+        <v>141.33344</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>135.41</v>
+        <v>134.59984</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>135.41</v>
+        <v>134.59602</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>135.41</v>
+        <v>134.59439</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>130.43</v>
+        <v>134.59277</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>135.41</v>
+        <v>134.59222</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>135.41</v>
+        <v>134.24372</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>136.84</v>
+        <v>134.59518</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>136.84</v>
+        <v>137.64282</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>137.0</v>
+        <v>141.42829</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>139.11</v>
+        <v>144.06157</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>139.69927</v>
+        <v>155.112</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>147.42753</v>
+        <v>155.11906</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>146.13097</v>
+        <v>155.8286</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>154.27663</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>160.32159</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>169.9185</v>
+        <v>140.55719</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>175.12151</v>
+        <v>156.33884</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>152.0</v>
+        <v>132.24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>152.0</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>158.56</v>
+        <v>134.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>183.28</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>156.39</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>162.14</v>
+        <v>136.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>177.78</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>194.0</v>
+        <v>163.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>155.09</v>
+        <v>154.38</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>175.0</v>
+        <v>166.06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>191.42</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>201.4914</v>
+        <v>203.93</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>187.0</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>177.78</v>
+        <v>185.64488</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>207.72</v>
+        <v>203.93</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>252.3</v>
+        <v>249.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>213.96</v>
+        <v>201.23</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>205.99</v>
+        <v>194.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>203.93</v>
+        <v>198.81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>200.0</v>
+        <v>197.94</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>205.99</v>
+        <v>204.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>191.42</v>
+        <v>185.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>187.0</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>177.78</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>220.0</v>
+        <v>177.78</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>204.76</v>
+        <v>175.63</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>205.99</v>
+        <v>180.00223</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>172.2</v>
+        <v>159.8</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>200.0</v>
+        <v>165.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>174.44</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>167.27</v>
+        <v>135.45</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>149.69</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="98">

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>174.99</v>
+        <v>183.99181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>166.06</v>
+        <v>162.30176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>163.0</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>156.0</v>
+        <v>146.38531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>166.06</v>
+        <v>160.02442</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>153.61</v>
+        <v>153.12411</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>141.67505</v>
+        <v>147.51781</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>135.45</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>140.0</v>
+        <v>146.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>135.45</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>135.45</v>
+        <v>135.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>135.45</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>135.45</v>
+        <v>138.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>135.45</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>135.0</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>134.94</v>
+        <v>129.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>135.45</v>
+        <v>139.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>135.45</v>
+        <v>128.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>135.0</v>
+        <v>137.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>135.45</v>
+        <v>136.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>135.45</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>135.45</v>
+        <v>136.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>134.94</v>
+        <v>135.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>134.94</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>135.45</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>146.06</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>162.37</v>
+        <v>157.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>158.52</v>
+        <v>154.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>166.06</v>
+        <v>144.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>177.78</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>173.71208</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>157.43935</v>
+        <v>160.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>173.68606</v>
+        <v>158.62734</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>159.8</v>
+        <v>164.22</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>136.73318</v>
+        <v>163.18375</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>135.45</v>
+        <v>133.96891</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>156.16824</v>
+        <v>160.44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>150.92628</v>
+        <v>143.81166</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>146.64421</v>
+        <v>127.61764</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>138.37</v>
+        <v>114.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>141.878</v>
+        <v>145.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>141.8779</v>
+        <v>130.79799</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>140.05108</v>
+        <v>123.74692</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>135.0</v>
+        <v>120.85509</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>133.59</v>
+        <v>140.08765</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>141.34535</v>
+        <v>128.88342</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>141.33344</v>
+        <v>129.18</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>134.59984</v>
+        <v>125.83957</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>134.59602</v>
+        <v>131.16348</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>134.59439</v>
+        <v>132.23188</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>134.59277</v>
+        <v>132.22849</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>134.59222</v>
+        <v>132.68517</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>134.24372</v>
+        <v>131.77758</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>134.59518</v>
+        <v>132.21351</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>137.64282</v>
+        <v>132.95285</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>141.42829</v>
+        <v>144.18577</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>144.06157</v>
+        <v>144.24466</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>155.112</v>
+        <v>144.24699</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>155.11906</v>
+        <v>150.30812</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>155.8286</v>
+        <v>173.26661</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>134.0</v>
+        <v>143.32318</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>135.0</v>
+        <v>148.16823</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>140.55719</v>
+        <v>167.21339</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>156.33884</v>
+        <v>187.19242</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>132.24</v>
+        <v>156.10098</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>133.92</v>
+        <v>171.51109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>134.94</v>
+        <v>190.24436</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>135.45</v>
+        <v>172.04104</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>135.45</v>
+        <v>140.56715</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>136.1</v>
+        <v>146.80001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>150.0</v>
+        <v>153.15679</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>163.0</v>
+        <v>163.16337</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>154.38</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>166.06</v>
+        <v>136.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>177.78</v>
+        <v>154.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>203.93</v>
+        <v>175.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>177.78</v>
+        <v>137.81</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>185.64488</v>
+        <v>162.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>203.93</v>
+        <v>179.36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>249.07</v>
+        <v>191.65</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>201.23</v>
+        <v>165.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>194.66</v>
+        <v>174.66</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>198.81</v>
+        <v>188.51</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>197.94</v>
+        <v>191.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>204.65</v>
+        <v>181.34</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>185.9</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>177.78</v>
+        <v>168.37</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>159.8</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>177.78</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>175.63</v>
+        <v>165.02</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>180.00223</v>
+        <v>148.23</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>159.8</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>165.0</v>
+        <v>174.86676</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>140.0</v>
+        <v>151.33521</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>135.45</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,7 +1649,7 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>133.92</v>
+        <v>118.79803</v>
       </c>
     </row>
     <row r="98">

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>174.99</v>
+        <v>161.381</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>166.06</v>
+        <v>157.64826</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>163.0</v>
+        <v>149.55655</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>156.0</v>
+        <v>138.85792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>166.06</v>
+        <v>153.33205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>153.61</v>
+        <v>142.01102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>141.67505</v>
+        <v>132.35385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>135.45</v>
+        <v>129.09876</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>140.0</v>
+        <v>133.464</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>135.45</v>
+        <v>132.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>135.45</v>
+        <v>132.51</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>135.45</v>
+        <v>133.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>135.45</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -501,12 +501,12 @@
         <v>14.0</v>
       </c>
       <c r="D15" s="1">
-        <v>135.45</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>135.0</v>
+        <v>136.47</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>134.94</v>
+        <v>132.18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>135.45</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>135.45</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>135.45</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>135.45</v>
+        <v>130.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>135.45</v>
+        <v>138.74607</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>134.94</v>
+        <v>139.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>134.94</v>
+        <v>133.03393</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>135.45</v>
+        <v>129.36141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>146.06</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>162.37</v>
+        <v>155.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>158.52</v>
+        <v>160.30497</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>166.06</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>177.78</v>
+        <v>142.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>173.71208</v>
+        <v>157.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>157.43935</v>
+        <v>143.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>173.68606</v>
+        <v>154.56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>159.8</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>136.73318</v>
+        <v>136.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>135.45</v>
+        <v>124.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>156.16824</v>
+        <v>170.93098</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>150.92628</v>
+        <v>150.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>146.64421</v>
+        <v>157.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>138.37</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>141.878</v>
+        <v>144.7452</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>141.8779</v>
+        <v>143.32869</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>140.05108</v>
+        <v>138.22569</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>135.0</v>
+        <v>129.05204</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>133.59</v>
+        <v>135.4549</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>141.34535</v>
+        <v>134.40851</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>141.33344</v>
+        <v>130.34208</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>134.59984</v>
+        <v>123.82599</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>134.59602</v>
+        <v>131.86534</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>134.59439</v>
+        <v>132.1795</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>134.59277</v>
+        <v>130.26788</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>134.59222</v>
+        <v>118.16962</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>134.24372</v>
+        <v>120.53019</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>134.59518</v>
+        <v>127.60973</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>137.64282</v>
+        <v>128.39114</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>141.42829</v>
+        <v>124.43429</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>144.06157</v>
+        <v>123.35455</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>155.112</v>
+        <v>125.07128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>155.11906</v>
+        <v>128.96373</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>155.8286</v>
+        <v>135.15186</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>134.0</v>
+        <v>130.27563</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>135.0</v>
+        <v>126.19221</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>140.55719</v>
+        <v>131.10639</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>156.33884</v>
+        <v>140.79515</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>132.24</v>
+        <v>134.7087</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>133.92</v>
+        <v>138.83513</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>134.94</v>
+        <v>142.74018</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>135.45</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>135.45</v>
+        <v>118.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>136.1</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>150.0</v>
+        <v>125.73552</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>163.0</v>
+        <v>156.49448</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>154.38</v>
+        <v>116.31</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>166.06</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>177.78</v>
+        <v>154.95821</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>203.93</v>
+        <v>177.04</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>177.78</v>
+        <v>140.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>185.64488</v>
+        <v>173.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>203.93</v>
+        <v>176.3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>249.07</v>
+        <v>189.77</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>201.23</v>
+        <v>174.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>194.66</v>
+        <v>174.94</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>198.81</v>
+        <v>174.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>197.94</v>
+        <v>174.94</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>204.65</v>
+        <v>182.37807</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>185.9</v>
+        <v>170.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>177.78</v>
+        <v>162.10193</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>159.8</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>177.78</v>
+        <v>161.0674</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>175.63</v>
+        <v>157.1626</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>180.00223</v>
+        <v>146.77</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>159.8</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>165.0</v>
+        <v>153.20497</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>140.0</v>
+        <v>140.24503</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>135.45</v>
+        <v>130.03</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46203.0</v>
+        <v>46205.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,1736 +1649,4040 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>133.92</v>
+        <v>119.6</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3"/>
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
+      <c r="A98" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C98" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D98" s="1">
+        <v>138.24452</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="3"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
+      <c r="A99" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B99" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C99" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D99" s="1">
+        <v>144.0</v>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="3"/>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
+      <c r="A100" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B100" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D100" s="1">
+        <v>137.73</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="3"/>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
+      <c r="A101" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B101" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D101" s="1">
+        <v>143.04</v>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
+      <c r="A102" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B102" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D102" s="1">
+        <v>153.0</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3"/>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
+      <c r="A103" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C103" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D103" s="1">
+        <v>153.0</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="3"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
+      <c r="A104" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B104" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C104" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D104" s="1">
+        <v>138.0</v>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="3"/>
-      <c r="B105" s="1"/>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
+      <c r="A105" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B105" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C105" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D105" s="1">
+        <v>134.92</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="3"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
+      <c r="A106" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C106" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D106" s="1">
+        <v>144.0</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="3"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
+      <c r="A107" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B107" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C107" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D107" s="1">
+        <v>136.66</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="3"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
+      <c r="A108" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B108" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C108" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D108" s="1">
+        <v>138.0</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="3"/>
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
+      <c r="A109" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C109" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D109" s="1">
+        <v>134.92</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="3"/>
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
+      <c r="A110" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C110" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D110" s="1">
+        <v>134.46</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="3"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
+      <c r="A111" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B111" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C111" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D111" s="1">
+        <v>133.49</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="3"/>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
+      <c r="A112" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B112" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C112" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D112" s="1">
+        <v>133.49</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="3"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
+      <c r="A113" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B113" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C113" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D113" s="1">
+        <v>134.92</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="3"/>
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
+      <c r="A114" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B114" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C114" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D114" s="1">
+        <v>133.34</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="3"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
+      <c r="A115" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B115" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C115" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D115" s="1">
+        <v>136.66</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="3"/>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
+      <c r="A116" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B116" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C116" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D116" s="1">
+        <v>132.52</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="3"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
+      <c r="A117" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B117" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C117" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D117" s="1">
+        <v>131.0</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="3"/>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
+      <c r="A118" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B118" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C118" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D118" s="1">
+        <v>138.12</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="3"/>
-      <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
+      <c r="A119" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B119" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C119" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D119" s="1">
+        <v>134.92</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="3"/>
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
+      <c r="A120" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B120" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C120" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D120" s="1">
+        <v>124.86</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="3"/>
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
+      <c r="A121" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B121" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C121" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D121" s="1">
+        <v>122.5</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="3"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
+      <c r="A122" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B122" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C122" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D122" s="1">
+        <v>125.0</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="3"/>
-      <c r="B123" s="1"/>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
+      <c r="A123" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B123" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C123" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D123" s="1">
+        <v>153.0</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="3"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
+      <c r="A124" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C124" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D124" s="1">
+        <v>148.41404</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="3"/>
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
+      <c r="A125" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B125" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C125" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D125" s="1">
+        <v>150.53</v>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="3"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
+      <c r="A126" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B126" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C126" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D126" s="1">
+        <v>148.0</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="3"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
+      <c r="A127" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B127" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C127" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D127" s="1">
+        <v>150.74</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="3"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
+      <c r="A128" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B128" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C128" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D128" s="1">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="3"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
+      <c r="A129" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B129" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C129" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D129" s="1">
+        <v>135.55</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="3"/>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
+      <c r="A130" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B130" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C130" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D130" s="1">
+        <v>139.5</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="3"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
+      <c r="A131" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B131" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C131" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D131" s="1">
+        <v>135.0</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="3"/>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
+      <c r="A132" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B132" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C132" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D132" s="1">
+        <v>132.63</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="3"/>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
+      <c r="A133" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B133" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C133" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D133" s="1">
+        <v>132.87</v>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="3"/>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
+      <c r="A134" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B134" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D134" s="1">
+        <v>122.4</v>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="3"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
+      <c r="A135" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B135" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D135" s="1">
+        <v>132.0</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="3"/>
-      <c r="B136" s="1"/>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
+      <c r="A136" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B136" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C136" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D136" s="1">
+        <v>131.05</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="3"/>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
+      <c r="A137" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B137" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C137" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D137" s="1">
+        <v>134.95</v>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="3"/>
-      <c r="B138" s="1"/>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
+      <c r="A138" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B138" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C138" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D138" s="1">
+        <v>138.98804</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="3"/>
-      <c r="B139" s="1"/>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
+      <c r="A139" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B139" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C139" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D139" s="1">
+        <v>124.74414</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="3"/>
-      <c r="B140" s="1"/>
-      <c r="C140" s="1"/>
-      <c r="D140" s="1"/>
+      <c r="A140" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B140" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C140" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D140" s="1">
+        <v>130.30468</v>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="3"/>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="D141" s="1"/>
+      <c r="A141" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B141" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C141" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D141" s="1">
+        <v>124.52</v>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="3"/>
-      <c r="B142" s="1"/>
-      <c r="C142" s="1"/>
-      <c r="D142" s="1"/>
+      <c r="A142" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B142" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C142" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D142" s="1">
+        <v>127.08493</v>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="3"/>
-      <c r="B143" s="1"/>
-      <c r="C143" s="1"/>
-      <c r="D143" s="1"/>
+      <c r="A143" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B143" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D143" s="1">
+        <v>133.45756</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="3"/>
-      <c r="B144" s="1"/>
-      <c r="C144" s="1"/>
-      <c r="D144" s="1"/>
+      <c r="A144" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B144" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C144" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D144" s="1">
+        <v>121.84111</v>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="3"/>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="D145" s="1"/>
+      <c r="A145" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B145" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C145" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D145" s="1">
+        <v>134.04681</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="3"/>
-      <c r="B146" s="1"/>
-      <c r="C146" s="1"/>
-      <c r="D146" s="1"/>
+      <c r="A146" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B146" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C146" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D146" s="1">
+        <v>114.58</v>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="3"/>
-      <c r="B147" s="1"/>
-      <c r="C147" s="1"/>
-      <c r="D147" s="1"/>
+      <c r="A147" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B147" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C147" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D147" s="1">
+        <v>114.86</v>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="3"/>
-      <c r="B148" s="1"/>
-      <c r="C148" s="1"/>
-      <c r="D148" s="1"/>
+      <c r="A148" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B148" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C148" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D148" s="1">
+        <v>115.18</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="3"/>
-      <c r="B149" s="1"/>
-      <c r="C149" s="1"/>
-      <c r="D149" s="1"/>
+      <c r="A149" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B149" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C149" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D149" s="1">
+        <v>124.52</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="3"/>
-      <c r="B150" s="1"/>
-      <c r="C150" s="1"/>
-      <c r="D150" s="1"/>
+      <c r="A150" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B150" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C150" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D150" s="1">
+        <v>127.39</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="3"/>
-      <c r="B151" s="1"/>
-      <c r="C151" s="1"/>
-      <c r="D151" s="1"/>
+      <c r="A151" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B151" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C151" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D151" s="1">
+        <v>128.57</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="3"/>
-      <c r="B152" s="1"/>
-      <c r="C152" s="1"/>
-      <c r="D152" s="1"/>
+      <c r="A152" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B152" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C152" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D152" s="1">
+        <v>132.45</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="3"/>
-      <c r="B153" s="1"/>
-      <c r="C153" s="1"/>
-      <c r="D153" s="1"/>
+      <c r="A153" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B153" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C153" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D153" s="1">
+        <v>131.59</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="3"/>
-      <c r="B154" s="1"/>
-      <c r="C154" s="1"/>
-      <c r="D154" s="1"/>
+      <c r="A154" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B154" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C154" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D154" s="1">
+        <v>127.06</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="3"/>
-      <c r="B155" s="1"/>
-      <c r="C155" s="1"/>
-      <c r="D155" s="1"/>
+      <c r="A155" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B155" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C155" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D155" s="1">
+        <v>130.7</v>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="3"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
+      <c r="A156" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B156" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C156" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D156" s="1">
+        <v>131.87</v>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="3"/>
-      <c r="B157" s="1"/>
-      <c r="C157" s="1"/>
-      <c r="D157" s="1"/>
+      <c r="A157" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B157" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C157" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D157" s="1">
+        <v>130.77</v>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="3"/>
-      <c r="B158" s="1"/>
-      <c r="C158" s="1"/>
-      <c r="D158" s="1"/>
+      <c r="A158" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B158" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C158" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D158" s="1">
+        <v>133.47</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="3"/>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
+      <c r="A159" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B159" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C159" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D159" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="3"/>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
+      <c r="A160" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B160" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C160" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D160" s="1">
+        <v>124.52</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="3"/>
-      <c r="B161" s="1"/>
-      <c r="C161" s="1"/>
-      <c r="D161" s="1"/>
+      <c r="A161" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B161" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C161" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D161" s="1">
+        <v>125.8</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="3"/>
-      <c r="B162" s="1"/>
-      <c r="C162" s="1"/>
-      <c r="D162" s="1"/>
+      <c r="A162" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B162" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C162" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D162" s="1">
+        <v>124.0</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="3"/>
-      <c r="B163" s="1"/>
-      <c r="C163" s="1"/>
-      <c r="D163" s="1"/>
+      <c r="A163" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B163" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C163" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D163" s="1">
+        <v>133.0</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="3"/>
-      <c r="B164" s="1"/>
-      <c r="C164" s="1"/>
-      <c r="D164" s="1"/>
+      <c r="A164" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B164" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C164" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D164" s="1">
+        <v>134.3</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="3"/>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="1"/>
+      <c r="A165" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B165" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C165" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D165" s="1">
+        <v>129.1</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="3"/>
-      <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
-      <c r="D166" s="1"/>
+      <c r="A166" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B166" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C166" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D166" s="1">
+        <v>121.63534</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="3"/>
-      <c r="B167" s="1"/>
-      <c r="C167" s="1"/>
-      <c r="D167" s="1"/>
+      <c r="A167" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B167" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C167" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D167" s="1">
+        <v>126.63</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="3"/>
-      <c r="B168" s="1"/>
-      <c r="C168" s="1"/>
-      <c r="D168" s="1"/>
+      <c r="A168" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B168" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C168" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D168" s="1">
+        <v>155.74</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="3"/>
-      <c r="B169" s="1"/>
-      <c r="C169" s="1"/>
-      <c r="D169" s="1"/>
+      <c r="A169" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B169" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C169" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D169" s="1">
+        <v>164.0</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="3"/>
-      <c r="B170" s="1"/>
-      <c r="C170" s="1"/>
-      <c r="D170" s="1"/>
+      <c r="A170" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B170" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C170" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D170" s="1">
+        <v>126.39</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="3"/>
-      <c r="B171" s="1"/>
-      <c r="C171" s="1"/>
-      <c r="D171" s="1"/>
+      <c r="A171" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B171" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C171" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D171" s="1">
+        <v>139.67</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="3"/>
-      <c r="B172" s="1"/>
-      <c r="C172" s="1"/>
-      <c r="D172" s="1"/>
+      <c r="A172" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B172" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C172" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D172" s="1">
+        <v>164.0</v>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="3"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="1"/>
-      <c r="D173" s="1"/>
+      <c r="A173" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B173" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C173" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D173" s="1">
+        <v>175.0</v>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="3"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="1"/>
-      <c r="D174" s="1"/>
+      <c r="A174" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B174" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C174" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D174" s="1">
+        <v>154.97</v>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="3"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="1"/>
-      <c r="D175" s="1"/>
+      <c r="A175" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B175" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C175" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D175" s="1">
+        <v>153.38</v>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="3"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1"/>
-      <c r="D176" s="1"/>
+      <c r="A176" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B176" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C176" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D176" s="1">
+        <v>159.82</v>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="3"/>
-      <c r="B177" s="1"/>
-      <c r="C177" s="1"/>
-      <c r="D177" s="1"/>
+      <c r="A177" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B177" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C177" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D177" s="1">
+        <v>170.8</v>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="3"/>
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
+      <c r="A178" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B178" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C178" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D178" s="1">
+        <v>168.0</v>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="3"/>
-      <c r="B179" s="1"/>
-      <c r="C179" s="1"/>
-      <c r="D179" s="1"/>
+      <c r="A179" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B179" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C179" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D179" s="1">
+        <v>167.1</v>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="3"/>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1"/>
-      <c r="D180" s="1"/>
+      <c r="A180" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B180" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C180" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D180" s="1">
+        <v>170.45</v>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="3"/>
-      <c r="B181" s="1"/>
-      <c r="C181" s="1"/>
-      <c r="D181" s="1"/>
+      <c r="A181" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B181" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C181" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D181" s="1">
+        <v>175.18</v>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="3"/>
-      <c r="B182" s="1"/>
-      <c r="C182" s="1"/>
-      <c r="D182" s="1"/>
+      <c r="A182" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B182" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C182" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D182" s="1">
+        <v>164.0</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="3"/>
-      <c r="B183" s="1"/>
-      <c r="C183" s="1"/>
-      <c r="D183" s="1"/>
+      <c r="A183" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B183" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C183" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D183" s="1">
+        <v>159.5</v>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="3"/>
-      <c r="B184" s="1"/>
-      <c r="C184" s="1"/>
-      <c r="D184" s="1"/>
+      <c r="A184" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B184" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C184" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D184" s="1">
+        <v>158.16</v>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="3"/>
-      <c r="B185" s="1"/>
-      <c r="C185" s="1"/>
-      <c r="D185" s="1"/>
+      <c r="A185" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B185" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C185" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D185" s="1">
+        <v>156.22</v>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="3"/>
-      <c r="B186" s="1"/>
-      <c r="C186" s="1"/>
-      <c r="D186" s="1"/>
+      <c r="A186" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B186" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C186" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D186" s="1">
+        <v>156.32623</v>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="3"/>
-      <c r="B187" s="1"/>
-      <c r="C187" s="1"/>
-      <c r="D187" s="1"/>
+      <c r="A187" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B187" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C187" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D187" s="1">
+        <v>163.35</v>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="3"/>
-      <c r="B188" s="1"/>
-      <c r="C188" s="1"/>
-      <c r="D188" s="1"/>
+      <c r="A188" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B188" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C188" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D188" s="1">
+        <v>145.61219</v>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="3"/>
-      <c r="B189" s="1"/>
-      <c r="C189" s="1"/>
-      <c r="D189" s="1"/>
+      <c r="A189" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B189" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C189" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D189" s="1">
+        <v>135.53</v>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="3"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
+      <c r="A190" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B190" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C190" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D190" s="1">
+        <v>156.53</v>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="3"/>
-      <c r="B191" s="1"/>
-      <c r="C191" s="1"/>
-      <c r="D191" s="1"/>
+      <c r="A191" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B191" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C191" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D191" s="1">
+        <v>141.20729</v>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="3"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
+      <c r="A192" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B192" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C192" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D192" s="1">
+        <v>134.99777</v>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="3"/>
-      <c r="B193" s="1"/>
-      <c r="C193" s="1"/>
-      <c r="D193" s="1"/>
+      <c r="A193" s="3">
+        <v>46206.0</v>
+      </c>
+      <c r="B193" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C193" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D193" s="1">
+        <v>131.0</v>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="3"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
+      <c r="A194" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B194" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C194" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D194" s="1">
+        <v>137.0</v>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="3"/>
-      <c r="B195" s="1"/>
-      <c r="C195" s="1"/>
-      <c r="D195" s="1"/>
+      <c r="A195" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B195" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C195" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D195" s="1">
+        <v>137.0</v>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="3"/>
-      <c r="B196" s="1"/>
-      <c r="C196" s="1"/>
-      <c r="D196" s="1"/>
+      <c r="A196" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B196" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C196" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D196" s="1">
+        <v>137.0</v>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="3"/>
-      <c r="B197" s="1"/>
-      <c r="C197" s="1"/>
-      <c r="D197" s="1"/>
+      <c r="A197" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B197" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C197" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D197" s="1">
+        <v>137.0</v>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="3"/>
-      <c r="B198" s="1"/>
-      <c r="C198" s="1"/>
-      <c r="D198" s="1"/>
+      <c r="A198" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B198" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C198" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D198" s="1">
+        <v>161.5</v>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="3"/>
-      <c r="B199" s="1"/>
-      <c r="C199" s="1"/>
-      <c r="D199" s="1"/>
+      <c r="A199" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B199" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C199" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D199" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="3"/>
-      <c r="B200" s="1"/>
-      <c r="C200" s="1"/>
-      <c r="D200" s="1"/>
+      <c r="A200" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B200" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C200" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D200" s="1">
+        <v>141.48</v>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="3"/>
-      <c r="B201" s="1"/>
-      <c r="C201" s="1"/>
-      <c r="D201" s="1"/>
+      <c r="A201" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B201" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C201" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D201" s="1">
+        <v>136.0</v>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="3"/>
-      <c r="B202" s="1"/>
-      <c r="C202" s="1"/>
-      <c r="D202" s="1"/>
+      <c r="A202" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B202" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C202" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D202" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="3"/>
-      <c r="B203" s="1"/>
-      <c r="C203" s="1"/>
-      <c r="D203" s="1"/>
+      <c r="A203" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B203" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C203" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D203" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="3"/>
-      <c r="B204" s="1"/>
-      <c r="C204" s="1"/>
-      <c r="D204" s="1"/>
+      <c r="A204" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B204" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C204" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D204" s="1">
+        <v>140.56</v>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="3"/>
-      <c r="B205" s="1"/>
-      <c r="C205" s="1"/>
-      <c r="D205" s="1"/>
+      <c r="A205" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B205" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C205" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D205" s="1">
+        <v>139.6</v>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="3"/>
-      <c r="B206" s="1"/>
-      <c r="C206" s="1"/>
-      <c r="D206" s="1"/>
+      <c r="A206" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B206" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C206" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D206" s="1">
+        <v>135.7</v>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="3"/>
-      <c r="B207" s="1"/>
-      <c r="C207" s="1"/>
-      <c r="D207" s="1"/>
+      <c r="A207" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B207" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C207" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D207" s="1">
+        <v>139.5</v>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="3"/>
-      <c r="B208" s="1"/>
-      <c r="C208" s="1"/>
-      <c r="D208" s="1"/>
+      <c r="A208" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B208" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C208" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D208" s="1">
+        <v>133.99</v>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="3"/>
-      <c r="B209" s="1"/>
-      <c r="C209" s="1"/>
-      <c r="D209" s="1"/>
+      <c r="A209" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B209" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C209" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D209" s="1">
+        <v>130.81</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="3"/>
-      <c r="B210" s="1"/>
-      <c r="C210" s="1"/>
-      <c r="D210" s="1"/>
+      <c r="A210" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B210" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C210" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D210" s="1">
+        <v>140.5</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="3"/>
-      <c r="B211" s="1"/>
-      <c r="C211" s="1"/>
-      <c r="D211" s="1"/>
+      <c r="A211" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B211" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C211" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D211" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="3"/>
-      <c r="B212" s="1"/>
-      <c r="C212" s="1"/>
-      <c r="D212" s="1"/>
+      <c r="A212" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B212" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C212" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D212" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="3"/>
-      <c r="B213" s="1"/>
-      <c r="C213" s="1"/>
-      <c r="D213" s="1"/>
+      <c r="A213" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B213" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C213" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D213" s="1">
+        <v>136.17</v>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="3"/>
-      <c r="B214" s="1"/>
-      <c r="C214" s="1"/>
-      <c r="D214" s="1"/>
+      <c r="A214" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B214" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C214" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D214" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="3"/>
-      <c r="B215" s="1"/>
-      <c r="C215" s="1"/>
-      <c r="D215" s="1"/>
+      <c r="A215" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B215" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C215" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D215" s="1">
+        <v>133.29</v>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="3"/>
-      <c r="B216" s="1"/>
-      <c r="C216" s="1"/>
-      <c r="D216" s="1"/>
+      <c r="A216" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B216" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C216" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D216" s="1">
+        <v>129.19</v>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="3"/>
-      <c r="B217" s="1"/>
-      <c r="C217" s="1"/>
-      <c r="D217" s="1"/>
+      <c r="A217" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B217" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C217" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D217" s="1">
+        <v>118.0</v>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="3"/>
-      <c r="B218" s="1"/>
-      <c r="C218" s="1"/>
-      <c r="D218" s="1"/>
+      <c r="A218" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B218" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C218" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D218" s="1">
+        <v>135.0</v>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="3"/>
-      <c r="B219" s="1"/>
-      <c r="C219" s="1"/>
-      <c r="D219" s="1"/>
+      <c r="A219" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B219" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C219" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D219" s="1">
+        <v>126.53</v>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="3"/>
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
+      <c r="A220" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B220" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C220" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D220" s="1">
+        <v>128.09</v>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="3"/>
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
+      <c r="A221" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B221" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C221" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D221" s="1">
+        <v>118.02</v>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="3"/>
-      <c r="B222" s="1"/>
-      <c r="C222" s="1"/>
-      <c r="D222" s="1"/>
+      <c r="A222" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B222" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C222" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D222" s="1">
+        <v>144.73</v>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="3"/>
-      <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-      <c r="D223" s="1"/>
+      <c r="A223" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B223" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C223" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D223" s="1">
+        <v>137.0</v>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="3"/>
-      <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
-      <c r="D224" s="1"/>
+      <c r="A224" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B224" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C224" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D224" s="1">
+        <v>122.31</v>
+      </c>
     </row>
     <row r="225">
-      <c r="A225" s="3"/>
-      <c r="B225" s="1"/>
-      <c r="C225" s="1"/>
-      <c r="D225" s="1"/>
+      <c r="A225" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B225" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C225" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D225" s="1">
+        <v>112.44</v>
+      </c>
     </row>
     <row r="226">
-      <c r="A226" s="3"/>
-      <c r="B226" s="1"/>
-      <c r="C226" s="1"/>
-      <c r="D226" s="1"/>
+      <c r="A226" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B226" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C226" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D226" s="1">
+        <v>173.0</v>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="3"/>
-      <c r="B227" s="1"/>
-      <c r="C227" s="1"/>
-      <c r="D227" s="1"/>
+      <c r="A227" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B227" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C227" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D227" s="1">
+        <v>162.54</v>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="3"/>
-      <c r="B228" s="1"/>
-      <c r="C228" s="1"/>
-      <c r="D228" s="1"/>
+      <c r="A228" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B228" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C228" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D228" s="1">
+        <v>123.0</v>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="3"/>
-      <c r="B229" s="1"/>
-      <c r="C229" s="1"/>
-      <c r="D229" s="1"/>
+      <c r="A229" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B229" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C229" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D229" s="1">
+        <v>111.43</v>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="3"/>
-      <c r="B230" s="1"/>
-      <c r="C230" s="1"/>
-      <c r="D230" s="1"/>
+      <c r="A230" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B230" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C230" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D230" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="3"/>
-      <c r="B231" s="1"/>
-      <c r="C231" s="1"/>
-      <c r="D231" s="1"/>
+      <c r="A231" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B231" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C231" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D231" s="1">
+        <v>134.04</v>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="3"/>
-      <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
+      <c r="A232" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B232" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C232" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D232" s="1">
+        <v>111.78</v>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="3"/>
-      <c r="B233" s="1"/>
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
+      <c r="A233" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B233" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C233" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D233" s="1">
+        <v>105.14</v>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="3"/>
-      <c r="B234" s="1"/>
-      <c r="C234" s="1"/>
-      <c r="D234" s="1"/>
+      <c r="A234" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B234" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C234" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D234" s="1">
+        <v>61.11</v>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="3"/>
-      <c r="B235" s="1"/>
-      <c r="C235" s="1"/>
-      <c r="D235" s="1"/>
+      <c r="A235" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B235" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C235" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D235" s="1">
+        <v>51.4</v>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="3"/>
-      <c r="B236" s="1"/>
-      <c r="C236" s="1"/>
-      <c r="D236" s="1"/>
+      <c r="A236" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B236" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C236" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D236" s="1">
+        <v>49.32</v>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="3"/>
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
+      <c r="A237" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B237" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C237" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D237" s="1">
+        <v>49.32</v>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="3"/>
-      <c r="B238" s="1"/>
-      <c r="C238" s="1"/>
-      <c r="D238" s="1"/>
+      <c r="A238" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B238" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C238" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D238" s="1">
+        <v>13.74653</v>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="3"/>
-      <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
-      <c r="D239" s="1"/>
+      <c r="A239" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B239" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C239" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D239" s="1">
+        <v>13.56261</v>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="3"/>
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-      <c r="D240" s="1"/>
+      <c r="A240" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B240" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C240" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D240" s="1">
+        <v>12.70886</v>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="3"/>
-      <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
-      <c r="D241" s="1"/>
+      <c r="A241" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B241" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C241" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D241" s="1">
+        <v>4.23241</v>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="3"/>
-      <c r="B242" s="1"/>
-      <c r="C242" s="1"/>
-      <c r="D242" s="1"/>
+      <c r="A242" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B242" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C242" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D242" s="1">
+        <v>35.21</v>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="3"/>
-      <c r="B243" s="1"/>
-      <c r="C243" s="1"/>
-      <c r="D243" s="1"/>
+      <c r="A243" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B243" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C243" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D243" s="1">
+        <v>40.57322</v>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="3"/>
-      <c r="B244" s="1"/>
-      <c r="C244" s="1"/>
-      <c r="D244" s="1"/>
+      <c r="A244" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B244" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C244" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D244" s="1">
+        <v>43.57981</v>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="3"/>
-      <c r="B245" s="1"/>
-      <c r="C245" s="1"/>
-      <c r="D245" s="1"/>
+      <c r="A245" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B245" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C245" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D245" s="1">
+        <v>40.98</v>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="3"/>
-      <c r="B246" s="1"/>
-      <c r="C246" s="1"/>
-      <c r="D246" s="1"/>
+      <c r="A246" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B246" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C246" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D246" s="1">
+        <v>38.92551</v>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="3"/>
-      <c r="B247" s="1"/>
-      <c r="C247" s="1"/>
-      <c r="D247" s="1"/>
+      <c r="A247" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B247" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C247" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D247" s="1">
+        <v>38.7889</v>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="3"/>
-      <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
-      <c r="D248" s="1"/>
+      <c r="A248" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B248" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C248" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D248" s="1">
+        <v>38.77696</v>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="3"/>
-      <c r="B249" s="1"/>
-      <c r="C249" s="1"/>
-      <c r="D249" s="1"/>
+      <c r="A249" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B249" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C249" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D249" s="1">
+        <v>38.77973</v>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="3"/>
-      <c r="B250" s="1"/>
-      <c r="C250" s="1"/>
-      <c r="D250" s="1"/>
+      <c r="A250" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B250" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C250" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D250" s="1">
+        <v>21.09769</v>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="3"/>
-      <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
-      <c r="D251" s="1"/>
+      <c r="A251" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B251" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C251" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D251" s="1">
+        <v>21.10135</v>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="3"/>
-      <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
-      <c r="D252" s="1"/>
+      <c r="A252" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B252" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C252" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D252" s="1">
+        <v>13.52318</v>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="3"/>
-      <c r="B253" s="1"/>
-      <c r="C253" s="1"/>
-      <c r="D253" s="1"/>
+      <c r="A253" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B253" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C253" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D253" s="1">
+        <v>1.50618</v>
+      </c>
     </row>
     <row r="254">
-      <c r="A254" s="3"/>
-      <c r="B254" s="1"/>
-      <c r="C254" s="1"/>
-      <c r="D254" s="1"/>
+      <c r="A254" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B254" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C254" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D254" s="1">
+        <v>0.84495</v>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="3"/>
-      <c r="B255" s="1"/>
-      <c r="C255" s="1"/>
-      <c r="D255" s="1"/>
+      <c r="A255" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B255" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C255" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D255" s="1">
+        <v>0.30105</v>
+      </c>
     </row>
     <row r="256">
-      <c r="A256" s="3"/>
-      <c r="B256" s="1"/>
-      <c r="C256" s="1"/>
-      <c r="D256" s="1"/>
+      <c r="A256" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B256" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C256" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D256" s="1">
+        <v>0.19925</v>
+      </c>
     </row>
     <row r="257">
-      <c r="A257" s="3"/>
-      <c r="B257" s="1"/>
-      <c r="C257" s="1"/>
-      <c r="D257" s="1"/>
+      <c r="A257" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B257" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C257" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D257" s="1">
+        <v>1.69597</v>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="3"/>
-      <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
+      <c r="A258" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B258" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C258" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D258" s="1">
+        <v>0.06958</v>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="3"/>
-      <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
+      <c r="A259" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B259" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C259" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D259" s="1">
+        <v>0.84677</v>
+      </c>
     </row>
     <row r="260">
-      <c r="A260" s="3"/>
-      <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
-      <c r="D260" s="1"/>
+      <c r="A260" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B260" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C260" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D260" s="1">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="3"/>
-      <c r="B261" s="1"/>
-      <c r="C261" s="1"/>
-      <c r="D261" s="1"/>
+      <c r="A261" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B261" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C261" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D261" s="1">
+        <v>25.84437</v>
+      </c>
     </row>
     <row r="262">
-      <c r="A262" s="3"/>
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
-      <c r="D262" s="1"/>
+      <c r="A262" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B262" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C262" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D262" s="1">
+        <v>75.0</v>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="3"/>
-      <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
-      <c r="D263" s="1"/>
+      <c r="A263" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B263" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C263" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D263" s="1">
+        <v>75.0</v>
+      </c>
     </row>
     <row r="264">
-      <c r="A264" s="3"/>
-      <c r="B264" s="1"/>
-      <c r="C264" s="1"/>
-      <c r="D264" s="1"/>
+      <c r="A264" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B264" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C264" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D264" s="1">
+        <v>106.71</v>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="3"/>
-      <c r="B265" s="1"/>
-      <c r="C265" s="1"/>
-      <c r="D265" s="1"/>
+      <c r="A265" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B265" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C265" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D265" s="1">
+        <v>124.0</v>
+      </c>
     </row>
     <row r="266">
-      <c r="A266" s="3"/>
-      <c r="B266" s="1"/>
-      <c r="C266" s="1"/>
-      <c r="D266" s="1"/>
+      <c r="A266" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B266" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C266" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D266" s="1">
+        <v>104.64</v>
+      </c>
     </row>
     <row r="267">
-      <c r="A267" s="3"/>
-      <c r="B267" s="1"/>
-      <c r="C267" s="1"/>
-      <c r="D267" s="1"/>
+      <c r="A267" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B267" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C267" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D267" s="1">
+        <v>109.37</v>
+      </c>
     </row>
     <row r="268">
-      <c r="A268" s="3"/>
-      <c r="B268" s="1"/>
-      <c r="C268" s="1"/>
-      <c r="D268" s="1"/>
+      <c r="A268" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B268" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C268" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D268" s="1">
+        <v>130.89</v>
+      </c>
     </row>
     <row r="269">
-      <c r="A269" s="3"/>
-      <c r="B269" s="1"/>
-      <c r="C269" s="1"/>
-      <c r="D269" s="1"/>
+      <c r="A269" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B269" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C269" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D269" s="1">
+        <v>175.5</v>
+      </c>
     </row>
     <row r="270">
-      <c r="A270" s="3"/>
-      <c r="B270" s="1"/>
-      <c r="C270" s="1"/>
-      <c r="D270" s="1"/>
+      <c r="A270" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B270" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C270" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D270" s="1">
+        <v>127.38</v>
+      </c>
     </row>
     <row r="271">
-      <c r="A271" s="3"/>
-      <c r="B271" s="1"/>
-      <c r="C271" s="1"/>
-      <c r="D271" s="1"/>
+      <c r="A271" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B271" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C271" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D271" s="1">
+        <v>131.99</v>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="3"/>
-      <c r="B272" s="1"/>
-      <c r="C272" s="1"/>
-      <c r="D272" s="1"/>
+      <c r="A272" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B272" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C272" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D272" s="1">
+        <v>147.4</v>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="3"/>
-      <c r="B273" s="1"/>
-      <c r="C273" s="1"/>
-      <c r="D273" s="1"/>
+      <c r="A273" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B273" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C273" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D273" s="1">
+        <v>175.89</v>
+      </c>
     </row>
     <row r="274">
-      <c r="A274" s="3"/>
-      <c r="B274" s="1"/>
-      <c r="C274" s="1"/>
-      <c r="D274" s="1"/>
+      <c r="A274" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B274" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C274" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D274" s="1">
+        <v>151.7</v>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="3"/>
-      <c r="B275" s="1"/>
-      <c r="C275" s="1"/>
-      <c r="D275" s="1"/>
+      <c r="A275" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B275" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C275" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D275" s="1">
+        <v>155.0</v>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="3"/>
-      <c r="B276" s="1"/>
-      <c r="C276" s="1"/>
-      <c r="D276" s="1"/>
+      <c r="A276" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B276" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C276" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D276" s="1">
+        <v>175.5</v>
+      </c>
     </row>
     <row r="277">
-      <c r="A277" s="3"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
+      <c r="A277" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B277" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C277" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D277" s="1">
+        <v>176.2</v>
+      </c>
     </row>
     <row r="278">
-      <c r="A278" s="3"/>
-      <c r="B278" s="1"/>
-      <c r="C278" s="1"/>
-      <c r="D278" s="1"/>
+      <c r="A278" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B278" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C278" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D278" s="1">
+        <v>160.0</v>
+      </c>
     </row>
     <row r="279">
-      <c r="A279" s="3"/>
-      <c r="B279" s="1"/>
-      <c r="C279" s="1"/>
-      <c r="D279" s="1"/>
+      <c r="A279" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B279" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C279" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D279" s="1">
+        <v>160.0</v>
+      </c>
     </row>
     <row r="280">
-      <c r="A280" s="3"/>
-      <c r="B280" s="1"/>
-      <c r="C280" s="1"/>
-      <c r="D280" s="1"/>
+      <c r="A280" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B280" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C280" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D280" s="1">
+        <v>160.0</v>
+      </c>
     </row>
     <row r="281">
-      <c r="A281" s="3"/>
-      <c r="B281" s="1"/>
-      <c r="C281" s="1"/>
-      <c r="D281" s="1"/>
+      <c r="A281" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B281" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C281" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D281" s="1">
+        <v>155.0</v>
+      </c>
     </row>
     <row r="282">
-      <c r="A282" s="3"/>
-      <c r="B282" s="1"/>
-      <c r="C282" s="1"/>
-      <c r="D282" s="1"/>
+      <c r="A282" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B282" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C282" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D282" s="1">
+        <v>187.11</v>
+      </c>
     </row>
     <row r="283">
-      <c r="A283" s="3"/>
-      <c r="B283" s="1"/>
-      <c r="C283" s="1"/>
-      <c r="D283" s="1"/>
+      <c r="A283" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B283" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C283" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D283" s="1">
+        <v>180.82</v>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="3"/>
-      <c r="B284" s="1"/>
-      <c r="C284" s="1"/>
-      <c r="D284" s="1"/>
+      <c r="A284" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B284" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C284" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D284" s="1">
+        <v>169.01</v>
+      </c>
     </row>
     <row r="285">
-      <c r="A285" s="3"/>
-      <c r="B285" s="1"/>
-      <c r="C285" s="1"/>
-      <c r="D285" s="1"/>
+      <c r="A285" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B285" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C285" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D285" s="1">
+        <v>131.38</v>
+      </c>
     </row>
     <row r="286">
-      <c r="A286" s="3"/>
-      <c r="B286" s="1"/>
-      <c r="C286" s="1"/>
-      <c r="D286" s="1"/>
+      <c r="A286" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B286" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C286" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D286" s="1">
+        <v>186.0</v>
+      </c>
     </row>
     <row r="287">
-      <c r="A287" s="3"/>
-      <c r="B287" s="1"/>
-      <c r="C287" s="1"/>
-      <c r="D287" s="1"/>
+      <c r="A287" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B287" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C287" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D287" s="1">
+        <v>163.8528</v>
+      </c>
     </row>
     <row r="288">
-      <c r="A288" s="3"/>
-      <c r="B288" s="1"/>
-      <c r="C288" s="1"/>
-      <c r="D288" s="1"/>
+      <c r="A288" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B288" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C288" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D288" s="1">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="289">
-      <c r="A289" s="3"/>
-      <c r="B289" s="1"/>
-      <c r="C289" s="1"/>
-      <c r="D289" s="1"/>
+      <c r="A289" s="3">
+        <v>46207.0</v>
+      </c>
+      <c r="B289" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C289" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D289" s="1">
+        <v>119.4672</v>
+      </c>
     </row>
     <row r="290">
-      <c r="A290" s="3"/>
-      <c r="B290" s="1"/>
-      <c r="C290" s="1"/>
-      <c r="D290" s="1"/>
+      <c r="A290" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B290" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C290" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="D290" s="1">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="291">
-      <c r="A291" s="3"/>
-      <c r="B291" s="1"/>
-      <c r="C291" s="1"/>
-      <c r="D291" s="1"/>
+      <c r="A291" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B291" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C291" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D291" s="1">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="292">
-      <c r="A292" s="3"/>
-      <c r="B292" s="1"/>
-      <c r="C292" s="1"/>
-      <c r="D292" s="1"/>
+      <c r="A292" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B292" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C292" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="D292" s="1">
+        <v>131.86</v>
+      </c>
     </row>
     <row r="293">
-      <c r="A293" s="3"/>
-      <c r="B293" s="1"/>
-      <c r="C293" s="1"/>
-      <c r="D293" s="1"/>
+      <c r="A293" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B293" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C293" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D293" s="1">
+        <v>127.8</v>
+      </c>
     </row>
     <row r="294">
-      <c r="A294" s="3"/>
-      <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
-      <c r="D294" s="1"/>
+      <c r="A294" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B294" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C294" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="D294" s="1">
+        <v>149.28</v>
+      </c>
     </row>
     <row r="295">
-      <c r="A295" s="3"/>
-      <c r="B295" s="1"/>
-      <c r="C295" s="1"/>
-      <c r="D295" s="1"/>
+      <c r="A295" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B295" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C295" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="D295" s="1">
+        <v>150.8</v>
+      </c>
     </row>
     <row r="296">
-      <c r="A296" s="3"/>
-      <c r="B296" s="1"/>
-      <c r="C296" s="1"/>
-      <c r="D296" s="1"/>
+      <c r="A296" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B296" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C296" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="D296" s="1">
+        <v>140.0</v>
+      </c>
     </row>
     <row r="297">
-      <c r="A297" s="3"/>
-      <c r="B297" s="1"/>
-      <c r="C297" s="1"/>
-      <c r="D297" s="1"/>
+      <c r="A297" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B297" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C297" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="D297" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="298">
-      <c r="A298" s="3"/>
-      <c r="B298" s="1"/>
-      <c r="C298" s="1"/>
-      <c r="D298" s="1"/>
+      <c r="A298" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B298" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C298" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="D298" s="1">
+        <v>140.79</v>
+      </c>
     </row>
     <row r="299">
-      <c r="A299" s="3"/>
-      <c r="B299" s="1"/>
-      <c r="C299" s="1"/>
-      <c r="D299" s="1"/>
+      <c r="A299" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B299" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C299" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D299" s="1">
+        <v>147.0</v>
+      </c>
     </row>
     <row r="300">
-      <c r="A300" s="3"/>
-      <c r="B300" s="1"/>
-      <c r="C300" s="1"/>
-      <c r="D300" s="1"/>
+      <c r="A300" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B300" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C300" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="D300" s="1">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="301">
-      <c r="A301" s="3"/>
-      <c r="B301" s="1"/>
-      <c r="C301" s="1"/>
-      <c r="D301" s="1"/>
+      <c r="A301" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B301" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C301" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="D301" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="302">
-      <c r="A302" s="3"/>
-      <c r="B302" s="1"/>
-      <c r="C302" s="1"/>
-      <c r="D302" s="1"/>
+      <c r="A302" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B302" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C302" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="D302" s="1">
+        <v>143.5</v>
+      </c>
     </row>
     <row r="303">
-      <c r="A303" s="3"/>
-      <c r="B303" s="1"/>
-      <c r="C303" s="1"/>
-      <c r="D303" s="1"/>
+      <c r="A303" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B303" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C303" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="D303" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="304">
-      <c r="A304" s="3"/>
-      <c r="B304" s="1"/>
-      <c r="C304" s="1"/>
-      <c r="D304" s="1"/>
+      <c r="A304" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B304" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C304" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="D304" s="1">
+        <v>135.0</v>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="3"/>
-      <c r="B305" s="1"/>
-      <c r="C305" s="1"/>
-      <c r="D305" s="1"/>
+      <c r="A305" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B305" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C305" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="D305" s="1">
+        <v>135.89</v>
+      </c>
     </row>
     <row r="306">
-      <c r="A306" s="3"/>
-      <c r="B306" s="1"/>
-      <c r="C306" s="1"/>
-      <c r="D306" s="1"/>
+      <c r="A306" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B306" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C306" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="D306" s="1">
+        <v>139.4</v>
+      </c>
     </row>
     <row r="307">
-      <c r="A307" s="3"/>
-      <c r="B307" s="1"/>
-      <c r="C307" s="1"/>
-      <c r="D307" s="1"/>
+      <c r="A307" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B307" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C307" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="D307" s="1">
+        <v>138.7</v>
+      </c>
     </row>
     <row r="308">
-      <c r="A308" s="3"/>
-      <c r="B308" s="1"/>
-      <c r="C308" s="1"/>
-      <c r="D308" s="1"/>
+      <c r="A308" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B308" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C308" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="D308" s="1">
+        <v>136.9</v>
+      </c>
     </row>
     <row r="309">
-      <c r="A309" s="3"/>
-      <c r="B309" s="1"/>
-      <c r="C309" s="1"/>
-      <c r="D309" s="1"/>
+      <c r="A309" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B309" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C309" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="D309" s="1">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="310">
-      <c r="A310" s="3"/>
-      <c r="B310" s="1"/>
-      <c r="C310" s="1"/>
-      <c r="D310" s="1"/>
+      <c r="A310" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B310" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C310" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="D310" s="1">
+        <v>187.11</v>
+      </c>
     </row>
     <row r="311">
-      <c r="A311" s="3"/>
-      <c r="B311" s="1"/>
-      <c r="C311" s="1"/>
-      <c r="D311" s="1"/>
+      <c r="A311" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B311" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C311" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="D311" s="1">
+        <v>167.5</v>
+      </c>
     </row>
     <row r="312">
-      <c r="A312" s="3"/>
-      <c r="B312" s="1"/>
-      <c r="C312" s="1"/>
-      <c r="D312" s="1"/>
+      <c r="A312" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B312" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C312" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="D312" s="1">
+        <v>159.19</v>
+      </c>
     </row>
     <row r="313">
-      <c r="A313" s="3"/>
-      <c r="B313" s="1"/>
-      <c r="C313" s="1"/>
-      <c r="D313" s="1"/>
+      <c r="A313" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B313" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C313" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D313" s="1">
+        <v>145.0</v>
+      </c>
     </row>
     <row r="314">
-      <c r="A314" s="3"/>
-      <c r="B314" s="1"/>
-      <c r="C314" s="1"/>
-      <c r="D314" s="1"/>
+      <c r="A314" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B314" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C314" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="D314" s="1">
+        <v>165.0</v>
+      </c>
     </row>
     <row r="315">
-      <c r="A315" s="3"/>
-      <c r="B315" s="1"/>
-      <c r="C315" s="1"/>
-      <c r="D315" s="1"/>
+      <c r="A315" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B315" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C315" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="D315" s="1">
+        <v>147.0</v>
+      </c>
     </row>
     <row r="316">
-      <c r="A316" s="3"/>
-      <c r="B316" s="1"/>
-      <c r="C316" s="1"/>
-      <c r="D316" s="1"/>
+      <c r="A316" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B316" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C316" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="D316" s="1">
+        <v>136.9</v>
+      </c>
     </row>
     <row r="317">
-      <c r="A317" s="3"/>
-      <c r="B317" s="1"/>
-      <c r="C317" s="1"/>
-      <c r="D317" s="1"/>
+      <c r="A317" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B317" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="C317" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="D317" s="1">
+        <v>119.7</v>
+      </c>
     </row>
     <row r="318">
-      <c r="A318" s="3"/>
-      <c r="B318" s="1"/>
-      <c r="C318" s="1"/>
-      <c r="D318" s="1"/>
+      <c r="A318" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B318" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C318" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="D318" s="1">
+        <v>140.5</v>
+      </c>
     </row>
     <row r="319">
-      <c r="A319" s="3"/>
-      <c r="B319" s="1"/>
-      <c r="C319" s="1"/>
-      <c r="D319" s="1"/>
+      <c r="A319" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B319" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C319" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="D319" s="1">
+        <v>124.4</v>
+      </c>
     </row>
     <row r="320">
-      <c r="A320" s="3"/>
-      <c r="B320" s="1"/>
-      <c r="C320" s="1"/>
-      <c r="D320" s="1"/>
+      <c r="A320" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B320" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C320" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="D320" s="1">
+        <v>119.7</v>
+      </c>
     </row>
     <row r="321">
-      <c r="A321" s="3"/>
-      <c r="B321" s="1"/>
-      <c r="C321" s="1"/>
-      <c r="D321" s="1"/>
+      <c r="A321" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B321" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="C321" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D321" s="1">
+        <v>100.0</v>
+      </c>
     </row>
     <row r="322">
-      <c r="A322" s="3"/>
-      <c r="B322" s="1"/>
-      <c r="C322" s="1"/>
-      <c r="D322" s="1"/>
+      <c r="A322" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B322" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C322" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="D322" s="1">
+        <v>143.08</v>
+      </c>
     </row>
     <row r="323">
-      <c r="A323" s="3"/>
-      <c r="B323" s="1"/>
-      <c r="C323" s="1"/>
-      <c r="D323" s="1"/>
+      <c r="A323" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B323" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C323" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="D323" s="1">
+        <v>119.5</v>
+      </c>
     </row>
     <row r="324">
-      <c r="A324" s="3"/>
-      <c r="B324" s="1"/>
-      <c r="C324" s="1"/>
-      <c r="D324" s="1"/>
+      <c r="A324" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B324" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C324" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="D324" s="1">
+        <v>87.29</v>
+      </c>
     </row>
     <row r="325">
-      <c r="A325" s="3"/>
-      <c r="B325" s="1"/>
-      <c r="C325" s="1"/>
-      <c r="D325" s="1"/>
+      <c r="A325" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B325" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C325" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="D325" s="1">
+        <v>50.13</v>
+      </c>
     </row>
     <row r="326">
-      <c r="A326" s="3"/>
-      <c r="B326" s="1"/>
-      <c r="C326" s="1"/>
-      <c r="D326" s="1"/>
+      <c r="A326" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B326" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C326" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D326" s="1">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="327">
-      <c r="A327" s="3"/>
-      <c r="B327" s="1"/>
-      <c r="C327" s="1"/>
-      <c r="D327" s="1"/>
+      <c r="A327" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B327" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C327" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D327" s="1">
+        <v>31.0</v>
+      </c>
     </row>
     <row r="328">
-      <c r="A328" s="3"/>
-      <c r="B328" s="1"/>
-      <c r="C328" s="1"/>
-      <c r="D328" s="1"/>
+      <c r="A328" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B328" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C328" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="D328" s="1">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="329">
-      <c r="A329" s="3"/>
-      <c r="B329" s="1"/>
-      <c r="C329" s="1"/>
-      <c r="D329" s="1"/>
+      <c r="A329" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B329" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C329" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="D329" s="1">
+        <v>11.0</v>
+      </c>
     </row>
     <row r="330">
-      <c r="A330" s="3"/>
-      <c r="B330" s="1"/>
-      <c r="C330" s="1"/>
-      <c r="D330" s="1"/>
+      <c r="A330" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B330" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C330" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="D330" s="1">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="331">
-      <c r="A331" s="3"/>
-      <c r="B331" s="1"/>
-      <c r="C331" s="1"/>
-      <c r="D331" s="1"/>
+      <c r="A331" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B331" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C331" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D331" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="332">
-      <c r="A332" s="3"/>
-      <c r="B332" s="1"/>
-      <c r="C332" s="1"/>
-      <c r="D332" s="1"/>
+      <c r="A332" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B332" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C332" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D332" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="333">
-      <c r="A333" s="3"/>
-      <c r="B333" s="1"/>
-      <c r="C333" s="1"/>
-      <c r="D333" s="1"/>
+      <c r="A333" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B333" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C333" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="D333" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="334">
-      <c r="A334" s="3"/>
-      <c r="B334" s="1"/>
-      <c r="C334" s="1"/>
-      <c r="D334" s="1"/>
+      <c r="A334" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B334" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C334" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="D334" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="335">
-      <c r="A335" s="3"/>
-      <c r="B335" s="1"/>
-      <c r="C335" s="1"/>
-      <c r="D335" s="1"/>
+      <c r="A335" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B335" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C335" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="D335" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="336">
-      <c r="A336" s="3"/>
-      <c r="B336" s="1"/>
-      <c r="C336" s="1"/>
-      <c r="D336" s="1"/>
+      <c r="A336" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B336" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C336" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="D336" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="337">
-      <c r="A337" s="3"/>
-      <c r="B337" s="1"/>
-      <c r="C337" s="1"/>
-      <c r="D337" s="1"/>
+      <c r="A337" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B337" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C337" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="D337" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="338">
-      <c r="A338" s="3"/>
-      <c r="B338" s="1"/>
-      <c r="C338" s="1"/>
-      <c r="D338" s="1"/>
+      <c r="A338" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B338" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C338" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="D338" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="339">
-      <c r="A339" s="3"/>
-      <c r="B339" s="1"/>
-      <c r="C339" s="1"/>
-      <c r="D339" s="1"/>
+      <c r="A339" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B339" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C339" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="D339" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="340">
-      <c r="A340" s="3"/>
-      <c r="B340" s="1"/>
-      <c r="C340" s="1"/>
-      <c r="D340" s="1"/>
+      <c r="A340" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B340" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C340" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="D340" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="341">
-      <c r="A341" s="3"/>
-      <c r="B341" s="1"/>
-      <c r="C341" s="1"/>
-      <c r="D341" s="1"/>
+      <c r="A341" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B341" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C341" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="D341" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="342">
-      <c r="A342" s="3"/>
-      <c r="B342" s="1"/>
-      <c r="C342" s="1"/>
-      <c r="D342" s="1"/>
+      <c r="A342" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B342" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C342" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="D342" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="343">
-      <c r="A343" s="3"/>
-      <c r="B343" s="1"/>
-      <c r="C343" s="1"/>
-      <c r="D343" s="1"/>
+      <c r="A343" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B343" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C343" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="D343" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="344">
-      <c r="A344" s="3"/>
-      <c r="B344" s="1"/>
-      <c r="C344" s="1"/>
-      <c r="D344" s="1"/>
+      <c r="A344" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B344" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C344" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="D344" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="345">
-      <c r="A345" s="3"/>
-      <c r="B345" s="1"/>
-      <c r="C345" s="1"/>
-      <c r="D345" s="1"/>
+      <c r="A345" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B345" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C345" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="D345" s="1">
+        <v>0.84843</v>
+      </c>
     </row>
     <row r="346">
-      <c r="A346" s="3"/>
-      <c r="B346" s="1"/>
-      <c r="C346" s="1"/>
-      <c r="D346" s="1"/>
+      <c r="A346" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B346" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C346" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="D346" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="347">
-      <c r="A347" s="3"/>
-      <c r="B347" s="1"/>
-      <c r="C347" s="1"/>
-      <c r="D347" s="1"/>
+      <c r="A347" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B347" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C347" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="D347" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="348">
-      <c r="A348" s="3"/>
-      <c r="B348" s="1"/>
-      <c r="C348" s="1"/>
-      <c r="D348" s="1"/>
+      <c r="A348" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B348" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C348" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D348" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="349">
-      <c r="A349" s="3"/>
-      <c r="B349" s="1"/>
-      <c r="C349" s="1"/>
-      <c r="D349" s="1"/>
+      <c r="A349" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B349" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C349" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D349" s="1">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="350">
-      <c r="A350" s="3"/>
-      <c r="B350" s="1"/>
-      <c r="C350" s="1"/>
-      <c r="D350" s="1"/>
+      <c r="A350" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B350" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C350" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="D350" s="1">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="351">
-      <c r="A351" s="3"/>
-      <c r="B351" s="1"/>
-      <c r="C351" s="1"/>
-      <c r="D351" s="1"/>
+      <c r="A351" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B351" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C351" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="D351" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="352">
-      <c r="A352" s="3"/>
-      <c r="B352" s="1"/>
-      <c r="C352" s="1"/>
-      <c r="D352" s="1"/>
+      <c r="A352" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B352" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C352" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="D352" s="1">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="353">
-      <c r="A353" s="3"/>
-      <c r="B353" s="1"/>
-      <c r="C353" s="1"/>
-      <c r="D353" s="1"/>
+      <c r="A353" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B353" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C353" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="D353" s="1">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="354">
-      <c r="A354" s="3"/>
-      <c r="B354" s="1"/>
-      <c r="C354" s="1"/>
-      <c r="D354" s="1"/>
+      <c r="A354" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B354" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C354" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="D354" s="1">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="355">
-      <c r="A355" s="3"/>
-      <c r="B355" s="1"/>
-      <c r="C355" s="1"/>
-      <c r="D355" s="1"/>
+      <c r="A355" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B355" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C355" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="D355" s="1">
+        <v>20.99</v>
+      </c>
     </row>
     <row r="356">
-      <c r="A356" s="3"/>
-      <c r="B356" s="1"/>
-      <c r="C356" s="1"/>
-      <c r="D356" s="1"/>
+      <c r="A356" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B356" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C356" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="D356" s="1">
+        <v>26.0</v>
+      </c>
     </row>
     <row r="357">
-      <c r="A357" s="3"/>
-      <c r="B357" s="1"/>
-      <c r="C357" s="1"/>
-      <c r="D357" s="1"/>
+      <c r="A357" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B357" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C357" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="D357" s="1">
+        <v>91.78747</v>
+      </c>
     </row>
     <row r="358">
-      <c r="A358" s="3"/>
-      <c r="B358" s="1"/>
-      <c r="C358" s="1"/>
-      <c r="D358" s="1"/>
+      <c r="A358" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B358" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C358" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="D358" s="1">
+        <v>86.5</v>
+      </c>
     </row>
     <row r="359">
-      <c r="A359" s="3"/>
-      <c r="B359" s="1"/>
-      <c r="C359" s="1"/>
-      <c r="D359" s="1"/>
+      <c r="A359" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B359" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C359" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="D359" s="1">
+        <v>110.5</v>
+      </c>
     </row>
     <row r="360">
-      <c r="A360" s="3"/>
-      <c r="B360" s="1"/>
-      <c r="C360" s="1"/>
-      <c r="D360" s="1"/>
+      <c r="A360" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B360" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C360" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="D360" s="1">
+        <v>147.2</v>
+      </c>
     </row>
     <row r="361">
-      <c r="A361" s="3"/>
-      <c r="B361" s="1"/>
-      <c r="C361" s="1"/>
-      <c r="D361" s="1"/>
+      <c r="A361" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B361" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C361" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="D361" s="1">
+        <v>175.5</v>
+      </c>
     </row>
     <row r="362">
-      <c r="A362" s="3"/>
-      <c r="B362" s="1"/>
-      <c r="C362" s="1"/>
-      <c r="D362" s="1"/>
+      <c r="A362" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B362" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C362" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="D362" s="1">
+        <v>119.7</v>
+      </c>
     </row>
     <row r="363">
-      <c r="A363" s="3"/>
-      <c r="B363" s="1"/>
-      <c r="C363" s="1"/>
-      <c r="D363" s="1"/>
+      <c r="A363" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B363" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C363" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="D363" s="1">
+        <v>131.1</v>
+      </c>
     </row>
     <row r="364">
-      <c r="A364" s="3"/>
-      <c r="B364" s="1"/>
-      <c r="C364" s="1"/>
-      <c r="D364" s="1"/>
+      <c r="A364" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B364" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C364" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D364" s="1">
+        <v>139.92</v>
+      </c>
     </row>
     <row r="365">
-      <c r="A365" s="3"/>
-      <c r="B365" s="1"/>
-      <c r="C365" s="1"/>
-      <c r="D365" s="1"/>
+      <c r="A365" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B365" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C365" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="D365" s="1">
+        <v>169.28</v>
+      </c>
     </row>
     <row r="366">
-      <c r="A366" s="3"/>
-      <c r="B366" s="1"/>
-      <c r="C366" s="1"/>
-      <c r="D366" s="1"/>
+      <c r="A366" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B366" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C366" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="D366" s="1">
+        <v>118.48</v>
+      </c>
     </row>
     <row r="367">
-      <c r="A367" s="3"/>
-      <c r="B367" s="1"/>
-      <c r="C367" s="1"/>
-      <c r="D367" s="1"/>
+      <c r="A367" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B367" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C367" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="D367" s="1">
+        <v>130.03</v>
+      </c>
     </row>
     <row r="368">
-      <c r="A368" s="3"/>
-      <c r="B368" s="1"/>
-      <c r="C368" s="1"/>
-      <c r="D368" s="1"/>
+      <c r="A368" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B368" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C368" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="D368" s="1">
+        <v>175.5</v>
+      </c>
     </row>
     <row r="369">
-      <c r="A369" s="3"/>
-      <c r="B369" s="1"/>
-      <c r="C369" s="1"/>
-      <c r="D369" s="1"/>
+      <c r="A369" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B369" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C369" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="D369" s="1">
+        <v>187.11</v>
+      </c>
     </row>
     <row r="370">
-      <c r="A370" s="3"/>
-      <c r="B370" s="1"/>
-      <c r="C370" s="1"/>
-      <c r="D370" s="1"/>
+      <c r="A370" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B370" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C370" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="D370" s="1">
+        <v>157.79</v>
+      </c>
     </row>
     <row r="371">
-      <c r="A371" s="3"/>
-      <c r="B371" s="1"/>
-      <c r="C371" s="1"/>
-      <c r="D371" s="1"/>
+      <c r="A371" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B371" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C371" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="D371" s="1">
+        <v>141.96</v>
+      </c>
     </row>
     <row r="372">
-      <c r="A372" s="3"/>
-      <c r="B372" s="1"/>
-      <c r="C372" s="1"/>
-      <c r="D372" s="1"/>
+      <c r="A372" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B372" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C372" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="D372" s="1">
+        <v>174.9</v>
+      </c>
     </row>
     <row r="373">
-      <c r="A373" s="3"/>
-      <c r="B373" s="1"/>
-      <c r="C373" s="1"/>
-      <c r="D373" s="1"/>
+      <c r="A373" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B373" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C373" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="D373" s="1">
+        <v>187.11</v>
+      </c>
     </row>
     <row r="374">
-      <c r="A374" s="3"/>
-      <c r="B374" s="1"/>
-      <c r="C374" s="1"/>
-      <c r="D374" s="1"/>
+      <c r="A374" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B374" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C374" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="D374" s="1">
+        <v>173.0</v>
+      </c>
     </row>
     <row r="375">
-      <c r="A375" s="3"/>
-      <c r="B375" s="1"/>
-      <c r="C375" s="1"/>
-      <c r="D375" s="1"/>
+      <c r="A375" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B375" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C375" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="D375" s="1">
+        <v>173.0</v>
+      </c>
     </row>
     <row r="376">
-      <c r="A376" s="3"/>
-      <c r="B376" s="1"/>
-      <c r="C376" s="1"/>
-      <c r="D376" s="1"/>
+      <c r="A376" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B376" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C376" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="D376" s="1">
+        <v>173.19</v>
+      </c>
     </row>
     <row r="377">
-      <c r="A377" s="3"/>
-      <c r="B377" s="1"/>
-      <c r="C377" s="1"/>
-      <c r="D377" s="1"/>
+      <c r="A377" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B377" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C377" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="D377" s="1">
+        <v>168.0</v>
+      </c>
     </row>
     <row r="378">
-      <c r="A378" s="3"/>
-      <c r="B378" s="1"/>
-      <c r="C378" s="1"/>
-      <c r="D378" s="1"/>
+      <c r="A378" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B378" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C378" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="D378" s="1">
+        <v>183.41</v>
+      </c>
     </row>
     <row r="379">
-      <c r="A379" s="3"/>
-      <c r="B379" s="1"/>
-      <c r="C379" s="1"/>
-      <c r="D379" s="1"/>
+      <c r="A379" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B379" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C379" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="D379" s="1">
+        <v>162.37</v>
+      </c>
     </row>
     <row r="380">
-      <c r="A380" s="3"/>
-      <c r="B380" s="1"/>
-      <c r="C380" s="1"/>
-      <c r="D380" s="1"/>
+      <c r="A380" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B380" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C380" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="D380" s="1">
+        <v>149.01</v>
+      </c>
     </row>
     <row r="381">
-      <c r="A381" s="3"/>
-      <c r="B381" s="1"/>
-      <c r="C381" s="1"/>
-      <c r="D381" s="1"/>
+      <c r="A381" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B381" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C381" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="D381" s="1">
+        <v>145.21</v>
+      </c>
     </row>
     <row r="382">
-      <c r="A382" s="3"/>
-      <c r="B382" s="1"/>
-      <c r="C382" s="1"/>
-      <c r="D382" s="1"/>
+      <c r="A382" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B382" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C382" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="D382" s="1">
+        <v>187.11</v>
+      </c>
     </row>
     <row r="383">
-      <c r="A383" s="3"/>
-      <c r="B383" s="1"/>
-      <c r="C383" s="1"/>
-      <c r="D383" s="1"/>
+      <c r="A383" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B383" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C383" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="D383" s="1">
+        <v>166.10596</v>
+      </c>
     </row>
     <row r="384">
-      <c r="A384" s="3"/>
-      <c r="B384" s="1"/>
-      <c r="C384" s="1"/>
-      <c r="D384" s="1"/>
+      <c r="A384" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B384" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C384" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="D384" s="1">
+        <v>133.95404</v>
+      </c>
     </row>
     <row r="385">
-      <c r="A385" s="3"/>
-      <c r="B385" s="1"/>
-      <c r="C385" s="1"/>
-      <c r="D385" s="1"/>
+      <c r="A385" s="3">
+        <v>46208.0</v>
+      </c>
+      <c r="B385" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C385" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="D385" s="1">
+        <v>127.03</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="3"/>

--- a/dati_input/Add_on_PUN.xlsx
+++ b/dati_input/Add_on_PUN.xlsx
@@ -310,7 +310,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B2" s="1">
         <v>1.0</v>
@@ -319,12 +319,12 @@
         <v>1.0</v>
       </c>
       <c r="D2" s="1">
-        <v>161.381</v>
+        <v>151.79829</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B3" s="1">
         <v>1.0</v>
@@ -333,12 +333,12 @@
         <v>2.0</v>
       </c>
       <c r="D3" s="1">
-        <v>157.64826</v>
+        <v>168.16851</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B4" s="1">
         <v>1.0</v>
@@ -347,12 +347,12 @@
         <v>3.0</v>
       </c>
       <c r="D4" s="1">
-        <v>149.55655</v>
+        <v>151.48084</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B5" s="1">
         <v>1.0</v>
@@ -361,12 +361,12 @@
         <v>4.0</v>
       </c>
       <c r="D5" s="1">
-        <v>138.85792</v>
+        <v>140.15835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B6" s="1">
         <v>2.0</v>
@@ -375,12 +375,12 @@
         <v>5.0</v>
       </c>
       <c r="D6" s="1">
-        <v>153.33205</v>
+        <v>160.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B7" s="1">
         <v>2.0</v>
@@ -389,12 +389,12 @@
         <v>6.0</v>
       </c>
       <c r="D7" s="1">
-        <v>142.01102</v>
+        <v>150.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B8" s="1">
         <v>2.0</v>
@@ -403,12 +403,12 @@
         <v>7.0</v>
       </c>
       <c r="D8" s="1">
-        <v>132.35385</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B9" s="1">
         <v>2.0</v>
@@ -417,12 +417,12 @@
         <v>8.0</v>
       </c>
       <c r="D9" s="1">
-        <v>129.09876</v>
+        <v>139.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B10" s="1">
         <v>3.0</v>
@@ -431,12 +431,12 @@
         <v>9.0</v>
       </c>
       <c r="D10" s="1">
-        <v>133.464</v>
+        <v>135.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B11" s="1">
         <v>3.0</v>
@@ -445,12 +445,12 @@
         <v>10.0</v>
       </c>
       <c r="D11" s="1">
-        <v>132.91</v>
+        <v>132.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B12" s="1">
         <v>3.0</v>
@@ -459,12 +459,12 @@
         <v>11.0</v>
       </c>
       <c r="D12" s="1">
-        <v>132.51</v>
+        <v>134.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B13" s="1">
         <v>3.0</v>
@@ -473,12 +473,12 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="1">
-        <v>133.43</v>
+        <v>130.52</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B14" s="1">
         <v>4.0</v>
@@ -487,12 +487,12 @@
         <v>13.0</v>
       </c>
       <c r="D14" s="1">
-        <v>135.0</v>
+        <v>135.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B15" s="1">
         <v>4.0</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B16" s="1">
         <v>4.0</v>
@@ -515,12 +515,12 @@
         <v>15.0</v>
       </c>
       <c r="D16" s="1">
-        <v>136.47</v>
+        <v>133.95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B17" s="1">
         <v>4.0</v>
@@ -529,12 +529,12 @@
         <v>16.0</v>
       </c>
       <c r="D17" s="1">
-        <v>132.18</v>
+        <v>131.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B18" s="1">
         <v>5.0</v>
@@ -543,12 +543,12 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="1">
-        <v>135.0</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B19" s="1">
         <v>5.0</v>
@@ -557,12 +557,12 @@
         <v>18.0</v>
       </c>
       <c r="D19" s="1">
-        <v>135.0</v>
+        <v>131.88</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B20" s="1">
         <v>5.0</v>
@@ -571,12 +571,12 @@
         <v>19.0</v>
       </c>
       <c r="D20" s="1">
-        <v>135.0</v>
+        <v>129.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B21" s="1">
         <v>5.0</v>
@@ -585,12 +585,12 @@
         <v>20.0</v>
       </c>
       <c r="D21" s="1">
-        <v>135.0</v>
+        <v>128.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B22" s="1">
         <v>6.0</v>
@@ -599,12 +599,12 @@
         <v>21.0</v>
       </c>
       <c r="D22" s="1">
-        <v>130.0</v>
+        <v>129.93532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B23" s="1">
         <v>6.0</v>
@@ -613,12 +613,12 @@
         <v>22.0</v>
       </c>
       <c r="D23" s="1">
-        <v>138.74607</v>
+        <v>130.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B24" s="1">
         <v>6.0</v>
@@ -627,12 +627,12 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="1">
-        <v>139.5</v>
+        <v>133.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B25" s="1">
         <v>6.0</v>
@@ -641,12 +641,12 @@
         <v>24.0</v>
       </c>
       <c r="D25" s="1">
-        <v>133.03393</v>
+        <v>138.58171</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B26" s="1">
         <v>7.0</v>
@@ -655,12 +655,12 @@
         <v>25.0</v>
       </c>
       <c r="D26" s="1">
-        <v>129.36141</v>
+        <v>131.42139</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B27" s="1">
         <v>7.0</v>
@@ -669,12 +669,12 @@
         <v>26.0</v>
       </c>
       <c r="D27" s="1">
-        <v>140.0</v>
+        <v>138.59657</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B28" s="1">
         <v>7.0</v>
@@ -683,12 +683,12 @@
         <v>27.0</v>
       </c>
       <c r="D28" s="1">
-        <v>155.93</v>
+        <v>140.03273</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B29" s="1">
         <v>7.0</v>
@@ -697,12 +697,12 @@
         <v>28.0</v>
       </c>
       <c r="D29" s="1">
-        <v>160.30497</v>
+        <v>137.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B30" s="1">
         <v>8.0</v>
@@ -711,12 +711,12 @@
         <v>29.0</v>
       </c>
       <c r="D30" s="1">
-        <v>140.0</v>
+        <v>148.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B31" s="1">
         <v>8.0</v>
@@ -725,12 +725,12 @@
         <v>30.0</v>
       </c>
       <c r="D31" s="1">
-        <v>142.03</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B32" s="1">
         <v>8.0</v>
@@ -739,12 +739,12 @@
         <v>31.0</v>
       </c>
       <c r="D32" s="1">
-        <v>157.75</v>
+        <v>155.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B33" s="1">
         <v>8.0</v>
@@ -753,12 +753,12 @@
         <v>32.0</v>
       </c>
       <c r="D33" s="1">
-        <v>143.64</v>
+        <v>153.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B34" s="1">
         <v>9.0</v>
@@ -767,12 +767,12 @@
         <v>33.0</v>
       </c>
       <c r="D34" s="1">
-        <v>154.56</v>
+        <v>156.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B35" s="1">
         <v>9.0</v>
@@ -781,12 +781,12 @@
         <v>34.0</v>
       </c>
       <c r="D35" s="1">
-        <v>140.0</v>
+        <v>148.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B36" s="1">
         <v>9.0</v>
@@ -795,12 +795,12 @@
         <v>35.0</v>
       </c>
       <c r="D36" s="1">
-        <v>136.1</v>
+        <v>150.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B37" s="1">
         <v>9.0</v>
@@ -809,12 +809,12 @@
         <v>36.0</v>
       </c>
       <c r="D37" s="1">
-        <v>124.5</v>
+        <v>144.22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B38" s="1">
         <v>10.0</v>
@@ -823,12 +823,12 @@
         <v>37.0</v>
       </c>
       <c r="D38" s="1">
-        <v>170.93098</v>
+        <v>143.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B39" s="1">
         <v>10.0</v>
@@ -837,12 +837,12 @@
         <v>38.0</v>
       </c>
       <c r="D39" s="1">
-        <v>150.23</v>
+        <v>139.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B40" s="1">
         <v>10.0</v>
@@ -851,12 +851,12 @@
         <v>39.0</v>
       </c>
       <c r="D40" s="1">
-        <v>157.62</v>
+        <v>127.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B41" s="1">
         <v>10.0</v>
@@ -865,12 +865,12 @@
         <v>40.0</v>
       </c>
       <c r="D41" s="1">
-        <v>150.0</v>
+        <v>122.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B42" s="1">
         <v>11.0</v>
@@ -879,12 +879,12 @@
         <v>41.0</v>
       </c>
       <c r="D42" s="1">
-        <v>144.7452</v>
+        <v>140.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B43" s="1">
         <v>11.0</v>
@@ -893,12 +893,12 @@
         <v>42.0</v>
       </c>
       <c r="D43" s="1">
-        <v>143.32869</v>
+        <v>139.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B44" s="1">
         <v>11.0</v>
@@ -907,12 +907,12 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="1">
-        <v>138.22569</v>
+        <v>130.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B45" s="1">
         <v>11.0</v>
@@ -921,12 +921,12 @@
         <v>44.0</v>
       </c>
       <c r="D45" s="1">
-        <v>129.05204</v>
+        <v>121.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B46" s="1">
         <v>12.0</v>
@@ -935,12 +935,12 @@
         <v>45.0</v>
       </c>
       <c r="D46" s="1">
-        <v>135.4549</v>
+        <v>137.28442</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B47" s="1">
         <v>12.0</v>
@@ -949,12 +949,12 @@
         <v>46.0</v>
       </c>
       <c r="D47" s="1">
-        <v>134.40851</v>
+        <v>134.79981</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B48" s="1">
         <v>12.0</v>
@@ -963,12 +963,12 @@
         <v>47.0</v>
       </c>
       <c r="D48" s="1">
-        <v>130.34208</v>
+        <v>130.24228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B49" s="1">
         <v>12.0</v>
@@ -977,12 +977,12 @@
         <v>48.0</v>
       </c>
       <c r="D49" s="1">
-        <v>123.82599</v>
+        <v>127.34467</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B50" s="1">
         <v>13.0</v>
@@ -991,12 +991,12 @@
         <v>49.0</v>
       </c>
       <c r="D50" s="1">
-        <v>131.86534</v>
+        <v>133.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B51" s="1">
         <v>13.0</v>
@@ -1005,12 +1005,12 @@
         <v>50.0</v>
       </c>
       <c r="D51" s="1">
-        <v>132.1795</v>
+        <v>129.71</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B52" s="1">
         <v>13.0</v>
@@ -1019,12 +1019,12 @@
         <v>51.0</v>
       </c>
       <c r="D52" s="1">
-        <v>130.26788</v>
+        <v>132.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B53" s="1">
         <v>13.0</v>
@@ -1033,12 +1033,12 @@
         <v>52.0</v>
       </c>
       <c r="D53" s="1">
-        <v>118.16962</v>
+        <v>127.38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B54" s="1">
         <v>14.0</v>
@@ -1047,12 +1047,12 @@
         <v>53.0</v>
       </c>
       <c r="D54" s="1">
-        <v>120.53019</v>
+        <v>127.38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B55" s="1">
         <v>14.0</v>
@@ -1061,12 +1061,12 @@
         <v>54.0</v>
       </c>
       <c r="D55" s="1">
-        <v>127.60973</v>
+        <v>132.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B56" s="1">
         <v>14.0</v>
@@ -1075,12 +1075,12 @@
         <v>55.0</v>
       </c>
       <c r="D56" s="1">
-        <v>128.39114</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B57" s="1">
         <v>14.0</v>
@@ -1089,12 +1089,12 @@
         <v>56.0</v>
       </c>
       <c r="D57" s="1">
-        <v>124.43429</v>
+        <v>131.61</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B58" s="1">
         <v>15.0</v>
@@ -1103,12 +1103,12 @@
         <v>57.0</v>
       </c>
       <c r="D58" s="1">
-        <v>123.35455</v>
+        <v>117.69476</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B59" s="1">
         <v>15.0</v>
@@ -1117,12 +1117,12 @@
         <v>58.0</v>
       </c>
       <c r="D59" s="1">
-        <v>125.07128</v>
+        <v>118.83196</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B60" s="1">
         <v>15.0</v>
@@ -1131,12 +1131,12 @@
         <v>59.0</v>
       </c>
       <c r="D60" s="1">
-        <v>128.96373</v>
+        <v>125.24628</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B61" s="1">
         <v>15.0</v>
@@ -1145,12 +1145,12 @@
         <v>60.0</v>
       </c>
       <c r="D61" s="1">
-        <v>135.15186</v>
+        <v>127.39841</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B62" s="1">
         <v>16.0</v>
@@ -1159,12 +1159,12 @@
         <v>61.0</v>
       </c>
       <c r="D62" s="1">
-        <v>130.27563</v>
+        <v>115.52722</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B63" s="1">
         <v>16.0</v>
@@ -1173,12 +1173,12 @@
         <v>62.0</v>
       </c>
       <c r="D63" s="1">
-        <v>126.19221</v>
+        <v>119.28192</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B64" s="1">
         <v>16.0</v>
@@ -1187,12 +1187,12 @@
         <v>63.0</v>
       </c>
       <c r="D64" s="1">
-        <v>131.10639</v>
+        <v>132.95524</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B65" s="1">
         <v>16.0</v>
@@ -1201,12 +1201,12 @@
         <v>64.0</v>
       </c>
       <c r="D65" s="1">
-        <v>140.79515</v>
+        <v>149.2446</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B66" s="1">
         <v>17.0</v>
@@ -1215,12 +1215,12 @@
         <v>65.0</v>
       </c>
       <c r="D66" s="1">
-        <v>134.7087</v>
+        <v>126.52</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B67" s="1">
         <v>17.0</v>
@@ -1229,12 +1229,12 @@
         <v>66.0</v>
       </c>
       <c r="D67" s="1">
-        <v>138.83513</v>
+        <v>140.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B68" s="1">
         <v>17.0</v>
@@ -1243,12 +1243,12 @@
         <v>67.0</v>
       </c>
       <c r="D68" s="1">
-        <v>142.74018</v>
+        <v>154.88681</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B69" s="1">
         <v>17.0</v>
@@ -1257,12 +1257,12 @@
         <v>68.0</v>
       </c>
       <c r="D69" s="1">
-        <v>136.89</v>
+        <v>157.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B70" s="1">
         <v>18.0</v>
@@ -1271,12 +1271,12 @@
         <v>69.0</v>
       </c>
       <c r="D70" s="1">
-        <v>118.17</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B71" s="1">
         <v>18.0</v>
@@ -1285,12 +1285,12 @@
         <v>70.0</v>
       </c>
       <c r="D71" s="1">
-        <v>119.6</v>
+        <v>119.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B72" s="1">
         <v>18.0</v>
@@ -1299,12 +1299,12 @@
         <v>71.0</v>
       </c>
       <c r="D72" s="1">
-        <v>125.73552</v>
+        <v>137.40144</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B73" s="1">
         <v>18.0</v>
@@ -1313,12 +1313,12 @@
         <v>72.0</v>
       </c>
       <c r="D73" s="1">
-        <v>156.49448</v>
+        <v>149.53856</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B74" s="1">
         <v>19.0</v>
@@ -1327,12 +1327,12 @@
         <v>73.0</v>
       </c>
       <c r="D74" s="1">
-        <v>116.31</v>
+        <v>133.76</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B75" s="1">
         <v>19.0</v>
@@ -1341,12 +1341,12 @@
         <v>74.0</v>
       </c>
       <c r="D75" s="1">
-        <v>135.0</v>
+        <v>145.96</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B76" s="1">
         <v>19.0</v>
@@ -1355,12 +1355,12 @@
         <v>75.0</v>
       </c>
       <c r="D76" s="1">
-        <v>154.95821</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B77" s="1">
         <v>19.0</v>
@@ -1369,12 +1369,12 @@
         <v>76.0</v>
       </c>
       <c r="D77" s="1">
-        <v>177.04</v>
+        <v>169.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B78" s="1">
         <v>20.0</v>
@@ -1383,12 +1383,12 @@
         <v>77.0</v>
       </c>
       <c r="D78" s="1">
-        <v>140.5</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B79" s="1">
         <v>20.0</v>
@@ -1397,12 +1397,12 @@
         <v>78.0</v>
       </c>
       <c r="D79" s="1">
-        <v>173.0</v>
+        <v>165.95</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B80" s="1">
         <v>20.0</v>
@@ -1411,12 +1411,12 @@
         <v>79.0</v>
       </c>
       <c r="D80" s="1">
-        <v>176.3</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B81" s="1">
         <v>20.0</v>
@@ -1425,12 +1425,12 @@
         <v>80.0</v>
       </c>
       <c r="D81" s="1">
-        <v>189.77</v>
+        <v>188.83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B82" s="1">
         <v>21.0</v>
@@ -1439,12 +1439,12 @@
         <v>81.0</v>
       </c>
       <c r="D82" s="1">
-        <v>174.65</v>
+        <v>167.79</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B83" s="1">
         <v>21.0</v>
@@ -1453,12 +1453,12 @@
         <v>82.0</v>
       </c>
       <c r="D83" s="1">
-        <v>174.94</v>
+        <v>171.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B84" s="1">
         <v>21.0</v>
@@ -1467,12 +1467,12 @@
         <v>83.0</v>
       </c>
       <c r="D84" s="1">
-        <v>174.94</v>
+        <v>174.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B85" s="1">
         <v>21.0</v>
@@ -1481,12 +1481,12 @@
         <v>84.0</v>
       </c>
       <c r="D85" s="1">
-        <v>174.94</v>
+        <v>184.12452</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B86" s="1">
         <v>22.0</v>
@@ -1495,12 +1495,12 @@
         <v>85.0</v>
       </c>
       <c r="D86" s="1">
-        <v>182.37807</v>
+        <v>174.65334</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B87" s="1">
         <v>22.0</v>
@@ -1509,12 +1509,12 @@
         <v>86.0</v>
       </c>
       <c r="D87" s="1">
-        <v>170.99</v>
+        <v>169.91467</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B88" s="1">
         <v>22.0</v>
@@ -1523,12 +1523,12 @@
         <v>87.0</v>
       </c>
       <c r="D88" s="1">
-        <v>162.10193</v>
+        <v>169.05464</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B89" s="1">
         <v>22.0</v>
@@ -1537,12 +1537,12 @@
         <v>88.0</v>
       </c>
       <c r="D89" s="1">
-        <v>144.53</v>
+        <v>166.6443</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B90" s="1">
         <v>23.0</v>
@@ -1551,12 +1551,12 @@
         <v>89.0</v>
       </c>
       <c r="D90" s="1">
-        <v>161.0674</v>
+        <v>174.77198</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B91" s="1">
         <v>23.0</v>
@@ -1565,12 +1565,12 @@
         <v>90.0</v>
       </c>
       <c r="D91" s="1">
-        <v>157.1626</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B92" s="1">
         <v>23.0</v>
@@ -1579,12 +1579,12 @@
         <v>91.0</v>
       </c>
       <c r="D92" s="1">
-        <v>146.77</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B93" s="1">
         <v>23.0</v>
@@ -1593,12 +1593,12 @@
         <v>92.0</v>
       </c>
       <c r="D93" s="1">
-        <v>135.0</v>
+        <v>158.21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B94" s="1">
         <v>24.0</v>
@@ -1607,12 +1607,12 @@
         <v>93.0</v>
       </c>
       <c r="D94" s="1">
-        <v>153.20497</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B95" s="1">
         <v>24.0</v>
@@ -1621,12 +1621,12 @@
         <v>94.0</v>
       </c>
       <c r="D95" s="1">
-        <v>140.24503</v>
+        <v>166.11</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B96" s="1">
         <v>24.0</v>
@@ -1635,12 +1635,12 @@
         <v>95.0</v>
       </c>
       <c r="D96" s="1">
-        <v>130.03</v>
+        <v>144.22</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3">
-        <v>46205.0</v>
+        <v>46209.0</v>
       </c>
       <c r="B97" s="1">
         <v>24.0</v>
@@ -1649,4040 +1649,1736 @@
         <v>96.0</v>
       </c>
       <c r="D97" s="1">
-        <v>119.6</v>
+        <v>135.0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B98" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C98" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D98" s="1">
-        <v>138.24452</v>
-      </c>
+      <c r="A98" s="3"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
     </row>
     <row r="99">
-      <c r="A99" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B99" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C99" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D99" s="1">
-        <v>144.0</v>
-      </c>
+      <c r="A99" s="3"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1"/>
     </row>
     <row r="100">
-      <c r="A100" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B100" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C100" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D100" s="1">
-        <v>137.73</v>
-      </c>
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
     </row>
     <row r="101">
-      <c r="A101" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B101" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C101" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D101" s="1">
-        <v>143.04</v>
-      </c>
+      <c r="A101" s="3"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
     </row>
     <row r="102">
-      <c r="A102" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B102" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C102" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D102" s="1">
-        <v>153.0</v>
-      </c>
+      <c r="A102" s="3"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
     </row>
     <row r="103">
-      <c r="A103" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B103" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C103" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D103" s="1">
-        <v>153.0</v>
-      </c>
+      <c r="A103" s="3"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1"/>
     </row>
     <row r="104">
-      <c r="A104" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B104" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C104" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D104" s="1">
-        <v>138.0</v>
-      </c>
+      <c r="A104" s="3"/>
+      <c r="B104" s="1"/>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
     </row>
     <row r="105">
-      <c r="A105" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B105" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C105" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D105" s="1">
-        <v>134.92</v>
-      </c>
+      <c r="A105" s="3"/>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1"/>
     </row>
     <row r="106">
-      <c r="A106" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B106" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C106" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D106" s="1">
-        <v>144.0</v>
-      </c>
+      <c r="A106" s="3"/>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
     </row>
     <row r="107">
-      <c r="A107" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B107" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C107" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D107" s="1">
-        <v>136.66</v>
-      </c>
+      <c r="A107" s="3"/>
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
     </row>
     <row r="108">
-      <c r="A108" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B108" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C108" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D108" s="1">
-        <v>138.0</v>
-      </c>
+      <c r="A108" s="3"/>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1"/>
     </row>
     <row r="109">
-      <c r="A109" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B109" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C109" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D109" s="1">
-        <v>134.92</v>
-      </c>
+      <c r="A109" s="3"/>
+      <c r="B109" s="1"/>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1"/>
     </row>
     <row r="110">
-      <c r="A110" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B110" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C110" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D110" s="1">
-        <v>134.46</v>
-      </c>
+      <c r="A110" s="3"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
     </row>
     <row r="111">
-      <c r="A111" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B111" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C111" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D111" s="1">
-        <v>133.49</v>
-      </c>
+      <c r="A111" s="3"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
     </row>
     <row r="112">
-      <c r="A112" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B112" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C112" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D112" s="1">
-        <v>133.49</v>
-      </c>
+      <c r="A112" s="3"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
     </row>
     <row r="113">
-      <c r="A113" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B113" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C113" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="D113" s="1">
-        <v>134.92</v>
-      </c>
+      <c r="A113" s="3"/>
+      <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
+      <c r="D113" s="1"/>
     </row>
     <row r="114">
-      <c r="A114" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B114" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C114" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D114" s="1">
-        <v>133.34</v>
-      </c>
+      <c r="A114" s="3"/>
+      <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
     </row>
     <row r="115">
-      <c r="A115" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B115" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C115" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="D115" s="1">
-        <v>136.66</v>
-      </c>
+      <c r="A115" s="3"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
     </row>
     <row r="116">
-      <c r="A116" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B116" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C116" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D116" s="1">
-        <v>132.52</v>
-      </c>
+      <c r="A116" s="3"/>
+      <c r="B116" s="1"/>
+      <c r="C116" s="1"/>
+      <c r="D116" s="1"/>
     </row>
     <row r="117">
-      <c r="A117" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B117" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C117" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D117" s="1">
-        <v>131.0</v>
-      </c>
+      <c r="A117" s="3"/>
+      <c r="B117" s="1"/>
+      <c r="C117" s="1"/>
+      <c r="D117" s="1"/>
     </row>
     <row r="118">
-      <c r="A118" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B118" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C118" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D118" s="1">
-        <v>138.12</v>
-      </c>
+      <c r="A118" s="3"/>
+      <c r="B118" s="1"/>
+      <c r="C118" s="1"/>
+      <c r="D118" s="1"/>
     </row>
     <row r="119">
-      <c r="A119" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B119" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C119" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="D119" s="1">
-        <v>134.92</v>
-      </c>
+      <c r="A119" s="3"/>
+      <c r="B119" s="1"/>
+      <c r="C119" s="1"/>
+      <c r="D119" s="1"/>
     </row>
     <row r="120">
-      <c r="A120" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B120" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C120" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D120" s="1">
-        <v>124.86</v>
-      </c>
+      <c r="A120" s="3"/>
+      <c r="B120" s="1"/>
+      <c r="C120" s="1"/>
+      <c r="D120" s="1"/>
     </row>
     <row r="121">
-      <c r="A121" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B121" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C121" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="D121" s="1">
-        <v>122.5</v>
-      </c>
+      <c r="A121" s="3"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
     </row>
     <row r="122">
-      <c r="A122" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B122" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C122" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="D122" s="1">
-        <v>125.0</v>
-      </c>
+      <c r="A122" s="3"/>
+      <c r="B122" s="1"/>
+      <c r="C122" s="1"/>
+      <c r="D122" s="1"/>
     </row>
     <row r="123">
-      <c r="A123" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B123" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C123" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D123" s="1">
-        <v>153.0</v>
-      </c>
+      <c r="A123" s="3"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
     </row>
     <row r="124">
-      <c r="A124" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B124" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C124" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D124" s="1">
-        <v>148.41404</v>
-      </c>
+      <c r="A124" s="3"/>
+      <c r="B124" s="1"/>
+      <c r="C124" s="1"/>
+      <c r="D124" s="1"/>
     </row>
     <row r="125">
-      <c r="A125" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B125" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C125" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="D125" s="1">
-        <v>150.53</v>
-      </c>
+      <c r="A125" s="3"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
     </row>
     <row r="126">
-      <c r="A126" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B126" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C126" s="1">
-        <v>29.0</v>
-      </c>
-      <c r="D126" s="1">
-        <v>148.0</v>
-      </c>
+      <c r="A126" s="3"/>
+      <c r="B126" s="1"/>
+      <c r="C126" s="1"/>
+      <c r="D126" s="1"/>
     </row>
     <row r="127">
-      <c r="A127" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B127" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C127" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D127" s="1">
-        <v>150.74</v>
-      </c>
+      <c r="A127" s="3"/>
+      <c r="B127" s="1"/>
+      <c r="C127" s="1"/>
+      <c r="D127" s="1"/>
     </row>
     <row r="128">
-      <c r="A128" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B128" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C128" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="D128" s="1">
-        <v>145.0</v>
-      </c>
+      <c r="A128" s="3"/>
+      <c r="B128" s="1"/>
+      <c r="C128" s="1"/>
+      <c r="D128" s="1"/>
     </row>
     <row r="129">
-      <c r="A129" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B129" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C129" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="D129" s="1">
-        <v>135.55</v>
-      </c>
+      <c r="A129" s="3"/>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="D129" s="1"/>
     </row>
     <row r="130">
-      <c r="A130" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B130" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C130" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D130" s="1">
-        <v>139.5</v>
-      </c>
+      <c r="A130" s="3"/>
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="D130" s="1"/>
     </row>
     <row r="131">
-      <c r="A131" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B131" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C131" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="D131" s="1">
-        <v>135.0</v>
-      </c>
+      <c r="A131" s="3"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
     </row>
     <row r="132">
-      <c r="A132" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B132" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C132" s="1">
-        <v>35.0</v>
-      </c>
-      <c r="D132" s="1">
-        <v>132.63</v>
-      </c>
+      <c r="A132" s="3"/>
+      <c r="B132" s="1"/>
+      <c r="C132" s="1"/>
+      <c r="D132" s="1"/>
     </row>
     <row r="133">
-      <c r="A133" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B133" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C133" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D133" s="1">
-        <v>132.87</v>
-      </c>
+      <c r="A133" s="3"/>
+      <c r="B133" s="1"/>
+      <c r="C133" s="1"/>
+      <c r="D133" s="1"/>
     </row>
     <row r="134">
-      <c r="A134" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B134" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C134" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D134" s="1">
-        <v>122.4</v>
-      </c>
+      <c r="A134" s="3"/>
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="D134" s="1"/>
     </row>
     <row r="135">
-      <c r="A135" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B135" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C135" s="1">
-        <v>38.0</v>
-      </c>
-      <c r="D135" s="1">
-        <v>132.0</v>
-      </c>
+      <c r="A135" s="3"/>
+      <c r="B135" s="1"/>
+      <c r="C135" s="1"/>
+      <c r="D135" s="1"/>
     </row>
     <row r="136">
-      <c r="A136" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B136" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C136" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D136" s="1">
-        <v>131.05</v>
-      </c>
+      <c r="A136" s="3"/>
+      <c r="B136" s="1"/>
+      <c r="C136" s="1"/>
+      <c r="D136" s="1"/>
     </row>
     <row r="137">
-      <c r="A137" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B137" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C137" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="D137" s="1">
-        <v>134.95</v>
-      </c>
+      <c r="A137" s="3"/>
+      <c r="B137" s="1"/>
+      <c r="C137" s="1"/>
+      <c r="D137" s="1"/>
     </row>
     <row r="138">
-      <c r="A138" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B138" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C138" s="1">
-        <v>41.0</v>
-      </c>
-      <c r="D138" s="1">
-        <v>138.98804</v>
-      </c>
+      <c r="A138" s="3"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
     </row>
     <row r="139">
-      <c r="A139" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B139" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C139" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="D139" s="1">
-        <v>124.74414</v>
-      </c>
+      <c r="A139" s="3"/>
+      <c r="B139" s="1"/>
+      <c r="C139" s="1"/>
+      <c r="D139" s="1"/>
     </row>
     <row r="140">
-      <c r="A140" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B140" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C140" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D140" s="1">
-        <v>130.30468</v>
-      </c>
+      <c r="A140" s="3"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
     </row>
     <row r="141">
-      <c r="A141" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B141" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C141" s="1">
-        <v>44.0</v>
-      </c>
-      <c r="D141" s="1">
-        <v>124.52</v>
-      </c>
+      <c r="A141" s="3"/>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
+      <c r="D141" s="1"/>
     </row>
     <row r="142">
-      <c r="A142" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B142" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C142" s="1">
-        <v>45.0</v>
-      </c>
-      <c r="D142" s="1">
-        <v>127.08493</v>
-      </c>
+      <c r="A142" s="3"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
     </row>
     <row r="143">
-      <c r="A143" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B143" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C143" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D143" s="1">
-        <v>133.45756</v>
-      </c>
+      <c r="A143" s="3"/>
+      <c r="B143" s="1"/>
+      <c r="C143" s="1"/>
+      <c r="D143" s="1"/>
     </row>
     <row r="144">
-      <c r="A144" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B144" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C144" s="1">
-        <v>47.0</v>
-      </c>
-      <c r="D144" s="1">
-        <v>121.84111</v>
-      </c>
+      <c r="A144" s="3"/>
+      <c r="B144" s="1"/>
+      <c r="C144" s="1"/>
+      <c r="D144" s="1"/>
     </row>
     <row r="145">
-      <c r="A145" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B145" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C145" s="1">
-        <v>48.0</v>
-      </c>
-      <c r="D145" s="1">
-        <v>134.04681</v>
-      </c>
+      <c r="A145" s="3"/>
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="D145" s="1"/>
     </row>
     <row r="146">
-      <c r="A146" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B146" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C146" s="1">
-        <v>49.0</v>
-      </c>
-      <c r="D146" s="1">
-        <v>114.58</v>
-      </c>
+      <c r="A146" s="3"/>
+      <c r="B146" s="1"/>
+      <c r="C146" s="1"/>
+      <c r="D146" s="1"/>
     </row>
     <row r="147">
-      <c r="A147" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B147" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C147" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D147" s="1">
-        <v>114.86</v>
-      </c>
+      <c r="A147" s="3"/>
+      <c r="B147" s="1"/>
+      <c r="C147" s="1"/>
+      <c r="D147" s="1"/>
     </row>
     <row r="148">
-      <c r="A148" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B148" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C148" s="1">
-        <v>51.0</v>
-      </c>
-      <c r="D148" s="1">
-        <v>115.18</v>
-      </c>
+      <c r="A148" s="3"/>
+      <c r="B148" s="1"/>
+      <c r="C148" s="1"/>
+      <c r="D148" s="1"/>
     </row>
     <row r="149">
-      <c r="A149" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B149" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C149" s="1">
-        <v>52.0</v>
-      </c>
-      <c r="D149" s="1">
-        <v>124.52</v>
-      </c>
+      <c r="A149" s="3"/>
+      <c r="B149" s="1"/>
+      <c r="C149" s="1"/>
+      <c r="D149" s="1"/>
     </row>
     <row r="150">
-      <c r="A150" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B150" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C150" s="1">
-        <v>53.0</v>
-      </c>
-      <c r="D150" s="1">
-        <v>127.39</v>
-      </c>
+      <c r="A150" s="3"/>
+      <c r="B150" s="1"/>
+      <c r="C150" s="1"/>
+      <c r="D150" s="1"/>
     </row>
     <row r="151">
-      <c r="A151" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B151" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C151" s="1">
-        <v>54.0</v>
-      </c>
-      <c r="D151" s="1">
-        <v>128.57</v>
-      </c>
+      <c r="A151" s="3"/>
+      <c r="B151" s="1"/>
+      <c r="C151" s="1"/>
+      <c r="D151" s="1"/>
     </row>
     <row r="152">
-      <c r="A152" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B152" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C152" s="1">
-        <v>55.0</v>
-      </c>
-      <c r="D152" s="1">
-        <v>132.45</v>
-      </c>
+      <c r="A152" s="3"/>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="D152" s="1"/>
     </row>
     <row r="153">
-      <c r="A153" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B153" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C153" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D153" s="1">
-        <v>131.59</v>
-      </c>
+      <c r="A153" s="3"/>
+      <c r="B153" s="1"/>
+      <c r="C153" s="1"/>
+      <c r="D153" s="1"/>
     </row>
     <row r="154">
-      <c r="A154" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B154" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C154" s="1">
-        <v>57.0</v>
-      </c>
-      <c r="D154" s="1">
-        <v>127.06</v>
-      </c>
+      <c r="A154" s="3"/>
+      <c r="B154" s="1"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="1"/>
     </row>
     <row r="155">
-      <c r="A155" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B155" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C155" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="D155" s="1">
-        <v>130.7</v>
-      </c>
+      <c r="A155" s="3"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
     </row>
     <row r="156">
-      <c r="A156" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B156" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C156" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D156" s="1">
-        <v>131.87</v>
-      </c>
+      <c r="A156" s="3"/>
+      <c r="B156" s="1"/>
+      <c r="C156" s="1"/>
+      <c r="D156" s="1"/>
     </row>
     <row r="157">
-      <c r="A157" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B157" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C157" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="D157" s="1">
-        <v>130.77</v>
-      </c>
+      <c r="A157" s="3"/>
+      <c r="B157" s="1"/>
+      <c r="C157" s="1"/>
+      <c r="D157" s="1"/>
     </row>
     <row r="158">
-      <c r="A158" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B158" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C158" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="D158" s="1">
-        <v>133.47</v>
-      </c>
+      <c r="A158" s="3"/>
+      <c r="B158" s="1"/>
+      <c r="C158" s="1"/>
+      <c r="D158" s="1"/>
     </row>
     <row r="159">
-      <c r="A159" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B159" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C159" s="1">
-        <v>62.0</v>
-      </c>
-      <c r="D159" s="1">
-        <v>133.0</v>
-      </c>
+      <c r="A159" s="3"/>
+      <c r="B159" s="1"/>
+      <c r="C159" s="1"/>
+      <c r="D159" s="1"/>
     </row>
     <row r="160">
-      <c r="A160" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B160" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C160" s="1">
-        <v>63.0</v>
-      </c>
-      <c r="D160" s="1">
-        <v>124.52</v>
-      </c>
+      <c r="A160" s="3"/>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
     </row>
     <row r="161">
-      <c r="A161" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B161" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C161" s="1">
-        <v>64.0</v>
-      </c>
-      <c r="D161" s="1">
-        <v>125.8</v>
-      </c>
+      <c r="A161" s="3"/>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
     </row>
     <row r="162">
-      <c r="A162" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B162" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C162" s="1">
-        <v>65.0</v>
-      </c>
-      <c r="D162" s="1">
-        <v>124.0</v>
-      </c>
+      <c r="A162" s="3"/>
+      <c r="B162" s="1"/>
+      <c r="C162" s="1"/>
+      <c r="D162" s="1"/>
     </row>
     <row r="163">
-      <c r="A163" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B163" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C163" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D163" s="1">
-        <v>133.0</v>
-      </c>
+      <c r="A163" s="3"/>
+      <c r="B163" s="1"/>
+      <c r="C163" s="1"/>
+      <c r="D163" s="1"/>
     </row>
     <row r="164">
-      <c r="A164" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B164" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C164" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="D164" s="1">
-        <v>134.3</v>
-      </c>
+      <c r="A164" s="3"/>
+      <c r="B164" s="1"/>
+      <c r="C164" s="1"/>
+      <c r="D164" s="1"/>
     </row>
     <row r="165">
-      <c r="A165" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B165" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C165" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D165" s="1">
-        <v>129.1</v>
-      </c>
+      <c r="A165" s="3"/>
+      <c r="B165" s="1"/>
+      <c r="C165" s="1"/>
+      <c r="D165" s="1"/>
     </row>
     <row r="166">
-      <c r="A166" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B166" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C166" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D166" s="1">
-        <v>121.63534</v>
-      </c>
+      <c r="A166" s="3"/>
+      <c r="B166" s="1"/>
+      <c r="C166" s="1"/>
+      <c r="D166" s="1"/>
     </row>
     <row r="167">
-      <c r="A167" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B167" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C167" s="1">
-        <v>70.0</v>
-      </c>
-      <c r="D167" s="1">
-        <v>126.63</v>
-      </c>
+      <c r="A167" s="3"/>
+      <c r="B167" s="1"/>
+      <c r="C167" s="1"/>
+      <c r="D167" s="1"/>
     </row>
     <row r="168">
-      <c r="A168" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B168" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C168" s="1">
-        <v>71.0</v>
-      </c>
-      <c r="D168" s="1">
-        <v>155.74</v>
-      </c>
+      <c r="A168" s="3"/>
+      <c r="B168" s="1"/>
+      <c r="C168" s="1"/>
+      <c r="D168" s="1"/>
     </row>
     <row r="169">
-      <c r="A169" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B169" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C169" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D169" s="1">
-        <v>164.0</v>
-      </c>
+      <c r="A169" s="3"/>
+      <c r="B169" s="1"/>
+      <c r="C169" s="1"/>
+      <c r="D169" s="1"/>
     </row>
     <row r="170">
-      <c r="A170" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B170" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C170" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="D170" s="1">
-        <v>126.39</v>
-      </c>
+      <c r="A170" s="3"/>
+      <c r="B170" s="1"/>
+      <c r="C170" s="1"/>
+      <c r="D170" s="1"/>
     </row>
     <row r="171">
-      <c r="A171" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B171" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C171" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="D171" s="1">
-        <v>139.67</v>
-      </c>
+      <c r="A171" s="3"/>
+      <c r="B171" s="1"/>
+      <c r="C171" s="1"/>
+      <c r="D171" s="1"/>
     </row>
     <row r="172">
-      <c r="A172" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B172" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C172" s="1">
-        <v>75.0</v>
-      </c>
-      <c r="D172" s="1">
-        <v>164.0</v>
-      </c>
+      <c r="A172" s="3"/>
+      <c r="B172" s="1"/>
+      <c r="C172" s="1"/>
+      <c r="D172" s="1"/>
     </row>
     <row r="173">
-      <c r="A173" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B173" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C173" s="1">
-        <v>76.0</v>
-      </c>
-      <c r="D173" s="1">
-        <v>175.0</v>
-      </c>
+      <c r="A173" s="3"/>
+      <c r="B173" s="1"/>
+      <c r="C173" s="1"/>
+      <c r="D173" s="1"/>
     </row>
     <row r="174">
-      <c r="A174" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B174" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C174" s="1">
-        <v>77.0</v>
-      </c>
-      <c r="D174" s="1">
-        <v>154.97</v>
-      </c>
+      <c r="A174" s="3"/>
+      <c r="B174" s="1"/>
+      <c r="C174" s="1"/>
+      <c r="D174" s="1"/>
     </row>
     <row r="175">
-      <c r="A175" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B175" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C175" s="1">
-        <v>78.0</v>
-      </c>
-      <c r="D175" s="1">
-        <v>153.38</v>
-      </c>
+      <c r="A175" s="3"/>
+      <c r="B175" s="1"/>
+      <c r="C175" s="1"/>
+      <c r="D175" s="1"/>
     </row>
     <row r="176">
-      <c r="A176" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B176" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C176" s="1">
-        <v>79.0</v>
-      </c>
-      <c r="D176" s="1">
-        <v>159.82</v>
-      </c>
+      <c r="A176" s="3"/>
+      <c r="B176" s="1"/>
+      <c r="C176" s="1"/>
+      <c r="D176" s="1"/>
     </row>
     <row r="177">
-      <c r="A177" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B177" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C177" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="D177" s="1">
-        <v>170.8</v>
-      </c>
+      <c r="A177" s="3"/>
+      <c r="B177" s="1"/>
+      <c r="C177" s="1"/>
+      <c r="D177" s="1"/>
     </row>
     <row r="178">
-      <c r="A178" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B178" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C178" s="1">
-        <v>81.0</v>
-      </c>
-      <c r="D178" s="1">
-        <v>168.0</v>
-      </c>
+      <c r="A178" s="3"/>
+      <c r="B178" s="1"/>
+      <c r="C178" s="1"/>
+      <c r="D178" s="1"/>
     </row>
     <row r="179">
-      <c r="A179" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B179" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C179" s="1">
-        <v>82.0</v>
-      </c>
-      <c r="D179" s="1">
-        <v>167.1</v>
-      </c>
+      <c r="A179" s="3"/>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1"/>
+      <c r="D179" s="1"/>
     </row>
     <row r="180">
-      <c r="A180" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B180" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C180" s="1">
-        <v>83.0</v>
-      </c>
-      <c r="D180" s="1">
-        <v>170.45</v>
-      </c>
+      <c r="A180" s="3"/>
+      <c r="B180" s="1"/>
+      <c r="C180" s="1"/>
+      <c r="D180" s="1"/>
     </row>
     <row r="181">
-      <c r="A181" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B181" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C181" s="1">
-        <v>84.0</v>
-      </c>
-      <c r="D181" s="1">
-        <v>175.18</v>
-      </c>
+      <c r="A181" s="3"/>
+      <c r="B181" s="1"/>
+      <c r="C181" s="1"/>
+      <c r="D181" s="1"/>
     </row>
     <row r="182">
-      <c r="A182" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B182" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C182" s="1">
-        <v>85.0</v>
-      </c>
-      <c r="D182" s="1">
-        <v>164.0</v>
-      </c>
+      <c r="A182" s="3"/>
+      <c r="B182" s="1"/>
+      <c r="C182" s="1"/>
+      <c r="D182" s="1"/>
     </row>
     <row r="183">
-      <c r="A183" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B183" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C183" s="1">
-        <v>86.0</v>
-      </c>
-      <c r="D183" s="1">
-        <v>159.5</v>
-      </c>
+      <c r="A183" s="3"/>
+      <c r="B183" s="1"/>
+      <c r="C183" s="1"/>
+      <c r="D183" s="1"/>
     </row>
     <row r="184">
-      <c r="A184" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B184" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C184" s="1">
-        <v>87.0</v>
-      </c>
-      <c r="D184" s="1">
-        <v>158.16</v>
-      </c>
+      <c r="A184" s="3"/>
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
     </row>
     <row r="185">
-      <c r="A185" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B185" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C185" s="1">
-        <v>88.0</v>
-      </c>
-      <c r="D185" s="1">
-        <v>156.22</v>
-      </c>
+      <c r="A185" s="3"/>
+      <c r="B185" s="1"/>
+      <c r="C185" s="1"/>
+      <c r="D185" s="1"/>
     </row>
     <row r="186">
-      <c r="A186" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B186" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C186" s="1">
-        <v>89.0</v>
-      </c>
-      <c r="D186" s="1">
-        <v>156.32623</v>
-      </c>
+      <c r="A186" s="3"/>
+      <c r="B186" s="1"/>
+      <c r="C186" s="1"/>
+      <c r="D186" s="1"/>
     </row>
     <row r="187">
-      <c r="A187" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B187" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C187" s="1">
-        <v>90.0</v>
-      </c>
-      <c r="D187" s="1">
-        <v>163.35</v>
-      </c>
+      <c r="A187" s="3"/>
+      <c r="B187" s="1"/>
+      <c r="C187" s="1"/>
+      <c r="D187" s="1"/>
     </row>
     <row r="188">
-      <c r="A188" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B188" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C188" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D188" s="1">
-        <v>145.61219</v>
-      </c>
+      <c r="A188" s="3"/>
+      <c r="B188" s="1"/>
+      <c r="C188" s="1"/>
+      <c r="D188" s="1"/>
     </row>
     <row r="189">
-      <c r="A189" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B189" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C189" s="1">
-        <v>92.0</v>
-      </c>
-      <c r="D189" s="1">
-        <v>135.53</v>
-      </c>
+      <c r="A189" s="3"/>
+      <c r="B189" s="1"/>
+      <c r="C189" s="1"/>
+      <c r="D189" s="1"/>
     </row>
     <row r="190">
-      <c r="A190" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B190" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C190" s="1">
-        <v>93.0</v>
-      </c>
-      <c r="D190" s="1">
-        <v>156.53</v>
-      </c>
+      <c r="A190" s="3"/>
+      <c r="B190" s="1"/>
+      <c r="C190" s="1"/>
+      <c r="D190" s="1"/>
     </row>
     <row r="191">
-      <c r="A191" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B191" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C191" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D191" s="1">
-        <v>141.20729</v>
-      </c>
+      <c r="A191" s="3"/>
+      <c r="B191" s="1"/>
+      <c r="C191" s="1"/>
+      <c r="D191" s="1"/>
     </row>
     <row r="192">
-      <c r="A192" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B192" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C192" s="1">
-        <v>95.0</v>
-      </c>
-      <c r="D192" s="1">
-        <v>134.99777</v>
-      </c>
+      <c r="A192" s="3"/>
+      <c r="B192" s="1"/>
+      <c r="C192" s="1"/>
+      <c r="D192" s="1"/>
     </row>
     <row r="193">
-      <c r="A193" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="B193" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C193" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="D193" s="1">
-        <v>131.0</v>
-      </c>
+      <c r="A193" s="3"/>
+      <c r="B193" s="1"/>
+      <c r="C193" s="1"/>
+      <c r="D193" s="1"/>
     </row>
     <row r="194">
-      <c r="A194" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B194" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C194" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D194" s="1">
-        <v>137.0</v>
-      </c>
+      <c r="A194" s="3"/>
+      <c r="B194" s="1"/>
+      <c r="C194" s="1"/>
+      <c r="D194" s="1"/>
     </row>
     <row r="195">
-      <c r="A195" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B195" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C195" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D195" s="1">
-        <v>137.0</v>
-      </c>
+      <c r="A195" s="3"/>
+      <c r="B195" s="1"/>
+      <c r="C195" s="1"/>
+      <c r="D195" s="1"/>
     </row>
     <row r="196">
-      <c r="A196" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B196" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C196" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D196" s="1">
-        <v>137.0</v>
-      </c>
+      <c r="A196" s="3"/>
+      <c r="B196" s="1"/>
+      <c r="C196" s="1"/>
+      <c r="D196" s="1"/>
     </row>
     <row r="197">
-      <c r="A197" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B197" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C197" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D197" s="1">
-        <v>137.0</v>
-      </c>
+      <c r="A197" s="3"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="1"/>
+      <c r="D197" s="1"/>
     </row>
     <row r="198">
-      <c r="A198" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B198" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C198" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D198" s="1">
-        <v>161.5</v>
-      </c>
+      <c r="A198" s="3"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="1"/>
+      <c r="D198" s="1"/>
     </row>
     <row r="199">
-      <c r="A199" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B199" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C199" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D199" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A199" s="3"/>
+      <c r="B199" s="1"/>
+      <c r="C199" s="1"/>
+      <c r="D199" s="1"/>
     </row>
     <row r="200">
-      <c r="A200" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B200" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C200" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D200" s="1">
-        <v>141.48</v>
-      </c>
+      <c r="A200" s="3"/>
+      <c r="B200" s="1"/>
+      <c r="C200" s="1"/>
+      <c r="D200" s="1"/>
     </row>
     <row r="201">
-      <c r="A201" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B201" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C201" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D201" s="1">
-        <v>136.0</v>
-      </c>
+      <c r="A201" s="3"/>
+      <c r="B201" s="1"/>
+      <c r="C201" s="1"/>
+      <c r="D201" s="1"/>
     </row>
     <row r="202">
-      <c r="A202" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B202" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C202" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D202" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A202" s="3"/>
+      <c r="B202" s="1"/>
+      <c r="C202" s="1"/>
+      <c r="D202" s="1"/>
     </row>
     <row r="203">
-      <c r="A203" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B203" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C203" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D203" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A203" s="3"/>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1"/>
+      <c r="D203" s="1"/>
     </row>
     <row r="204">
-      <c r="A204" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B204" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C204" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D204" s="1">
-        <v>140.56</v>
-      </c>
+      <c r="A204" s="3"/>
+      <c r="B204" s="1"/>
+      <c r="C204" s="1"/>
+      <c r="D204" s="1"/>
     </row>
     <row r="205">
-      <c r="A205" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B205" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C205" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D205" s="1">
-        <v>139.6</v>
-      </c>
+      <c r="A205" s="3"/>
+      <c r="B205" s="1"/>
+      <c r="C205" s="1"/>
+      <c r="D205" s="1"/>
     </row>
     <row r="206">
-      <c r="A206" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B206" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C206" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D206" s="1">
-        <v>135.7</v>
-      </c>
+      <c r="A206" s="3"/>
+      <c r="B206" s="1"/>
+      <c r="C206" s="1"/>
+      <c r="D206" s="1"/>
     </row>
     <row r="207">
-      <c r="A207" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B207" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C207" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D207" s="1">
-        <v>139.5</v>
-      </c>
+      <c r="A207" s="3"/>
+      <c r="B207" s="1"/>
+      <c r="C207" s="1"/>
+      <c r="D207" s="1"/>
     </row>
     <row r="208">
-      <c r="A208" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B208" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C208" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D208" s="1">
-        <v>133.99</v>
-      </c>
+      <c r="A208" s="3"/>
+      <c r="B208" s="1"/>
+      <c r="C208" s="1"/>
+      <c r="D208" s="1"/>
     </row>
     <row r="209">
-      <c r="A209" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B209" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C209" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="D209" s="1">
-        <v>130.81</v>
-      </c>
+      <c r="A209" s="3"/>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1"/>
+      <c r="D209" s="1"/>
     </row>
     <row r="210">
-      <c r="A210" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B210" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C210" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D210" s="1">
-        <v>140.5</v>
-      </c>
+      <c r="A210" s="3"/>
+      <c r="B210" s="1"/>
+      <c r="C210" s="1"/>
+      <c r="D210" s="1"/>
     </row>
     <row r="211">
-      <c r="A211" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B211" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C211" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="D211" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A211" s="3"/>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1"/>
+      <c r="D211" s="1"/>
     </row>
     <row r="212">
-      <c r="A212" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B212" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C212" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D212" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A212" s="3"/>
+      <c r="B212" s="1"/>
+      <c r="C212" s="1"/>
+      <c r="D212" s="1"/>
     </row>
     <row r="213">
-      <c r="A213" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B213" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C213" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D213" s="1">
-        <v>136.17</v>
-      </c>
+      <c r="A213" s="3"/>
+      <c r="B213" s="1"/>
+      <c r="C213" s="1"/>
+      <c r="D213" s="1"/>
     </row>
     <row r="214">
-      <c r="A214" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B214" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C214" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D214" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A214" s="3"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
     </row>
     <row r="215">
-      <c r="A215" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B215" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C215" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="D215" s="1">
-        <v>133.29</v>
-      </c>
+      <c r="A215" s="3"/>
+      <c r="B215" s="1"/>
+      <c r="C215" s="1"/>
+      <c r="D215" s="1"/>
     </row>
     <row r="216">
-      <c r="A216" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B216" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C216" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D216" s="1">
-        <v>129.19</v>
-      </c>
+      <c r="A216" s="3"/>
+      <c r="B216" s="1"/>
+      <c r="C216" s="1"/>
+      <c r="D216" s="1"/>
     </row>
     <row r="217">
-      <c r="A217" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B217" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C217" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="D217" s="1">
-        <v>118.0</v>
-      </c>
+      <c r="A217" s="3"/>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1"/>
+      <c r="D217" s="1"/>
     </row>
     <row r="218">
-      <c r="A218" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B218" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C218" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="D218" s="1">
-        <v>135.0</v>
-      </c>
+      <c r="A218" s="3"/>
+      <c r="B218" s="1"/>
+      <c r="C218" s="1"/>
+      <c r="D218" s="1"/>
     </row>
     <row r="219">
-      <c r="A219" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B219" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C219" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D219" s="1">
-        <v>126.53</v>
-      </c>
+      <c r="A219" s="3"/>
+      <c r="B219" s="1"/>
+      <c r="C219" s="1"/>
+      <c r="D219" s="1"/>
     </row>
     <row r="220">
-      <c r="A220" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B220" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C220" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D220" s="1">
-        <v>128.09</v>
-      </c>
+      <c r="A220" s="3"/>
+      <c r="B220" s="1"/>
+      <c r="C220" s="1"/>
+      <c r="D220" s="1"/>
     </row>
     <row r="221">
-      <c r="A221" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B221" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C221" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="D221" s="1">
-        <v>118.02</v>
-      </c>
+      <c r="A221" s="3"/>
+      <c r="B221" s="1"/>
+      <c r="C221" s="1"/>
+      <c r="D221" s="1"/>
     </row>
     <row r="222">
-      <c r="A222" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B222" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C222" s="1">
-        <v>29.0</v>
-      </c>
-      <c r="D222" s="1">
-        <v>144.73</v>
-      </c>
+      <c r="A222" s="3"/>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1"/>
+      <c r="D222" s="1"/>
     </row>
     <row r="223">
-      <c r="A223" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B223" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C223" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D223" s="1">
-        <v>137.0</v>
-      </c>
+      <c r="A223" s="3"/>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
     </row>
     <row r="224">
-      <c r="A224" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B224" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C224" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="D224" s="1">
-        <v>122.31</v>
-      </c>
+      <c r="A224" s="3"/>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
     </row>
     <row r="225">
-      <c r="A225" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B225" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C225" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="D225" s="1">
-        <v>112.44</v>
-      </c>
+      <c r="A225" s="3"/>
+      <c r="B225" s="1"/>
+      <c r="C225" s="1"/>
+      <c r="D225" s="1"/>
     </row>
     <row r="226">
-      <c r="A226" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B226" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C226" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D226" s="1">
-        <v>173.0</v>
-      </c>
+      <c r="A226" s="3"/>
+      <c r="B226" s="1"/>
+      <c r="C226" s="1"/>
+      <c r="D226" s="1"/>
     </row>
     <row r="227">
-      <c r="A227" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B227" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C227" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="D227" s="1">
-        <v>162.54</v>
-      </c>
+      <c r="A227" s="3"/>
+      <c r="B227" s="1"/>
+      <c r="C227" s="1"/>
+      <c r="D227" s="1"/>
     </row>
     <row r="228">
-      <c r="A228" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B228" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C228" s="1">
-        <v>35.0</v>
-      </c>
-      <c r="D228" s="1">
-        <v>123.0</v>
-      </c>
+      <c r="A228" s="3"/>
+      <c r="B228" s="1"/>
+      <c r="C228" s="1"/>
+      <c r="D228" s="1"/>
     </row>
     <row r="229">
-      <c r="A229" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B229" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C229" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D229" s="1">
-        <v>111.43</v>
-      </c>
+      <c r="A229" s="3"/>
+      <c r="B229" s="1"/>
+      <c r="C229" s="1"/>
+      <c r="D229" s="1"/>
     </row>
     <row r="230">
-      <c r="A230" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B230" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C230" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D230" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A230" s="3"/>
+      <c r="B230" s="1"/>
+      <c r="C230" s="1"/>
+      <c r="D230" s="1"/>
     </row>
     <row r="231">
-      <c r="A231" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B231" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C231" s="1">
-        <v>38.0</v>
-      </c>
-      <c r="D231" s="1">
-        <v>134.04</v>
-      </c>
+      <c r="A231" s="3"/>
+      <c r="B231" s="1"/>
+      <c r="C231" s="1"/>
+      <c r="D231" s="1"/>
     </row>
     <row r="232">
-      <c r="A232" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B232" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C232" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D232" s="1">
-        <v>111.78</v>
-      </c>
+      <c r="A232" s="3"/>
+      <c r="B232" s="1"/>
+      <c r="C232" s="1"/>
+      <c r="D232" s="1"/>
     </row>
     <row r="233">
-      <c r="A233" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B233" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C233" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="D233" s="1">
-        <v>105.14</v>
-      </c>
+      <c r="A233" s="3"/>
+      <c r="B233" s="1"/>
+      <c r="C233" s="1"/>
+      <c r="D233" s="1"/>
     </row>
     <row r="234">
-      <c r="A234" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B234" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C234" s="1">
-        <v>41.0</v>
-      </c>
-      <c r="D234" s="1">
-        <v>61.11</v>
-      </c>
+      <c r="A234" s="3"/>
+      <c r="B234" s="1"/>
+      <c r="C234" s="1"/>
+      <c r="D234" s="1"/>
     </row>
     <row r="235">
-      <c r="A235" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B235" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C235" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="D235" s="1">
-        <v>51.4</v>
-      </c>
+      <c r="A235" s="3"/>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
     </row>
     <row r="236">
-      <c r="A236" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B236" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C236" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D236" s="1">
-        <v>49.32</v>
-      </c>
+      <c r="A236" s="3"/>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
     </row>
     <row r="237">
-      <c r="A237" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B237" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C237" s="1">
-        <v>44.0</v>
-      </c>
-      <c r="D237" s="1">
-        <v>49.32</v>
-      </c>
+      <c r="A237" s="3"/>
+      <c r="B237" s="1"/>
+      <c r="C237" s="1"/>
+      <c r="D237" s="1"/>
     </row>
     <row r="238">
-      <c r="A238" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B238" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C238" s="1">
-        <v>45.0</v>
-      </c>
-      <c r="D238" s="1">
-        <v>13.74653</v>
-      </c>
+      <c r="A238" s="3"/>
+      <c r="B238" s="1"/>
+      <c r="C238" s="1"/>
+      <c r="D238" s="1"/>
     </row>
     <row r="239">
-      <c r="A239" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B239" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C239" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D239" s="1">
-        <v>13.56261</v>
-      </c>
+      <c r="A239" s="3"/>
+      <c r="B239" s="1"/>
+      <c r="C239" s="1"/>
+      <c r="D239" s="1"/>
     </row>
     <row r="240">
-      <c r="A240" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B240" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C240" s="1">
-        <v>47.0</v>
-      </c>
-      <c r="D240" s="1">
-        <v>12.70886</v>
-      </c>
+      <c r="A240" s="3"/>
+      <c r="B240" s="1"/>
+      <c r="C240" s="1"/>
+      <c r="D240" s="1"/>
     </row>
     <row r="241">
-      <c r="A241" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B241" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C241" s="1">
-        <v>48.0</v>
-      </c>
-      <c r="D241" s="1">
-        <v>4.23241</v>
-      </c>
+      <c r="A241" s="3"/>
+      <c r="B241" s="1"/>
+      <c r="C241" s="1"/>
+      <c r="D241" s="1"/>
     </row>
     <row r="242">
-      <c r="A242" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B242" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C242" s="1">
-        <v>49.0</v>
-      </c>
-      <c r="D242" s="1">
-        <v>35.21</v>
-      </c>
+      <c r="A242" s="3"/>
+      <c r="B242" s="1"/>
+      <c r="C242" s="1"/>
+      <c r="D242" s="1"/>
     </row>
     <row r="243">
-      <c r="A243" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B243" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C243" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D243" s="1">
-        <v>40.57322</v>
-      </c>
+      <c r="A243" s="3"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
     </row>
     <row r="244">
-      <c r="A244" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B244" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C244" s="1">
-        <v>51.0</v>
-      </c>
-      <c r="D244" s="1">
-        <v>43.57981</v>
-      </c>
+      <c r="A244" s="3"/>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1"/>
+      <c r="D244" s="1"/>
     </row>
     <row r="245">
-      <c r="A245" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B245" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C245" s="1">
-        <v>52.0</v>
-      </c>
-      <c r="D245" s="1">
-        <v>40.98</v>
-      </c>
+      <c r="A245" s="3"/>
+      <c r="B245" s="1"/>
+      <c r="C245" s="1"/>
+      <c r="D245" s="1"/>
     </row>
     <row r="246">
-      <c r="A246" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B246" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C246" s="1">
-        <v>53.0</v>
-      </c>
-      <c r="D246" s="1">
-        <v>38.92551</v>
-      </c>
+      <c r="A246" s="3"/>
+      <c r="B246" s="1"/>
+      <c r="C246" s="1"/>
+      <c r="D246" s="1"/>
     </row>
     <row r="247">
-      <c r="A247" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B247" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C247" s="1">
-        <v>54.0</v>
-      </c>
-      <c r="D247" s="1">
-        <v>38.7889</v>
-      </c>
+      <c r="A247" s="3"/>
+      <c r="B247" s="1"/>
+      <c r="C247" s="1"/>
+      <c r="D247" s="1"/>
     </row>
     <row r="248">
-      <c r="A248" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B248" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C248" s="1">
-        <v>55.0</v>
-      </c>
-      <c r="D248" s="1">
-        <v>38.77696</v>
-      </c>
+      <c r="A248" s="3"/>
+      <c r="B248" s="1"/>
+      <c r="C248" s="1"/>
+      <c r="D248" s="1"/>
     </row>
     <row r="249">
-      <c r="A249" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B249" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C249" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D249" s="1">
-        <v>38.77973</v>
-      </c>
+      <c r="A249" s="3"/>
+      <c r="B249" s="1"/>
+      <c r="C249" s="1"/>
+      <c r="D249" s="1"/>
     </row>
     <row r="250">
-      <c r="A250" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B250" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C250" s="1">
-        <v>57.0</v>
-      </c>
-      <c r="D250" s="1">
-        <v>21.09769</v>
-      </c>
+      <c r="A250" s="3"/>
+      <c r="B250" s="1"/>
+      <c r="C250" s="1"/>
+      <c r="D250" s="1"/>
     </row>
     <row r="251">
-      <c r="A251" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B251" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C251" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="D251" s="1">
-        <v>21.10135</v>
-      </c>
+      <c r="A251" s="3"/>
+      <c r="B251" s="1"/>
+      <c r="C251" s="1"/>
+      <c r="D251" s="1"/>
     </row>
     <row r="252">
-      <c r="A252" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B252" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C252" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D252" s="1">
-        <v>13.52318</v>
-      </c>
+      <c r="A252" s="3"/>
+      <c r="B252" s="1"/>
+      <c r="C252" s="1"/>
+      <c r="D252" s="1"/>
     </row>
     <row r="253">
-      <c r="A253" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B253" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C253" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="D253" s="1">
-        <v>1.50618</v>
-      </c>
+      <c r="A253" s="3"/>
+      <c r="B253" s="1"/>
+      <c r="C253" s="1"/>
+      <c r="D253" s="1"/>
     </row>
     <row r="254">
-      <c r="A254" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B254" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C254" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="D254" s="1">
-        <v>0.84495</v>
-      </c>
+      <c r="A254" s="3"/>
+      <c r="B254" s="1"/>
+      <c r="C254" s="1"/>
+      <c r="D254" s="1"/>
     </row>
     <row r="255">
-      <c r="A255" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B255" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C255" s="1">
-        <v>62.0</v>
-      </c>
-      <c r="D255" s="1">
-        <v>0.30105</v>
-      </c>
+      <c r="A255" s="3"/>
+      <c r="B255" s="1"/>
+      <c r="C255" s="1"/>
+      <c r="D255" s="1"/>
     </row>
     <row r="256">
-      <c r="A256" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B256" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C256" s="1">
-        <v>63.0</v>
-      </c>
-      <c r="D256" s="1">
-        <v>0.19925</v>
-      </c>
+      <c r="A256" s="3"/>
+      <c r="B256" s="1"/>
+      <c r="C256" s="1"/>
+      <c r="D256" s="1"/>
     </row>
     <row r="257">
-      <c r="A257" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B257" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C257" s="1">
-        <v>64.0</v>
-      </c>
-      <c r="D257" s="1">
-        <v>1.69597</v>
-      </c>
+      <c r="A257" s="3"/>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1"/>
+      <c r="D257" s="1"/>
     </row>
     <row r="258">
-      <c r="A258" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B258" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C258" s="1">
-        <v>65.0</v>
-      </c>
-      <c r="D258" s="1">
-        <v>0.06958</v>
-      </c>
+      <c r="A258" s="3"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
     </row>
     <row r="259">
-      <c r="A259" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B259" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C259" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D259" s="1">
-        <v>0.84677</v>
-      </c>
+      <c r="A259" s="3"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
     </row>
     <row r="260">
-      <c r="A260" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B260" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C260" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="D260" s="1">
-        <v>2.0</v>
-      </c>
+      <c r="A260" s="3"/>
+      <c r="B260" s="1"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="1"/>
     </row>
     <row r="261">
-      <c r="A261" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B261" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C261" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D261" s="1">
-        <v>25.84437</v>
-      </c>
+      <c r="A261" s="3"/>
+      <c r="B261" s="1"/>
+      <c r="C261" s="1"/>
+      <c r="D261" s="1"/>
     </row>
     <row r="262">
-      <c r="A262" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B262" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C262" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D262" s="1">
-        <v>75.0</v>
-      </c>
+      <c r="A262" s="3"/>
+      <c r="B262" s="1"/>
+      <c r="C262" s="1"/>
+      <c r="D262" s="1"/>
     </row>
     <row r="263">
-      <c r="A263" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B263" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C263" s="1">
-        <v>70.0</v>
-      </c>
-      <c r="D263" s="1">
-        <v>75.0</v>
-      </c>
+      <c r="A263" s="3"/>
+      <c r="B263" s="1"/>
+      <c r="C263" s="1"/>
+      <c r="D263" s="1"/>
     </row>
     <row r="264">
-      <c r="A264" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B264" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C264" s="1">
-        <v>71.0</v>
-      </c>
-      <c r="D264" s="1">
-        <v>106.71</v>
-      </c>
+      <c r="A264" s="3"/>
+      <c r="B264" s="1"/>
+      <c r="C264" s="1"/>
+      <c r="D264" s="1"/>
     </row>
     <row r="265">
-      <c r="A265" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B265" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C265" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D265" s="1">
-        <v>124.0</v>
-      </c>
+      <c r="A265" s="3"/>
+      <c r="B265" s="1"/>
+      <c r="C265" s="1"/>
+      <c r="D265" s="1"/>
     </row>
     <row r="266">
-      <c r="A266" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B266" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C266" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="D266" s="1">
-        <v>104.64</v>
-      </c>
+      <c r="A266" s="3"/>
+      <c r="B266" s="1"/>
+      <c r="C266" s="1"/>
+      <c r="D266" s="1"/>
     </row>
     <row r="267">
-      <c r="A267" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B267" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C267" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="D267" s="1">
-        <v>109.37</v>
-      </c>
+      <c r="A267" s="3"/>
+      <c r="B267" s="1"/>
+      <c r="C267" s="1"/>
+      <c r="D267" s="1"/>
     </row>
     <row r="268">
-      <c r="A268" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B268" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C268" s="1">
-        <v>75.0</v>
-      </c>
-      <c r="D268" s="1">
-        <v>130.89</v>
-      </c>
+      <c r="A268" s="3"/>
+      <c r="B268" s="1"/>
+      <c r="C268" s="1"/>
+      <c r="D268" s="1"/>
     </row>
     <row r="269">
-      <c r="A269" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B269" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C269" s="1">
-        <v>76.0</v>
-      </c>
-      <c r="D269" s="1">
-        <v>175.5</v>
-      </c>
+      <c r="A269" s="3"/>
+      <c r="B269" s="1"/>
+      <c r="C269" s="1"/>
+      <c r="D269" s="1"/>
     </row>
     <row r="270">
-      <c r="A270" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B270" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C270" s="1">
-        <v>77.0</v>
-      </c>
-      <c r="D270" s="1">
-        <v>127.38</v>
-      </c>
+      <c r="A270" s="3"/>
+      <c r="B270" s="1"/>
+      <c r="C270" s="1"/>
+      <c r="D270" s="1"/>
     </row>
     <row r="271">
-      <c r="A271" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B271" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C271" s="1">
-        <v>78.0</v>
-      </c>
-      <c r="D271" s="1">
-        <v>131.99</v>
-      </c>
+      <c r="A271" s="3"/>
+      <c r="B271" s="1"/>
+      <c r="C271" s="1"/>
+      <c r="D271" s="1"/>
     </row>
     <row r="272">
-      <c r="A272" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B272" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C272" s="1">
-        <v>79.0</v>
-      </c>
-      <c r="D272" s="1">
-        <v>147.4</v>
-      </c>
+      <c r="A272" s="3"/>
+      <c r="B272" s="1"/>
+      <c r="C272" s="1"/>
+      <c r="D272" s="1"/>
     </row>
     <row r="273">
-      <c r="A273" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B273" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C273" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="D273" s="1">
-        <v>175.89</v>
-      </c>
+      <c r="A273" s="3"/>
+      <c r="B273" s="1"/>
+      <c r="C273" s="1"/>
+      <c r="D273" s="1"/>
     </row>
     <row r="274">
-      <c r="A274" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B274" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C274" s="1">
-        <v>81.0</v>
-      </c>
-      <c r="D274" s="1">
-        <v>151.7</v>
-      </c>
+      <c r="A274" s="3"/>
+      <c r="B274" s="1"/>
+      <c r="C274" s="1"/>
+      <c r="D274" s="1"/>
     </row>
     <row r="275">
-      <c r="A275" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B275" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C275" s="1">
-        <v>82.0</v>
-      </c>
-      <c r="D275" s="1">
-        <v>155.0</v>
-      </c>
+      <c r="A275" s="3"/>
+      <c r="B275" s="1"/>
+      <c r="C275" s="1"/>
+      <c r="D275" s="1"/>
     </row>
     <row r="276">
-      <c r="A276" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B276" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C276" s="1">
-        <v>83.0</v>
-      </c>
-      <c r="D276" s="1">
-        <v>175.5</v>
-      </c>
+      <c r="A276" s="3"/>
+      <c r="B276" s="1"/>
+      <c r="C276" s="1"/>
+      <c r="D276" s="1"/>
     </row>
     <row r="277">
-      <c r="A277" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B277" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C277" s="1">
-        <v>84.0</v>
-      </c>
-      <c r="D277" s="1">
-        <v>176.2</v>
-      </c>
+      <c r="A277" s="3"/>
+      <c r="B277" s="1"/>
+      <c r="C277" s="1"/>
+      <c r="D277" s="1"/>
     </row>
     <row r="278">
-      <c r="A278" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B278" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C278" s="1">
-        <v>85.0</v>
-      </c>
-      <c r="D278" s="1">
-        <v>160.0</v>
-      </c>
+      <c r="A278" s="3"/>
+      <c r="B278" s="1"/>
+      <c r="C278" s="1"/>
+      <c r="D278" s="1"/>
     </row>
     <row r="279">
-      <c r="A279" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B279" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C279" s="1">
-        <v>86.0</v>
-      </c>
-      <c r="D279" s="1">
-        <v>160.0</v>
-      </c>
+      <c r="A279" s="3"/>
+      <c r="B279" s="1"/>
+      <c r="C279" s="1"/>
+      <c r="D279" s="1"/>
     </row>
     <row r="280">
-      <c r="A280" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B280" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C280" s="1">
-        <v>87.0</v>
-      </c>
-      <c r="D280" s="1">
-        <v>160.0</v>
-      </c>
+      <c r="A280" s="3"/>
+      <c r="B280" s="1"/>
+      <c r="C280" s="1"/>
+      <c r="D280" s="1"/>
     </row>
     <row r="281">
-      <c r="A281" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B281" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C281" s="1">
-        <v>88.0</v>
-      </c>
-      <c r="D281" s="1">
-        <v>155.0</v>
-      </c>
+      <c r="A281" s="3"/>
+      <c r="B281" s="1"/>
+      <c r="C281" s="1"/>
+      <c r="D281" s="1"/>
     </row>
     <row r="282">
-      <c r="A282" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B282" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C282" s="1">
-        <v>89.0</v>
-      </c>
-      <c r="D282" s="1">
-        <v>187.11</v>
-      </c>
+      <c r="A282" s="3"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
     </row>
     <row r="283">
-      <c r="A283" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B283" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C283" s="1">
-        <v>90.0</v>
-      </c>
-      <c r="D283" s="1">
-        <v>180.82</v>
-      </c>
+      <c r="A283" s="3"/>
+      <c r="B283" s="1"/>
+      <c r="C283" s="1"/>
+      <c r="D283" s="1"/>
     </row>
     <row r="284">
-      <c r="A284" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B284" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C284" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D284" s="1">
-        <v>169.01</v>
-      </c>
+      <c r="A284" s="3"/>
+      <c r="B284" s="1"/>
+      <c r="C284" s="1"/>
+      <c r="D284" s="1"/>
     </row>
     <row r="285">
-      <c r="A285" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B285" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C285" s="1">
-        <v>92.0</v>
-      </c>
-      <c r="D285" s="1">
-        <v>131.38</v>
-      </c>
+      <c r="A285" s="3"/>
+      <c r="B285" s="1"/>
+      <c r="C285" s="1"/>
+      <c r="D285" s="1"/>
     </row>
     <row r="286">
-      <c r="A286" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B286" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C286" s="1">
-        <v>93.0</v>
-      </c>
-      <c r="D286" s="1">
-        <v>186.0</v>
-      </c>
+      <c r="A286" s="3"/>
+      <c r="B286" s="1"/>
+      <c r="C286" s="1"/>
+      <c r="D286" s="1"/>
     </row>
     <row r="287">
-      <c r="A287" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B287" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C287" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D287" s="1">
-        <v>163.8528</v>
-      </c>
+      <c r="A287" s="3"/>
+      <c r="B287" s="1"/>
+      <c r="C287" s="1"/>
+      <c r="D287" s="1"/>
     </row>
     <row r="288">
-      <c r="A288" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B288" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C288" s="1">
-        <v>95.0</v>
-      </c>
-      <c r="D288" s="1">
-        <v>145.0</v>
-      </c>
+      <c r="A288" s="3"/>
+      <c r="B288" s="1"/>
+      <c r="C288" s="1"/>
+      <c r="D288" s="1"/>
     </row>
     <row r="289">
-      <c r="A289" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="B289" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C289" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="D289" s="1">
-        <v>119.4672</v>
-      </c>
+      <c r="A289" s="3"/>
+      <c r="B289" s="1"/>
+      <c r="C289" s="1"/>
+      <c r="D289" s="1"/>
     </row>
     <row r="290">
-      <c r="A290" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B290" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C290" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D290" s="1">
-        <v>140.0</v>
-      </c>
+      <c r="A290" s="3"/>
+      <c r="B290" s="1"/>
+      <c r="C290" s="1"/>
+      <c r="D290" s="1"/>
     </row>
     <row r="291">
-      <c r="A291" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B291" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C291" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="D291" s="1">
-        <v>145.0</v>
-      </c>
+      <c r="A291" s="3"/>
+      <c r="B291" s="1"/>
+      <c r="C291" s="1"/>
+      <c r="D291" s="1"/>
     </row>
     <row r="292">
-      <c r="A292" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B292" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C292" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="D292" s="1">
-        <v>131.86</v>
-      </c>
+      <c r="A292" s="3"/>
+      <c r="B292" s="1"/>
+      <c r="C292" s="1"/>
+      <c r="D292" s="1"/>
     </row>
     <row r="293">
-      <c r="A293" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B293" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C293" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="D293" s="1">
-        <v>127.8</v>
-      </c>
+      <c r="A293" s="3"/>
+      <c r="B293" s="1"/>
+      <c r="C293" s="1"/>
+      <c r="D293" s="1"/>
     </row>
     <row r="294">
-      <c r="A294" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B294" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C294" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="D294" s="1">
-        <v>149.28</v>
-      </c>
+      <c r="A294" s="3"/>
+      <c r="B294" s="1"/>
+      <c r="C294" s="1"/>
+      <c r="D294" s="1"/>
     </row>
     <row r="295">
-      <c r="A295" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B295" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C295" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="D295" s="1">
-        <v>150.8</v>
-      </c>
+      <c r="A295" s="3"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
     </row>
     <row r="296">
-      <c r="A296" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B296" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C296" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="D296" s="1">
-        <v>140.0</v>
-      </c>
+      <c r="A296" s="3"/>
+      <c r="B296" s="1"/>
+      <c r="C296" s="1"/>
+      <c r="D296" s="1"/>
     </row>
     <row r="297">
-      <c r="A297" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B297" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C297" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D297" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A297" s="3"/>
+      <c r="B297" s="1"/>
+      <c r="C297" s="1"/>
+      <c r="D297" s="1"/>
     </row>
     <row r="298">
-      <c r="A298" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B298" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C298" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D298" s="1">
-        <v>140.79</v>
-      </c>
+      <c r="A298" s="3"/>
+      <c r="B298" s="1"/>
+      <c r="C298" s="1"/>
+      <c r="D298" s="1"/>
     </row>
     <row r="299">
-      <c r="A299" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B299" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C299" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D299" s="1">
-        <v>147.0</v>
-      </c>
+      <c r="A299" s="3"/>
+      <c r="B299" s="1"/>
+      <c r="C299" s="1"/>
+      <c r="D299" s="1"/>
     </row>
     <row r="300">
-      <c r="A300" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B300" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C300" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="D300" s="1">
-        <v>145.0</v>
-      </c>
+      <c r="A300" s="3"/>
+      <c r="B300" s="1"/>
+      <c r="C300" s="1"/>
+      <c r="D300" s="1"/>
     </row>
     <row r="301">
-      <c r="A301" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B301" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C301" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="D301" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A301" s="3"/>
+      <c r="B301" s="1"/>
+      <c r="C301" s="1"/>
+      <c r="D301" s="1"/>
     </row>
     <row r="302">
-      <c r="A302" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B302" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C302" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="D302" s="1">
-        <v>143.5</v>
-      </c>
+      <c r="A302" s="3"/>
+      <c r="B302" s="1"/>
+      <c r="C302" s="1"/>
+      <c r="D302" s="1"/>
     </row>
     <row r="303">
-      <c r="A303" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B303" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C303" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="D303" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A303" s="3"/>
+      <c r="B303" s="1"/>
+      <c r="C303" s="1"/>
+      <c r="D303" s="1"/>
     </row>
     <row r="304">
-      <c r="A304" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B304" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C304" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="D304" s="1">
-        <v>135.0</v>
-      </c>
+      <c r="A304" s="3"/>
+      <c r="B304" s="1"/>
+      <c r="C304" s="1"/>
+      <c r="D304" s="1"/>
     </row>
     <row r="305">
-      <c r="A305" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B305" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="C305" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="D305" s="1">
-        <v>135.89</v>
-      </c>
+      <c r="A305" s="3"/>
+      <c r="B305" s="1"/>
+      <c r="C305" s="1"/>
+      <c r="D305" s="1"/>
     </row>
     <row r="306">
-      <c r="A306" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B306" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C306" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="D306" s="1">
-        <v>139.4</v>
-      </c>
+      <c r="A306" s="3"/>
+      <c r="B306" s="1"/>
+      <c r="C306" s="1"/>
+      <c r="D306" s="1"/>
     </row>
     <row r="307">
-      <c r="A307" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B307" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C307" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="D307" s="1">
-        <v>138.7</v>
-      </c>
+      <c r="A307" s="3"/>
+      <c r="B307" s="1"/>
+      <c r="C307" s="1"/>
+      <c r="D307" s="1"/>
     </row>
     <row r="308">
-      <c r="A308" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B308" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C308" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="D308" s="1">
-        <v>136.9</v>
-      </c>
+      <c r="A308" s="3"/>
+      <c r="B308" s="1"/>
+      <c r="C308" s="1"/>
+      <c r="D308" s="1"/>
     </row>
     <row r="309">
-      <c r="A309" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B309" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="C309" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="D309" s="1">
-        <v>145.0</v>
-      </c>
+      <c r="A309" s="3"/>
+      <c r="B309" s="1"/>
+      <c r="C309" s="1"/>
+      <c r="D309" s="1"/>
     </row>
     <row r="310">
-      <c r="A310" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B310" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C310" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="D310" s="1">
-        <v>187.11</v>
-      </c>
+      <c r="A310" s="3"/>
+      <c r="B310" s="1"/>
+      <c r="C310" s="1"/>
+      <c r="D310" s="1"/>
     </row>
     <row r="311">
-      <c r="A311" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B311" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C311" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="D311" s="1">
-        <v>167.5</v>
-      </c>
+      <c r="A311" s="3"/>
+      <c r="B311" s="1"/>
+      <c r="C311" s="1"/>
+      <c r="D311" s="1"/>
     </row>
     <row r="312">
-      <c r="A312" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B312" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C312" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="D312" s="1">
-        <v>159.19</v>
-      </c>
+      <c r="A312" s="3"/>
+      <c r="B312" s="1"/>
+      <c r="C312" s="1"/>
+      <c r="D312" s="1"/>
     </row>
     <row r="313">
-      <c r="A313" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B313" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="C313" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="D313" s="1">
-        <v>145.0</v>
-      </c>
+      <c r="A313" s="3"/>
+      <c r="B313" s="1"/>
+      <c r="C313" s="1"/>
+      <c r="D313" s="1"/>
     </row>
     <row r="314">
-      <c r="A314" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B314" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C314" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="D314" s="1">
-        <v>165.0</v>
-      </c>
+      <c r="A314" s="3"/>
+      <c r="B314" s="1"/>
+      <c r="C314" s="1"/>
+      <c r="D314" s="1"/>
     </row>
     <row r="315">
-      <c r="A315" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B315" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C315" s="1">
-        <v>26.0</v>
-      </c>
-      <c r="D315" s="1">
-        <v>147.0</v>
-      </c>
+      <c r="A315" s="3"/>
+      <c r="B315" s="1"/>
+      <c r="C315" s="1"/>
+      <c r="D315" s="1"/>
     </row>
     <row r="316">
-      <c r="A316" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B316" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C316" s="1">
-        <v>27.0</v>
-      </c>
-      <c r="D316" s="1">
-        <v>136.9</v>
-      </c>
+      <c r="A316" s="3"/>
+      <c r="B316" s="1"/>
+      <c r="C316" s="1"/>
+      <c r="D316" s="1"/>
     </row>
     <row r="317">
-      <c r="A317" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B317" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="C317" s="1">
-        <v>28.0</v>
-      </c>
-      <c r="D317" s="1">
-        <v>119.7</v>
-      </c>
+      <c r="A317" s="3"/>
+      <c r="B317" s="1"/>
+      <c r="C317" s="1"/>
+      <c r="D317" s="1"/>
     </row>
     <row r="318">
-      <c r="A318" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B318" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C318" s="1">
-        <v>29.0</v>
-      </c>
-      <c r="D318" s="1">
-        <v>140.5</v>
-      </c>
+      <c r="A318" s="3"/>
+      <c r="B318" s="1"/>
+      <c r="C318" s="1"/>
+      <c r="D318" s="1"/>
     </row>
     <row r="319">
-      <c r="A319" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B319" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C319" s="1">
-        <v>30.0</v>
-      </c>
-      <c r="D319" s="1">
-        <v>124.4</v>
-      </c>
+      <c r="A319" s="3"/>
+      <c r="B319" s="1"/>
+      <c r="C319" s="1"/>
+      <c r="D319" s="1"/>
     </row>
     <row r="320">
-      <c r="A320" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B320" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C320" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="D320" s="1">
-        <v>119.7</v>
-      </c>
+      <c r="A320" s="3"/>
+      <c r="B320" s="1"/>
+      <c r="C320" s="1"/>
+      <c r="D320" s="1"/>
     </row>
     <row r="321">
-      <c r="A321" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B321" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="C321" s="1">
-        <v>32.0</v>
-      </c>
-      <c r="D321" s="1">
-        <v>100.0</v>
-      </c>
+      <c r="A321" s="3"/>
+      <c r="B321" s="1"/>
+      <c r="C321" s="1"/>
+      <c r="D321" s="1"/>
     </row>
     <row r="322">
-      <c r="A322" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B322" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C322" s="1">
-        <v>33.0</v>
-      </c>
-      <c r="D322" s="1">
-        <v>143.08</v>
-      </c>
+      <c r="A322" s="3"/>
+      <c r="B322" s="1"/>
+      <c r="C322" s="1"/>
+      <c r="D322" s="1"/>
     </row>
     <row r="323">
-      <c r="A323" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B323" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C323" s="1">
-        <v>34.0</v>
-      </c>
-      <c r="D323" s="1">
-        <v>119.5</v>
-      </c>
+      <c r="A323" s="3"/>
+      <c r="B323" s="1"/>
+      <c r="C323" s="1"/>
+      <c r="D323" s="1"/>
     </row>
     <row r="324">
-      <c r="A324" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B324" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C324" s="1">
-        <v>35.0</v>
-      </c>
-      <c r="D324" s="1">
-        <v>87.29</v>
-      </c>
+      <c r="A324" s="3"/>
+      <c r="B324" s="1"/>
+      <c r="C324" s="1"/>
+      <c r="D324" s="1"/>
     </row>
     <row r="325">
-      <c r="A325" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B325" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="C325" s="1">
-        <v>36.0</v>
-      </c>
-      <c r="D325" s="1">
-        <v>50.13</v>
-      </c>
+      <c r="A325" s="3"/>
+      <c r="B325" s="1"/>
+      <c r="C325" s="1"/>
+      <c r="D325" s="1"/>
     </row>
     <row r="326">
-      <c r="A326" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B326" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C326" s="1">
-        <v>37.0</v>
-      </c>
-      <c r="D326" s="1">
-        <v>40.0</v>
-      </c>
+      <c r="A326" s="3"/>
+      <c r="B326" s="1"/>
+      <c r="C326" s="1"/>
+      <c r="D326" s="1"/>
     </row>
     <row r="327">
-      <c r="A327" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B327" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C327" s="1">
-        <v>38.0</v>
-      </c>
-      <c r="D327" s="1">
-        <v>31.0</v>
-      </c>
+      <c r="A327" s="3"/>
+      <c r="B327" s="1"/>
+      <c r="C327" s="1"/>
+      <c r="D327" s="1"/>
     </row>
     <row r="328">
-      <c r="A328" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B328" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C328" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="D328" s="1">
-        <v>20.99</v>
-      </c>
+      <c r="A328" s="3"/>
+      <c r="B328" s="1"/>
+      <c r="C328" s="1"/>
+      <c r="D328" s="1"/>
     </row>
     <row r="329">
-      <c r="A329" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B329" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="C329" s="1">
-        <v>40.0</v>
-      </c>
-      <c r="D329" s="1">
-        <v>11.0</v>
-      </c>
+      <c r="A329" s="3"/>
+      <c r="B329" s="1"/>
+      <c r="C329" s="1"/>
+      <c r="D329" s="1"/>
     </row>
     <row r="330">
-      <c r="A330" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B330" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C330" s="1">
-        <v>41.0</v>
-      </c>
-      <c r="D330" s="1">
-        <v>0.13</v>
-      </c>
+      <c r="A330" s="3"/>
+      <c r="B330" s="1"/>
+      <c r="C330" s="1"/>
+      <c r="D330" s="1"/>
     </row>
     <row r="331">
-      <c r="A331" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B331" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C331" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="D331" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A331" s="3"/>
+      <c r="B331" s="1"/>
+      <c r="C331" s="1"/>
+      <c r="D331" s="1"/>
     </row>
     <row r="332">
-      <c r="A332" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B332" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C332" s="1">
-        <v>43.0</v>
-      </c>
-      <c r="D332" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A332" s="3"/>
+      <c r="B332" s="1"/>
+      <c r="C332" s="1"/>
+      <c r="D332" s="1"/>
     </row>
     <row r="333">
-      <c r="A333" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B333" s="1">
-        <v>11.0</v>
-      </c>
-      <c r="C333" s="1">
-        <v>44.0</v>
-      </c>
-      <c r="D333" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A333" s="3"/>
+      <c r="B333" s="1"/>
+      <c r="C333" s="1"/>
+      <c r="D333" s="1"/>
     </row>
     <row r="334">
-      <c r="A334" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B334" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C334" s="1">
-        <v>45.0</v>
-      </c>
-      <c r="D334" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A334" s="3"/>
+      <c r="B334" s="1"/>
+      <c r="C334" s="1"/>
+      <c r="D334" s="1"/>
     </row>
     <row r="335">
-      <c r="A335" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B335" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C335" s="1">
-        <v>46.0</v>
-      </c>
-      <c r="D335" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A335" s="3"/>
+      <c r="B335" s="1"/>
+      <c r="C335" s="1"/>
+      <c r="D335" s="1"/>
     </row>
     <row r="336">
-      <c r="A336" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B336" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C336" s="1">
-        <v>47.0</v>
-      </c>
-      <c r="D336" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A336" s="3"/>
+      <c r="B336" s="1"/>
+      <c r="C336" s="1"/>
+      <c r="D336" s="1"/>
     </row>
     <row r="337">
-      <c r="A337" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B337" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="C337" s="1">
-        <v>48.0</v>
-      </c>
-      <c r="D337" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A337" s="3"/>
+      <c r="B337" s="1"/>
+      <c r="C337" s="1"/>
+      <c r="D337" s="1"/>
     </row>
     <row r="338">
-      <c r="A338" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B338" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C338" s="1">
-        <v>49.0</v>
-      </c>
-      <c r="D338" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A338" s="3"/>
+      <c r="B338" s="1"/>
+      <c r="C338" s="1"/>
+      <c r="D338" s="1"/>
     </row>
     <row r="339">
-      <c r="A339" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B339" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C339" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="D339" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A339" s="3"/>
+      <c r="B339" s="1"/>
+      <c r="C339" s="1"/>
+      <c r="D339" s="1"/>
     </row>
     <row r="340">
-      <c r="A340" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B340" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C340" s="1">
-        <v>51.0</v>
-      </c>
-      <c r="D340" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A340" s="3"/>
+      <c r="B340" s="1"/>
+      <c r="C340" s="1"/>
+      <c r="D340" s="1"/>
     </row>
     <row r="341">
-      <c r="A341" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B341" s="1">
-        <v>13.0</v>
-      </c>
-      <c r="C341" s="1">
-        <v>52.0</v>
-      </c>
-      <c r="D341" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A341" s="3"/>
+      <c r="B341" s="1"/>
+      <c r="C341" s="1"/>
+      <c r="D341" s="1"/>
     </row>
     <row r="342">
-      <c r="A342" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B342" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C342" s="1">
-        <v>53.0</v>
-      </c>
-      <c r="D342" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A342" s="3"/>
+      <c r="B342" s="1"/>
+      <c r="C342" s="1"/>
+      <c r="D342" s="1"/>
     </row>
     <row r="343">
-      <c r="A343" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B343" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C343" s="1">
-        <v>54.0</v>
-      </c>
-      <c r="D343" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A343" s="3"/>
+      <c r="B343" s="1"/>
+      <c r="C343" s="1"/>
+      <c r="D343" s="1"/>
     </row>
     <row r="344">
-      <c r="A344" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B344" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C344" s="1">
-        <v>55.0</v>
-      </c>
-      <c r="D344" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A344" s="3"/>
+      <c r="B344" s="1"/>
+      <c r="C344" s="1"/>
+      <c r="D344" s="1"/>
     </row>
     <row r="345">
-      <c r="A345" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B345" s="1">
-        <v>14.0</v>
-      </c>
-      <c r="C345" s="1">
-        <v>56.0</v>
-      </c>
-      <c r="D345" s="1">
-        <v>0.84843</v>
-      </c>
+      <c r="A345" s="3"/>
+      <c r="B345" s="1"/>
+      <c r="C345" s="1"/>
+      <c r="D345" s="1"/>
     </row>
     <row r="346">
-      <c r="A346" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B346" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C346" s="1">
-        <v>57.0</v>
-      </c>
-      <c r="D346" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A346" s="3"/>
+      <c r="B346" s="1"/>
+      <c r="C346" s="1"/>
+      <c r="D346" s="1"/>
     </row>
     <row r="347">
-      <c r="A347" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B347" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C347" s="1">
-        <v>58.0</v>
-      </c>
-      <c r="D347" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A347" s="3"/>
+      <c r="B347" s="1"/>
+      <c r="C347" s="1"/>
+      <c r="D347" s="1"/>
     </row>
     <row r="348">
-      <c r="A348" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B348" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C348" s="1">
-        <v>59.0</v>
-      </c>
-      <c r="D348" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A348" s="3"/>
+      <c r="B348" s="1"/>
+      <c r="C348" s="1"/>
+      <c r="D348" s="1"/>
     </row>
     <row r="349">
-      <c r="A349" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B349" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="C349" s="1">
-        <v>60.0</v>
-      </c>
-      <c r="D349" s="1">
-        <v>1.0</v>
-      </c>
+      <c r="A349" s="3"/>
+      <c r="B349" s="1"/>
+      <c r="C349" s="1"/>
+      <c r="D349" s="1"/>
     </row>
     <row r="350">
-      <c r="A350" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B350" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C350" s="1">
-        <v>61.0</v>
-      </c>
-      <c r="D350" s="1">
-        <v>0.02</v>
-      </c>
+      <c r="A350" s="3"/>
+      <c r="B350" s="1"/>
+      <c r="C350" s="1"/>
+      <c r="D350" s="1"/>
     </row>
     <row r="351">
-      <c r="A351" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B351" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C351" s="1">
-        <v>62.0</v>
-      </c>
-      <c r="D351" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A351" s="3"/>
+      <c r="B351" s="1"/>
+      <c r="C351" s="1"/>
+      <c r="D351" s="1"/>
     </row>
     <row r="352">
-      <c r="A352" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B352" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C352" s="1">
-        <v>63.0</v>
-      </c>
-      <c r="D352" s="1">
-        <v>0.0</v>
-      </c>
+      <c r="A352" s="3"/>
+      <c r="B352" s="1"/>
+      <c r="C352" s="1"/>
+      <c r="D352" s="1"/>
     </row>
     <row r="353">
-      <c r="A353" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B353" s="1">
-        <v>16.0</v>
-      </c>
-      <c r="C353" s="1">
-        <v>64.0</v>
-      </c>
-      <c r="D353" s="1">
-        <v>0.1</v>
-      </c>
+      <c r="A353" s="3"/>
+      <c r="B353" s="1"/>
+      <c r="C353" s="1"/>
+      <c r="D353" s="1"/>
     </row>
     <row r="354">
-      <c r="A354" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B354" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C354" s="1">
-        <v>65.0</v>
-      </c>
-      <c r="D354" s="1">
-        <v>6.0</v>
-      </c>
+      <c r="A354" s="3"/>
+      <c r="B354" s="1"/>
+      <c r="C354" s="1"/>
+      <c r="D354" s="1"/>
     </row>
     <row r="355">
-      <c r="A355" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B355" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C355" s="1">
-        <v>66.0</v>
-      </c>
-      <c r="D355" s="1">
-        <v>20.99</v>
-      </c>
+      <c r="A355" s="3"/>
+      <c r="B355" s="1"/>
+      <c r="C355" s="1"/>
+      <c r="D355" s="1"/>
     </row>
     <row r="356">
-      <c r="A356" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B356" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C356" s="1">
-        <v>67.0</v>
-      </c>
-      <c r="D356" s="1">
-        <v>26.0</v>
-      </c>
+      <c r="A356" s="3"/>
+      <c r="B356" s="1"/>
+      <c r="C356" s="1"/>
+      <c r="D356" s="1"/>
     </row>
     <row r="357">
-      <c r="A357" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B357" s="1">
-        <v>17.0</v>
-      </c>
-      <c r="C357" s="1">
-        <v>68.0</v>
-      </c>
-      <c r="D357" s="1">
-        <v>91.78747</v>
-      </c>
+      <c r="A357" s="3"/>
+      <c r="B357" s="1"/>
+      <c r="C357" s="1"/>
+      <c r="D357" s="1"/>
     </row>
     <row r="358">
-      <c r="A358" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B358" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C358" s="1">
-        <v>69.0</v>
-      </c>
-      <c r="D358" s="1">
-        <v>86.5</v>
-      </c>
+      <c r="A358" s="3"/>
+      <c r="B358" s="1"/>
+      <c r="C358" s="1"/>
+      <c r="D358" s="1"/>
     </row>
     <row r="359">
-      <c r="A359" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B359" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C359" s="1">
-        <v>70.0</v>
-      </c>
-      <c r="D359" s="1">
-        <v>110.5</v>
-      </c>
+      <c r="A359" s="3"/>
+      <c r="B359" s="1"/>
+      <c r="C359" s="1"/>
+      <c r="D359" s="1"/>
     </row>
     <row r="360">
-      <c r="A360" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B360" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C360" s="1">
-        <v>71.0</v>
-      </c>
-      <c r="D360" s="1">
-        <v>147.2</v>
-      </c>
+      <c r="A360" s="3"/>
+      <c r="B360" s="1"/>
+      <c r="C360" s="1"/>
+      <c r="D360" s="1"/>
     </row>
     <row r="361">
-      <c r="A361" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B361" s="1">
-        <v>18.0</v>
-      </c>
-      <c r="C361" s="1">
-        <v>72.0</v>
-      </c>
-      <c r="D361" s="1">
-        <v>175.5</v>
-      </c>
+      <c r="A361" s="3"/>
+      <c r="B361" s="1"/>
+      <c r="C361" s="1"/>
+      <c r="D361" s="1"/>
     </row>
     <row r="362">
-      <c r="A362" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B362" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C362" s="1">
-        <v>73.0</v>
-      </c>
-      <c r="D362" s="1">
-        <v>119.7</v>
-      </c>
+      <c r="A362" s="3"/>
+      <c r="B362" s="1"/>
+      <c r="C362" s="1"/>
+      <c r="D362" s="1"/>
     </row>
     <row r="363">
-      <c r="A363" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B363" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C363" s="1">
-        <v>74.0</v>
-      </c>
-      <c r="D363" s="1">
-        <v>131.1</v>
-      </c>
+      <c r="A363" s="3"/>
+      <c r="B363" s="1"/>
+      <c r="C363" s="1"/>
+      <c r="D363" s="1"/>
     </row>
     <row r="364">
-      <c r="A364" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B364" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C364" s="1">
-        <v>75.0</v>
-      </c>
-      <c r="D364" s="1">
-        <v>139.92</v>
-      </c>
+      <c r="A364" s="3"/>
+      <c r="B364" s="1"/>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1"/>
     </row>
     <row r="365">
-      <c r="A365" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B365" s="1">
-        <v>19.0</v>
-      </c>
-      <c r="C365" s="1">
-        <v>76.0</v>
-      </c>
-      <c r="D365" s="1">
-        <v>169.28</v>
-      </c>
+      <c r="A365" s="3"/>
+      <c r="B365" s="1"/>
+      <c r="C365" s="1"/>
+      <c r="D365" s="1"/>
     </row>
     <row r="366">
-      <c r="A366" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B366" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C366" s="1">
-        <v>77.0</v>
-      </c>
-      <c r="D366" s="1">
-        <v>118.48</v>
-      </c>
+      <c r="A366" s="3"/>
+      <c r="B366" s="1"/>
+      <c r="C366" s="1"/>
+      <c r="D366" s="1"/>
     </row>
     <row r="367">
-      <c r="A367" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B367" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C367" s="1">
-        <v>78.0</v>
-      </c>
-      <c r="D367" s="1">
-        <v>130.03</v>
-      </c>
+      <c r="A367" s="3"/>
+      <c r="B367" s="1"/>
+      <c r="C367" s="1"/>
+      <c r="D367" s="1"/>
     </row>
     <row r="368">
-      <c r="A368" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B368" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C368" s="1">
-        <v>79.0</v>
-      </c>
-      <c r="D368" s="1">
-        <v>175.5</v>
-      </c>
+      <c r="A368" s="3"/>
+      <c r="B368" s="1"/>
+      <c r="C368" s="1"/>
+      <c r="D368" s="1"/>
     </row>
     <row r="369">
-      <c r="A369" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B369" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="C369" s="1">
-        <v>80.0</v>
-      </c>
-      <c r="D369" s="1">
-        <v>187.11</v>
-      </c>
+      <c r="A369" s="3"/>
+      <c r="B369" s="1"/>
+      <c r="C369" s="1"/>
+      <c r="D369" s="1"/>
     </row>
     <row r="370">
-      <c r="A370" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B370" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C370" s="1">
-        <v>81.0</v>
-      </c>
-      <c r="D370" s="1">
-        <v>157.79</v>
-      </c>
+      <c r="A370" s="3"/>
+      <c r="B370" s="1"/>
+      <c r="C370" s="1"/>
+      <c r="D370" s="1"/>
     </row>
     <row r="371">
-      <c r="A371" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B371" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C371" s="1">
-        <v>82.0</v>
-      </c>
-      <c r="D371" s="1">
-        <v>141.96</v>
-      </c>
+      <c r="A371" s="3"/>
+      <c r="B371" s="1"/>
+      <c r="C371" s="1"/>
+      <c r="D371" s="1"/>
     </row>
     <row r="372">
-      <c r="A372" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B372" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C372" s="1">
-        <v>83.0</v>
-      </c>
-      <c r="D372" s="1">
-        <v>174.9</v>
-      </c>
+      <c r="A372" s="3"/>
+      <c r="B372" s="1"/>
+      <c r="C372" s="1"/>
+      <c r="D372" s="1"/>
     </row>
     <row r="373">
-      <c r="A373" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B373" s="1">
-        <v>21.0</v>
-      </c>
-      <c r="C373" s="1">
-        <v>84.0</v>
-      </c>
-      <c r="D373" s="1">
-        <v>187.11</v>
-      </c>
+      <c r="A373" s="3"/>
+      <c r="B373" s="1"/>
+      <c r="C373" s="1"/>
+      <c r="D373" s="1"/>
     </row>
     <row r="374">
-      <c r="A374" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B374" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C374" s="1">
-        <v>85.0</v>
-      </c>
-      <c r="D374" s="1">
-        <v>173.0</v>
-      </c>
+      <c r="A374" s="3"/>
+      <c r="B374" s="1"/>
+      <c r="C374" s="1"/>
+      <c r="D374" s="1"/>
     </row>
     <row r="375">
-      <c r="A375" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B375" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C375" s="1">
-        <v>86.0</v>
-      </c>
-      <c r="D375" s="1">
-        <v>173.0</v>
-      </c>
+      <c r="A375" s="3"/>
+      <c r="B375" s="1"/>
+      <c r="C375" s="1"/>
+      <c r="D375" s="1"/>
     </row>
     <row r="376">
-      <c r="A376" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B376" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C376" s="1">
-        <v>87.0</v>
-      </c>
-      <c r="D376" s="1">
-        <v>173.19</v>
-      </c>
+      <c r="A376" s="3"/>
+      <c r="B376" s="1"/>
+      <c r="C376" s="1"/>
+      <c r="D376" s="1"/>
     </row>
     <row r="377">
-      <c r="A377" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B377" s="1">
-        <v>22.0</v>
-      </c>
-      <c r="C377" s="1">
-        <v>88.0</v>
-      </c>
-      <c r="D377" s="1">
-        <v>168.0</v>
-      </c>
+      <c r="A377" s="3"/>
+      <c r="B377" s="1"/>
+      <c r="C377" s="1"/>
+      <c r="D377" s="1"/>
     </row>
     <row r="378">
-      <c r="A378" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B378" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C378" s="1">
-        <v>89.0</v>
-      </c>
-      <c r="D378" s="1">
-        <v>183.41</v>
-      </c>
+      <c r="A378" s="3"/>
+      <c r="B378" s="1"/>
+      <c r="C378" s="1"/>
+      <c r="D378" s="1"/>
     </row>
     <row r="379">
-      <c r="A379" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B379" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C379" s="1">
-        <v>90.0</v>
-      </c>
-      <c r="D379" s="1">
-        <v>162.37</v>
-      </c>
+      <c r="A379" s="3"/>
+      <c r="B379" s="1"/>
+      <c r="C379" s="1"/>
+      <c r="D379" s="1"/>
     </row>
     <row r="380">
-      <c r="A380" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B380" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C380" s="1">
-        <v>91.0</v>
-      </c>
-      <c r="D380" s="1">
-        <v>149.01</v>
-      </c>
+      <c r="A380" s="3"/>
+      <c r="B380" s="1"/>
+      <c r="C380" s="1"/>
+      <c r="D380" s="1"/>
     </row>
     <row r="381">
-      <c r="A381" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B381" s="1">
-        <v>23.0</v>
-      </c>
-      <c r="C381" s="1">
-        <v>92.0</v>
-      </c>
-      <c r="D381" s="1">
-        <v>145.21</v>
-      </c>
+      <c r="A381" s="3"/>
+      <c r="B381" s="1"/>
+      <c r="C381" s="1"/>
+      <c r="D381" s="1"/>
     </row>
     <row r="382">
-      <c r="A382" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B382" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C382" s="1">
-        <v>93.0</v>
-      </c>
-      <c r="D382" s="1">
-        <v>187.11</v>
-      </c>
+      <c r="A382" s="3"/>
+      <c r="B382" s="1"/>
+      <c r="C382" s="1"/>
+      <c r="D382" s="1"/>
     </row>
     <row r="383">
-      <c r="A383" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B383" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C383" s="1">
-        <v>94.0</v>
-      </c>
-      <c r="D383" s="1">
-        <v>166.10596</v>
-      </c>
+      <c r="A383" s="3"/>
+      <c r="B383" s="1"/>
+      <c r="C383" s="1"/>
+      <c r="D383" s="1"/>
     </row>
     <row r="384">
-      <c r="A384" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B384" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C384" s="1">
-        <v>95.0</v>
-      </c>
-      <c r="D384" s="1">
-        <v>133.95404</v>
-      </c>
+      <c r="A384" s="3"/>
+      <c r="B384" s="1"/>
+      <c r="C384" s="1"/>
+      <c r="D384" s="1"/>
     </row>
     <row r="385">
-      <c r="A385" s="3">
-        <v>46208.0</v>
-      </c>
-      <c r="B385" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="C385" s="1">
-        <v>96.0</v>
-      </c>
-      <c r="D385" s="1">
-        <v>127.03</v>
-      </c>
+      <c r="A385" s="3"/>
+      <c r="B385" s="1"/>
+      <c r="C385" s="1"/>
+      <c r="D385" s="1"/>
     </row>
     <row r="386">
       <c r="A386" s="3"/>
